--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -1115,14 +1115,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="B2:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1130,7 +1129,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1145,7 +1143,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1153,7 +1150,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1171,7 +1167,6 @@
     <row r="11">
       <c r="B11" s="7" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1193,7 +1188,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -1201,7 +1195,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="11" t="inlineStr">
         <is>
@@ -1229,7 +1222,7 @@
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1310,7 +1303,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1418,7 +1410,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1628,7 +1619,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1664,7 +1654,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -1752,7 +1741,7 @@
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="38" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -2228,7 +2217,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4231,7 +4219,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4289,7 +4276,6 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4297,7 +4283,6 @@
         </is>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5382,10 +5367,6 @@
         <v>119068</v>
       </c>
     </row>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
@@ -5447,10 +5428,10 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col hidden="1" outlineLevel="1" width="40" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="10" max="10"/>
     <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="11" max="11"/>
-    <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6110,7 +6091,6 @@
       <c r="I20" s="17" t="n"/>
       <c r="J20" s="24" t="n"/>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6565,7 +6545,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -6767,7 +6746,6 @@
       <c r="I41" s="17" t="n"/>
       <c r="J41" s="24" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7116,7 +7094,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7372,7 +7349,7 @@
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="22" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -7447,7 +7424,6 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7650,7 +7626,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8444,7 +8419,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" hidden="1" outlineLevel="1" ht="28" customHeight="1">
+    <row r="41" ht="28" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
           <t>NORMALIZED NOPAT</t>
@@ -8478,7 +8453,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="61" t="inlineStr">
         <is>
@@ -8554,7 +8528,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J104"/>
@@ -8562,7 +8536,7 @@
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -8571,8 +8545,8 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="12" max="12"/>
-    <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -9716,7 +9690,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="n"/>
     </row>
@@ -9931,8 +9904,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -9951,7 +9922,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -10012,7 +9982,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -10097,7 +10066,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10218,7 +10186,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10279,7 +10246,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="n"/>
       <c r="B80" s="13" t="n"/>
@@ -10354,7 +10320,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -10461,8 +10426,6 @@
       </c>
       <c r="D94" s="26" t="n"/>
     </row>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -10722,7 +10685,7 @@
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="44" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -10883,7 +10846,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -11201,7 +11163,6 @@
         <v>407521</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="n"/>
     </row>
@@ -11279,7 +11240,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -11330,7 +11290,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -11416,7 +11375,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -11563,7 +11521,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -1221,9 +1221,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col hidden="1" outlineLevel="1" width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1740,9 +1740,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col hidden="1" outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col hidden="1" outlineLevel="1" width="38" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>'Scenarios'!G25</t>
+          <t>Scenarios tab: base revenue</t>
         </is>
       </c>
     </row>
@@ -7348,9 +7348,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
-    <col hidden="1" outlineLevel="1" width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -7424,6 +7424,7 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7626,6 +7627,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -7805,9 +7807,10 @@
       </c>
     </row>
     <row r="21" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A21" s="23">
-        <f> Adjusted EBIT (Phase 1)</f>
-        <v/>
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Adjusted EBIT (Phase 1)</t>
+        </is>
       </c>
       <c r="B21" s="17" t="n"/>
       <c r="C21" s="24" t="inlineStr">
@@ -7946,9 +7949,10 @@
       </c>
     </row>
     <row r="26" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A26" s="23">
-        <f> EBIT after lease &amp; capitalization (Phase 2)</f>
-        <v/>
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>EBIT after lease &amp; capitalization (Phase 2)</t>
+        </is>
       </c>
       <c r="B26" s="17" t="n"/>
       <c r="C26" s="24" t="inlineStr">
@@ -8242,9 +8246,10 @@
       </c>
     </row>
     <row r="35" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A35" s="23">
-        <f> EBIT after channel mix (Phase 3)</f>
-        <v/>
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>EBIT after channel mix (Phase 3)</t>
+        </is>
       </c>
       <c r="B35" s="17" t="n"/>
       <c r="C35" s="24" t="inlineStr">
@@ -8278,9 +8283,10 @@
       </c>
     </row>
     <row r="36" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A36" s="23">
-        <f> Normalized EBIT (tax base for NOPAT)</f>
-        <v/>
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>Normalized EBIT (tax base for NOPAT)</t>
+        </is>
       </c>
       <c r="B36" s="17" t="n"/>
       <c r="C36" s="24" t="inlineStr">
@@ -8453,6 +8459,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="61" t="inlineStr">
         <is>
@@ -8535,9 +8542,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col hidden="1" outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -8630,7 +8637,7 @@
       </c>
       <c r="D4" s="85" t="inlineStr">
         <is>
-          <t>'Revenue Drivers'!A1</t>
+          <t>Revenue Drivers tab</t>
         </is>
       </c>
     </row>
@@ -10684,9 +10691,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col hidden="1" outlineLevel="1" width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -5429,9 +5429,8 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="10" max="10"/>
-    <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="10" max="11"/>
+    <col collapsed="1" width="36" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8425,7 +8424,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="28" customHeight="1">
+    <row r="41" collapsed="1" ht="28" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
           <t>NORMALIZED NOPAT</t>
@@ -9075,7 +9074,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" collapsed="1">
       <c r="A19" s="52" t="inlineStr">
         <is>
           <t>Working capital schedule (driver-based) [click − to collapse detail]</t>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -1115,13 +1115,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1129,6 +1130,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1143,6 +1145,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1150,6 +1153,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1167,6 +1171,7 @@
     <row r="11">
       <c r="B11" s="7" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1188,6 +1193,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -1195,12 +1201,9 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Built from scratch for the GIS IR selection assignment.</t>
-        </is>
-      </c>
+      <c r="B19" s="11" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1"/>
     <row r="21" ht="36" customHeight="1"/>
@@ -7423,7 +7426,6 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7626,7 +7628,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8458,7 +8459,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="61" t="inlineStr">
         <is>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -1187,11 +1187,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>ASSUMPTIONS GUIDE (PDF — every tab)</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="n"/>
     </row>
     <row r="16"/>
     <row r="17" ht="36" customHeight="1">
@@ -1306,6 +1302,7 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1413,6 +1410,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1622,6 +1620,7 @@
         <v/>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1657,6 +1656,7 @@
         <v/>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -2220,6 +2220,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4222,6 +4223,7 @@
         <v/>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4279,6 +4281,7 @@
         <v/>
       </c>
     </row>
+    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4286,6 +4289,7 @@
         </is>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5370,6 +5374,10 @@
         <v>119068</v>
       </c>
     </row>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
@@ -6093,6 +6101,7 @@
       <c r="I20" s="17" t="n"/>
       <c r="J20" s="24" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6547,6 +6556,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -6748,6 +6758,7 @@
       <c r="I41" s="17" t="n"/>
       <c r="J41" s="24" t="n"/>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7096,6 +7107,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7426,6 +7438,7 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7628,6 +7641,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8459,6 +8473,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="61" t="inlineStr">
         <is>
@@ -8624,11 +8639,7 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
-        <is>
-          <t>LULU_Assumptions_Memo.pdf</t>
-        </is>
-      </c>
+      <c r="A4" s="38" t="n"/>
       <c r="C4" s="85" t="inlineStr">
         <is>
           <t>NOPAT Bridge tab</t>
@@ -9696,6 +9707,7 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="n"/>
     </row>
@@ -9910,6 +9922,8 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -9928,6 +9942,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -9988,6 +10003,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -10072,6 +10088,7 @@
         <v/>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10192,6 +10209,7 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10252,6 +10270,7 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="n"/>
       <c r="B80" s="13" t="n"/>
@@ -10326,6 +10345,7 @@
         <v/>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -10432,6 +10452,8 @@
       </c>
       <c r="D94" s="26" t="n"/>
     </row>
+    <row r="95"/>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -10622,58 +10644,57 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
     <hyperlink ref="C4" location="'NOPAT Bridge'!A1"/>
     <hyperlink ref="D4" location="'Revenue Drivers'!A1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId33"/>
     <hyperlink ref="C30" location="'Scenarios'!A105"/>
     <hyperlink ref="C31" location="'Scenarios'!A110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId35"/>
     <hyperlink ref="C33" location="'Scenarios'!A120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId44"/>
     <hyperlink ref="C82" location="'DCF'!E46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId46"/>
     <hyperlink ref="C104" location="'Scenarios'!G9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10852,6 +10873,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -11169,6 +11191,7 @@
         <v>407521</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="n"/>
     </row>
@@ -11246,6 +11269,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -11296,6 +11320,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -11381,6 +11406,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -11527,6 +11553,7 @@
         <v/>
       </c>
     </row>
+    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="54">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -346,6 +346,11 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -405,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -749,6 +754,9 @@
     </xf>
     <xf numFmtId="165" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1115,14 +1123,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="B2:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1130,7 +1137,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1145,7 +1151,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1153,7 +1158,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1171,7 +1175,6 @@
     <row r="11">
       <c r="B11" s="7" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1189,7 +1192,6 @@
     <row r="15">
       <c r="B15" s="5" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -1197,7 +1199,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="11" t="n"/>
     </row>
@@ -1302,7 +1303,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1410,7 +1410,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1620,7 +1619,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1656,7 +1654,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -2220,7 +2217,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4223,7 +4219,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4281,7 +4276,6 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4289,7 +4283,6 @@
         </is>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5374,10 +5367,6 @@
         <v>119068</v>
       </c>
     </row>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
@@ -6101,7 +6090,6 @@
       <c r="I20" s="17" t="n"/>
       <c r="J20" s="24" t="n"/>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6556,7 +6544,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -6758,7 +6745,6 @@
       <c r="I41" s="17" t="n"/>
       <c r="J41" s="24" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7107,7 +7093,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7438,7 +7423,6 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7641,7 +7625,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8473,7 +8456,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="61" t="inlineStr">
         <is>
@@ -8494,18 +8476,14 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="26" t="inlineStr">
-        <is>
-          <t>Steps 1–4: DCF unchanged on FY26. Step 5 changes NOPAT only (tax). Step 6 changes FY26 EBIT (+ tariff).</t>
+      <c r="A44" s="126" t="inlineStr">
+        <is>
+          <t>FY26 EBIT adjusted for one-time tariff refund. Base/Bear/Bull paths link to normalized NOPAT using a flat operating tax rate.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="26" t="inlineStr">
-        <is>
-          <t>Scenarios base-case NOPAT (col G) links to NORMALIZED NOPAT above. Bear/bull apply the same t_operating to their EBIT paths.</t>
-        </is>
-      </c>
+      <c r="A45" s="26" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8638,7 +8616,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="38" t="n"/>
       <c r="C4" s="85" t="inlineStr">
         <is>
@@ -9707,7 +9685,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="n"/>
     </row>
@@ -9922,8 +9899,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -9942,7 +9917,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -10003,7 +9977,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -10088,7 +10061,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10209,7 +10181,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10270,7 +10241,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="n"/>
       <c r="B80" s="13" t="n"/>
@@ -10345,7 +10315,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -10452,8 +10421,6 @@
       </c>
       <c r="D94" s="26" t="n"/>
     </row>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -10873,7 +10840,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -11191,7 +11157,6 @@
         <v>407521</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="n"/>
     </row>
@@ -11269,7 +11234,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -11320,7 +11284,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -11406,7 +11369,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -11553,7 +11515,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -11,9 +11,8 @@
     <sheet name="WACC" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Revenue Drivers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NOPAT Bridge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DCF" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Comps" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Comps" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1185,7 +1184,7 @@
     <row r="14">
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>WACC • Revenue Drivers • NOPAT Bridge • Scenarios • DCF • Comps / Football Field</t>
+          <t>WACC • Revenue Drivers • Scenarios • DCF • Comps / Football Field</t>
         </is>
       </c>
     </row>
@@ -2706,15 +2705,15 @@
         </is>
       </c>
       <c r="F50" s="42">
-        <f>F45*(1-'NOPAT Bridge'!F$39)</f>
+        <f>F45*(1-$G$11)</f>
         <v/>
       </c>
       <c r="G50" s="42">
-        <f>'NOPAT Bridge'!F41</f>
+        <f>G45*(1-$G$11)</f>
         <v/>
       </c>
       <c r="H50" s="42">
-        <f>H45*(1-'NOPAT Bridge'!F$39)</f>
+        <f>H45*(1-$G$11)</f>
         <v/>
       </c>
     </row>
@@ -2725,15 +2724,15 @@
         </is>
       </c>
       <c r="F51" s="42">
-        <f>F46*(1-'NOPAT Bridge'!G$39)</f>
+        <f>F46*(1-$G$11)</f>
         <v/>
       </c>
       <c r="G51" s="42">
-        <f>'NOPAT Bridge'!G41</f>
+        <f>G46*(1-$G$11)</f>
         <v/>
       </c>
       <c r="H51" s="42">
-        <f>H46*(1-'NOPAT Bridge'!G$39)</f>
+        <f>H46*(1-$G$11)</f>
         <v/>
       </c>
     </row>
@@ -2744,15 +2743,15 @@
         </is>
       </c>
       <c r="F52" s="42">
-        <f>F47*(1-'NOPAT Bridge'!H$39)</f>
+        <f>F47*(1-$G$11)</f>
         <v/>
       </c>
       <c r="G52" s="42">
-        <f>'NOPAT Bridge'!H41</f>
+        <f>G47*(1-$G$11)</f>
         <v/>
       </c>
       <c r="H52" s="42">
-        <f>H47*(1-'NOPAT Bridge'!H$39)</f>
+        <f>H47*(1-$G$11)</f>
         <v/>
       </c>
     </row>
@@ -2763,15 +2762,15 @@
         </is>
       </c>
       <c r="F53" s="42">
-        <f>F48*(1-'NOPAT Bridge'!I$39)</f>
+        <f>F48*(1-$G$11)</f>
         <v/>
       </c>
       <c r="G53" s="42">
-        <f>'NOPAT Bridge'!I41</f>
+        <f>G48*(1-$G$11)</f>
         <v/>
       </c>
       <c r="H53" s="42">
-        <f>H48*(1-'NOPAT Bridge'!I$39)</f>
+        <f>H48*(1-$G$11)</f>
         <v/>
       </c>
     </row>
@@ -2782,15 +2781,15 @@
         </is>
       </c>
       <c r="F54" s="42">
-        <f>F49*(1-'NOPAT Bridge'!J$39)</f>
+        <f>F49*(1-$G$11)</f>
         <v/>
       </c>
       <c r="G54" s="42">
-        <f>'NOPAT Bridge'!J41</f>
+        <f>G49*(1-$G$11)</f>
         <v/>
       </c>
       <c r="H54" s="42">
-        <f>H49*(1-'NOPAT Bridge'!J$39)</f>
+        <f>H49*(1-$G$11)</f>
         <v/>
       </c>
     </row>
@@ -7340,1193 +7339,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>NOPAT bridge</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-      <c r="E1" s="13" t="n"/>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="13" t="n"/>
-      <c r="I1" s="13" t="n"/>
-      <c r="J1" s="13" t="n"/>
-    </row>
-    <row r="2">
-      <c r="B2" s="51" t="n"/>
-      <c r="C2" s="51" t="inlineStr">
-        <is>
-          <t>Source (click)</t>
-        </is>
-      </c>
-      <c r="D2" s="51" t="n"/>
-      <c r="E2" s="71" t="inlineStr">
-        <is>
-          <t>FY2025A</t>
-        </is>
-      </c>
-      <c r="F2" s="72" t="inlineStr">
-        <is>
-          <t>FY2026E</t>
-        </is>
-      </c>
-      <c r="G2" s="72" t="inlineStr">
-        <is>
-          <t>FY2027E</t>
-        </is>
-      </c>
-      <c r="H2" s="72" t="inlineStr">
-        <is>
-          <t>FY2028E</t>
-        </is>
-      </c>
-      <c r="I2" s="72" t="inlineStr">
-        <is>
-          <t>FY2029E</t>
-        </is>
-      </c>
-      <c r="J2" s="72" t="inlineStr">
-        <is>
-          <t>FY2030E</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="52" t="inlineStr">
-        <is>
-          <t>NOPAT bridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="26" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="52" t="inlineStr">
-        <is>
-          <t>Driver assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>SBC add-back (0)</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K): stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="n"/>
-      <c r="E7" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="26" t="n"/>
-    </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Store-channel EBIT margin %</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: company-operated stores net revenue</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="I9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="J9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>E-commerce EBIT margin %</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: e-commerce net revenue</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-    </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Other-channels EBIT margin %</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: other channels (residual)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="J11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Terminal marginal tax rate</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>R&amp;D amortization period (years)</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge: capitalization convention</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" s="40" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" hidden="1" outlineLevel="1">
-      <c r="A15" s="73" t="inlineStr">
-        <is>
-          <t>Reported EBIT adjustments</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Reported operating income (EBIT)</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: Income from operations</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="74" t="n">
-        <v>2210615</v>
-      </c>
-      <c r="F16" s="75">
-        <f>Scenarios!G45</f>
-        <v/>
-      </c>
-      <c r="G16" s="75">
-        <f>Scenarios!G46</f>
-        <v/>
-      </c>
-      <c r="H16" s="75">
-        <f>Scenarios!G47</f>
-        <v/>
-      </c>
-      <c r="I16" s="75">
-        <f>Scenarios!G48</f>
-        <v/>
-      </c>
-      <c r="J16" s="75">
-        <f>Scenarios!G49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>+ Impairment / intangible amortization (add-back)</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: amortization of intangible assets</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="74" t="n">
-        <v>6961</v>
-      </c>
-      <c r="F17" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>+ Restructuring costs (add-back)</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: restructuring charges</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>+ Legal / M&amp;A one-offs (add-back)</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: SG&amp;A one-offs</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" hidden="1" outlineLevel="1" ht="42" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>+ Stock-based compensation (add-back only if flag = 1)</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K): stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="75">
-        <f>Scenarios!$B$202*$E$7</f>
-        <v/>
-      </c>
-      <c r="F20" s="75">
-        <f>Scenarios!G25/DCF!$E$5*Scenarios!$B$202*$E$7</f>
-        <v/>
-      </c>
-      <c r="G20" s="75">
-        <f>Scenarios!G26/DCF!$E$5*Scenarios!$B$202*$E$7</f>
-        <v/>
-      </c>
-      <c r="H20" s="75">
-        <f>Scenarios!G27/DCF!$E$5*Scenarios!$B$202*$E$7</f>
-        <v/>
-      </c>
-      <c r="I20" s="75">
-        <f>Scenarios!G28/DCF!$E$5*Scenarios!$B$202*$E$7</f>
-        <v/>
-      </c>
-      <c r="J20" s="75">
-        <f>Scenarios!G29/DCF!$E$5*Scenarios!$B$202*$E$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>Adjusted EBIT (Phase 1)</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="n"/>
-      <c r="F21" s="25">
-        <f>F16+F17+F18+F19+F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="25">
-        <f>G16+G17+G18+G19+G20</f>
-        <v/>
-      </c>
-      <c r="H21" s="25">
-        <f>H16+H17+H18+H19+H20</f>
-        <v/>
-      </c>
-      <c r="I21" s="25">
-        <f>I16+I17+I18+I19+I20</f>
-        <v/>
-      </c>
-      <c r="J21" s="25">
-        <f>J16+J17+J18+J19+J20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" hidden="1" outlineLevel="1">
-      <c r="A22" s="73" t="inlineStr">
-        <is>
-          <t>Lease &amp; R&amp;D adjustments</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" hidden="1" outlineLevel="1" ht="42" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>+ Implied lease interest expense (reclass from rent)</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: interest on lease liabilities (supplemental)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="74" t="n">
-        <v>1028</v>
-      </c>
-      <c r="F23" s="75">
-        <f>Scenarios!$B$203*(Scenarios!G25/DCF!$E$5)</f>
-        <v/>
-      </c>
-      <c r="G23" s="75">
-        <f>Scenarios!$B$203*(Scenarios!G26/DCF!$E$5)</f>
-        <v/>
-      </c>
-      <c r="H23" s="75">
-        <f>Scenarios!$B$203*(Scenarios!G27/DCF!$E$5)</f>
-        <v/>
-      </c>
-      <c r="I23" s="75">
-        <f>Scenarios!$B$203*(Scenarios!G28/DCF!$E$5)</f>
-        <v/>
-      </c>
-      <c r="J23" s="75">
-        <f>Scenarios!$B$203*(Scenarios!G29/DCF!$E$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>+ Capitalize R&amp;D / software (current-year expense)</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: R&amp;D / software expense</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>− Amortization of prior capitalized intangibles</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: intangible amortization</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="74" t="n">
-        <v>6961</v>
-      </c>
-      <c r="F25" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>EBIT after lease &amp; capitalization (Phase 2)</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="n"/>
-      <c r="F26" s="25">
-        <f>F21+F23+F24-F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="25">
-        <f>G21+G23+G24-G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="25">
-        <f>H21+H23+H24-H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="25">
-        <f>I21+I23+I24-I25</f>
-        <v/>
-      </c>
-      <c r="J26" s="25">
-        <f>J21+J23+J24-J25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" hidden="1" outlineLevel="1">
-      <c r="A27" s="73" t="inlineStr">
-        <is>
-          <t>Channel EBIT mix</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>Store-channel revenue</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>Revenue Drivers tab: store-channel revenue</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="74" t="n">
-        <v>5049744</v>
-      </c>
-      <c r="F28" s="75">
-        <f>'Revenue Drivers'!C31</f>
-        <v/>
-      </c>
-      <c r="G28" s="75">
-        <f>'Revenue Drivers'!D31</f>
-        <v/>
-      </c>
-      <c r="H28" s="75">
-        <f>'Revenue Drivers'!E31</f>
-        <v/>
-      </c>
-      <c r="I28" s="75">
-        <f>'Revenue Drivers'!F31</f>
-        <v/>
-      </c>
-      <c r="J28" s="75">
-        <f>'Revenue Drivers'!G31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>E-commerce revenue</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>Revenue Drivers tab: e-commerce revenue</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="74" t="n">
-        <v>4918697</v>
-      </c>
-      <c r="F29" s="75">
-        <f>'Revenue Drivers'!C41</f>
-        <v/>
-      </c>
-      <c r="G29" s="75">
-        <f>'Revenue Drivers'!D41</f>
-        <v/>
-      </c>
-      <c r="H29" s="75">
-        <f>'Revenue Drivers'!E41</f>
-        <v/>
-      </c>
-      <c r="I29" s="75">
-        <f>'Revenue Drivers'!F41</f>
-        <v/>
-      </c>
-      <c r="J29" s="75">
-        <f>'Revenue Drivers'!G41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>Other channels revenue</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Revenue Drivers tab: other channels revenue</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="74" t="n">
-        <v>1134159</v>
-      </c>
-      <c r="F30" s="75">
-        <f>'Revenue Drivers'!C45</f>
-        <v/>
-      </c>
-      <c r="G30" s="75">
-        <f>'Revenue Drivers'!D45</f>
-        <v/>
-      </c>
-      <c r="H30" s="75">
-        <f>'Revenue Drivers'!E45</f>
-        <v/>
-      </c>
-      <c r="I30" s="75">
-        <f>'Revenue Drivers'!F45</f>
-        <v/>
-      </c>
-      <c r="J30" s="75">
-        <f>'Revenue Drivers'!G45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" hidden="1" outlineLevel="1" ht="70" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>Store-channel EBIT (= Rev × store margin)</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="n"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: company-operated stores net revenue</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="75" t="n">
-        <v>939252.384</v>
-      </c>
-      <c r="F31" s="75">
-        <f>F28*E$9</f>
-        <v/>
-      </c>
-      <c r="G31" s="75">
-        <f>G28*E$9</f>
-        <v/>
-      </c>
-      <c r="H31" s="75">
-        <f>H28*E$9</f>
-        <v/>
-      </c>
-      <c r="I31" s="75">
-        <f>I28*E$9</f>
-        <v/>
-      </c>
-      <c r="J31" s="75">
-        <f>J28*E$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" hidden="1" outlineLevel="1" ht="70" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>E-commerce EBIT (= Rev × e-comm margin)</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="n"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: e-commerce net revenue</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="75" t="n">
-        <v>1160812.492</v>
-      </c>
-      <c r="F32" s="75">
-        <f>F29*E$10</f>
-        <v/>
-      </c>
-      <c r="G32" s="75">
-        <f>G29*E$10</f>
-        <v/>
-      </c>
-      <c r="H32" s="75">
-        <f>H29*E$10</f>
-        <v/>
-      </c>
-      <c r="I32" s="75">
-        <f>I29*E$10</f>
-        <v/>
-      </c>
-      <c r="J32" s="75">
-        <f>J29*E$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" hidden="1" outlineLevel="1" ht="56" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>Other-channels EBIT (= Rev × other margin)</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: other channels (residual)</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="75" t="n">
-        <v>103208.469</v>
-      </c>
-      <c r="F33" s="75">
-        <f>F30*E$11</f>
-        <v/>
-      </c>
-      <c r="G33" s="75">
-        <f>G30*E$11</f>
-        <v/>
-      </c>
-      <c r="H33" s="75">
-        <f>H30*E$11</f>
-        <v/>
-      </c>
-      <c r="I33" s="75">
-        <f>I30*E$11</f>
-        <v/>
-      </c>
-      <c r="J33" s="75">
-        <f>J30*E$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>Channel EBIT (sum of sector EBIT)</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: sector EBIT subtotal</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="n"/>
-      <c r="F34" s="70">
-        <f>F31+F32+F33+Scenarios!G7</f>
-        <v/>
-      </c>
-      <c r="G34" s="70">
-        <f>G31+G32+G33</f>
-        <v/>
-      </c>
-      <c r="H34" s="70">
-        <f>H31+H32+H33</f>
-        <v/>
-      </c>
-      <c r="I34" s="70">
-        <f>I31+I32+I33</f>
-        <v/>
-      </c>
-      <c r="J34" s="70">
-        <f>J31+J32+J33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>EBIT after channel mix (Phase 3)</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="76" t="n">
-        <v>2203273.345</v>
-      </c>
-      <c r="F35" s="25">
-        <f>F34</f>
-        <v/>
-      </c>
-      <c r="G35" s="25">
-        <f>G34</f>
-        <v/>
-      </c>
-      <c r="H35" s="25">
-        <f>H34</f>
-        <v/>
-      </c>
-      <c r="I35" s="25">
-        <f>I34</f>
-        <v/>
-      </c>
-      <c r="J35" s="25">
-        <f>J34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>Normalized EBIT (tax base for NOPAT)</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>Scenarios tab: base-case EBIT (forecast)</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="25">
-        <f>E21+E23+E24-E25</f>
-        <v/>
-      </c>
-      <c r="F36" s="25">
-        <f>Scenarios!G45</f>
-        <v/>
-      </c>
-      <c r="G36" s="25">
-        <f>Scenarios!G46</f>
-        <v/>
-      </c>
-      <c r="H36" s="25">
-        <f>Scenarios!G47</f>
-        <v/>
-      </c>
-      <c r="I36" s="25">
-        <f>Scenarios!G48</f>
-        <v/>
-      </c>
-      <c r="J36" s="25">
-        <f>Scenarios!G49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" hidden="1" outlineLevel="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>Check vs Scenarios EBIT (base case)</t>
-        </is>
-      </c>
-      <c r="F37" s="75">
-        <f>F36-Scenarios!G45</f>
-        <v/>
-      </c>
-      <c r="G37" s="75">
-        <f>G36-Scenarios!G46</f>
-        <v/>
-      </c>
-      <c r="H37" s="75">
-        <f>H36-Scenarios!G47</f>
-        <v/>
-      </c>
-      <c r="I37" s="75">
-        <f>I36-Scenarios!G48</f>
-        <v/>
-      </c>
-      <c r="J37" s="75">
-        <f>J36-Scenarios!G49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" hidden="1" outlineLevel="1">
-      <c r="A38" s="73" t="inlineStr">
-        <is>
-          <t>Tax normalization</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" hidden="1" outlineLevel="1" ht="70" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>Operating effective tax rate (t_operating)</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: income tax &amp; interest expense</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="77" t="n">
-        <v>0.2946847649213503</v>
-      </c>
-      <c r="F39" s="32">
-        <f>0.29468476492135026+(F$12-0.29468476492135026)*1/5</f>
-        <v/>
-      </c>
-      <c r="G39" s="32">
-        <f>0.29468476492135026+(G$12-0.29468476492135026)*2/5</f>
-        <v/>
-      </c>
-      <c r="H39" s="32">
-        <f>0.29468476492135026+(H$12-0.29468476492135026)*3/5</f>
-        <v/>
-      </c>
-      <c r="I39" s="32">
-        <f>0.29468476492135026+(I$12-0.29468476492135026)*4/5</f>
-        <v/>
-      </c>
-      <c r="J39" s="32">
-        <f>0.29468476492135026+(J$12-0.29468476492135026)*5/5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>Unlevered tax on normalized EBIT</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="n"/>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: unlevered tax expense</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="n"/>
-      <c r="F40" s="75">
-        <f>F36*F39</f>
-        <v/>
-      </c>
-      <c r="G40" s="75">
-        <f>G36*G39</f>
-        <v/>
-      </c>
-      <c r="H40" s="75">
-        <f>H36*H39</f>
-        <v/>
-      </c>
-      <c r="I40" s="75">
-        <f>I36*I39</f>
-        <v/>
-      </c>
-      <c r="J40" s="75">
-        <f>J36*J39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" collapsed="1" ht="28" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>NORMALIZED NOPAT</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: normalized NOPAT</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="n"/>
-      <c r="F41" s="25">
-        <f>F36-F40</f>
-        <v/>
-      </c>
-      <c r="G41" s="25">
-        <f>G36-G40</f>
-        <v/>
-      </c>
-      <c r="H41" s="25">
-        <f>H36-H40</f>
-        <v/>
-      </c>
-      <c r="I41" s="25">
-        <f>I36-I40</f>
-        <v/>
-      </c>
-      <c r="J41" s="25">
-        <f>J36-J40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="61" t="inlineStr">
-        <is>
-          <t>6. Tariff refund (Scenarios)</t>
-        </is>
-      </c>
-      <c r="B43" s="79" t="n"/>
-      <c r="C43" s="79" t="inlineStr">
-        <is>
-          <t>EBIT = Rev × 13.2% only (no refund).</t>
-        </is>
-      </c>
-      <c r="D43" s="79" t="n"/>
-      <c r="F43" s="80" t="inlineStr">
-        <is>
-          <t>Scenarios EBIT (FY26)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="126" t="inlineStr">
-        <is>
-          <t>FY26 EBIT adjusted for one-time tariff refund. Base/Bear/Bull paths link to normalized NOPAT using a flat operating tax rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="26" t="n"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId20"/>
-    <hyperlink ref="C28" location="'Revenue Drivers'!B31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId21"/>
-    <hyperlink ref="C29" location="'Revenue Drivers'!B41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId22"/>
-    <hyperlink ref="C30" location="'Revenue Drivers'!B45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -8618,11 +7430,7 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="38" t="n"/>
-      <c r="C4" s="85" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab</t>
-        </is>
-      </c>
+      <c r="C4" s="85" t="n"/>
       <c r="D4" s="85" t="inlineStr">
         <is>
           <t>Revenue Drivers tab</t>
@@ -8890,27 +7698,27 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Less: unlevered tax (t_operating from NOPAT Bridge)</t>
+          <t>Less: unlevered tax (cash tax rate)</t>
         </is>
       </c>
       <c r="F13" s="75">
-        <f>-'NOPAT Bridge'!F40</f>
+        <f>-F11*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="G13" s="75">
-        <f>-'NOPAT Bridge'!G40</f>
+        <f>-G11*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="H13" s="75">
-        <f>-'NOPAT Bridge'!H40</f>
+        <f>-H11*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="I13" s="75">
-        <f>-'NOPAT Bridge'!I40</f>
+        <f>-I11*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="J13" s="75">
-        <f>-'NOPAT Bridge'!J40</f>
+        <f>-J11*Scenarios!$G$11</f>
         <v/>
       </c>
     </row>
@@ -10191,23 +8999,23 @@
         <v>1579183</v>
       </c>
       <c r="F77" s="75">
-        <f>('NOPAT Bridge'!F36-'NOPAT Bridge'!F23)*(1-'NOPAT Bridge'!F$39)</f>
+        <f>F14</f>
         <v/>
       </c>
       <c r="G77" s="75">
-        <f>('NOPAT Bridge'!G36-'NOPAT Bridge'!G23)*(1-'NOPAT Bridge'!G$39)</f>
+        <f>G14</f>
         <v/>
       </c>
       <c r="H77" s="75">
-        <f>('NOPAT Bridge'!H36-'NOPAT Bridge'!H23)*(1-'NOPAT Bridge'!H$39)</f>
+        <f>H14</f>
         <v/>
       </c>
       <c r="I77" s="75">
-        <f>('NOPAT Bridge'!I36-'NOPAT Bridge'!I23)*(1-'NOPAT Bridge'!I$39)</f>
+        <f>I14</f>
         <v/>
       </c>
       <c r="J77" s="75">
-        <f>('NOPAT Bridge'!J36-'NOPAT Bridge'!J23)*(1-'NOPAT Bridge'!J$39)</f>
+        <f>J14</f>
         <v/>
       </c>
     </row>
@@ -10611,7 +9419,6 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
-    <hyperlink ref="C4" location="'NOPAT Bridge'!A1"/>
     <hyperlink ref="D4" location="'Revenue Drivers'!A1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
@@ -10668,7 +9475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -1192,11 +1192,7 @@
       <c r="B15" s="5" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="11" t="n"/>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="56">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -350,6 +350,16 @@
       <i val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -409,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -757,6 +767,11 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2212,6 +2227,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -2226,15 +2242,15 @@
         </is>
       </c>
       <c r="F25" s="42">
-        <f>DCF!$E$5*(1+F4)</f>
+        <f>$B$198*(1+F4)</f>
         <v/>
       </c>
       <c r="G25" s="42">
-        <f>DCF!$E$5*(1+G4)</f>
+        <f>$B$198*(1+G4)</f>
         <v/>
       </c>
       <c r="H25" s="42">
-        <f>DCF!$E$5*(1+H4)</f>
+        <f>$B$198*(1+H4)</f>
         <v/>
       </c>
     </row>
@@ -4214,6 +4230,7 @@
         <v/>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4240,15 +4257,15 @@
         </is>
       </c>
       <c r="F132" s="46">
-        <f>(F131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
+        <f>(F131+$B$1980+$B$1981)/$B$1985</f>
         <v/>
       </c>
       <c r="G132" s="47">
-        <f>(G131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
+        <f>(G131+$B$1980+$B$1981)/$B$1985</f>
         <v/>
       </c>
       <c r="H132" s="46">
-        <f>(H131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
+        <f>(H131+$B$1980+$B$1981)/$B$1985</f>
         <v/>
       </c>
     </row>
@@ -4271,6 +4288,7 @@
         <v/>
       </c>
     </row>
+    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4278,6 +4296,7 @@
         </is>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -4752,15 +4771,15 @@
         </is>
       </c>
       <c r="F163" s="42">
-        <f>DCF!$E$50+F153+F158</f>
+        <f>$B$1980+F153+F158</f>
         <v/>
       </c>
       <c r="G163" s="42">
-        <f>DCF!$E$50+G153+G158</f>
+        <f>$B$1980+G153+G158</f>
         <v/>
       </c>
       <c r="H163" s="42">
-        <f>DCF!$E$50+H153+H158</f>
+        <f>$B$1980+H153+H158</f>
         <v/>
       </c>
     </row>
@@ -4847,15 +4866,15 @@
         </is>
       </c>
       <c r="F168" s="42">
-        <f>Scenarios!$B$194*F25/DCF!$E$5</f>
+        <f>$B$194*F25/$B$198</f>
         <v/>
       </c>
       <c r="G168" s="42">
-        <f>Scenarios!$B$194*G25/DCF!$E$5</f>
+        <f>$B$194*G25/$B$198</f>
         <v/>
       </c>
       <c r="H168" s="42">
-        <f>Scenarios!$B$194*H25/DCF!$E$5</f>
+        <f>$B$194*H25/$B$198</f>
         <v/>
       </c>
     </row>
@@ -4866,15 +4885,15 @@
         </is>
       </c>
       <c r="F169" s="42">
-        <f>Scenarios!$B$194*F26/DCF!$E$5</f>
+        <f>$B$194*F26/$B$198</f>
         <v/>
       </c>
       <c r="G169" s="42">
-        <f>Scenarios!$B$194*G26/DCF!$E$5</f>
+        <f>$B$194*G26/$B$198</f>
         <v/>
       </c>
       <c r="H169" s="42">
-        <f>Scenarios!$B$194*H26/DCF!$E$5</f>
+        <f>$B$194*H26/$B$198</f>
         <v/>
       </c>
     </row>
@@ -4885,15 +4904,15 @@
         </is>
       </c>
       <c r="F170" s="42">
-        <f>Scenarios!$B$194*F27/DCF!$E$5</f>
+        <f>$B$194*F27/$B$198</f>
         <v/>
       </c>
       <c r="G170" s="42">
-        <f>Scenarios!$B$194*G27/DCF!$E$5</f>
+        <f>$B$194*G27/$B$198</f>
         <v/>
       </c>
       <c r="H170" s="42">
-        <f>Scenarios!$B$194*H27/DCF!$E$5</f>
+        <f>$B$194*H27/$B$198</f>
         <v/>
       </c>
     </row>
@@ -4904,15 +4923,15 @@
         </is>
       </c>
       <c r="F171" s="42">
-        <f>Scenarios!$B$194*F28/DCF!$E$5</f>
+        <f>$B$194*F28/$B$198</f>
         <v/>
       </c>
       <c r="G171" s="42">
-        <f>Scenarios!$B$194*G28/DCF!$E$5</f>
+        <f>$B$194*G28/$B$198</f>
         <v/>
       </c>
       <c r="H171" s="42">
-        <f>Scenarios!$B$194*H28/DCF!$E$5</f>
+        <f>$B$194*H28/$B$198</f>
         <v/>
       </c>
     </row>
@@ -4923,15 +4942,15 @@
         </is>
       </c>
       <c r="F172" s="42">
-        <f>Scenarios!$B$194*F29/DCF!$E$5</f>
+        <f>$B$194*F29/$B$198</f>
         <v/>
       </c>
       <c r="G172" s="42">
-        <f>Scenarios!$B$194*G29/DCF!$E$5</f>
+        <f>$B$194*G29/$B$198</f>
         <v/>
       </c>
       <c r="H172" s="42">
-        <f>Scenarios!$B$194*H29/DCF!$E$5</f>
+        <f>$B$194*H29/$B$198</f>
         <v/>
       </c>
     </row>
@@ -4942,15 +4961,15 @@
         </is>
       </c>
       <c r="F173" s="42">
-        <f>Scenarios!$B$195*F25/DCF!$E$5</f>
+        <f>$B$195*F25/$B$198</f>
         <v/>
       </c>
       <c r="G173" s="42">
-        <f>Scenarios!$B$195*G25/DCF!$E$5</f>
+        <f>$B$195*G25/$B$198</f>
         <v/>
       </c>
       <c r="H173" s="42">
-        <f>Scenarios!$B$195*H25/DCF!$E$5</f>
+        <f>$B$195*H25/$B$198</f>
         <v/>
       </c>
     </row>
@@ -4961,15 +4980,15 @@
         </is>
       </c>
       <c r="F174" s="42">
-        <f>Scenarios!$B$195*F26/DCF!$E$5</f>
+        <f>$B$195*F26/$B$198</f>
         <v/>
       </c>
       <c r="G174" s="42">
-        <f>Scenarios!$B$195*G26/DCF!$E$5</f>
+        <f>$B$195*G26/$B$198</f>
         <v/>
       </c>
       <c r="H174" s="42">
-        <f>Scenarios!$B$195*H26/DCF!$E$5</f>
+        <f>$B$195*H26/$B$198</f>
         <v/>
       </c>
     </row>
@@ -4980,15 +4999,15 @@
         </is>
       </c>
       <c r="F175" s="42">
-        <f>Scenarios!$B$195*F27/DCF!$E$5</f>
+        <f>$B$195*F27/$B$198</f>
         <v/>
       </c>
       <c r="G175" s="42">
-        <f>Scenarios!$B$195*G27/DCF!$E$5</f>
+        <f>$B$195*G27/$B$198</f>
         <v/>
       </c>
       <c r="H175" s="42">
-        <f>Scenarios!$B$195*H27/DCF!$E$5</f>
+        <f>$B$195*H27/$B$198</f>
         <v/>
       </c>
     </row>
@@ -4999,15 +5018,15 @@
         </is>
       </c>
       <c r="F176" s="42">
-        <f>Scenarios!$B$195*F28/DCF!$E$5</f>
+        <f>$B$195*F28/$B$198</f>
         <v/>
       </c>
       <c r="G176" s="42">
-        <f>Scenarios!$B$195*G28/DCF!$E$5</f>
+        <f>$B$195*G28/$B$198</f>
         <v/>
       </c>
       <c r="H176" s="42">
-        <f>Scenarios!$B$195*H28/DCF!$E$5</f>
+        <f>$B$195*H28/$B$198</f>
         <v/>
       </c>
     </row>
@@ -5018,15 +5037,15 @@
         </is>
       </c>
       <c r="F177" s="42">
-        <f>Scenarios!$B$195*F29/DCF!$E$5</f>
+        <f>$B$195*F29/$B$198</f>
         <v/>
       </c>
       <c r="G177" s="42">
-        <f>Scenarios!$B$195*G29/DCF!$E$5</f>
+        <f>$B$195*G29/$B$198</f>
         <v/>
       </c>
       <c r="H177" s="42">
-        <f>Scenarios!$B$195*H29/DCF!$E$5</f>
+        <f>$B$195*H29/$B$198</f>
         <v/>
       </c>
     </row>
@@ -5037,15 +5056,15 @@
         </is>
       </c>
       <c r="F178" s="42">
-        <f>Scenarios!$B$196*F25/DCF!$E$5</f>
+        <f>$B$196*F25/$B$198</f>
         <v/>
       </c>
       <c r="G178" s="42">
-        <f>Scenarios!$B$196*G25/DCF!$E$5</f>
+        <f>$B$196*G25/$B$198</f>
         <v/>
       </c>
       <c r="H178" s="42">
-        <f>Scenarios!$B$196*H25/DCF!$E$5</f>
+        <f>$B$196*H25/$B$198</f>
         <v/>
       </c>
     </row>
@@ -5056,15 +5075,15 @@
         </is>
       </c>
       <c r="F179" s="42">
-        <f>Scenarios!$B$196*F26/DCF!$E$5</f>
+        <f>$B$196*F26/$B$198</f>
         <v/>
       </c>
       <c r="G179" s="42">
-        <f>Scenarios!$B$196*G26/DCF!$E$5</f>
+        <f>$B$196*G26/$B$198</f>
         <v/>
       </c>
       <c r="H179" s="42">
-        <f>Scenarios!$B$196*H26/DCF!$E$5</f>
+        <f>$B$196*H26/$B$198</f>
         <v/>
       </c>
     </row>
@@ -5075,15 +5094,15 @@
         </is>
       </c>
       <c r="F180" s="42">
-        <f>Scenarios!$B$196*F27/DCF!$E$5</f>
+        <f>$B$196*F27/$B$198</f>
         <v/>
       </c>
       <c r="G180" s="42">
-        <f>Scenarios!$B$196*G27/DCF!$E$5</f>
+        <f>$B$196*G27/$B$198</f>
         <v/>
       </c>
       <c r="H180" s="42">
-        <f>Scenarios!$B$196*H27/DCF!$E$5</f>
+        <f>$B$196*H27/$B$198</f>
         <v/>
       </c>
     </row>
@@ -5094,15 +5113,15 @@
         </is>
       </c>
       <c r="F181" s="42">
-        <f>Scenarios!$B$196*F28/DCF!$E$5</f>
+        <f>$B$196*F28/$B$198</f>
         <v/>
       </c>
       <c r="G181" s="42">
-        <f>Scenarios!$B$196*G28/DCF!$E$5</f>
+        <f>$B$196*G28/$B$198</f>
         <v/>
       </c>
       <c r="H181" s="42">
-        <f>Scenarios!$B$196*H28/DCF!$E$5</f>
+        <f>$B$196*H28/$B$198</f>
         <v/>
       </c>
     </row>
@@ -5113,15 +5132,15 @@
         </is>
       </c>
       <c r="F182" s="42">
-        <f>Scenarios!$B$196*F29/DCF!$E$5</f>
+        <f>$B$196*F29/$B$198</f>
         <v/>
       </c>
       <c r="G182" s="42">
-        <f>Scenarios!$B$196*G29/DCF!$E$5</f>
+        <f>$B$196*G29/$B$198</f>
         <v/>
       </c>
       <c r="H182" s="42">
-        <f>Scenarios!$B$196*H29/DCF!$E$5</f>
+        <f>$B$196*H29/$B$198</f>
         <v/>
       </c>
     </row>
@@ -5132,15 +5151,15 @@
         </is>
       </c>
       <c r="F183" s="42">
-        <f>Scenarios!$B$197-F21/100</f>
+        <f>$B$197-F21/100</f>
         <v/>
       </c>
       <c r="G183" s="42">
-        <f>Scenarios!$B$197-G21/100</f>
+        <f>$B$197-G21/100</f>
         <v/>
       </c>
       <c r="H183" s="42">
-        <f>Scenarios!$B$197-H22*H153/100</f>
+        <f>$B$197-H22*H153/100</f>
         <v/>
       </c>
     </row>
@@ -5362,6 +5381,19 @@
         <v>119068</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>FY25 net revenue ($000)</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>11102600</v>
+      </c>
+    </row>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
@@ -5424,7 +5456,8 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="10" max="11"/>
+    <col width="28" customWidth="1" min="10" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col collapsed="1" width="36" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -5517,7 +5550,7 @@
         </is>
       </c>
       <c r="I5" s="56" t="n"/>
-      <c r="J5" s="56" t="inlineStr">
+      <c r="J5" s="127" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -5559,7 +5592,11 @@
         </is>
       </c>
       <c r="I6" s="17" t="n"/>
-      <c r="J6" s="24" t="n"/>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: beginning-stores formula</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="41" t="inlineStr">
@@ -5672,7 +5709,11 @@
         </is>
       </c>
       <c r="I9" s="17" t="n"/>
-      <c r="J9" s="24" t="n"/>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: ending-stores formula</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="41" t="inlineStr">
@@ -5709,7 +5750,11 @@
         </is>
       </c>
       <c r="I10" s="17" t="n"/>
-      <c r="J10" s="24" t="n"/>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: beginning-stores formula</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="41" t="inlineStr">
@@ -5822,7 +5867,11 @@
         </is>
       </c>
       <c r="I13" s="17" t="n"/>
-      <c r="J13" s="24" t="n"/>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: ending-stores formula</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="41" t="inlineStr">
@@ -5859,7 +5908,11 @@
         </is>
       </c>
       <c r="I14" s="17" t="n"/>
-      <c r="J14" s="24" t="n"/>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: beginning-stores formula</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="41" t="inlineStr">
@@ -5972,7 +6025,11 @@
         </is>
       </c>
       <c r="I17" s="17" t="n"/>
-      <c r="J17" s="24" t="n"/>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: ending-stores formula</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="61" t="inlineStr">
@@ -6004,7 +6061,11 @@
         <v/>
       </c>
       <c r="I18" s="17" t="n"/>
-      <c r="J18" s="24" t="n"/>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: total-stores formula</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="41" t="inlineStr">
@@ -6083,8 +6144,13 @@
         </is>
       </c>
       <c r="I20" s="17" t="n"/>
-      <c r="J20" s="24" t="n"/>
-    </row>
+      <c r="J20" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: total-sqft formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6134,7 +6200,7 @@
         </is>
       </c>
       <c r="I23" s="56" t="n"/>
-      <c r="J23" s="56" t="inlineStr">
+      <c r="J23" s="129" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -6340,7 +6406,11 @@
         </is>
       </c>
       <c r="I28" s="17" t="n"/>
-      <c r="J28" s="24" t="n"/>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: prior store-rev formula</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="41" t="inlineStr">
@@ -6372,7 +6442,11 @@
         <v/>
       </c>
       <c r="I29" s="17" t="n"/>
-      <c r="J29" s="24" t="n"/>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: comp-store formula</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="41" t="inlineStr">
@@ -6404,7 +6478,11 @@
         <v/>
       </c>
       <c r="I30" s="17" t="n"/>
-      <c r="J30" s="24" t="n"/>
+      <c r="J30" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: net-new-store formula</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="61" t="inlineStr">
@@ -6436,7 +6514,11 @@
         <v/>
       </c>
       <c r="I31" s="17" t="n"/>
-      <c r="J31" s="24" t="n"/>
+      <c r="J31" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: store-channel formula</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="41" t="n"/>
@@ -6539,6 +6621,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -6588,7 +6671,7 @@
         </is>
       </c>
       <c r="I37" s="56" t="n"/>
-      <c r="J37" s="56" t="inlineStr">
+      <c r="J37" s="129" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -6738,8 +6821,13 @@
         <v/>
       </c>
       <c r="I41" s="17" t="n"/>
-      <c r="J41" s="24" t="n"/>
-    </row>
+      <c r="J41" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: e-comm formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -6789,7 +6877,7 @@
         </is>
       </c>
       <c r="I44" s="56" t="n"/>
-      <c r="J44" s="56" t="inlineStr">
+      <c r="J44" s="129" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -7088,6 +7176,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7137,7 +7226,7 @@
         </is>
       </c>
       <c r="I54" s="56" t="n"/>
-      <c r="J54" s="56" t="inlineStr">
+      <c r="J54" s="129" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -7174,7 +7263,11 @@
         <v/>
       </c>
       <c r="I55" s="17" t="n"/>
-      <c r="J55" s="24" t="n"/>
+      <c r="J55" s="18" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: total-rev formula</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="41" t="inlineStr">
@@ -7248,7 +7341,11 @@
         <v/>
       </c>
       <c r="I57" s="17" t="n"/>
-      <c r="J57" s="24" t="n"/>
+      <c r="J57" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: variance formula</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="41" t="inlineStr">
@@ -7281,7 +7378,11 @@
         <v/>
       </c>
       <c r="I58" s="17" t="n"/>
-      <c r="J58" s="24" t="n"/>
+      <c r="J58" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: variance % formula</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="26" t="inlineStr">
@@ -7292,40 +7393,74 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId67"/>
+    <hyperlink ref="J56" location="'Scenarios'!G25"/>
     <hyperlink ref="K56" location="'Scenarios'!G25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7874,7 +8009,7 @@
         </is>
       </c>
     </row>
-    <row r="20" hidden="1" outlineLevel="1" ht="150" customHeight="1">
+    <row r="20" outlineLevel="1" ht="150" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>DSO (days) — flat vs FY25</t>
@@ -7911,7 +8046,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" hidden="1" outlineLevel="1" ht="98" customHeight="1">
+    <row r="21" outlineLevel="1" ht="98" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Accounts receivable, net</t>
@@ -7948,7 +8083,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" hidden="1" outlineLevel="1" ht="150" customHeight="1">
+    <row r="22" outlineLevel="1" ht="150" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>DIO (days) — FY25 anchor, −1 day/yr</t>
@@ -7985,7 +8120,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" hidden="1" outlineLevel="1" ht="112" customHeight="1">
+    <row r="23" outlineLevel="1" ht="112" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Inventories</t>
@@ -8022,7 +8157,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="24" outlineLevel="1" ht="84" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
           <t>DPO (days) — flat vs FY25</t>
@@ -8059,7 +8194,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="25" outlineLevel="1" ht="84" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Accounts payable</t>
@@ -8096,7 +8231,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="26" outlineLevel="1" ht="84" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Prepaid expenses (% of revenue)</t>
@@ -8133,7 +8268,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="27" outlineLevel="1" ht="84" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Prepaid expenses (other current assets)</t>
@@ -8170,7 +8305,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="28" outlineLevel="1" ht="84" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Accrued liabilities (% of revenue)</t>
@@ -8207,7 +8342,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="29" outlineLevel="1" ht="84" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Accrued liabilities and other</t>
@@ -8244,7 +8379,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="30" outlineLevel="1" ht="42" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Current operating assets (AR + inv + prepaids)</t>
@@ -8278,7 +8413,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="31" outlineLevel="1" ht="42" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Current operating liabilities (AP + accruals)</t>
@@ -8312,7 +8447,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="32" outlineLevel="1" ht="42" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
           <t>Net working capital</t>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -21,13 +21,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0)"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.0x"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="56">
     <font>
@@ -419,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -772,6 +773,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1137,13 +1144,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1151,6 +1159,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1165,6 +1174,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1172,6 +1182,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1189,6 +1200,7 @@
     <row r="11">
       <c r="B11" s="7" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1206,9 +1218,11 @@
     <row r="15">
       <c r="B15" s="5" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="5" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="11" t="n"/>
     </row>
@@ -1313,6 +1327,7 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1420,6 +1435,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1629,6 +1645,7 @@
         <v/>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1664,6 +1681,7 @@
         <v/>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -2070,14 +2088,17 @@
         </is>
       </c>
       <c r="D15" s="19" t="n"/>
-      <c r="F15" s="39" t="n">
-        <v>6.267883648875038</v>
-      </c>
-      <c r="G15" s="39" t="n">
-        <v>6.267883648875038</v>
-      </c>
-      <c r="H15" s="39" t="n">
-        <v>6.267883648875038</v>
+      <c r="F15" s="130">
+        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <v/>
+      </c>
+      <c r="G15" s="130">
+        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <v/>
+      </c>
+      <c r="H15" s="130">
+        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <v/>
       </c>
     </row>
     <row r="16" ht="140" customHeight="1">
@@ -2093,14 +2114,17 @@
         </is>
       </c>
       <c r="D16" s="19" t="n"/>
-      <c r="F16" s="39" t="n">
-        <v>128.8324100108167</v>
-      </c>
-      <c r="G16" s="39" t="n">
-        <v>128.8324100108167</v>
-      </c>
-      <c r="H16" s="39" t="n">
-        <v>128.8324100108167</v>
+      <c r="F16" s="130">
+        <f>(DCF!$E$23/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="G16" s="130">
+        <f>(DCF!$E$23/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="H16" s="130">
+        <f>(DCF!$E$23/DCF!$E$8)*365</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="70" customHeight="1">
@@ -2139,14 +2163,17 @@
         </is>
       </c>
       <c r="D18" s="19" t="n"/>
-      <c r="F18" s="39" t="n">
-        <v>25.10521290169407</v>
-      </c>
-      <c r="G18" s="39" t="n">
-        <v>25.10521290169407</v>
-      </c>
-      <c r="H18" s="39" t="n">
-        <v>25.10521290169407</v>
+      <c r="F18" s="130">
+        <f>(DCF!$E$25/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="G18" s="130">
+        <f>(DCF!$E$25/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="H18" s="130">
+        <f>(DCF!$E$25/DCF!$E$8)*365</f>
+        <v/>
       </c>
     </row>
     <row r="19" ht="84" customHeight="1">
@@ -2162,14 +2189,17 @@
         </is>
       </c>
       <c r="D19" s="19" t="n"/>
-      <c r="F19" s="20" t="n">
-        <v>0.05080692810692991</v>
-      </c>
-      <c r="G19" s="20" t="n">
-        <v>0.05080692810692991</v>
-      </c>
-      <c r="H19" s="20" t="n">
-        <v>0.05080692810692991</v>
+      <c r="F19" s="20">
+        <f>DCF!$E$27/DCF!$E$5</f>
+        <v/>
+      </c>
+      <c r="G19" s="20">
+        <f>DCF!$E$27/DCF!$E$5</f>
+        <v/>
+      </c>
+      <c r="H19" s="20">
+        <f>DCF!$E$27/DCF!$E$5</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="84" customHeight="1">
@@ -2185,14 +2215,17 @@
         </is>
       </c>
       <c r="D20" s="19" t="n"/>
-      <c r="F20" s="20" t="n">
-        <v>0.05971412101669879</v>
-      </c>
-      <c r="G20" s="20" t="n">
-        <v>0.05971412101669879</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>0.05971412101669879</v>
+      <c r="F20" s="20">
+        <f>DCF!$E$29/DCF!$E$5</f>
+        <v/>
+      </c>
+      <c r="G20" s="20">
+        <f>DCF!$E$29/DCF!$E$5</f>
+        <v/>
+      </c>
+      <c r="H20" s="20">
+        <f>DCF!$E$29/DCF!$E$5</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -2202,10 +2235,10 @@
         </is>
       </c>
       <c r="F21" s="37" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="G21" s="37" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="H21" s="37" t="n">
         <v>0</v>
@@ -7645,8 +7678,9 @@
         </is>
       </c>
       <c r="D7" s="19" t="n"/>
-      <c r="E7" s="77" t="n">
-        <v>0.566005440167168</v>
+      <c r="E7" s="77">
+        <f>(E5-E8)/E5</f>
+        <v/>
       </c>
       <c r="F7" s="20">
         <f>Scenarios!$G$14</f>
@@ -7803,7 +7837,7 @@
         </is>
       </c>
       <c r="E12" s="77" t="n">
-        <v>0.1991078666258354</v>
+        <v>0.199</v>
       </c>
       <c r="F12" s="32">
         <f>F11/F5</f>
@@ -8022,8 +8056,9 @@
         </is>
       </c>
       <c r="D20" s="19" t="n"/>
-      <c r="E20" s="88" t="n">
-        <v>6.267883648875038</v>
+      <c r="E20" s="131">
+        <f>(E21/E5)*365</f>
+        <v/>
       </c>
       <c r="F20" s="28">
         <f>Scenarios!G65</f>
@@ -8096,8 +8131,9 @@
         </is>
       </c>
       <c r="D22" s="19" t="n"/>
-      <c r="E22" s="88" t="n">
-        <v>128.8324100108167</v>
+      <c r="E22" s="131">
+        <f>(E23/E8)*365</f>
+        <v/>
       </c>
       <c r="F22" s="28">
         <f>Scenarios!G75</f>
@@ -8170,8 +8206,9 @@
         </is>
       </c>
       <c r="D24" s="19" t="n"/>
-      <c r="E24" s="88" t="n">
-        <v>25.10521290169407</v>
+      <c r="E24" s="131">
+        <f>(E25/E8)*365</f>
+        <v/>
       </c>
       <c r="F24" s="28">
         <f>Scenarios!G85</f>
@@ -8244,8 +8281,9 @@
         </is>
       </c>
       <c r="D26" s="19" t="n"/>
-      <c r="E26" s="77" t="n">
-        <v>0.05080692810692991</v>
+      <c r="E26" s="77">
+        <f>E27/E5</f>
+        <v/>
       </c>
       <c r="F26" s="20">
         <f>Scenarios!$G$19</f>
@@ -8318,8 +8356,9 @@
         </is>
       </c>
       <c r="D28" s="19" t="n"/>
-      <c r="E28" s="77" t="n">
-        <v>0.05971412101669879</v>
+      <c r="E28" s="77">
+        <f>E29/E5</f>
+        <v/>
       </c>
       <c r="F28" s="20">
         <f>Scenarios!$G$20</f>
@@ -8624,6 +8663,7 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="n"/>
     </row>
@@ -8838,6 +8878,8 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -8856,14 +8898,16 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
           <t>Annual repurchase budget ($000) — base case</t>
         </is>
       </c>
-      <c r="E65" s="37" t="n">
-        <v>500000</v>
+      <c r="E65" s="37">
+        <f>Scenarios!$G$21</f>
+        <v/>
       </c>
       <c r="F65" s="37">
         <f>$E$65</f>
@@ -8916,6 +8960,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -9000,6 +9045,7 @@
         <v/>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -9120,6 +9166,7 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -9156,8 +9203,9 @@
           <t>Accretive EPS ($/share) = Net income ÷ ending shares</t>
         </is>
       </c>
-      <c r="E78" s="101" t="n">
-        <v>14.1783354282636</v>
+      <c r="E78" s="101">
+        <f>E77/E75</f>
+        <v/>
       </c>
       <c r="F78" s="101">
         <f>F77/F75</f>
@@ -9180,6 +9228,7 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="n"/>
       <c r="B80" s="13" t="n"/>
@@ -9254,6 +9303,7 @@
         <v/>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -9360,6 +9410,8 @@
       </c>
       <c r="D94" s="26" t="n"/>
     </row>
+    <row r="95"/>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -9778,6 +9830,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -10095,6 +10148,7 @@
         <v>407521</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="n"/>
     </row>
@@ -10172,6 +10226,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -10222,6 +10277,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -10307,6 +10363,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -10453,6 +10510,7 @@
         <v/>
       </c>
     </row>
+    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -7836,8 +7836,9 @@
           <t>Reported EBIT margin % (incl. FY26 refund)</t>
         </is>
       </c>
-      <c r="E12" s="77" t="n">
-        <v>0.199</v>
+      <c r="E12" s="77">
+        <f>E11/E5</f>
+        <v/>
       </c>
       <c r="F12" s="32">
         <f>F11/F5</f>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -1144,14 +1144,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="B2:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1159,7 +1158,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1172,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1182,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1200,7 +1196,6 @@
     <row r="11">
       <c r="B11" s="7" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1218,11 +1213,9 @@
     <row r="15">
       <c r="B15" s="5" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="5" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="11" t="n"/>
     </row>
@@ -1327,7 +1320,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1435,7 +1427,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1645,7 +1636,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1681,7 +1671,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -2089,15 +2078,15 @@
       </c>
       <c r="D15" s="19" t="n"/>
       <c r="F15" s="130">
-        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <f>(DCF!$E$21/$B$198)*365</f>
         <v/>
       </c>
       <c r="G15" s="130">
-        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <f>(DCF!$E$21/$B$198)*365</f>
         <v/>
       </c>
       <c r="H15" s="130">
-        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <f>(DCF!$E$21/$B$198)*365</f>
         <v/>
       </c>
     </row>
@@ -2190,15 +2179,15 @@
       </c>
       <c r="D19" s="19" t="n"/>
       <c r="F19" s="20">
-        <f>DCF!$E$27/DCF!$E$5</f>
+        <f>DCF!$E$27/$B$198</f>
         <v/>
       </c>
       <c r="G19" s="20">
-        <f>DCF!$E$27/DCF!$E$5</f>
+        <f>DCF!$E$27/$B$198</f>
         <v/>
       </c>
       <c r="H19" s="20">
-        <f>DCF!$E$27/DCF!$E$5</f>
+        <f>DCF!$E$27/$B$198</f>
         <v/>
       </c>
     </row>
@@ -2216,15 +2205,15 @@
       </c>
       <c r="D20" s="19" t="n"/>
       <c r="F20" s="20">
-        <f>DCF!$E$29/DCF!$E$5</f>
+        <f>DCF!$E$29/$B$198</f>
         <v/>
       </c>
       <c r="G20" s="20">
-        <f>DCF!$E$29/DCF!$E$5</f>
+        <f>DCF!$E$29/$B$198</f>
         <v/>
       </c>
       <c r="H20" s="20">
-        <f>DCF!$E$29/DCF!$E$5</f>
+        <f>DCF!$E$29/$B$198</f>
         <v/>
       </c>
     </row>
@@ -4290,15 +4279,15 @@
         </is>
       </c>
       <c r="F132" s="46">
-        <f>(F131+$B$1980+$B$1981)/$B$1985</f>
+        <f>(F131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
         <v/>
       </c>
       <c r="G132" s="47">
-        <f>(G131+$B$1980+$B$1981)/$B$1985</f>
+        <f>(G131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
         <v/>
       </c>
       <c r="H132" s="46">
-        <f>(H131+$B$1980+$B$1981)/$B$1985</f>
+        <f>(H131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
         <v/>
       </c>
     </row>
@@ -4804,15 +4793,15 @@
         </is>
       </c>
       <c r="F163" s="42">
-        <f>$B$1980+F153+F158</f>
+        <f>DCF!$E$50+F153+F158</f>
         <v/>
       </c>
       <c r="G163" s="42">
-        <f>$B$1980+G153+G158</f>
+        <f>DCF!$E$50+G153+G158</f>
         <v/>
       </c>
       <c r="H163" s="42">
-        <f>$B$1980+H153+H158</f>
+        <f>DCF!$E$50+H153+H158</f>
         <v/>
       </c>
     </row>
@@ -5491,7 +5480,7 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="11"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col collapsed="1" width="36" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8664,7 +8653,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="n"/>
     </row>
@@ -8879,8 +8867,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -8899,7 +8885,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -8961,7 +8946,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -9046,7 +9030,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -9167,7 +9150,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -9229,7 +9211,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="n"/>
       <c r="B80" s="13" t="n"/>
@@ -9304,7 +9285,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -9411,8 +9391,6 @@
       </c>
       <c r="D94" s="26" t="n"/>
     </row>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -9831,7 +9809,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -10149,7 +10126,6 @@
         <v>407521</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="n"/>
     </row>
@@ -10227,7 +10203,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -10278,7 +10253,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -10364,7 +10338,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -10511,7 +10484,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="169" formatCode="0.0x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="58">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -361,6 +361,14 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -420,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -779,6 +787,8 @@
     <xf numFmtId="170" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2249,7 +2259,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4252,7 +4261,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4310,7 +4318,6 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4318,7 +4325,6 @@
         </is>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5413,9 +5419,6 @@
         <v>11102600</v>
       </c>
     </row>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
@@ -5502,6 +5505,16 @@
     </row>
     <row r="2">
       <c r="A2" s="26" t="n"/>
+      <c r="B2" s="132" t="inlineStr">
+        <is>
+          <t>×1,000,000 (sessions in millions → count)</t>
+        </is>
+      </c>
+      <c r="C2" s="132" t="inlineStr">
+        <is>
+          <t>÷1,000 ($ → $000 on this tab)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5515,6 +5528,11 @@
       <c r="C3" t="n">
         <v>1000</v>
       </c>
+      <c r="H3" s="133" t="inlineStr">
+        <is>
+          <t>see B2/C2</t>
+        </is>
+      </c>
       <c r="I3" s="51" t="n"/>
       <c r="J3" s="51" t="inlineStr">
         <is>
@@ -6172,7 +6190,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6643,7 +6660,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -6849,7 +6865,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7198,7 +7213,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="WACC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Revenue Drivers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="DCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Comps" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Drivers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +30,7 @@
     <numFmt numFmtId="169" formatCode="0.0x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="58">
+  <fonts count="60">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -369,6 +369,15 @@
       <i val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -428,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -789,6 +798,12 @@
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1812,7 +1827,11 @@
           <t>Key assumptions (5-yr forecast)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n"/>
+      <c r="B3" s="134" t="inlineStr">
+        <is>
+          <t>How it moves</t>
+        </is>
+      </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Source (click)</t>
@@ -1826,7 +1845,11 @@
           <t>FY2026E revenue growth</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n"/>
+      <c r="B4" s="135" t="inlineStr">
+        <is>
+          <t>Year-one sales change: bear falls most.</t>
+        </is>
+      </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release</t>
@@ -1849,7 +1872,11 @@
           <t>FY2027–FY2030E revenue growth (avg)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
+      <c r="B5" s="135" t="inlineStr">
+        <is>
+          <t>Years two-five average growth: bull fastest.</t>
+        </is>
+      </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU 3Y revenue forecast</t>
@@ -1872,7 +1899,11 @@
           <t>Run-rate EBIT margin (clean, ex-refunds)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n"/>
+      <c r="B6" s="135" t="inlineStr">
+        <is>
+          <t>Starting operating margin before linear ramp.</t>
+        </is>
+      </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs</t>
@@ -1895,7 +1926,11 @@
           <t>FY26 IEEPA tariff refunds ($k, already in guide)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
+      <c r="B7" s="135" t="inlineStr">
+        <is>
+          <t>One-time year-one EBIT boost: zero after.</t>
+        </is>
+      </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
@@ -1918,7 +1953,11 @@
           <t>Terminal (FY2030E) EBIT margin</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n"/>
+      <c r="B8" s="135" t="inlineStr">
+        <is>
+          <t>Year-five target margin after linear ramp.</t>
+        </is>
+      </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: Operating margin 19.9% (one hit)</t>
@@ -1941,7 +1980,11 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n"/>
+      <c r="B9" s="135" t="inlineStr">
+        <is>
+          <t>Flat discount rate: higher bear, lower bull.</t>
+        </is>
+      </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
           <t>WACC tab: CAPM build</t>
@@ -1965,7 +2008,11 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n"/>
+      <c r="B10" s="135" t="inlineStr">
+        <is>
+          <t>Perpetuity growth rate: flat across all years.</t>
+        </is>
+      </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
@@ -1988,7 +2035,11 @@
           <t>Cash tax rate</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
+      <c r="B11" s="135" t="inlineStr">
+        <is>
+          <t>Flat tax percentage applied every forecast year.</t>
+        </is>
+      </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
@@ -2011,7 +2062,11 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
+      <c r="B12" s="135" t="inlineStr">
+        <is>
+          <t>Depreciation scales as fixed percent of revenue.</t>
+        </is>
+      </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)</t>
@@ -2034,7 +2089,11 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n"/>
+      <c r="B13" s="135" t="inlineStr">
+        <is>
+          <t>Investment scales as fixed percent of revenue.</t>
+        </is>
+      </c>
       <c r="C13" s="38" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M</t>
@@ -2057,7 +2116,11 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n"/>
+      <c r="B14" s="135" t="inlineStr">
+        <is>
+          <t>Merchandise margin held flat every forecast year.</t>
+        </is>
+      </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Gross profit &amp; COGS</t>
@@ -2077,10 +2140,14 @@
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>DSO (days) — flat vs FY25</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="n"/>
+          <t>DSO (days): flat vs FY25</t>
+        </is>
+      </c>
+      <c r="B15" s="135" t="inlineStr">
+        <is>
+          <t>Collection days held flat near six yearly.</t>
+        </is>
+      </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts receivable, net</t>
@@ -2106,7 +2173,11 @@
           <t>FY25 DIO anchor (days)</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n"/>
+      <c r="B16" s="135" t="inlineStr">
+        <is>
+          <t>Starting inventory days before annual decline begins.</t>
+        </is>
+      </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Inventories &amp; COGS</t>
@@ -2132,7 +2203,11 @@
           <t>DIO decline (days / forecast yr)</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n"/>
+      <c r="B17" s="135" t="inlineStr">
+        <is>
+          <t>Inventory days fall one day each year.</t>
+        </is>
+      </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: inventory &amp; markdown outlook</t>
@@ -2152,10 +2227,14 @@
     <row r="18" ht="84" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>DPO (days) — flat vs FY25</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n"/>
+          <t>DPO (days): flat vs FY25</t>
+        </is>
+      </c>
+      <c r="B18" s="135" t="inlineStr">
+        <is>
+          <t>Payment days held flat near twenty-five yearly.</t>
+        </is>
+      </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts payable &amp; COGS</t>
@@ -2181,7 +2260,11 @@
           <t>Prepaid expenses (% of revenue)</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n"/>
+      <c r="B19" s="135" t="inlineStr">
+        <is>
+          <t>Other current assets flat percent of revenue.</t>
+        </is>
+      </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: other current assets (residual)</t>
@@ -2207,7 +2290,11 @@
           <t>Accrued liabilities (% of revenue)</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n"/>
+      <c r="B20" s="135" t="inlineStr">
+        <is>
+          <t>Accrued payables flat percent of revenue.</t>
+        </is>
+      </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
@@ -2233,6 +2320,11 @@
           <t>Pitch CFF: fixed buyback ($k/yr) bear/base</t>
         </is>
       </c>
+      <c r="B21" s="135" t="inlineStr">
+        <is>
+          <t>Bear base retire fixed dollars yearly.</t>
+        </is>
+      </c>
       <c r="F21" s="37" t="n">
         <v>750000</v>
       </c>
@@ -2249,6 +2341,11 @@
           <t>Pitch CFF: % of FCF to buybacks (bull)</t>
         </is>
       </c>
+      <c r="B22" s="135" t="inlineStr">
+        <is>
+          <t>Bull spends set percent of free cash.</t>
+        </is>
+      </c>
       <c r="F22" s="20" t="n">
         <v>0</v>
       </c>
@@ -2259,6 +2356,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -2269,7 +2367,12 @@
     <row r="25">
       <c r="A25" s="41" t="inlineStr">
         <is>
-          <t>Revenue – year 1</t>
+          <t>Revenue: year 1</t>
+        </is>
+      </c>
+      <c r="B25" s="135" t="inlineStr">
+        <is>
+          <t>Grows or shrinks using scenario-specific growth rates.</t>
         </is>
       </c>
       <c r="F25" s="42">
@@ -2288,7 +2391,7 @@
     <row r="26">
       <c r="A26" s="41" t="inlineStr">
         <is>
-          <t>Revenue – year 2</t>
+          <t>Revenue: year 2</t>
         </is>
       </c>
       <c r="F26" s="42">
@@ -2307,7 +2410,7 @@
     <row r="27">
       <c r="A27" s="41" t="inlineStr">
         <is>
-          <t>Revenue – year 3</t>
+          <t>Revenue: year 3</t>
         </is>
       </c>
       <c r="F27" s="42">
@@ -2326,7 +2429,7 @@
     <row r="28">
       <c r="A28" s="41" t="inlineStr">
         <is>
-          <t>Revenue – year 4</t>
+          <t>Revenue: year 4</t>
         </is>
       </c>
       <c r="F28" s="42">
@@ -2345,7 +2448,7 @@
     <row r="29">
       <c r="A29" s="41" t="inlineStr">
         <is>
-          <t>Revenue – year 5</t>
+          <t>Revenue: year 5</t>
         </is>
       </c>
       <c r="F29" s="42">
@@ -2364,7 +2467,12 @@
     <row r="30">
       <c r="A30" s="41" t="inlineStr">
         <is>
-          <t>Gross margin % – year 1</t>
+          <t>Gross margin %: year 1</t>
+        </is>
+      </c>
+      <c r="B30" s="135" t="inlineStr">
+        <is>
+          <t>Stays flat at scenario margin every year.</t>
         </is>
       </c>
       <c r="F30" s="43">
@@ -2383,7 +2491,7 @@
     <row r="31">
       <c r="A31" s="41" t="inlineStr">
         <is>
-          <t>Gross margin % – year 2</t>
+          <t>Gross margin %: year 2</t>
         </is>
       </c>
       <c r="F31" s="43">
@@ -2402,7 +2510,7 @@
     <row r="32">
       <c r="A32" s="41" t="inlineStr">
         <is>
-          <t>Gross margin % – year 3</t>
+          <t>Gross margin %: year 3</t>
         </is>
       </c>
       <c r="F32" s="43">
@@ -2421,7 +2529,7 @@
     <row r="33">
       <c r="A33" s="41" t="inlineStr">
         <is>
-          <t>Gross margin % – year 4</t>
+          <t>Gross margin %: year 4</t>
         </is>
       </c>
       <c r="F33" s="43">
@@ -2440,7 +2548,7 @@
     <row r="34">
       <c r="A34" s="41" t="inlineStr">
         <is>
-          <t>Gross margin % – year 5</t>
+          <t>Gross margin %: year 5</t>
         </is>
       </c>
       <c r="F34" s="43">
@@ -2459,7 +2567,12 @@
     <row r="35">
       <c r="A35" s="41" t="inlineStr">
         <is>
-          <t>Cost of goods sold (COGS) – year 1</t>
+          <t>Cost of goods sold (COGS): year 1</t>
+        </is>
+      </c>
+      <c r="B35" s="135" t="inlineStr">
+        <is>
+          <t>Moves with revenue when gross margin stays flat.</t>
         </is>
       </c>
       <c r="F35" s="42">
@@ -2478,7 +2591,7 @@
     <row r="36">
       <c r="A36" s="41" t="inlineStr">
         <is>
-          <t>Cost of goods sold (COGS) – year 2</t>
+          <t>Cost of goods sold (COGS): year 2</t>
         </is>
       </c>
       <c r="F36" s="42">
@@ -2497,7 +2610,7 @@
     <row r="37">
       <c r="A37" s="41" t="inlineStr">
         <is>
-          <t>Cost of goods sold (COGS) – year 3</t>
+          <t>Cost of goods sold (COGS): year 3</t>
         </is>
       </c>
       <c r="F37" s="42">
@@ -2516,7 +2629,7 @@
     <row r="38">
       <c r="A38" s="41" t="inlineStr">
         <is>
-          <t>Cost of goods sold (COGS) – year 4</t>
+          <t>Cost of goods sold (COGS): year 4</t>
         </is>
       </c>
       <c r="F38" s="42">
@@ -2535,7 +2648,7 @@
     <row r="39">
       <c r="A39" s="41" t="inlineStr">
         <is>
-          <t>Cost of goods sold (COGS) – year 5</t>
+          <t>Cost of goods sold (COGS): year 5</t>
         </is>
       </c>
       <c r="F39" s="42">
@@ -2554,7 +2667,12 @@
     <row r="40">
       <c r="A40" s="41" t="inlineStr">
         <is>
-          <t>Clean EBIT margin – year 1</t>
+          <t>Clean EBIT margin: year 1</t>
+        </is>
+      </c>
+      <c r="B40" s="135" t="inlineStr">
+        <is>
+          <t>Linearly ramps from run-rate toward terminal margin.</t>
         </is>
       </c>
       <c r="F40" s="43">
@@ -2573,7 +2691,7 @@
     <row r="41">
       <c r="A41" s="41" t="inlineStr">
         <is>
-          <t>Clean EBIT margin – year 2</t>
+          <t>Clean EBIT margin: year 2</t>
         </is>
       </c>
       <c r="F41" s="43">
@@ -2592,7 +2710,7 @@
     <row r="42">
       <c r="A42" s="41" t="inlineStr">
         <is>
-          <t>Clean EBIT margin – year 3</t>
+          <t>Clean EBIT margin: year 3</t>
         </is>
       </c>
       <c r="F42" s="43">
@@ -2611,7 +2729,7 @@
     <row r="43">
       <c r="A43" s="41" t="inlineStr">
         <is>
-          <t>Clean EBIT margin – year 4</t>
+          <t>Clean EBIT margin: year 4</t>
         </is>
       </c>
       <c r="F43" s="43">
@@ -2630,7 +2748,7 @@
     <row r="44">
       <c r="A44" s="41" t="inlineStr">
         <is>
-          <t>Clean EBIT margin – year 5</t>
+          <t>Clean EBIT margin: year 5</t>
         </is>
       </c>
       <c r="F44" s="43">
@@ -2649,7 +2767,12 @@
     <row r="45">
       <c r="A45" s="41" t="inlineStr">
         <is>
-          <t>EBIT – year 1</t>
+          <t>EBIT: year 1</t>
+        </is>
+      </c>
+      <c r="B45" s="135" t="inlineStr">
+        <is>
+          <t>Revenue times margin: year one adds tariff refund.</t>
         </is>
       </c>
       <c r="F45" s="42">
@@ -2668,7 +2791,7 @@
     <row r="46">
       <c r="A46" s="41" t="inlineStr">
         <is>
-          <t>EBIT – year 2</t>
+          <t>EBIT: year 2</t>
         </is>
       </c>
       <c r="F46" s="42">
@@ -2687,7 +2810,7 @@
     <row r="47">
       <c r="A47" s="41" t="inlineStr">
         <is>
-          <t>EBIT – year 3</t>
+          <t>EBIT: year 3</t>
         </is>
       </c>
       <c r="F47" s="42">
@@ -2706,7 +2829,7 @@
     <row r="48">
       <c r="A48" s="41" t="inlineStr">
         <is>
-          <t>EBIT – year 4</t>
+          <t>EBIT: year 4</t>
         </is>
       </c>
       <c r="F48" s="42">
@@ -2725,7 +2848,7 @@
     <row r="49">
       <c r="A49" s="41" t="inlineStr">
         <is>
-          <t>EBIT – year 5</t>
+          <t>EBIT: year 5</t>
         </is>
       </c>
       <c r="F49" s="42">
@@ -2744,7 +2867,12 @@
     <row r="50">
       <c r="A50" s="41" t="inlineStr">
         <is>
-          <t>NOPAT – year 1</t>
+          <t>NOPAT: year 1</t>
+        </is>
+      </c>
+      <c r="B50" s="135" t="inlineStr">
+        <is>
+          <t>EBIT taxed at flat cash rate each year.</t>
         </is>
       </c>
       <c r="F50" s="42">
@@ -2763,7 +2891,7 @@
     <row r="51">
       <c r="A51" s="41" t="inlineStr">
         <is>
-          <t>NOPAT – year 2</t>
+          <t>NOPAT: year 2</t>
         </is>
       </c>
       <c r="F51" s="42">
@@ -2782,7 +2910,7 @@
     <row r="52">
       <c r="A52" s="41" t="inlineStr">
         <is>
-          <t>NOPAT – year 3</t>
+          <t>NOPAT: year 3</t>
         </is>
       </c>
       <c r="F52" s="42">
@@ -2801,7 +2929,7 @@
     <row r="53">
       <c r="A53" s="41" t="inlineStr">
         <is>
-          <t>NOPAT – year 4</t>
+          <t>NOPAT: year 4</t>
         </is>
       </c>
       <c r="F53" s="42">
@@ -2820,7 +2948,7 @@
     <row r="54">
       <c r="A54" s="41" t="inlineStr">
         <is>
-          <t>NOPAT – year 5</t>
+          <t>NOPAT: year 5</t>
         </is>
       </c>
       <c r="F54" s="42">
@@ -2839,7 +2967,12 @@
     <row r="55">
       <c r="A55" s="41" t="inlineStr">
         <is>
-          <t>D&amp;A – year 1</t>
+          <t>D&amp;A: year 1</t>
+        </is>
+      </c>
+      <c r="B55" s="135" t="inlineStr">
+        <is>
+          <t>Scales upward with revenue at fixed percentage annually.</t>
         </is>
       </c>
       <c r="F55" s="42">
@@ -2858,7 +2991,7 @@
     <row r="56">
       <c r="A56" s="41" t="inlineStr">
         <is>
-          <t>D&amp;A – year 2</t>
+          <t>D&amp;A: year 2</t>
         </is>
       </c>
       <c r="F56" s="42">
@@ -2877,7 +3010,7 @@
     <row r="57">
       <c r="A57" s="41" t="inlineStr">
         <is>
-          <t>D&amp;A – year 3</t>
+          <t>D&amp;A: year 3</t>
         </is>
       </c>
       <c r="F57" s="42">
@@ -2896,7 +3029,7 @@
     <row r="58">
       <c r="A58" s="41" t="inlineStr">
         <is>
-          <t>D&amp;A – year 4</t>
+          <t>D&amp;A: year 4</t>
         </is>
       </c>
       <c r="F58" s="42">
@@ -2915,7 +3048,7 @@
     <row r="59">
       <c r="A59" s="41" t="inlineStr">
         <is>
-          <t>D&amp;A – year 5</t>
+          <t>D&amp;A: year 5</t>
         </is>
       </c>
       <c r="F59" s="42">
@@ -2934,7 +3067,12 @@
     <row r="60">
       <c r="A60" s="41" t="inlineStr">
         <is>
-          <t>Capex – year 1</t>
+          <t>Capex: year 1</t>
+        </is>
+      </c>
+      <c r="B60" s="135" t="inlineStr">
+        <is>
+          <t>Scales upward with revenue at fixed percentage annually.</t>
         </is>
       </c>
       <c r="F60" s="42">
@@ -2953,7 +3091,7 @@
     <row r="61">
       <c r="A61" s="41" t="inlineStr">
         <is>
-          <t>Capex – year 2</t>
+          <t>Capex: year 2</t>
         </is>
       </c>
       <c r="F61" s="42">
@@ -2972,7 +3110,7 @@
     <row r="62">
       <c r="A62" s="41" t="inlineStr">
         <is>
-          <t>Capex – year 3</t>
+          <t>Capex: year 3</t>
         </is>
       </c>
       <c r="F62" s="42">
@@ -2991,7 +3129,7 @@
     <row r="63">
       <c r="A63" s="41" t="inlineStr">
         <is>
-          <t>Capex – year 4</t>
+          <t>Capex: year 4</t>
         </is>
       </c>
       <c r="F63" s="42">
@@ -3010,7 +3148,7 @@
     <row r="64">
       <c r="A64" s="41" t="inlineStr">
         <is>
-          <t>Capex – year 5</t>
+          <t>Capex: year 5</t>
         </is>
       </c>
       <c r="F64" s="42">
@@ -3029,7 +3167,12 @@
     <row r="65">
       <c r="A65" s="41" t="inlineStr">
         <is>
-          <t>DSO (days) – year 1</t>
+          <t>DSO (days): year 1</t>
+        </is>
+      </c>
+      <c r="B65" s="135" t="inlineStr">
+        <is>
+          <t>Held flat at six days every forecast year.</t>
         </is>
       </c>
       <c r="F65" s="44">
@@ -3048,7 +3191,7 @@
     <row r="66">
       <c r="A66" s="41" t="inlineStr">
         <is>
-          <t>DSO (days) – year 2</t>
+          <t>DSO (days): year 2</t>
         </is>
       </c>
       <c r="F66" s="44">
@@ -3067,7 +3210,7 @@
     <row r="67">
       <c r="A67" s="41" t="inlineStr">
         <is>
-          <t>DSO (days) – year 3</t>
+          <t>DSO (days): year 3</t>
         </is>
       </c>
       <c r="F67" s="44">
@@ -3086,7 +3229,7 @@
     <row r="68">
       <c r="A68" s="41" t="inlineStr">
         <is>
-          <t>DSO (days) – year 4</t>
+          <t>DSO (days): year 4</t>
         </is>
       </c>
       <c r="F68" s="44">
@@ -3105,7 +3248,7 @@
     <row r="69">
       <c r="A69" s="41" t="inlineStr">
         <is>
-          <t>DSO (days) – year 5</t>
+          <t>DSO (days): year 5</t>
         </is>
       </c>
       <c r="F69" s="44">
@@ -3124,7 +3267,12 @@
     <row r="70">
       <c r="A70" s="41" t="inlineStr">
         <is>
-          <t>Accounts receivable – year 1</t>
+          <t>Accounts receivable: year 1</t>
+        </is>
+      </c>
+      <c r="B70" s="135" t="inlineStr">
+        <is>
+          <t>Tracks revenue changes while collection days stay flat.</t>
         </is>
       </c>
       <c r="F70" s="42">
@@ -3143,7 +3291,7 @@
     <row r="71">
       <c r="A71" s="41" t="inlineStr">
         <is>
-          <t>Accounts receivable – year 2</t>
+          <t>Accounts receivable: year 2</t>
         </is>
       </c>
       <c r="F71" s="42">
@@ -3162,7 +3310,7 @@
     <row r="72">
       <c r="A72" s="41" t="inlineStr">
         <is>
-          <t>Accounts receivable – year 3</t>
+          <t>Accounts receivable: year 3</t>
         </is>
       </c>
       <c r="F72" s="42">
@@ -3181,7 +3329,7 @@
     <row r="73">
       <c r="A73" s="41" t="inlineStr">
         <is>
-          <t>Accounts receivable – year 4</t>
+          <t>Accounts receivable: year 4</t>
         </is>
       </c>
       <c r="F73" s="42">
@@ -3200,7 +3348,7 @@
     <row r="74">
       <c r="A74" s="41" t="inlineStr">
         <is>
-          <t>Accounts receivable – year 5</t>
+          <t>Accounts receivable: year 5</t>
         </is>
       </c>
       <c r="F74" s="42">
@@ -3219,7 +3367,12 @@
     <row r="75">
       <c r="A75" s="41" t="inlineStr">
         <is>
-          <t>DIO (days) – year 1</t>
+          <t>DIO (days): year 1</t>
+        </is>
+      </c>
+      <c r="B75" s="135" t="inlineStr">
+        <is>
+          <t>Falls one day per year across five years.</t>
         </is>
       </c>
       <c r="F75" s="44">
@@ -3238,7 +3391,7 @@
     <row r="76">
       <c r="A76" s="41" t="inlineStr">
         <is>
-          <t>DIO (days) – year 2</t>
+          <t>DIO (days): year 2</t>
         </is>
       </c>
       <c r="F76" s="44">
@@ -3257,7 +3410,7 @@
     <row r="77">
       <c r="A77" s="41" t="inlineStr">
         <is>
-          <t>DIO (days) – year 3</t>
+          <t>DIO (days): year 3</t>
         </is>
       </c>
       <c r="F77" s="44">
@@ -3276,7 +3429,7 @@
     <row r="78">
       <c r="A78" s="41" t="inlineStr">
         <is>
-          <t>DIO (days) – year 4</t>
+          <t>DIO (days): year 4</t>
         </is>
       </c>
       <c r="F78" s="44">
@@ -3295,7 +3448,7 @@
     <row r="79">
       <c r="A79" s="41" t="inlineStr">
         <is>
-          <t>DIO (days) – year 5</t>
+          <t>DIO (days): year 5</t>
         </is>
       </c>
       <c r="F79" s="44">
@@ -3314,7 +3467,12 @@
     <row r="80">
       <c r="A80" s="41" t="inlineStr">
         <is>
-          <t>Inventories – year 1</t>
+          <t>Inventories: year 1</t>
+        </is>
+      </c>
+      <c r="B80" s="135" t="inlineStr">
+        <is>
+          <t>Declines with DIO days: grows with rising COGS.</t>
         </is>
       </c>
       <c r="F80" s="42">
@@ -3333,7 +3491,7 @@
     <row r="81">
       <c r="A81" s="41" t="inlineStr">
         <is>
-          <t>Inventories – year 2</t>
+          <t>Inventories: year 2</t>
         </is>
       </c>
       <c r="F81" s="42">
@@ -3352,7 +3510,7 @@
     <row r="82">
       <c r="A82" s="41" t="inlineStr">
         <is>
-          <t>Inventories – year 3</t>
+          <t>Inventories: year 3</t>
         </is>
       </c>
       <c r="F82" s="42">
@@ -3371,7 +3529,7 @@
     <row r="83">
       <c r="A83" s="41" t="inlineStr">
         <is>
-          <t>Inventories – year 4</t>
+          <t>Inventories: year 4</t>
         </is>
       </c>
       <c r="F83" s="42">
@@ -3390,7 +3548,7 @@
     <row r="84">
       <c r="A84" s="41" t="inlineStr">
         <is>
-          <t>Inventories – year 5</t>
+          <t>Inventories: year 5</t>
         </is>
       </c>
       <c r="F84" s="42">
@@ -3409,7 +3567,12 @@
     <row r="85">
       <c r="A85" s="41" t="inlineStr">
         <is>
-          <t>DPO (days) – year 1</t>
+          <t>DPO (days): year 1</t>
+        </is>
+      </c>
+      <c r="B85" s="135" t="inlineStr">
+        <is>
+          <t>Held flat at twenty-five days every year.</t>
         </is>
       </c>
       <c r="F85" s="44">
@@ -3428,7 +3591,7 @@
     <row r="86">
       <c r="A86" s="41" t="inlineStr">
         <is>
-          <t>DPO (days) – year 2</t>
+          <t>DPO (days): year 2</t>
         </is>
       </c>
       <c r="F86" s="44">
@@ -3447,7 +3610,7 @@
     <row r="87">
       <c r="A87" s="41" t="inlineStr">
         <is>
-          <t>DPO (days) – year 3</t>
+          <t>DPO (days): year 3</t>
         </is>
       </c>
       <c r="F87" s="44">
@@ -3466,7 +3629,7 @@
     <row r="88">
       <c r="A88" s="41" t="inlineStr">
         <is>
-          <t>DPO (days) – year 4</t>
+          <t>DPO (days): year 4</t>
         </is>
       </c>
       <c r="F88" s="44">
@@ -3485,7 +3648,7 @@
     <row r="89">
       <c r="A89" s="41" t="inlineStr">
         <is>
-          <t>DPO (days) – year 5</t>
+          <t>DPO (days): year 5</t>
         </is>
       </c>
       <c r="F89" s="44">
@@ -3504,7 +3667,12 @@
     <row r="90">
       <c r="A90" s="41" t="inlineStr">
         <is>
-          <t>Accounts payable – year 1</t>
+          <t>Accounts payable: year 1</t>
+        </is>
+      </c>
+      <c r="B90" s="135" t="inlineStr">
+        <is>
+          <t>Grows with COGS while payment days remain flat.</t>
         </is>
       </c>
       <c r="F90" s="42">
@@ -3523,7 +3691,7 @@
     <row r="91">
       <c r="A91" s="41" t="inlineStr">
         <is>
-          <t>Accounts payable – year 2</t>
+          <t>Accounts payable: year 2</t>
         </is>
       </c>
       <c r="F91" s="42">
@@ -3542,7 +3710,7 @@
     <row r="92">
       <c r="A92" s="41" t="inlineStr">
         <is>
-          <t>Accounts payable – year 3</t>
+          <t>Accounts payable: year 3</t>
         </is>
       </c>
       <c r="F92" s="42">
@@ -3561,7 +3729,7 @@
     <row r="93">
       <c r="A93" s="41" t="inlineStr">
         <is>
-          <t>Accounts payable – year 4</t>
+          <t>Accounts payable: year 4</t>
         </is>
       </c>
       <c r="F93" s="42">
@@ -3580,7 +3748,7 @@
     <row r="94">
       <c r="A94" s="41" t="inlineStr">
         <is>
-          <t>Accounts payable – year 5</t>
+          <t>Accounts payable: year 5</t>
         </is>
       </c>
       <c r="F94" s="42">
@@ -3599,7 +3767,12 @@
     <row r="95">
       <c r="A95" s="41" t="inlineStr">
         <is>
-          <t>Prepaid expenses (other current assets) – year 1</t>
+          <t>Prepaid expenses (other current assets): year 1</t>
+        </is>
+      </c>
+      <c r="B95" s="135" t="inlineStr">
+        <is>
+          <t>Grows at flat percent of revenue yearly.</t>
         </is>
       </c>
       <c r="F95" s="42">
@@ -3618,7 +3791,7 @@
     <row r="96">
       <c r="A96" s="41" t="inlineStr">
         <is>
-          <t>Prepaid expenses (other current assets) – year 2</t>
+          <t>Prepaid expenses (other current assets): year 2</t>
         </is>
       </c>
       <c r="F96" s="42">
@@ -3637,7 +3810,7 @@
     <row r="97">
       <c r="A97" s="41" t="inlineStr">
         <is>
-          <t>Prepaid expenses (other current assets) – year 3</t>
+          <t>Prepaid expenses (other current assets): year 3</t>
         </is>
       </c>
       <c r="F97" s="42">
@@ -3656,7 +3829,7 @@
     <row r="98">
       <c r="A98" s="41" t="inlineStr">
         <is>
-          <t>Prepaid expenses (other current assets) – year 4</t>
+          <t>Prepaid expenses (other current assets): year 4</t>
         </is>
       </c>
       <c r="F98" s="42">
@@ -3675,7 +3848,7 @@
     <row r="99">
       <c r="A99" s="41" t="inlineStr">
         <is>
-          <t>Prepaid expenses (other current assets) – year 5</t>
+          <t>Prepaid expenses (other current assets): year 5</t>
         </is>
       </c>
       <c r="F99" s="42">
@@ -3694,7 +3867,12 @@
     <row r="100">
       <c r="A100" s="41" t="inlineStr">
         <is>
-          <t>Accrued liabilities – year 1</t>
+          <t>Accrued liabilities: year 1</t>
+        </is>
+      </c>
+      <c r="B100" s="135" t="inlineStr">
+        <is>
+          <t>Grows at flat percent of revenue every year.</t>
         </is>
       </c>
       <c r="F100" s="42">
@@ -3713,7 +3891,7 @@
     <row r="101">
       <c r="A101" s="41" t="inlineStr">
         <is>
-          <t>Accrued liabilities – year 2</t>
+          <t>Accrued liabilities: year 2</t>
         </is>
       </c>
       <c r="F101" s="42">
@@ -3732,7 +3910,7 @@
     <row r="102">
       <c r="A102" s="41" t="inlineStr">
         <is>
-          <t>Accrued liabilities – year 3</t>
+          <t>Accrued liabilities: year 3</t>
         </is>
       </c>
       <c r="F102" s="42">
@@ -3751,7 +3929,7 @@
     <row r="103">
       <c r="A103" s="41" t="inlineStr">
         <is>
-          <t>Accrued liabilities – year 4</t>
+          <t>Accrued liabilities: year 4</t>
         </is>
       </c>
       <c r="F103" s="42">
@@ -3770,7 +3948,7 @@
     <row r="104">
       <c r="A104" s="41" t="inlineStr">
         <is>
-          <t>Accrued liabilities – year 5</t>
+          <t>Accrued liabilities: year 5</t>
         </is>
       </c>
       <c r="F104" s="42">
@@ -3789,7 +3967,12 @@
     <row r="105">
       <c r="A105" s="41" t="inlineStr">
         <is>
-          <t>Current operating assets (AR + inv + prepaids) – year 1</t>
+          <t>Current operating assets (AR + inv + prepaids): year 1</t>
+        </is>
+      </c>
+      <c r="B105" s="135" t="inlineStr">
+        <is>
+          <t>Rises as receivables, inventory, prepaids expand.</t>
         </is>
       </c>
       <c r="F105" s="42">
@@ -3808,7 +3991,7 @@
     <row r="106">
       <c r="A106" s="41" t="inlineStr">
         <is>
-          <t>Current operating assets (AR + inv + prepaids) – year 2</t>
+          <t>Current operating assets (AR + inv + prepaids): year 2</t>
         </is>
       </c>
       <c r="F106" s="42">
@@ -3827,7 +4010,7 @@
     <row r="107">
       <c r="A107" s="41" t="inlineStr">
         <is>
-          <t>Current operating assets (AR + inv + prepaids) – year 3</t>
+          <t>Current operating assets (AR + inv + prepaids): year 3</t>
         </is>
       </c>
       <c r="F107" s="42">
@@ -3846,7 +4029,7 @@
     <row r="108">
       <c r="A108" s="41" t="inlineStr">
         <is>
-          <t>Current operating assets (AR + inv + prepaids) – year 4</t>
+          <t>Current operating assets (AR + inv + prepaids): year 4</t>
         </is>
       </c>
       <c r="F108" s="42">
@@ -3865,7 +4048,7 @@
     <row r="109">
       <c r="A109" s="41" t="inlineStr">
         <is>
-          <t>Current operating assets (AR + inv + prepaids) – year 5</t>
+          <t>Current operating assets (AR + inv + prepaids): year 5</t>
         </is>
       </c>
       <c r="F109" s="42">
@@ -3884,7 +4067,12 @@
     <row r="110">
       <c r="A110" s="41" t="inlineStr">
         <is>
-          <t>Current operating liabilities (AP + accruals) – year 1</t>
+          <t>Current operating liabilities (AP + accruals): year 1</t>
+        </is>
+      </c>
+      <c r="B110" s="135" t="inlineStr">
+        <is>
+          <t>Rises as payables and accruals grow with sales.</t>
         </is>
       </c>
       <c r="F110" s="42">
@@ -3903,7 +4091,7 @@
     <row r="111">
       <c r="A111" s="41" t="inlineStr">
         <is>
-          <t>Current operating liabilities (AP + accruals) – year 2</t>
+          <t>Current operating liabilities (AP + accruals): year 2</t>
         </is>
       </c>
       <c r="F111" s="42">
@@ -3922,7 +4110,7 @@
     <row r="112">
       <c r="A112" s="41" t="inlineStr">
         <is>
-          <t>Current operating liabilities (AP + accruals) – year 3</t>
+          <t>Current operating liabilities (AP + accruals): year 3</t>
         </is>
       </c>
       <c r="F112" s="42">
@@ -3941,7 +4129,7 @@
     <row r="113">
       <c r="A113" s="41" t="inlineStr">
         <is>
-          <t>Current operating liabilities (AP + accruals) – year 4</t>
+          <t>Current operating liabilities (AP + accruals): year 4</t>
         </is>
       </c>
       <c r="F113" s="42">
@@ -3960,7 +4148,7 @@
     <row r="114">
       <c r="A114" s="41" t="inlineStr">
         <is>
-          <t>Current operating liabilities (AP + accruals) – year 5</t>
+          <t>Current operating liabilities (AP + accruals): year 5</t>
         </is>
       </c>
       <c r="F114" s="42">
@@ -3979,7 +4167,12 @@
     <row r="115">
       <c r="A115" s="41" t="inlineStr">
         <is>
-          <t>Net working capital – year 1</t>
+          <t>Net working capital: year 1</t>
+        </is>
+      </c>
+      <c r="B115" s="135" t="inlineStr">
+        <is>
+          <t>Operating assets minus liabilities: level shifts yearly.</t>
         </is>
       </c>
       <c r="F115" s="42">
@@ -3998,7 +4191,7 @@
     <row r="116">
       <c r="A116" s="41" t="inlineStr">
         <is>
-          <t>Net working capital – year 2</t>
+          <t>Net working capital: year 2</t>
         </is>
       </c>
       <c r="F116" s="42">
@@ -4017,7 +4210,7 @@
     <row r="117">
       <c r="A117" s="41" t="inlineStr">
         <is>
-          <t>Net working capital – year 3</t>
+          <t>Net working capital: year 3</t>
         </is>
       </c>
       <c r="F117" s="42">
@@ -4036,7 +4229,7 @@
     <row r="118">
       <c r="A118" s="41" t="inlineStr">
         <is>
-          <t>Net working capital – year 4</t>
+          <t>Net working capital: year 4</t>
         </is>
       </c>
       <c r="F118" s="42">
@@ -4055,7 +4248,7 @@
     <row r="119">
       <c r="A119" s="41" t="inlineStr">
         <is>
-          <t>Net working capital – year 5</t>
+          <t>Net working capital: year 5</t>
         </is>
       </c>
       <c r="F119" s="42">
@@ -4074,7 +4267,12 @@
     <row r="120">
       <c r="A120" s="41" t="inlineStr">
         <is>
-          <t>ΔNWC (prior yr − current yr) – year 1</t>
+          <t>ΔNWC (prior yr: prior yr minus current yr): year 1</t>
+        </is>
+      </c>
+      <c r="B120" s="135" t="inlineStr">
+        <is>
+          <t>Prior minus current NWC: positive releases cash.</t>
         </is>
       </c>
       <c r="F120" s="42">
@@ -4093,7 +4291,7 @@
     <row r="121">
       <c r="A121" s="41" t="inlineStr">
         <is>
-          <t>ΔNWC (prior yr − current yr) – year 2</t>
+          <t>ΔNWC (prior yr: prior yr minus current yr): year 2</t>
         </is>
       </c>
       <c r="F121" s="42">
@@ -4112,7 +4310,7 @@
     <row r="122">
       <c r="A122" s="41" t="inlineStr">
         <is>
-          <t>ΔNWC (prior yr − current yr) – year 3</t>
+          <t>ΔNWC (prior yr: prior yr minus current yr): year 3</t>
         </is>
       </c>
       <c r="F122" s="42">
@@ -4131,7 +4329,7 @@
     <row r="123">
       <c r="A123" s="41" t="inlineStr">
         <is>
-          <t>ΔNWC (prior yr − current yr) – year 4</t>
+          <t>ΔNWC (prior yr: prior yr minus current yr): year 4</t>
         </is>
       </c>
       <c r="F123" s="42">
@@ -4150,7 +4348,7 @@
     <row r="124">
       <c r="A124" s="41" t="inlineStr">
         <is>
-          <t>ΔNWC (prior yr − current yr) – year 5</t>
+          <t>ΔNWC (prior yr: prior yr minus current yr): year 5</t>
         </is>
       </c>
       <c r="F124" s="42">
@@ -4169,7 +4367,12 @@
     <row r="125">
       <c r="A125" s="41" t="inlineStr">
         <is>
-          <t>Unlevered FCF – year 1</t>
+          <t>Unlevered FCF: year 1</t>
+        </is>
+      </c>
+      <c r="B125" s="135" t="inlineStr">
+        <is>
+          <t>NOPAT plus depreciation minus capex plus working capital.</t>
         </is>
       </c>
       <c r="F125" s="42">
@@ -4188,7 +4391,7 @@
     <row r="126">
       <c r="A126" s="41" t="inlineStr">
         <is>
-          <t>Unlevered FCF – year 2</t>
+          <t>Unlevered FCF: year 2</t>
         </is>
       </c>
       <c r="F126" s="42">
@@ -4207,7 +4410,7 @@
     <row r="127">
       <c r="A127" s="41" t="inlineStr">
         <is>
-          <t>Unlevered FCF – year 3</t>
+          <t>Unlevered FCF: year 3</t>
         </is>
       </c>
       <c r="F127" s="42">
@@ -4226,7 +4429,7 @@
     <row r="128">
       <c r="A128" s="41" t="inlineStr">
         <is>
-          <t>Unlevered FCF – year 4</t>
+          <t>Unlevered FCF: year 4</t>
         </is>
       </c>
       <c r="F128" s="42">
@@ -4245,7 +4448,7 @@
     <row r="129">
       <c r="A129" s="41" t="inlineStr">
         <is>
-          <t>Unlevered FCF – year 5</t>
+          <t>Unlevered FCF: year 5</t>
         </is>
       </c>
       <c r="F129" s="42">
@@ -4261,6 +4464,7 @@
         <v/>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4318,6 +4522,7 @@
         <v/>
       </c>
     </row>
+    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4325,6 +4530,7 @@
         </is>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -4335,7 +4541,7 @@
     <row r="138">
       <c r="A138" s="41" t="inlineStr">
         <is>
-          <t>Other income – year 1</t>
+          <t>Other income: year 1</t>
         </is>
       </c>
       <c r="F138" s="42" t="n">
@@ -4351,7 +4557,7 @@
     <row r="139">
       <c r="A139" s="41" t="inlineStr">
         <is>
-          <t>Other income – year 2</t>
+          <t>Other income: year 2</t>
         </is>
       </c>
       <c r="F139" s="42" t="n">
@@ -4367,7 +4573,7 @@
     <row r="140">
       <c r="A140" s="41" t="inlineStr">
         <is>
-          <t>Other income – year 3</t>
+          <t>Other income: year 3</t>
         </is>
       </c>
       <c r="F140" s="42" t="n">
@@ -4383,7 +4589,7 @@
     <row r="141">
       <c r="A141" s="41" t="inlineStr">
         <is>
-          <t>Other income – year 4</t>
+          <t>Other income: year 4</t>
         </is>
       </c>
       <c r="F141" s="42" t="n">
@@ -4399,7 +4605,7 @@
     <row r="142">
       <c r="A142" s="41" t="inlineStr">
         <is>
-          <t>Other income – year 5</t>
+          <t>Other income: year 5</t>
         </is>
       </c>
       <c r="F142" s="42" t="n">
@@ -4415,7 +4621,7 @@
     <row r="143">
       <c r="A143" s="41" t="inlineStr">
         <is>
-          <t>Net income – year 1</t>
+          <t>Net income: year 1</t>
         </is>
       </c>
       <c r="F143" s="42">
@@ -4434,7 +4640,7 @@
     <row r="144">
       <c r="A144" s="41" t="inlineStr">
         <is>
-          <t>Net income – year 2</t>
+          <t>Net income: year 2</t>
         </is>
       </c>
       <c r="F144" s="42">
@@ -4453,7 +4659,7 @@
     <row r="145">
       <c r="A145" s="41" t="inlineStr">
         <is>
-          <t>Net income – year 3</t>
+          <t>Net income: year 3</t>
         </is>
       </c>
       <c r="F145" s="42">
@@ -4472,7 +4678,7 @@
     <row r="146">
       <c r="A146" s="41" t="inlineStr">
         <is>
-          <t>Net income – year 4</t>
+          <t>Net income: year 4</t>
         </is>
       </c>
       <c r="F146" s="42">
@@ -4491,7 +4697,7 @@
     <row r="147">
       <c r="A147" s="41" t="inlineStr">
         <is>
-          <t>Net income – year 5</t>
+          <t>Net income: year 5</t>
         </is>
       </c>
       <c r="F147" s="42">
@@ -4510,7 +4716,7 @@
     <row r="148">
       <c r="A148" s="41" t="inlineStr">
         <is>
-          <t>Cash from operations – year 1</t>
+          <t>Cash from operations: year 1</t>
         </is>
       </c>
       <c r="F148" s="42">
@@ -4529,7 +4735,7 @@
     <row r="149">
       <c r="A149" s="41" t="inlineStr">
         <is>
-          <t>Cash from operations – year 2</t>
+          <t>Cash from operations: year 2</t>
         </is>
       </c>
       <c r="F149" s="42">
@@ -4548,7 +4754,7 @@
     <row r="150">
       <c r="A150" s="41" t="inlineStr">
         <is>
-          <t>Cash from operations – year 3</t>
+          <t>Cash from operations: year 3</t>
         </is>
       </c>
       <c r="F150" s="42">
@@ -4567,7 +4773,7 @@
     <row r="151">
       <c r="A151" s="41" t="inlineStr">
         <is>
-          <t>Cash from operations – year 4</t>
+          <t>Cash from operations: year 4</t>
         </is>
       </c>
       <c r="F151" s="42">
@@ -4586,7 +4792,7 @@
     <row r="152">
       <c r="A152" s="41" t="inlineStr">
         <is>
-          <t>Cash from operations – year 5</t>
+          <t>Cash from operations: year 5</t>
         </is>
       </c>
       <c r="F152" s="42">
@@ -4605,7 +4811,7 @@
     <row r="153">
       <c r="A153" s="41" t="inlineStr">
         <is>
-          <t>Free cash flow (CFS) – year 1</t>
+          <t>Free cash flow (CFS): year 1</t>
         </is>
       </c>
       <c r="F153" s="42">
@@ -4624,7 +4830,7 @@
     <row r="154">
       <c r="A154" s="41" t="inlineStr">
         <is>
-          <t>Free cash flow (CFS) – year 2</t>
+          <t>Free cash flow (CFS): year 2</t>
         </is>
       </c>
       <c r="F154" s="42">
@@ -4643,7 +4849,7 @@
     <row r="155">
       <c r="A155" s="41" t="inlineStr">
         <is>
-          <t>Free cash flow (CFS) – year 3</t>
+          <t>Free cash flow (CFS): year 3</t>
         </is>
       </c>
       <c r="F155" s="42">
@@ -4662,7 +4868,7 @@
     <row r="156">
       <c r="A156" s="41" t="inlineStr">
         <is>
-          <t>Free cash flow (CFS) – year 4</t>
+          <t>Free cash flow (CFS): year 4</t>
         </is>
       </c>
       <c r="F156" s="42">
@@ -4681,7 +4887,7 @@
     <row r="157">
       <c r="A157" s="41" t="inlineStr">
         <is>
-          <t>Free cash flow (CFS) – year 5</t>
+          <t>Free cash flow (CFS): year 5</t>
         </is>
       </c>
       <c r="F157" s="42">
@@ -4700,7 +4906,7 @@
     <row r="158">
       <c r="A158" s="41" t="inlineStr">
         <is>
-          <t>Share repurchases – year 1</t>
+          <t>Share repurchases: year 1</t>
         </is>
       </c>
       <c r="F158" s="42">
@@ -4719,7 +4925,7 @@
     <row r="159">
       <c r="A159" s="41" t="inlineStr">
         <is>
-          <t>Share repurchases – year 2</t>
+          <t>Share repurchases: year 2</t>
         </is>
       </c>
       <c r="F159" s="42">
@@ -4738,7 +4944,7 @@
     <row r="160">
       <c r="A160" s="41" t="inlineStr">
         <is>
-          <t>Share repurchases – year 3</t>
+          <t>Share repurchases: year 3</t>
         </is>
       </c>
       <c r="F160" s="42">
@@ -4757,7 +4963,7 @@
     <row r="161">
       <c r="A161" s="41" t="inlineStr">
         <is>
-          <t>Share repurchases – year 4</t>
+          <t>Share repurchases: year 4</t>
         </is>
       </c>
       <c r="F161" s="42">
@@ -4776,7 +4982,7 @@
     <row r="162">
       <c r="A162" s="41" t="inlineStr">
         <is>
-          <t>Share repurchases – year 5</t>
+          <t>Share repurchases: year 5</t>
         </is>
       </c>
       <c r="F162" s="42">
@@ -4795,7 +5001,7 @@
     <row r="163">
       <c r="A163" s="41" t="inlineStr">
         <is>
-          <t>Cash &amp; equivalents – year 1</t>
+          <t>Cash &amp; equivalents: year 1</t>
         </is>
       </c>
       <c r="F163" s="42">
@@ -4814,7 +5020,7 @@
     <row r="164">
       <c r="A164" s="41" t="inlineStr">
         <is>
-          <t>Cash &amp; equivalents – year 2</t>
+          <t>Cash &amp; equivalents: year 2</t>
         </is>
       </c>
       <c r="F164" s="42">
@@ -4833,7 +5039,7 @@
     <row r="165">
       <c r="A165" s="41" t="inlineStr">
         <is>
-          <t>Cash &amp; equivalents – year 3</t>
+          <t>Cash &amp; equivalents: year 3</t>
         </is>
       </c>
       <c r="F165" s="42">
@@ -4852,7 +5058,7 @@
     <row r="166">
       <c r="A166" s="41" t="inlineStr">
         <is>
-          <t>Cash &amp; equivalents – year 4</t>
+          <t>Cash &amp; equivalents: year 4</t>
         </is>
       </c>
       <c r="F166" s="42">
@@ -4871,7 +5077,7 @@
     <row r="167">
       <c r="A167" s="41" t="inlineStr">
         <is>
-          <t>Cash &amp; equivalents – year 5</t>
+          <t>Cash &amp; equivalents: year 5</t>
         </is>
       </c>
       <c r="F167" s="42">
@@ -4890,7 +5096,7 @@
     <row r="168">
       <c r="A168" s="41" t="inlineStr">
         <is>
-          <t>Total assets – year 1</t>
+          <t>Total assets: year 1</t>
         </is>
       </c>
       <c r="F168" s="42">
@@ -4909,7 +5115,7 @@
     <row r="169">
       <c r="A169" s="41" t="inlineStr">
         <is>
-          <t>Total assets – year 2</t>
+          <t>Total assets: year 2</t>
         </is>
       </c>
       <c r="F169" s="42">
@@ -4928,7 +5134,7 @@
     <row r="170">
       <c r="A170" s="41" t="inlineStr">
         <is>
-          <t>Total assets – year 3</t>
+          <t>Total assets: year 3</t>
         </is>
       </c>
       <c r="F170" s="42">
@@ -4947,7 +5153,7 @@
     <row r="171">
       <c r="A171" s="41" t="inlineStr">
         <is>
-          <t>Total assets – year 4</t>
+          <t>Total assets: year 4</t>
         </is>
       </c>
       <c r="F171" s="42">
@@ -4966,7 +5172,7 @@
     <row r="172">
       <c r="A172" s="41" t="inlineStr">
         <is>
-          <t>Total assets – year 5</t>
+          <t>Total assets: year 5</t>
         </is>
       </c>
       <c r="F172" s="42">
@@ -4985,7 +5191,7 @@
     <row r="173">
       <c r="A173" s="41" t="inlineStr">
         <is>
-          <t>Total liabilities – year 1</t>
+          <t>Total liabilities: year 1</t>
         </is>
       </c>
       <c r="F173" s="42">
@@ -5004,7 +5210,7 @@
     <row r="174">
       <c r="A174" s="41" t="inlineStr">
         <is>
-          <t>Total liabilities – year 2</t>
+          <t>Total liabilities: year 2</t>
         </is>
       </c>
       <c r="F174" s="42">
@@ -5023,7 +5229,7 @@
     <row r="175">
       <c r="A175" s="41" t="inlineStr">
         <is>
-          <t>Total liabilities – year 3</t>
+          <t>Total liabilities: year 3</t>
         </is>
       </c>
       <c r="F175" s="42">
@@ -5042,7 +5248,7 @@
     <row r="176">
       <c r="A176" s="41" t="inlineStr">
         <is>
-          <t>Total liabilities – year 4</t>
+          <t>Total liabilities: year 4</t>
         </is>
       </c>
       <c r="F176" s="42">
@@ -5061,7 +5267,7 @@
     <row r="177">
       <c r="A177" s="41" t="inlineStr">
         <is>
-          <t>Total liabilities – year 5</t>
+          <t>Total liabilities: year 5</t>
         </is>
       </c>
       <c r="F177" s="42">
@@ -5080,7 +5286,7 @@
     <row r="178">
       <c r="A178" s="41" t="inlineStr">
         <is>
-          <t>Total equity – year 1</t>
+          <t>Total equity: year 1</t>
         </is>
       </c>
       <c r="F178" s="42">
@@ -5099,7 +5305,7 @@
     <row r="179">
       <c r="A179" s="41" t="inlineStr">
         <is>
-          <t>Total equity – year 2</t>
+          <t>Total equity: year 2</t>
         </is>
       </c>
       <c r="F179" s="42">
@@ -5118,7 +5324,7 @@
     <row r="180">
       <c r="A180" s="41" t="inlineStr">
         <is>
-          <t>Total equity – year 3</t>
+          <t>Total equity: year 3</t>
         </is>
       </c>
       <c r="F180" s="42">
@@ -5137,7 +5343,7 @@
     <row r="181">
       <c r="A181" s="41" t="inlineStr">
         <is>
-          <t>Total equity – year 4</t>
+          <t>Total equity: year 4</t>
         </is>
       </c>
       <c r="F181" s="42">
@@ -5156,7 +5362,7 @@
     <row r="182">
       <c r="A182" s="41" t="inlineStr">
         <is>
-          <t>Total equity – year 5</t>
+          <t>Total equity: year 5</t>
         </is>
       </c>
       <c r="F182" s="42">
@@ -5175,7 +5381,7 @@
     <row r="183">
       <c r="A183" s="41" t="inlineStr">
         <is>
-          <t>Diluted shares (000) – year 1</t>
+          <t>Diluted shares (000): year 1</t>
         </is>
       </c>
       <c r="F183" s="42">
@@ -5194,7 +5400,7 @@
     <row r="184">
       <c r="A184" s="41" t="inlineStr">
         <is>
-          <t>Diluted shares (000) – year 2</t>
+          <t>Diluted shares (000): year 2</t>
         </is>
       </c>
       <c r="F184" s="42">
@@ -5213,7 +5419,7 @@
     <row r="185">
       <c r="A185" s="41" t="inlineStr">
         <is>
-          <t>Diluted shares (000) – year 3</t>
+          <t>Diluted shares (000): year 3</t>
         </is>
       </c>
       <c r="F185" s="42">
@@ -5232,7 +5438,7 @@
     <row r="186">
       <c r="A186" s="41" t="inlineStr">
         <is>
-          <t>Diluted shares (000) – year 4</t>
+          <t>Diluted shares (000): year 4</t>
         </is>
       </c>
       <c r="F186" s="42">
@@ -5251,7 +5457,7 @@
     <row r="187">
       <c r="A187" s="41" t="inlineStr">
         <is>
-          <t>Diluted shares (000) – year 5</t>
+          <t>Diluted shares (000): year 5</t>
         </is>
       </c>
       <c r="F187" s="42">
@@ -5270,7 +5476,7 @@
     <row r="188">
       <c r="A188" s="41" t="inlineStr">
         <is>
-          <t>Diluted EPS ($) – year 1</t>
+          <t>Diluted EPS ($): year 1</t>
         </is>
       </c>
       <c r="F188" s="49">
@@ -5289,7 +5495,7 @@
     <row r="189">
       <c r="A189" s="41" t="inlineStr">
         <is>
-          <t>Diluted EPS ($) – year 2</t>
+          <t>Diluted EPS ($): year 2</t>
         </is>
       </c>
       <c r="F189" s="49">
@@ -5308,7 +5514,7 @@
     <row r="190">
       <c r="A190" s="41" t="inlineStr">
         <is>
-          <t>Diluted EPS ($) – year 3</t>
+          <t>Diluted EPS ($): year 3</t>
         </is>
       </c>
       <c r="F190" s="49">
@@ -5327,7 +5533,7 @@
     <row r="191">
       <c r="A191" s="41" t="inlineStr">
         <is>
-          <t>Diluted EPS ($) – year 4</t>
+          <t>Diluted EPS ($): year 4</t>
         </is>
       </c>
       <c r="F191" s="49">
@@ -5346,7 +5552,7 @@
     <row r="192">
       <c r="A192" s="41" t="inlineStr">
         <is>
-          <t>Diluted EPS ($) – year 5</t>
+          <t>Diluted EPS ($): year 5</t>
         </is>
       </c>
       <c r="F192" s="49">
@@ -5419,6 +5625,9 @@
         <v>11102600</v>
       </c>
     </row>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="169" formatCode="0.0x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="60">
+  <fonts count="61">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -378,8 +378,13 @@
       <color rgb="00404040"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -411,8 +416,23 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -433,11 +453,12 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -804,6 +825,95 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1781,3870 +1891,4646 @@
   <dimension ref="A1:H203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="2" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+    <col width="2" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>SCENARIO ANALYSIS</t>
         </is>
       </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-      <c r="E1" s="13" t="n"/>
-      <c r="F1" s="13" t="n"/>
+      <c r="B1" s="137" t="n"/>
+      <c r="C1" s="137" t="n"/>
+      <c r="D1" s="137" t="n"/>
+      <c r="E1" s="137" t="n"/>
+      <c r="F1" s="137" t="n"/>
       <c r="G1" s="13" t="n"/>
       <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="F2" s="34" t="inlineStr">
+      <c r="A2" s="138" t="n"/>
+      <c r="B2" s="165" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="G2" s="35" t="inlineStr">
+      <c r="C2" s="166" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="H2" s="36" t="inlineStr">
+      <c r="D2" s="167" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
+      <c r="E2" s="138" t="n"/>
+      <c r="F2" s="138" t="n"/>
+      <c r="G2" s="35" t="n"/>
+      <c r="H2" s="36" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="142" t="inlineStr">
         <is>
           <t>Key assumptions (5-yr forecast)</t>
         </is>
       </c>
-      <c r="B3" s="134" t="inlineStr">
+      <c r="B3" s="138" t="n"/>
+      <c r="C3" s="138" t="n"/>
+      <c r="D3" s="138" t="n"/>
+      <c r="E3" s="143" t="inlineStr">
+        <is>
+          <t>Source (click)</t>
+        </is>
+      </c>
+      <c r="F3" s="143" t="inlineStr">
         <is>
           <t>How it moves</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>Source (click)</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="144" t="inlineStr">
         <is>
           <t>FY2026E revenue growth</t>
         </is>
       </c>
-      <c r="B4" s="135" t="inlineStr">
+      <c r="B4" s="145" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="C4" s="145" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="D4" s="145" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E4" s="146" t="inlineStr">
+        <is>
+          <t>LULU Q2 FY2026 earnings release</t>
+        </is>
+      </c>
+      <c r="F4" s="147" t="inlineStr">
         <is>
           <t>Year-one sales change: bear falls most.</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>LULU Q2 FY2026 earnings release</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="n"/>
-      <c r="F4" s="20" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G4" s="20" t="n">
-        <v>-0.061</v>
-      </c>
-      <c r="H4" s="20" t="n">
-        <v>-0.04</v>
-      </c>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="20" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="144" t="inlineStr">
         <is>
           <t>FY2027–FY2030E revenue growth (avg)</t>
         </is>
       </c>
-      <c r="B5" s="135" t="inlineStr">
+      <c r="B5" s="145" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C5" s="145" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="D5" s="145" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E5" s="146" t="inlineStr">
+        <is>
+          <t>StockAnalysis: LULU 3Y revenue forecast</t>
+        </is>
+      </c>
+      <c r="F5" s="147" t="inlineStr">
         <is>
           <t>Years two-five average growth: bull fastest.</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>StockAnalysis: LULU 3Y revenue forecast</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="n"/>
-      <c r="F5" s="20" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G5" s="20" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="H5" s="20" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="144" t="inlineStr">
         <is>
           <t>Run-rate EBIT margin (clean, ex-refunds)</t>
         </is>
       </c>
-      <c r="B6" s="135" t="inlineStr">
+      <c r="B6" s="145" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C6" s="145" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="D6" s="145" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="E6" s="146" t="inlineStr">
+        <is>
+          <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs</t>
+        </is>
+      </c>
+      <c r="F6" s="147" t="inlineStr">
         <is>
           <t>Starting operating margin before linear ramp.</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="n"/>
-      <c r="F6" s="20" t="n">
+      <c r="G6" s="20" t="n"/>
+      <c r="H6" s="20" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="144" t="inlineStr">
+        <is>
+          <t>FY26 IEEPA tariff refunds ($k, already in guide)</t>
+        </is>
+      </c>
+      <c r="B7" s="148" t="n">
+        <v>134500</v>
+      </c>
+      <c r="C7" s="148" t="n">
+        <v>134500</v>
+      </c>
+      <c r="D7" s="148" t="n">
+        <v>134500</v>
+      </c>
+      <c r="E7" s="146" t="inlineStr">
+        <is>
+          <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
+        </is>
+      </c>
+      <c r="F7" s="147" t="inlineStr">
+        <is>
+          <t>One-time year-one EBIT boost: zero after.</t>
+        </is>
+      </c>
+      <c r="G7" s="37" t="n"/>
+      <c r="H7" s="37" t="n"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="144" t="inlineStr">
+        <is>
+          <t>Terminal (FY2030E) EBIT margin</t>
+        </is>
+      </c>
+      <c r="B8" s="145" t="n">
         <v>0.12</v>
       </c>
-      <c r="G6" s="20" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <v>0.145</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>FY26 IEEPA tariff refunds ($k, already in guide)</t>
-        </is>
-      </c>
-      <c r="B7" s="135" t="inlineStr">
-        <is>
-          <t>One-time year-one EBIT boost: zero after.</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="n"/>
-      <c r="F7" s="37" t="n">
-        <v>134500</v>
-      </c>
-      <c r="G7" s="37" t="n">
-        <v>134500</v>
-      </c>
-      <c r="H7" s="37" t="n">
-        <v>134500</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Terminal (FY2030E) EBIT margin</t>
-        </is>
-      </c>
-      <c r="B8" s="135" t="inlineStr">
+      <c r="C8" s="145" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="D8" s="145" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E8" s="146" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: Operating margin 19.9% (one hit)</t>
+        </is>
+      </c>
+      <c r="F8" s="147" t="inlineStr">
         <is>
           <t>Year-five target margin after linear ramp.</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: Operating margin 19.9% (one hit)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="n"/>
-      <c r="F8" s="20" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="H8" s="20" t="n">
-        <v>0.19</v>
-      </c>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="144" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B9" s="135" t="inlineStr">
+      <c r="B9" s="145" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C9" s="149">
+        <f>WACC!E41</f>
+        <v/>
+      </c>
+      <c r="D9" s="145" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="E9" s="146" t="inlineStr">
+        <is>
+          <t>WACC tab: CAPM build</t>
+        </is>
+      </c>
+      <c r="F9" s="147" t="inlineStr">
         <is>
           <t>Flat discount rate: higher bear, lower bull.</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>WACC tab: CAPM build</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="n"/>
-      <c r="F9" s="20" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G9" s="32">
-        <f>WACC!E41</f>
-        <v/>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>0.095</v>
-      </c>
+      <c r="G9" s="32" t="n"/>
+      <c r="H9" s="20" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="144" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="B10" s="135" t="inlineStr">
+      <c r="B10" s="145" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C10" s="145" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D10" s="145" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E10" s="146" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
+      <c r="F10" s="147" t="inlineStr">
         <is>
           <t>Perpetuity growth rate: flat across all years.</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>FRED: Real GDP (GDPC1)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="n"/>
-      <c r="F10" s="20" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="144" t="inlineStr">
         <is>
           <t>Cash tax rate</t>
         </is>
       </c>
-      <c r="B11" s="135" t="inlineStr">
+      <c r="B11" s="145" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C11" s="145" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D11" s="145" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E11" s="146" t="inlineStr">
+        <is>
+          <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
+        </is>
+      </c>
+      <c r="F11" s="147" t="inlineStr">
         <is>
           <t>Flat tax percentage applied every forecast year.</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="n"/>
-      <c r="F11" s="20" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>0.28</v>
-      </c>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="144" t="inlineStr">
         <is>
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B12" s="135" t="inlineStr">
+      <c r="B12" s="145" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="C12" s="145" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D12" s="145" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E12" s="146" t="inlineStr">
+        <is>
+          <t>LULU CF statement (10-K)</t>
+        </is>
+      </c>
+      <c r="F12" s="147" t="inlineStr">
         <is>
           <t>Depreciation scales as fixed percent of revenue.</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="n"/>
-      <c r="F12" s="20" t="n">
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="144" t="inlineStr">
+        <is>
+          <t>Capex % of revenue</t>
+        </is>
+      </c>
+      <c r="B13" s="145" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C13" s="145" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D13" s="145" t="n">
         <v>0.045</v>
       </c>
-      <c r="G12" s="20" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>0.045</v>
-      </c>
-    </row>
-    <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Capex % of revenue</t>
-        </is>
-      </c>
-      <c r="B13" s="135" t="inlineStr">
+      <c r="E13" s="150" t="inlineStr">
+        <is>
+          <t>LULU 10-K: 2026 capex guide $725–745M</t>
+        </is>
+      </c>
+      <c r="F13" s="147" t="inlineStr">
         <is>
           <t>Investment scales as fixed percent of revenue.</t>
         </is>
       </c>
-      <c r="C13" s="38" t="inlineStr">
-        <is>
-          <t>LULU 10-K: 2026 capex guide $725–745M</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="n"/>
-      <c r="F13" s="20" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>0.045</v>
-      </c>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
     </row>
     <row r="14" ht="112" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="144" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B14" s="135" t="inlineStr">
+      <c r="B14" s="145" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C14" s="145" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="D14" s="145" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E14" s="146" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Gross profit &amp; COGS</t>
+        </is>
+      </c>
+      <c r="F14" s="147" t="inlineStr">
         <is>
           <t>Merchandise margin held flat every forecast year.</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: Gross profit &amp; COGS</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="n"/>
-      <c r="F14" s="20" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>0.575</v>
-      </c>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
     </row>
     <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="144" t="inlineStr">
         <is>
           <t>DSO (days): flat vs FY25</t>
         </is>
       </c>
-      <c r="B15" s="135" t="inlineStr">
+      <c r="B15" s="151">
+        <f>(DCF!$E$21/$B$198)*365</f>
+        <v/>
+      </c>
+      <c r="C15" s="151">
+        <f>(DCF!$E$21/$B$198)*365</f>
+        <v/>
+      </c>
+      <c r="D15" s="151">
+        <f>(DCF!$E$21/$B$198)*365</f>
+        <v/>
+      </c>
+      <c r="E15" s="146" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Accounts receivable, net</t>
+        </is>
+      </c>
+      <c r="F15" s="147" t="inlineStr">
         <is>
           <t>Collection days held flat near six yearly.</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: Accounts receivable, net</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="n"/>
-      <c r="F15" s="130">
-        <f>(DCF!$E$21/$B$198)*365</f>
-        <v/>
-      </c>
-      <c r="G15" s="130">
-        <f>(DCF!$E$21/$B$198)*365</f>
-        <v/>
-      </c>
-      <c r="H15" s="130">
-        <f>(DCF!$E$21/$B$198)*365</f>
-        <v/>
-      </c>
+      <c r="G15" s="130" t="n"/>
+      <c r="H15" s="130" t="n"/>
     </row>
     <row r="16" ht="140" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="144" t="inlineStr">
         <is>
           <t>FY25 DIO anchor (days)</t>
         </is>
       </c>
-      <c r="B16" s="135" t="inlineStr">
+      <c r="B16" s="151">
+        <f>(DCF!$E$23/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="C16" s="151">
+        <f>(DCF!$E$23/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="D16" s="151">
+        <f>(DCF!$E$23/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="E16" s="146" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Inventories &amp; COGS</t>
+        </is>
+      </c>
+      <c r="F16" s="147" t="inlineStr">
         <is>
           <t>Starting inventory days before annual decline begins.</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: Inventories &amp; COGS</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="n"/>
-      <c r="F16" s="130">
-        <f>(DCF!$E$23/DCF!$E$8)*365</f>
-        <v/>
-      </c>
-      <c r="G16" s="130">
-        <f>(DCF!$E$23/DCF!$E$8)*365</f>
-        <v/>
-      </c>
-      <c r="H16" s="130">
-        <f>(DCF!$E$23/DCF!$E$8)*365</f>
-        <v/>
-      </c>
+      <c r="G16" s="130" t="n"/>
+      <c r="H16" s="130" t="n"/>
     </row>
     <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="144" t="inlineStr">
         <is>
           <t>DIO decline (days / forecast yr)</t>
         </is>
       </c>
-      <c r="B17" s="135" t="inlineStr">
+      <c r="B17" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="146" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: inventory &amp; markdown outlook</t>
+        </is>
+      </c>
+      <c r="F17" s="147" t="inlineStr">
         <is>
           <t>Inventory days fall one day each year.</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: inventory &amp; markdown outlook</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="n"/>
-      <c r="F17" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="40" t="n">
-        <v>1</v>
-      </c>
+      <c r="G17" s="40" t="n"/>
+      <c r="H17" s="40" t="n"/>
     </row>
     <row r="18" ht="84" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="144" t="inlineStr">
         <is>
           <t>DPO (days): flat vs FY25</t>
         </is>
       </c>
-      <c r="B18" s="135" t="inlineStr">
+      <c r="B18" s="151">
+        <f>(DCF!$E$25/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="C18" s="151">
+        <f>(DCF!$E$25/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="D18" s="151">
+        <f>(DCF!$E$25/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="E18" s="146" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Accounts payable &amp; COGS</t>
+        </is>
+      </c>
+      <c r="F18" s="147" t="inlineStr">
         <is>
           <t>Payment days held flat near twenty-five yearly.</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: Accounts payable &amp; COGS</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="n"/>
-      <c r="F18" s="130">
-        <f>(DCF!$E$25/DCF!$E$8)*365</f>
-        <v/>
-      </c>
-      <c r="G18" s="130">
-        <f>(DCF!$E$25/DCF!$E$8)*365</f>
-        <v/>
-      </c>
-      <c r="H18" s="130">
-        <f>(DCF!$E$25/DCF!$E$8)*365</f>
-        <v/>
-      </c>
+      <c r="G18" s="130" t="n"/>
+      <c r="H18" s="130" t="n"/>
     </row>
     <row r="19" ht="84" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="144" t="inlineStr">
         <is>
           <t>Prepaid expenses (% of revenue)</t>
         </is>
       </c>
-      <c r="B19" s="135" t="inlineStr">
+      <c r="B19" s="145">
+        <f>DCF!$E$27/$B$198</f>
+        <v/>
+      </c>
+      <c r="C19" s="145">
+        <f>DCF!$E$27/$B$198</f>
+        <v/>
+      </c>
+      <c r="D19" s="145">
+        <f>DCF!$E$27/$B$198</f>
+        <v/>
+      </c>
+      <c r="E19" s="146" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: other current assets (residual)</t>
+        </is>
+      </c>
+      <c r="F19" s="147" t="inlineStr">
         <is>
           <t>Other current assets flat percent of revenue.</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: other current assets (residual)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="n"/>
-      <c r="F19" s="20">
-        <f>DCF!$E$27/$B$198</f>
-        <v/>
-      </c>
-      <c r="G19" s="20">
-        <f>DCF!$E$27/$B$198</f>
-        <v/>
-      </c>
-      <c r="H19" s="20">
-        <f>DCF!$E$27/$B$198</f>
-        <v/>
-      </c>
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="20" t="n"/>
     </row>
     <row r="20" ht="84" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="144" t="inlineStr">
         <is>
           <t>Accrued liabilities (% of revenue)</t>
         </is>
       </c>
-      <c r="B20" s="135" t="inlineStr">
+      <c r="B20" s="145">
+        <f>DCF!$E$29/$B$198</f>
+        <v/>
+      </c>
+      <c r="C20" s="145">
+        <f>DCF!$E$29/$B$198</f>
+        <v/>
+      </c>
+      <c r="D20" s="145">
+        <f>DCF!$E$29/$B$198</f>
+        <v/>
+      </c>
+      <c r="E20" s="146" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Accrued liabilities and other</t>
+        </is>
+      </c>
+      <c r="F20" s="147" t="inlineStr">
         <is>
           <t>Accrued payables flat percent of revenue.</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: Accrued liabilities and other</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="n"/>
-      <c r="F20" s="20">
-        <f>DCF!$E$29/$B$198</f>
-        <v/>
-      </c>
-      <c r="G20" s="20">
-        <f>DCF!$E$29/$B$198</f>
-        <v/>
-      </c>
-      <c r="H20" s="20">
-        <f>DCF!$E$29/$B$198</f>
-        <v/>
-      </c>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="144" t="inlineStr">
         <is>
           <t>Pitch CFF: fixed buyback ($k/yr) bear/base</t>
         </is>
       </c>
-      <c r="B21" s="135" t="inlineStr">
+      <c r="B21" s="148" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C21" s="148" t="n">
+        <v>750000</v>
+      </c>
+      <c r="D21" s="148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="138" t="n"/>
+      <c r="F21" s="147" t="inlineStr">
         <is>
           <t>Bear base retire fixed dollars yearly.</t>
         </is>
       </c>
-      <c r="F21" s="37" t="n">
-        <v>750000</v>
-      </c>
-      <c r="G21" s="37" t="n">
-        <v>750000</v>
-      </c>
-      <c r="H21" s="37" t="n">
+      <c r="G21" s="37" t="n"/>
+      <c r="H21" s="37" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="144" t="inlineStr">
+        <is>
+          <t>Pitch CFF: % of FCF to buybacks (bull)</t>
+        </is>
+      </c>
+      <c r="B22" s="145" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>Pitch CFF: % of FCF to buybacks (bull)</t>
-        </is>
-      </c>
-      <c r="B22" s="135" t="inlineStr">
+      <c r="C22" s="145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="145" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E22" s="138" t="n"/>
+      <c r="F22" s="147" t="inlineStr">
         <is>
           <t>Bull spends set percent of free cash.</t>
         </is>
       </c>
-      <c r="F22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="23"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="138" t="n"/>
+      <c r="B23" s="138" t="n"/>
+      <c r="C23" s="138" t="n"/>
+      <c r="D23" s="138" t="n"/>
+      <c r="E23" s="138" t="n"/>
+      <c r="F23" s="138" t="n"/>
+    </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="142" t="inlineStr">
         <is>
           <t>5-year forecast paths (by scenario)</t>
         </is>
       </c>
+      <c r="B24" s="138" t="n"/>
+      <c r="C24" s="138" t="n"/>
+      <c r="D24" s="138" t="n"/>
+      <c r="E24" s="138" t="n"/>
+      <c r="F24" s="138" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="41" t="inlineStr">
+      <c r="A25" s="153" t="inlineStr">
         <is>
           <t>Revenue: year 1</t>
         </is>
       </c>
-      <c r="B25" s="135" t="inlineStr">
+      <c r="B25" s="154">
+        <f>$B$198*(1+B4)</f>
+        <v/>
+      </c>
+      <c r="C25" s="154">
+        <f>$B$198*(1+C4)</f>
+        <v/>
+      </c>
+      <c r="D25" s="154">
+        <f>$B$198*(1+D4)</f>
+        <v/>
+      </c>
+      <c r="E25" s="138" t="n"/>
+      <c r="F25" s="147" t="inlineStr">
         <is>
           <t>Grows or shrinks using scenario-specific growth rates.</t>
         </is>
       </c>
-      <c r="F25" s="42">
-        <f>$B$198*(1+F4)</f>
-        <v/>
-      </c>
-      <c r="G25" s="42">
-        <f>$B$198*(1+G4)</f>
-        <v/>
-      </c>
-      <c r="H25" s="42">
-        <f>$B$198*(1+H4)</f>
-        <v/>
-      </c>
+      <c r="G25" s="42" t="n"/>
+      <c r="H25" s="42" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="41" t="inlineStr">
+      <c r="A26" s="153" t="inlineStr">
         <is>
           <t>Revenue: year 2</t>
         </is>
       </c>
-      <c r="F26" s="42">
-        <f>F25*(1+F5)</f>
-        <v/>
-      </c>
-      <c r="G26" s="42">
-        <f>G25*(1+G5)</f>
-        <v/>
-      </c>
-      <c r="H26" s="42">
-        <f>H25*(1+H5)</f>
-        <v/>
-      </c>
+      <c r="B26" s="154">
+        <f>B25*(1+B5)</f>
+        <v/>
+      </c>
+      <c r="C26" s="154">
+        <f>C25*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D26" s="154">
+        <f>D25*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E26" s="138" t="n"/>
+      <c r="F26" s="138" t="n"/>
+      <c r="G26" s="42" t="n"/>
+      <c r="H26" s="42" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="41" t="inlineStr">
+      <c r="A27" s="153" t="inlineStr">
         <is>
           <t>Revenue: year 3</t>
         </is>
       </c>
-      <c r="F27" s="42">
-        <f>F26*(1+F5)</f>
-        <v/>
-      </c>
-      <c r="G27" s="42">
-        <f>G26*(1+G5)</f>
-        <v/>
-      </c>
-      <c r="H27" s="42">
-        <f>H26*(1+H5)</f>
-        <v/>
-      </c>
+      <c r="B27" s="154">
+        <f>B26*(1+B5)</f>
+        <v/>
+      </c>
+      <c r="C27" s="154">
+        <f>C26*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D27" s="154">
+        <f>D26*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E27" s="138" t="n"/>
+      <c r="F27" s="138" t="n"/>
+      <c r="G27" s="42" t="n"/>
+      <c r="H27" s="42" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="41" t="inlineStr">
+      <c r="A28" s="153" t="inlineStr">
         <is>
           <t>Revenue: year 4</t>
         </is>
       </c>
-      <c r="F28" s="42">
-        <f>F27*(1+F5)</f>
-        <v/>
-      </c>
-      <c r="G28" s="42">
-        <f>G27*(1+G5)</f>
-        <v/>
-      </c>
-      <c r="H28" s="42">
-        <f>H27*(1+H5)</f>
-        <v/>
-      </c>
+      <c r="B28" s="154">
+        <f>B27*(1+B5)</f>
+        <v/>
+      </c>
+      <c r="C28" s="154">
+        <f>C27*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D28" s="154">
+        <f>D27*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E28" s="138" t="n"/>
+      <c r="F28" s="138" t="n"/>
+      <c r="G28" s="42" t="n"/>
+      <c r="H28" s="42" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="41" t="inlineStr">
+      <c r="A29" s="153" t="inlineStr">
         <is>
           <t>Revenue: year 5</t>
         </is>
       </c>
-      <c r="F29" s="42">
-        <f>F28*(1+F5)</f>
-        <v/>
-      </c>
-      <c r="G29" s="42">
-        <f>G28*(1+G5)</f>
-        <v/>
-      </c>
-      <c r="H29" s="42">
-        <f>H28*(1+H5)</f>
-        <v/>
-      </c>
+      <c r="B29" s="154">
+        <f>B28*(1+B5)</f>
+        <v/>
+      </c>
+      <c r="C29" s="154">
+        <f>C28*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D29" s="154">
+        <f>D28*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E29" s="138" t="n"/>
+      <c r="F29" s="138" t="n"/>
+      <c r="G29" s="42" t="n"/>
+      <c r="H29" s="42" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="41" t="inlineStr">
+      <c r="A30" s="153" t="inlineStr">
         <is>
           <t>Gross margin %: year 1</t>
         </is>
       </c>
-      <c r="B30" s="135" t="inlineStr">
+      <c r="B30" s="155">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="C30" s="155">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="D30" s="155">
+        <f>D14</f>
+        <v/>
+      </c>
+      <c r="E30" s="138" t="n"/>
+      <c r="F30" s="147" t="inlineStr">
         <is>
           <t>Stays flat at scenario margin every year.</t>
         </is>
       </c>
-      <c r="F30" s="43">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="G30" s="43">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="H30" s="43">
-        <f>H14</f>
-        <v/>
-      </c>
+      <c r="G30" s="43" t="n"/>
+      <c r="H30" s="43" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="41" t="inlineStr">
+      <c r="A31" s="153" t="inlineStr">
         <is>
           <t>Gross margin %: year 2</t>
         </is>
       </c>
-      <c r="F31" s="43">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="G31" s="43">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="H31" s="43">
-        <f>H14</f>
-        <v/>
-      </c>
+      <c r="B31" s="155">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="C31" s="155">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="D31" s="155">
+        <f>D14</f>
+        <v/>
+      </c>
+      <c r="E31" s="138" t="n"/>
+      <c r="F31" s="138" t="n"/>
+      <c r="G31" s="43" t="n"/>
+      <c r="H31" s="43" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="41" t="inlineStr">
+      <c r="A32" s="153" t="inlineStr">
         <is>
           <t>Gross margin %: year 3</t>
         </is>
       </c>
-      <c r="F32" s="43">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="G32" s="43">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="H32" s="43">
-        <f>H14</f>
-        <v/>
-      </c>
+      <c r="B32" s="155">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="C32" s="155">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="D32" s="155">
+        <f>D14</f>
+        <v/>
+      </c>
+      <c r="E32" s="138" t="n"/>
+      <c r="F32" s="138" t="n"/>
+      <c r="G32" s="43" t="n"/>
+      <c r="H32" s="43" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="41" t="inlineStr">
+      <c r="A33" s="153" t="inlineStr">
         <is>
           <t>Gross margin %: year 4</t>
         </is>
       </c>
-      <c r="F33" s="43">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="G33" s="43">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="H33" s="43">
-        <f>H14</f>
-        <v/>
-      </c>
+      <c r="B33" s="155">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="C33" s="155">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="D33" s="155">
+        <f>D14</f>
+        <v/>
+      </c>
+      <c r="E33" s="138" t="n"/>
+      <c r="F33" s="138" t="n"/>
+      <c r="G33" s="43" t="n"/>
+      <c r="H33" s="43" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="41" t="inlineStr">
+      <c r="A34" s="153" t="inlineStr">
         <is>
           <t>Gross margin %: year 5</t>
         </is>
       </c>
-      <c r="F34" s="43">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="G34" s="43">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="H34" s="43">
-        <f>H14</f>
-        <v/>
-      </c>
+      <c r="B34" s="155">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="C34" s="155">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="D34" s="155">
+        <f>D14</f>
+        <v/>
+      </c>
+      <c r="E34" s="138" t="n"/>
+      <c r="F34" s="138" t="n"/>
+      <c r="G34" s="43" t="n"/>
+      <c r="H34" s="43" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="41" t="inlineStr">
+      <c r="A35" s="153" t="inlineStr">
         <is>
           <t>Cost of goods sold (COGS): year 1</t>
         </is>
       </c>
-      <c r="B35" s="135" t="inlineStr">
+      <c r="B35" s="154">
+        <f>B25*(1-B30)</f>
+        <v/>
+      </c>
+      <c r="C35" s="154">
+        <f>C25*(1-C30)</f>
+        <v/>
+      </c>
+      <c r="D35" s="154">
+        <f>D25*(1-D30)</f>
+        <v/>
+      </c>
+      <c r="E35" s="138" t="n"/>
+      <c r="F35" s="147" t="inlineStr">
         <is>
           <t>Moves with revenue when gross margin stays flat.</t>
         </is>
       </c>
-      <c r="F35" s="42">
-        <f>F25*(1-F30)</f>
-        <v/>
-      </c>
-      <c r="G35" s="42">
-        <f>G25*(1-G30)</f>
-        <v/>
-      </c>
-      <c r="H35" s="42">
-        <f>H25*(1-H30)</f>
-        <v/>
-      </c>
+      <c r="G35" s="42" t="n"/>
+      <c r="H35" s="42" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="41" t="inlineStr">
+      <c r="A36" s="153" t="inlineStr">
         <is>
           <t>Cost of goods sold (COGS): year 2</t>
         </is>
       </c>
-      <c r="F36" s="42">
-        <f>F26*(1-F31)</f>
-        <v/>
-      </c>
-      <c r="G36" s="42">
-        <f>G26*(1-G31)</f>
-        <v/>
-      </c>
-      <c r="H36" s="42">
-        <f>H26*(1-H31)</f>
-        <v/>
-      </c>
+      <c r="B36" s="154">
+        <f>B26*(1-B31)</f>
+        <v/>
+      </c>
+      <c r="C36" s="154">
+        <f>C26*(1-C31)</f>
+        <v/>
+      </c>
+      <c r="D36" s="154">
+        <f>D26*(1-D31)</f>
+        <v/>
+      </c>
+      <c r="E36" s="138" t="n"/>
+      <c r="F36" s="138" t="n"/>
+      <c r="G36" s="42" t="n"/>
+      <c r="H36" s="42" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="41" t="inlineStr">
+      <c r="A37" s="153" t="inlineStr">
         <is>
           <t>Cost of goods sold (COGS): year 3</t>
         </is>
       </c>
-      <c r="F37" s="42">
-        <f>F27*(1-F32)</f>
-        <v/>
-      </c>
-      <c r="G37" s="42">
-        <f>G27*(1-G32)</f>
-        <v/>
-      </c>
-      <c r="H37" s="42">
-        <f>H27*(1-H32)</f>
-        <v/>
-      </c>
+      <c r="B37" s="154">
+        <f>B27*(1-B32)</f>
+        <v/>
+      </c>
+      <c r="C37" s="154">
+        <f>C27*(1-C32)</f>
+        <v/>
+      </c>
+      <c r="D37" s="154">
+        <f>D27*(1-D32)</f>
+        <v/>
+      </c>
+      <c r="E37" s="138" t="n"/>
+      <c r="F37" s="138" t="n"/>
+      <c r="G37" s="42" t="n"/>
+      <c r="H37" s="42" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="41" t="inlineStr">
+      <c r="A38" s="153" t="inlineStr">
         <is>
           <t>Cost of goods sold (COGS): year 4</t>
         </is>
       </c>
-      <c r="F38" s="42">
-        <f>F28*(1-F33)</f>
-        <v/>
-      </c>
-      <c r="G38" s="42">
-        <f>G28*(1-G33)</f>
-        <v/>
-      </c>
-      <c r="H38" s="42">
-        <f>H28*(1-H33)</f>
-        <v/>
-      </c>
+      <c r="B38" s="154">
+        <f>B28*(1-B33)</f>
+        <v/>
+      </c>
+      <c r="C38" s="154">
+        <f>C28*(1-C33)</f>
+        <v/>
+      </c>
+      <c r="D38" s="154">
+        <f>D28*(1-D33)</f>
+        <v/>
+      </c>
+      <c r="E38" s="138" t="n"/>
+      <c r="F38" s="138" t="n"/>
+      <c r="G38" s="42" t="n"/>
+      <c r="H38" s="42" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="41" t="inlineStr">
+      <c r="A39" s="153" t="inlineStr">
         <is>
           <t>Cost of goods sold (COGS): year 5</t>
         </is>
       </c>
-      <c r="F39" s="42">
-        <f>F29*(1-F34)</f>
-        <v/>
-      </c>
-      <c r="G39" s="42">
-        <f>G29*(1-G34)</f>
-        <v/>
-      </c>
-      <c r="H39" s="42">
-        <f>H29*(1-H34)</f>
-        <v/>
-      </c>
+      <c r="B39" s="154">
+        <f>B29*(1-B34)</f>
+        <v/>
+      </c>
+      <c r="C39" s="154">
+        <f>C29*(1-C34)</f>
+        <v/>
+      </c>
+      <c r="D39" s="154">
+        <f>D29*(1-D34)</f>
+        <v/>
+      </c>
+      <c r="E39" s="138" t="n"/>
+      <c r="F39" s="138" t="n"/>
+      <c r="G39" s="42" t="n"/>
+      <c r="H39" s="42" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="41" t="inlineStr">
+      <c r="A40" s="153" t="inlineStr">
         <is>
           <t>Clean EBIT margin: year 1</t>
         </is>
       </c>
-      <c r="B40" s="135" t="inlineStr">
+      <c r="B40" s="155">
+        <f>B6+(B8-B6)*0/4</f>
+        <v/>
+      </c>
+      <c r="C40" s="155">
+        <f>C6+(C8-C6)*0/4</f>
+        <v/>
+      </c>
+      <c r="D40" s="155">
+        <f>D6+(D8-D6)*0/4</f>
+        <v/>
+      </c>
+      <c r="E40" s="138" t="n"/>
+      <c r="F40" s="147" t="inlineStr">
         <is>
           <t>Linearly ramps from run-rate toward terminal margin.</t>
         </is>
       </c>
-      <c r="F40" s="43">
-        <f>F6+(F8-F6)*0/4</f>
-        <v/>
-      </c>
-      <c r="G40" s="43">
-        <f>G6+(G8-G6)*0/4</f>
-        <v/>
-      </c>
-      <c r="H40" s="43">
-        <f>H6+(H8-H6)*0/4</f>
-        <v/>
-      </c>
+      <c r="G40" s="43" t="n"/>
+      <c r="H40" s="43" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="41" t="inlineStr">
+      <c r="A41" s="153" t="inlineStr">
         <is>
           <t>Clean EBIT margin: year 2</t>
         </is>
       </c>
-      <c r="F41" s="43">
-        <f>F6+(F8-F6)*1/4</f>
-        <v/>
-      </c>
-      <c r="G41" s="43">
-        <f>G6+(G8-G6)*1/4</f>
-        <v/>
-      </c>
-      <c r="H41" s="43">
-        <f>H6+(H8-H6)*1/4</f>
-        <v/>
-      </c>
+      <c r="B41" s="155">
+        <f>B6+(B8-B6)*1/4</f>
+        <v/>
+      </c>
+      <c r="C41" s="155">
+        <f>C6+(C8-C6)*1/4</f>
+        <v/>
+      </c>
+      <c r="D41" s="155">
+        <f>D6+(D8-D6)*1/4</f>
+        <v/>
+      </c>
+      <c r="E41" s="138" t="n"/>
+      <c r="F41" s="138" t="n"/>
+      <c r="G41" s="43" t="n"/>
+      <c r="H41" s="43" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="41" t="inlineStr">
+      <c r="A42" s="153" t="inlineStr">
         <is>
           <t>Clean EBIT margin: year 3</t>
         </is>
       </c>
-      <c r="F42" s="43">
-        <f>F6+(F8-F6)*2/4</f>
-        <v/>
-      </c>
-      <c r="G42" s="43">
-        <f>G6+(G8-G6)*2/4</f>
-        <v/>
-      </c>
-      <c r="H42" s="43">
-        <f>H6+(H8-H6)*2/4</f>
-        <v/>
-      </c>
+      <c r="B42" s="155">
+        <f>B6+(B8-B6)*2/4</f>
+        <v/>
+      </c>
+      <c r="C42" s="155">
+        <f>C6+(C8-C6)*2/4</f>
+        <v/>
+      </c>
+      <c r="D42" s="155">
+        <f>D6+(D8-D6)*2/4</f>
+        <v/>
+      </c>
+      <c r="E42" s="138" t="n"/>
+      <c r="F42" s="138" t="n"/>
+      <c r="G42" s="43" t="n"/>
+      <c r="H42" s="43" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="41" t="inlineStr">
+      <c r="A43" s="153" t="inlineStr">
         <is>
           <t>Clean EBIT margin: year 4</t>
         </is>
       </c>
-      <c r="F43" s="43">
-        <f>F6+(F8-F6)*3/4</f>
-        <v/>
-      </c>
-      <c r="G43" s="43">
-        <f>G6+(G8-G6)*3/4</f>
-        <v/>
-      </c>
-      <c r="H43" s="43">
-        <f>H6+(H8-H6)*3/4</f>
-        <v/>
-      </c>
+      <c r="B43" s="155">
+        <f>B6+(B8-B6)*3/4</f>
+        <v/>
+      </c>
+      <c r="C43" s="155">
+        <f>C6+(C8-C6)*3/4</f>
+        <v/>
+      </c>
+      <c r="D43" s="155">
+        <f>D6+(D8-D6)*3/4</f>
+        <v/>
+      </c>
+      <c r="E43" s="138" t="n"/>
+      <c r="F43" s="138" t="n"/>
+      <c r="G43" s="43" t="n"/>
+      <c r="H43" s="43" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="41" t="inlineStr">
+      <c r="A44" s="153" t="inlineStr">
         <is>
           <t>Clean EBIT margin: year 5</t>
         </is>
       </c>
-      <c r="F44" s="43">
-        <f>F6+(F8-F6)*4/4</f>
-        <v/>
-      </c>
-      <c r="G44" s="43">
-        <f>G6+(G8-G6)*4/4</f>
-        <v/>
-      </c>
-      <c r="H44" s="43">
-        <f>H6+(H8-H6)*4/4</f>
-        <v/>
-      </c>
+      <c r="B44" s="155">
+        <f>B6+(B8-B6)*4/4</f>
+        <v/>
+      </c>
+      <c r="C44" s="155">
+        <f>C6+(C8-C6)*4/4</f>
+        <v/>
+      </c>
+      <c r="D44" s="155">
+        <f>D6+(D8-D6)*4/4</f>
+        <v/>
+      </c>
+      <c r="E44" s="138" t="n"/>
+      <c r="F44" s="138" t="n"/>
+      <c r="G44" s="43" t="n"/>
+      <c r="H44" s="43" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="41" t="inlineStr">
+      <c r="A45" s="153" t="inlineStr">
         <is>
           <t>EBIT: year 1</t>
         </is>
       </c>
-      <c r="B45" s="135" t="inlineStr">
+      <c r="B45" s="154">
+        <f>B25*B40+B7</f>
+        <v/>
+      </c>
+      <c r="C45" s="154">
+        <f>C25*C40+C7</f>
+        <v/>
+      </c>
+      <c r="D45" s="154">
+        <f>D25*D40+D7</f>
+        <v/>
+      </c>
+      <c r="E45" s="138" t="n"/>
+      <c r="F45" s="147" t="inlineStr">
         <is>
           <t>Revenue times margin: year one adds tariff refund.</t>
         </is>
       </c>
-      <c r="F45" s="42">
-        <f>F25*F40+F7</f>
-        <v/>
-      </c>
-      <c r="G45" s="42">
-        <f>G25*G40+G7</f>
-        <v/>
-      </c>
-      <c r="H45" s="42">
-        <f>H25*H40+H7</f>
-        <v/>
-      </c>
+      <c r="G45" s="42" t="n"/>
+      <c r="H45" s="42" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="41" t="inlineStr">
+      <c r="A46" s="153" t="inlineStr">
         <is>
           <t>EBIT: year 2</t>
         </is>
       </c>
-      <c r="F46" s="42">
-        <f>F26*F41</f>
-        <v/>
-      </c>
-      <c r="G46" s="42">
-        <f>G26*G41</f>
-        <v/>
-      </c>
-      <c r="H46" s="42">
-        <f>H26*H41</f>
-        <v/>
-      </c>
+      <c r="B46" s="154">
+        <f>B26*B41</f>
+        <v/>
+      </c>
+      <c r="C46" s="154">
+        <f>C26*C41</f>
+        <v/>
+      </c>
+      <c r="D46" s="154">
+        <f>D26*D41</f>
+        <v/>
+      </c>
+      <c r="E46" s="138" t="n"/>
+      <c r="F46" s="138" t="n"/>
+      <c r="G46" s="42" t="n"/>
+      <c r="H46" s="42" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="41" t="inlineStr">
+      <c r="A47" s="153" t="inlineStr">
         <is>
           <t>EBIT: year 3</t>
         </is>
       </c>
-      <c r="F47" s="42">
-        <f>F27*F42</f>
-        <v/>
-      </c>
-      <c r="G47" s="42">
-        <f>G27*G42</f>
-        <v/>
-      </c>
-      <c r="H47" s="42">
-        <f>H27*H42</f>
-        <v/>
-      </c>
+      <c r="B47" s="154">
+        <f>B27*B42</f>
+        <v/>
+      </c>
+      <c r="C47" s="154">
+        <f>C27*C42</f>
+        <v/>
+      </c>
+      <c r="D47" s="154">
+        <f>D27*D42</f>
+        <v/>
+      </c>
+      <c r="E47" s="138" t="n"/>
+      <c r="F47" s="138" t="n"/>
+      <c r="G47" s="42" t="n"/>
+      <c r="H47" s="42" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="41" t="inlineStr">
+      <c r="A48" s="153" t="inlineStr">
         <is>
           <t>EBIT: year 4</t>
         </is>
       </c>
-      <c r="F48" s="42">
-        <f>F28*F43</f>
-        <v/>
-      </c>
-      <c r="G48" s="42">
-        <f>G28*G43</f>
-        <v/>
-      </c>
-      <c r="H48" s="42">
-        <f>H28*H43</f>
-        <v/>
-      </c>
+      <c r="B48" s="154">
+        <f>B28*B43</f>
+        <v/>
+      </c>
+      <c r="C48" s="154">
+        <f>C28*C43</f>
+        <v/>
+      </c>
+      <c r="D48" s="154">
+        <f>D28*D43</f>
+        <v/>
+      </c>
+      <c r="E48" s="138" t="n"/>
+      <c r="F48" s="138" t="n"/>
+      <c r="G48" s="42" t="n"/>
+      <c r="H48" s="42" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="41" t="inlineStr">
+      <c r="A49" s="153" t="inlineStr">
         <is>
           <t>EBIT: year 5</t>
         </is>
       </c>
-      <c r="F49" s="42">
-        <f>F29*F44</f>
-        <v/>
-      </c>
-      <c r="G49" s="42">
-        <f>G29*G44</f>
-        <v/>
-      </c>
-      <c r="H49" s="42">
-        <f>H29*H44</f>
-        <v/>
-      </c>
+      <c r="B49" s="154">
+        <f>B29*B44</f>
+        <v/>
+      </c>
+      <c r="C49" s="154">
+        <f>C29*C44</f>
+        <v/>
+      </c>
+      <c r="D49" s="154">
+        <f>D29*D44</f>
+        <v/>
+      </c>
+      <c r="E49" s="138" t="n"/>
+      <c r="F49" s="138" t="n"/>
+      <c r="G49" s="42" t="n"/>
+      <c r="H49" s="42" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="41" t="inlineStr">
+      <c r="A50" s="153" t="inlineStr">
         <is>
           <t>NOPAT: year 1</t>
         </is>
       </c>
-      <c r="B50" s="135" t="inlineStr">
+      <c r="B50" s="154">
+        <f>B45*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="C50" s="154">
+        <f>C45*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="D50" s="154">
+        <f>D45*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="E50" s="138" t="n"/>
+      <c r="F50" s="147" t="inlineStr">
         <is>
           <t>EBIT taxed at flat cash rate each year.</t>
         </is>
       </c>
-      <c r="F50" s="42">
-        <f>F45*(1-$G$11)</f>
-        <v/>
-      </c>
-      <c r="G50" s="42">
-        <f>G45*(1-$G$11)</f>
-        <v/>
-      </c>
-      <c r="H50" s="42">
-        <f>H45*(1-$G$11)</f>
-        <v/>
-      </c>
+      <c r="G50" s="42" t="n"/>
+      <c r="H50" s="42" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="41" t="inlineStr">
+      <c r="A51" s="153" t="inlineStr">
         <is>
           <t>NOPAT: year 2</t>
         </is>
       </c>
-      <c r="F51" s="42">
-        <f>F46*(1-$G$11)</f>
-        <v/>
-      </c>
-      <c r="G51" s="42">
-        <f>G46*(1-$G$11)</f>
-        <v/>
-      </c>
-      <c r="H51" s="42">
-        <f>H46*(1-$G$11)</f>
-        <v/>
-      </c>
+      <c r="B51" s="154">
+        <f>B46*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="C51" s="154">
+        <f>C46*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="D51" s="154">
+        <f>D46*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="E51" s="138" t="n"/>
+      <c r="F51" s="138" t="n"/>
+      <c r="G51" s="42" t="n"/>
+      <c r="H51" s="42" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="41" t="inlineStr">
+      <c r="A52" s="153" t="inlineStr">
         <is>
           <t>NOPAT: year 3</t>
         </is>
       </c>
-      <c r="F52" s="42">
-        <f>F47*(1-$G$11)</f>
-        <v/>
-      </c>
-      <c r="G52" s="42">
-        <f>G47*(1-$G$11)</f>
-        <v/>
-      </c>
-      <c r="H52" s="42">
-        <f>H47*(1-$G$11)</f>
-        <v/>
-      </c>
+      <c r="B52" s="154">
+        <f>B47*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="C52" s="154">
+        <f>C47*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="D52" s="154">
+        <f>D47*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="E52" s="138" t="n"/>
+      <c r="F52" s="138" t="n"/>
+      <c r="G52" s="42" t="n"/>
+      <c r="H52" s="42" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="41" t="inlineStr">
+      <c r="A53" s="153" t="inlineStr">
         <is>
           <t>NOPAT: year 4</t>
         </is>
       </c>
-      <c r="F53" s="42">
-        <f>F48*(1-$G$11)</f>
-        <v/>
-      </c>
-      <c r="G53" s="42">
-        <f>G48*(1-$G$11)</f>
-        <v/>
-      </c>
-      <c r="H53" s="42">
-        <f>H48*(1-$G$11)</f>
-        <v/>
-      </c>
+      <c r="B53" s="154">
+        <f>B48*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="C53" s="154">
+        <f>C48*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="D53" s="154">
+        <f>D48*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="E53" s="138" t="n"/>
+      <c r="F53" s="138" t="n"/>
+      <c r="G53" s="42" t="n"/>
+      <c r="H53" s="42" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="41" t="inlineStr">
+      <c r="A54" s="153" t="inlineStr">
         <is>
           <t>NOPAT: year 5</t>
         </is>
       </c>
-      <c r="F54" s="42">
-        <f>F49*(1-$G$11)</f>
-        <v/>
-      </c>
-      <c r="G54" s="42">
-        <f>G49*(1-$G$11)</f>
-        <v/>
-      </c>
-      <c r="H54" s="42">
-        <f>H49*(1-$G$11)</f>
-        <v/>
-      </c>
+      <c r="B54" s="154">
+        <f>B49*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="C54" s="154">
+        <f>C49*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="D54" s="154">
+        <f>D49*(1-$C$11)</f>
+        <v/>
+      </c>
+      <c r="E54" s="138" t="n"/>
+      <c r="F54" s="138" t="n"/>
+      <c r="G54" s="42" t="n"/>
+      <c r="H54" s="42" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="41" t="inlineStr">
+      <c r="A55" s="153" t="inlineStr">
         <is>
           <t>D&amp;A: year 1</t>
         </is>
       </c>
-      <c r="B55" s="135" t="inlineStr">
+      <c r="B55" s="154">
+        <f>B25*B12</f>
+        <v/>
+      </c>
+      <c r="C55" s="154">
+        <f>C25*C12</f>
+        <v/>
+      </c>
+      <c r="D55" s="154">
+        <f>D25*D12</f>
+        <v/>
+      </c>
+      <c r="E55" s="138" t="n"/>
+      <c r="F55" s="147" t="inlineStr">
         <is>
           <t>Scales upward with revenue at fixed percentage annually.</t>
         </is>
       </c>
-      <c r="F55" s="42">
-        <f>F25*F12</f>
-        <v/>
-      </c>
-      <c r="G55" s="42">
-        <f>G25*G12</f>
-        <v/>
-      </c>
-      <c r="H55" s="42">
-        <f>H25*H12</f>
-        <v/>
-      </c>
+      <c r="G55" s="42" t="n"/>
+      <c r="H55" s="42" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="41" t="inlineStr">
+      <c r="A56" s="153" t="inlineStr">
         <is>
           <t>D&amp;A: year 2</t>
         </is>
       </c>
-      <c r="F56" s="42">
-        <f>F26*F12</f>
-        <v/>
-      </c>
-      <c r="G56" s="42">
-        <f>G26*G12</f>
-        <v/>
-      </c>
-      <c r="H56" s="42">
-        <f>H26*H12</f>
-        <v/>
-      </c>
+      <c r="B56" s="154">
+        <f>B26*B12</f>
+        <v/>
+      </c>
+      <c r="C56" s="154">
+        <f>C26*C12</f>
+        <v/>
+      </c>
+      <c r="D56" s="154">
+        <f>D26*D12</f>
+        <v/>
+      </c>
+      <c r="E56" s="138" t="n"/>
+      <c r="F56" s="138" t="n"/>
+      <c r="G56" s="42" t="n"/>
+      <c r="H56" s="42" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="41" t="inlineStr">
+      <c r="A57" s="153" t="inlineStr">
         <is>
           <t>D&amp;A: year 3</t>
         </is>
       </c>
-      <c r="F57" s="42">
-        <f>F27*F12</f>
-        <v/>
-      </c>
-      <c r="G57" s="42">
-        <f>G27*G12</f>
-        <v/>
-      </c>
-      <c r="H57" s="42">
-        <f>H27*H12</f>
-        <v/>
-      </c>
+      <c r="B57" s="154">
+        <f>B27*B12</f>
+        <v/>
+      </c>
+      <c r="C57" s="154">
+        <f>C27*C12</f>
+        <v/>
+      </c>
+      <c r="D57" s="154">
+        <f>D27*D12</f>
+        <v/>
+      </c>
+      <c r="E57" s="138" t="n"/>
+      <c r="F57" s="138" t="n"/>
+      <c r="G57" s="42" t="n"/>
+      <c r="H57" s="42" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="41" t="inlineStr">
+      <c r="A58" s="153" t="inlineStr">
         <is>
           <t>D&amp;A: year 4</t>
         </is>
       </c>
-      <c r="F58" s="42">
-        <f>F28*F12</f>
-        <v/>
-      </c>
-      <c r="G58" s="42">
-        <f>G28*G12</f>
-        <v/>
-      </c>
-      <c r="H58" s="42">
-        <f>H28*H12</f>
-        <v/>
-      </c>
+      <c r="B58" s="154">
+        <f>B28*B12</f>
+        <v/>
+      </c>
+      <c r="C58" s="154">
+        <f>C28*C12</f>
+        <v/>
+      </c>
+      <c r="D58" s="154">
+        <f>D28*D12</f>
+        <v/>
+      </c>
+      <c r="E58" s="138" t="n"/>
+      <c r="F58" s="138" t="n"/>
+      <c r="G58" s="42" t="n"/>
+      <c r="H58" s="42" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="41" t="inlineStr">
+      <c r="A59" s="153" t="inlineStr">
         <is>
           <t>D&amp;A: year 5</t>
         </is>
       </c>
-      <c r="F59" s="42">
-        <f>F29*F12</f>
-        <v/>
-      </c>
-      <c r="G59" s="42">
-        <f>G29*G12</f>
-        <v/>
-      </c>
-      <c r="H59" s="42">
-        <f>H29*H12</f>
-        <v/>
-      </c>
+      <c r="B59" s="154">
+        <f>B29*B12</f>
+        <v/>
+      </c>
+      <c r="C59" s="154">
+        <f>C29*C12</f>
+        <v/>
+      </c>
+      <c r="D59" s="154">
+        <f>D29*D12</f>
+        <v/>
+      </c>
+      <c r="E59" s="138" t="n"/>
+      <c r="F59" s="138" t="n"/>
+      <c r="G59" s="42" t="n"/>
+      <c r="H59" s="42" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="41" t="inlineStr">
+      <c r="A60" s="153" t="inlineStr">
         <is>
           <t>Capex: year 1</t>
         </is>
       </c>
-      <c r="B60" s="135" t="inlineStr">
+      <c r="B60" s="154">
+        <f>B25*B13</f>
+        <v/>
+      </c>
+      <c r="C60" s="154">
+        <f>C25*C13</f>
+        <v/>
+      </c>
+      <c r="D60" s="154">
+        <f>D25*D13</f>
+        <v/>
+      </c>
+      <c r="E60" s="138" t="n"/>
+      <c r="F60" s="147" t="inlineStr">
         <is>
           <t>Scales upward with revenue at fixed percentage annually.</t>
         </is>
       </c>
-      <c r="F60" s="42">
-        <f>F25*F13</f>
-        <v/>
-      </c>
-      <c r="G60" s="42">
-        <f>G25*G13</f>
-        <v/>
-      </c>
-      <c r="H60" s="42">
-        <f>H25*H13</f>
-        <v/>
-      </c>
+      <c r="G60" s="42" t="n"/>
+      <c r="H60" s="42" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="41" t="inlineStr">
+      <c r="A61" s="153" t="inlineStr">
         <is>
           <t>Capex: year 2</t>
         </is>
       </c>
-      <c r="F61" s="42">
-        <f>F26*F13</f>
-        <v/>
-      </c>
-      <c r="G61" s="42">
-        <f>G26*G13</f>
-        <v/>
-      </c>
-      <c r="H61" s="42">
-        <f>H26*H13</f>
-        <v/>
-      </c>
+      <c r="B61" s="154">
+        <f>B26*B13</f>
+        <v/>
+      </c>
+      <c r="C61" s="154">
+        <f>C26*C13</f>
+        <v/>
+      </c>
+      <c r="D61" s="154">
+        <f>D26*D13</f>
+        <v/>
+      </c>
+      <c r="E61" s="138" t="n"/>
+      <c r="F61" s="138" t="n"/>
+      <c r="G61" s="42" t="n"/>
+      <c r="H61" s="42" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="41" t="inlineStr">
+      <c r="A62" s="153" t="inlineStr">
         <is>
           <t>Capex: year 3</t>
         </is>
       </c>
-      <c r="F62" s="42">
-        <f>F27*F13</f>
-        <v/>
-      </c>
-      <c r="G62" s="42">
-        <f>G27*G13</f>
-        <v/>
-      </c>
-      <c r="H62" s="42">
-        <f>H27*H13</f>
-        <v/>
-      </c>
+      <c r="B62" s="154">
+        <f>B27*B13</f>
+        <v/>
+      </c>
+      <c r="C62" s="154">
+        <f>C27*C13</f>
+        <v/>
+      </c>
+      <c r="D62" s="154">
+        <f>D27*D13</f>
+        <v/>
+      </c>
+      <c r="E62" s="138" t="n"/>
+      <c r="F62" s="138" t="n"/>
+      <c r="G62" s="42" t="n"/>
+      <c r="H62" s="42" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="41" t="inlineStr">
+      <c r="A63" s="153" t="inlineStr">
         <is>
           <t>Capex: year 4</t>
         </is>
       </c>
-      <c r="F63" s="42">
-        <f>F28*F13</f>
-        <v/>
-      </c>
-      <c r="G63" s="42">
-        <f>G28*G13</f>
-        <v/>
-      </c>
-      <c r="H63" s="42">
-        <f>H28*H13</f>
-        <v/>
-      </c>
+      <c r="B63" s="154">
+        <f>B28*B13</f>
+        <v/>
+      </c>
+      <c r="C63" s="154">
+        <f>C28*C13</f>
+        <v/>
+      </c>
+      <c r="D63" s="154">
+        <f>D28*D13</f>
+        <v/>
+      </c>
+      <c r="E63" s="138" t="n"/>
+      <c r="F63" s="138" t="n"/>
+      <c r="G63" s="42" t="n"/>
+      <c r="H63" s="42" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="41" t="inlineStr">
+      <c r="A64" s="153" t="inlineStr">
         <is>
           <t>Capex: year 5</t>
         </is>
       </c>
-      <c r="F64" s="42">
-        <f>F29*F13</f>
-        <v/>
-      </c>
-      <c r="G64" s="42">
-        <f>G29*G13</f>
-        <v/>
-      </c>
-      <c r="H64" s="42">
-        <f>H29*H13</f>
-        <v/>
-      </c>
+      <c r="B64" s="154">
+        <f>B29*B13</f>
+        <v/>
+      </c>
+      <c r="C64" s="154">
+        <f>C29*C13</f>
+        <v/>
+      </c>
+      <c r="D64" s="154">
+        <f>D29*D13</f>
+        <v/>
+      </c>
+      <c r="E64" s="138" t="n"/>
+      <c r="F64" s="138" t="n"/>
+      <c r="G64" s="42" t="n"/>
+      <c r="H64" s="42" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="41" t="inlineStr">
+      <c r="A65" s="153" t="inlineStr">
         <is>
           <t>DSO (days): year 1</t>
         </is>
       </c>
-      <c r="B65" s="135" t="inlineStr">
+      <c r="B65" s="156">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="C65" s="156">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="D65" s="156">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="E65" s="138" t="n"/>
+      <c r="F65" s="147" t="inlineStr">
         <is>
           <t>Held flat at six days every forecast year.</t>
         </is>
       </c>
-      <c r="F65" s="44">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="G65" s="44">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="H65" s="44">
-        <f>H15</f>
-        <v/>
-      </c>
+      <c r="G65" s="44" t="n"/>
+      <c r="H65" s="44" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="41" t="inlineStr">
+      <c r="A66" s="153" t="inlineStr">
         <is>
           <t>DSO (days): year 2</t>
         </is>
       </c>
-      <c r="F66" s="44">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="G66" s="44">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="H66" s="44">
-        <f>H15</f>
-        <v/>
-      </c>
+      <c r="B66" s="156">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="C66" s="156">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="D66" s="156">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="E66" s="138" t="n"/>
+      <c r="F66" s="138" t="n"/>
+      <c r="G66" s="44" t="n"/>
+      <c r="H66" s="44" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="41" t="inlineStr">
+      <c r="A67" s="153" t="inlineStr">
         <is>
           <t>DSO (days): year 3</t>
         </is>
       </c>
-      <c r="F67" s="44">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="G67" s="44">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="H67" s="44">
-        <f>H15</f>
-        <v/>
-      </c>
+      <c r="B67" s="156">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="C67" s="156">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="D67" s="156">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="E67" s="138" t="n"/>
+      <c r="F67" s="138" t="n"/>
+      <c r="G67" s="44" t="n"/>
+      <c r="H67" s="44" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="41" t="inlineStr">
+      <c r="A68" s="153" t="inlineStr">
         <is>
           <t>DSO (days): year 4</t>
         </is>
       </c>
-      <c r="F68" s="44">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="G68" s="44">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="H68" s="44">
-        <f>H15</f>
-        <v/>
-      </c>
+      <c r="B68" s="156">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="C68" s="156">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="D68" s="156">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="E68" s="138" t="n"/>
+      <c r="F68" s="138" t="n"/>
+      <c r="G68" s="44" t="n"/>
+      <c r="H68" s="44" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="41" t="inlineStr">
+      <c r="A69" s="153" t="inlineStr">
         <is>
           <t>DSO (days): year 5</t>
         </is>
       </c>
-      <c r="F69" s="44">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="G69" s="44">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="H69" s="44">
-        <f>H15</f>
-        <v/>
-      </c>
+      <c r="B69" s="156">
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="C69" s="156">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="D69" s="156">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="E69" s="138" t="n"/>
+      <c r="F69" s="138" t="n"/>
+      <c r="G69" s="44" t="n"/>
+      <c r="H69" s="44" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="41" t="inlineStr">
+      <c r="A70" s="153" t="inlineStr">
         <is>
           <t>Accounts receivable: year 1</t>
         </is>
       </c>
-      <c r="B70" s="135" t="inlineStr">
+      <c r="B70" s="154">
+        <f>(B65/365)*B25</f>
+        <v/>
+      </c>
+      <c r="C70" s="154">
+        <f>(C65/365)*C25</f>
+        <v/>
+      </c>
+      <c r="D70" s="154">
+        <f>(D65/365)*D25</f>
+        <v/>
+      </c>
+      <c r="E70" s="138" t="n"/>
+      <c r="F70" s="147" t="inlineStr">
         <is>
           <t>Tracks revenue changes while collection days stay flat.</t>
         </is>
       </c>
-      <c r="F70" s="42">
-        <f>(F65/365)*F25</f>
-        <v/>
-      </c>
-      <c r="G70" s="42">
-        <f>(G65/365)*G25</f>
-        <v/>
-      </c>
-      <c r="H70" s="42">
-        <f>(H65/365)*H25</f>
-        <v/>
-      </c>
+      <c r="G70" s="42" t="n"/>
+      <c r="H70" s="42" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="41" t="inlineStr">
+      <c r="A71" s="153" t="inlineStr">
         <is>
           <t>Accounts receivable: year 2</t>
         </is>
       </c>
-      <c r="F71" s="42">
-        <f>(F66/365)*F26</f>
-        <v/>
-      </c>
-      <c r="G71" s="42">
-        <f>(G66/365)*G26</f>
-        <v/>
-      </c>
-      <c r="H71" s="42">
-        <f>(H66/365)*H26</f>
-        <v/>
-      </c>
+      <c r="B71" s="154">
+        <f>(B66/365)*B26</f>
+        <v/>
+      </c>
+      <c r="C71" s="154">
+        <f>(C66/365)*C26</f>
+        <v/>
+      </c>
+      <c r="D71" s="154">
+        <f>(D66/365)*D26</f>
+        <v/>
+      </c>
+      <c r="E71" s="138" t="n"/>
+      <c r="F71" s="138" t="n"/>
+      <c r="G71" s="42" t="n"/>
+      <c r="H71" s="42" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="41" t="inlineStr">
+      <c r="A72" s="153" t="inlineStr">
         <is>
           <t>Accounts receivable: year 3</t>
         </is>
       </c>
-      <c r="F72" s="42">
-        <f>(F67/365)*F27</f>
-        <v/>
-      </c>
-      <c r="G72" s="42">
-        <f>(G67/365)*G27</f>
-        <v/>
-      </c>
-      <c r="H72" s="42">
-        <f>(H67/365)*H27</f>
-        <v/>
-      </c>
+      <c r="B72" s="154">
+        <f>(B67/365)*B27</f>
+        <v/>
+      </c>
+      <c r="C72" s="154">
+        <f>(C67/365)*C27</f>
+        <v/>
+      </c>
+      <c r="D72" s="154">
+        <f>(D67/365)*D27</f>
+        <v/>
+      </c>
+      <c r="E72" s="138" t="n"/>
+      <c r="F72" s="138" t="n"/>
+      <c r="G72" s="42" t="n"/>
+      <c r="H72" s="42" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="41" t="inlineStr">
+      <c r="A73" s="153" t="inlineStr">
         <is>
           <t>Accounts receivable: year 4</t>
         </is>
       </c>
-      <c r="F73" s="42">
-        <f>(F68/365)*F28</f>
-        <v/>
-      </c>
-      <c r="G73" s="42">
-        <f>(G68/365)*G28</f>
-        <v/>
-      </c>
-      <c r="H73" s="42">
-        <f>(H68/365)*H28</f>
-        <v/>
-      </c>
+      <c r="B73" s="154">
+        <f>(B68/365)*B28</f>
+        <v/>
+      </c>
+      <c r="C73" s="154">
+        <f>(C68/365)*C28</f>
+        <v/>
+      </c>
+      <c r="D73" s="154">
+        <f>(D68/365)*D28</f>
+        <v/>
+      </c>
+      <c r="E73" s="138" t="n"/>
+      <c r="F73" s="138" t="n"/>
+      <c r="G73" s="42" t="n"/>
+      <c r="H73" s="42" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="41" t="inlineStr">
+      <c r="A74" s="153" t="inlineStr">
         <is>
           <t>Accounts receivable: year 5</t>
         </is>
       </c>
-      <c r="F74" s="42">
-        <f>(F69/365)*F29</f>
-        <v/>
-      </c>
-      <c r="G74" s="42">
-        <f>(G69/365)*G29</f>
-        <v/>
-      </c>
-      <c r="H74" s="42">
-        <f>(H69/365)*H29</f>
-        <v/>
-      </c>
+      <c r="B74" s="154">
+        <f>(B69/365)*B29</f>
+        <v/>
+      </c>
+      <c r="C74" s="154">
+        <f>(C69/365)*C29</f>
+        <v/>
+      </c>
+      <c r="D74" s="154">
+        <f>(D69/365)*D29</f>
+        <v/>
+      </c>
+      <c r="E74" s="138" t="n"/>
+      <c r="F74" s="138" t="n"/>
+      <c r="G74" s="42" t="n"/>
+      <c r="H74" s="42" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="41" t="inlineStr">
+      <c r="A75" s="153" t="inlineStr">
         <is>
           <t>DIO (days): year 1</t>
         </is>
       </c>
-      <c r="B75" s="135" t="inlineStr">
+      <c r="B75" s="156">
+        <f>B16-B17*1</f>
+        <v/>
+      </c>
+      <c r="C75" s="156">
+        <f>C16-C17*1</f>
+        <v/>
+      </c>
+      <c r="D75" s="156">
+        <f>D16-D17*1</f>
+        <v/>
+      </c>
+      <c r="E75" s="138" t="n"/>
+      <c r="F75" s="147" t="inlineStr">
         <is>
           <t>Falls one day per year across five years.</t>
         </is>
       </c>
-      <c r="F75" s="44">
-        <f>F16-F17*1</f>
-        <v/>
-      </c>
-      <c r="G75" s="44">
-        <f>G16-G17*1</f>
-        <v/>
-      </c>
-      <c r="H75" s="44">
-        <f>H16-H17*1</f>
-        <v/>
-      </c>
+      <c r="G75" s="44" t="n"/>
+      <c r="H75" s="44" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="41" t="inlineStr">
+      <c r="A76" s="153" t="inlineStr">
         <is>
           <t>DIO (days): year 2</t>
         </is>
       </c>
-      <c r="F76" s="44">
-        <f>F16-F17*2</f>
-        <v/>
-      </c>
-      <c r="G76" s="44">
-        <f>G16-G17*2</f>
-        <v/>
-      </c>
-      <c r="H76" s="44">
-        <f>H16-H17*2</f>
-        <v/>
-      </c>
+      <c r="B76" s="156">
+        <f>B16-B17*2</f>
+        <v/>
+      </c>
+      <c r="C76" s="156">
+        <f>C16-C17*2</f>
+        <v/>
+      </c>
+      <c r="D76" s="156">
+        <f>D16-D17*2</f>
+        <v/>
+      </c>
+      <c r="E76" s="138" t="n"/>
+      <c r="F76" s="138" t="n"/>
+      <c r="G76" s="44" t="n"/>
+      <c r="H76" s="44" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="41" t="inlineStr">
+      <c r="A77" s="153" t="inlineStr">
         <is>
           <t>DIO (days): year 3</t>
         </is>
       </c>
-      <c r="F77" s="44">
-        <f>F16-F17*3</f>
-        <v/>
-      </c>
-      <c r="G77" s="44">
-        <f>G16-G17*3</f>
-        <v/>
-      </c>
-      <c r="H77" s="44">
-        <f>H16-H17*3</f>
-        <v/>
-      </c>
+      <c r="B77" s="156">
+        <f>B16-B17*3</f>
+        <v/>
+      </c>
+      <c r="C77" s="156">
+        <f>C16-C17*3</f>
+        <v/>
+      </c>
+      <c r="D77" s="156">
+        <f>D16-D17*3</f>
+        <v/>
+      </c>
+      <c r="E77" s="138" t="n"/>
+      <c r="F77" s="138" t="n"/>
+      <c r="G77" s="44" t="n"/>
+      <c r="H77" s="44" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="41" t="inlineStr">
+      <c r="A78" s="153" t="inlineStr">
         <is>
           <t>DIO (days): year 4</t>
         </is>
       </c>
-      <c r="F78" s="44">
-        <f>F16-F17*4</f>
-        <v/>
-      </c>
-      <c r="G78" s="44">
-        <f>G16-G17*4</f>
-        <v/>
-      </c>
-      <c r="H78" s="44">
-        <f>H16-H17*4</f>
-        <v/>
-      </c>
+      <c r="B78" s="156">
+        <f>B16-B17*4</f>
+        <v/>
+      </c>
+      <c r="C78" s="156">
+        <f>C16-C17*4</f>
+        <v/>
+      </c>
+      <c r="D78" s="156">
+        <f>D16-D17*4</f>
+        <v/>
+      </c>
+      <c r="E78" s="138" t="n"/>
+      <c r="F78" s="138" t="n"/>
+      <c r="G78" s="44" t="n"/>
+      <c r="H78" s="44" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="41" t="inlineStr">
+      <c r="A79" s="153" t="inlineStr">
         <is>
           <t>DIO (days): year 5</t>
         </is>
       </c>
-      <c r="F79" s="44">
-        <f>F16-F17*5</f>
-        <v/>
-      </c>
-      <c r="G79" s="44">
-        <f>G16-G17*5</f>
-        <v/>
-      </c>
-      <c r="H79" s="44">
-        <f>H16-H17*5</f>
-        <v/>
-      </c>
+      <c r="B79" s="156">
+        <f>B16-B17*5</f>
+        <v/>
+      </c>
+      <c r="C79" s="156">
+        <f>C16-C17*5</f>
+        <v/>
+      </c>
+      <c r="D79" s="156">
+        <f>D16-D17*5</f>
+        <v/>
+      </c>
+      <c r="E79" s="138" t="n"/>
+      <c r="F79" s="138" t="n"/>
+      <c r="G79" s="44" t="n"/>
+      <c r="H79" s="44" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="41" t="inlineStr">
+      <c r="A80" s="153" t="inlineStr">
         <is>
           <t>Inventories: year 1</t>
         </is>
       </c>
-      <c r="B80" s="135" t="inlineStr">
+      <c r="B80" s="154">
+        <f>(B75/365)*B35</f>
+        <v/>
+      </c>
+      <c r="C80" s="154">
+        <f>(C75/365)*C35</f>
+        <v/>
+      </c>
+      <c r="D80" s="154">
+        <f>(D75/365)*D35</f>
+        <v/>
+      </c>
+      <c r="E80" s="138" t="n"/>
+      <c r="F80" s="147" t="inlineStr">
         <is>
           <t>Declines with DIO days: grows with rising COGS.</t>
         </is>
       </c>
-      <c r="F80" s="42">
-        <f>(F75/365)*F35</f>
-        <v/>
-      </c>
-      <c r="G80" s="42">
-        <f>(G75/365)*G35</f>
-        <v/>
-      </c>
-      <c r="H80" s="42">
-        <f>(H75/365)*H35</f>
-        <v/>
-      </c>
+      <c r="G80" s="42" t="n"/>
+      <c r="H80" s="42" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="41" t="inlineStr">
+      <c r="A81" s="153" t="inlineStr">
         <is>
           <t>Inventories: year 2</t>
         </is>
       </c>
-      <c r="F81" s="42">
-        <f>(F76/365)*F36</f>
-        <v/>
-      </c>
-      <c r="G81" s="42">
-        <f>(G76/365)*G36</f>
-        <v/>
-      </c>
-      <c r="H81" s="42">
-        <f>(H76/365)*H36</f>
-        <v/>
-      </c>
+      <c r="B81" s="154">
+        <f>(B76/365)*B36</f>
+        <v/>
+      </c>
+      <c r="C81" s="154">
+        <f>(C76/365)*C36</f>
+        <v/>
+      </c>
+      <c r="D81" s="154">
+        <f>(D76/365)*D36</f>
+        <v/>
+      </c>
+      <c r="E81" s="138" t="n"/>
+      <c r="F81" s="138" t="n"/>
+      <c r="G81" s="42" t="n"/>
+      <c r="H81" s="42" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="41" t="inlineStr">
+      <c r="A82" s="153" t="inlineStr">
         <is>
           <t>Inventories: year 3</t>
         </is>
       </c>
-      <c r="F82" s="42">
-        <f>(F77/365)*F37</f>
-        <v/>
-      </c>
-      <c r="G82" s="42">
-        <f>(G77/365)*G37</f>
-        <v/>
-      </c>
-      <c r="H82" s="42">
-        <f>(H77/365)*H37</f>
-        <v/>
-      </c>
+      <c r="B82" s="154">
+        <f>(B77/365)*B37</f>
+        <v/>
+      </c>
+      <c r="C82" s="154">
+        <f>(C77/365)*C37</f>
+        <v/>
+      </c>
+      <c r="D82" s="154">
+        <f>(D77/365)*D37</f>
+        <v/>
+      </c>
+      <c r="E82" s="138" t="n"/>
+      <c r="F82" s="138" t="n"/>
+      <c r="G82" s="42" t="n"/>
+      <c r="H82" s="42" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="41" t="inlineStr">
+      <c r="A83" s="153" t="inlineStr">
         <is>
           <t>Inventories: year 4</t>
         </is>
       </c>
-      <c r="F83" s="42">
-        <f>(F78/365)*F38</f>
-        <v/>
-      </c>
-      <c r="G83" s="42">
-        <f>(G78/365)*G38</f>
-        <v/>
-      </c>
-      <c r="H83" s="42">
-        <f>(H78/365)*H38</f>
-        <v/>
-      </c>
+      <c r="B83" s="154">
+        <f>(B78/365)*B38</f>
+        <v/>
+      </c>
+      <c r="C83" s="154">
+        <f>(C78/365)*C38</f>
+        <v/>
+      </c>
+      <c r="D83" s="154">
+        <f>(D78/365)*D38</f>
+        <v/>
+      </c>
+      <c r="E83" s="138" t="n"/>
+      <c r="F83" s="138" t="n"/>
+      <c r="G83" s="42" t="n"/>
+      <c r="H83" s="42" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="41" t="inlineStr">
+      <c r="A84" s="153" t="inlineStr">
         <is>
           <t>Inventories: year 5</t>
         </is>
       </c>
-      <c r="F84" s="42">
-        <f>(F79/365)*F39</f>
-        <v/>
-      </c>
-      <c r="G84" s="42">
-        <f>(G79/365)*G39</f>
-        <v/>
-      </c>
-      <c r="H84" s="42">
-        <f>(H79/365)*H39</f>
-        <v/>
-      </c>
+      <c r="B84" s="154">
+        <f>(B79/365)*B39</f>
+        <v/>
+      </c>
+      <c r="C84" s="154">
+        <f>(C79/365)*C39</f>
+        <v/>
+      </c>
+      <c r="D84" s="154">
+        <f>(D79/365)*D39</f>
+        <v/>
+      </c>
+      <c r="E84" s="138" t="n"/>
+      <c r="F84" s="138" t="n"/>
+      <c r="G84" s="42" t="n"/>
+      <c r="H84" s="42" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="41" t="inlineStr">
+      <c r="A85" s="153" t="inlineStr">
         <is>
           <t>DPO (days): year 1</t>
         </is>
       </c>
-      <c r="B85" s="135" t="inlineStr">
+      <c r="B85" s="156">
+        <f>B18</f>
+        <v/>
+      </c>
+      <c r="C85" s="156">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="D85" s="156">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="E85" s="138" t="n"/>
+      <c r="F85" s="147" t="inlineStr">
         <is>
           <t>Held flat at twenty-five days every year.</t>
         </is>
       </c>
-      <c r="F85" s="44">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="G85" s="44">
-        <f>G18</f>
-        <v/>
-      </c>
-      <c r="H85" s="44">
-        <f>H18</f>
-        <v/>
-      </c>
+      <c r="G85" s="44" t="n"/>
+      <c r="H85" s="44" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="41" t="inlineStr">
+      <c r="A86" s="153" t="inlineStr">
         <is>
           <t>DPO (days): year 2</t>
         </is>
       </c>
-      <c r="F86" s="44">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="G86" s="44">
-        <f>G18</f>
-        <v/>
-      </c>
-      <c r="H86" s="44">
-        <f>H18</f>
-        <v/>
-      </c>
+      <c r="B86" s="156">
+        <f>B18</f>
+        <v/>
+      </c>
+      <c r="C86" s="156">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="D86" s="156">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="E86" s="138" t="n"/>
+      <c r="F86" s="138" t="n"/>
+      <c r="G86" s="44" t="n"/>
+      <c r="H86" s="44" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="41" t="inlineStr">
+      <c r="A87" s="153" t="inlineStr">
         <is>
           <t>DPO (days): year 3</t>
         </is>
       </c>
-      <c r="F87" s="44">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="G87" s="44">
-        <f>G18</f>
-        <v/>
-      </c>
-      <c r="H87" s="44">
-        <f>H18</f>
-        <v/>
-      </c>
+      <c r="B87" s="156">
+        <f>B18</f>
+        <v/>
+      </c>
+      <c r="C87" s="156">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="D87" s="156">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="E87" s="138" t="n"/>
+      <c r="F87" s="138" t="n"/>
+      <c r="G87" s="44" t="n"/>
+      <c r="H87" s="44" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="41" t="inlineStr">
+      <c r="A88" s="153" t="inlineStr">
         <is>
           <t>DPO (days): year 4</t>
         </is>
       </c>
-      <c r="F88" s="44">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="G88" s="44">
-        <f>G18</f>
-        <v/>
-      </c>
-      <c r="H88" s="44">
-        <f>H18</f>
-        <v/>
-      </c>
+      <c r="B88" s="156">
+        <f>B18</f>
+        <v/>
+      </c>
+      <c r="C88" s="156">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="D88" s="156">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="E88" s="138" t="n"/>
+      <c r="F88" s="138" t="n"/>
+      <c r="G88" s="44" t="n"/>
+      <c r="H88" s="44" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="41" t="inlineStr">
+      <c r="A89" s="153" t="inlineStr">
         <is>
           <t>DPO (days): year 5</t>
         </is>
       </c>
-      <c r="F89" s="44">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="G89" s="44">
-        <f>G18</f>
-        <v/>
-      </c>
-      <c r="H89" s="44">
-        <f>H18</f>
-        <v/>
-      </c>
+      <c r="B89" s="156">
+        <f>B18</f>
+        <v/>
+      </c>
+      <c r="C89" s="156">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="D89" s="156">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="E89" s="138" t="n"/>
+      <c r="F89" s="138" t="n"/>
+      <c r="G89" s="44" t="n"/>
+      <c r="H89" s="44" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="41" t="inlineStr">
+      <c r="A90" s="153" t="inlineStr">
         <is>
           <t>Accounts payable: year 1</t>
         </is>
       </c>
-      <c r="B90" s="135" t="inlineStr">
+      <c r="B90" s="154">
+        <f>(B85/365)*B35</f>
+        <v/>
+      </c>
+      <c r="C90" s="154">
+        <f>(C85/365)*C35</f>
+        <v/>
+      </c>
+      <c r="D90" s="154">
+        <f>(D85/365)*D35</f>
+        <v/>
+      </c>
+      <c r="E90" s="138" t="n"/>
+      <c r="F90" s="147" t="inlineStr">
         <is>
           <t>Grows with COGS while payment days remain flat.</t>
         </is>
       </c>
-      <c r="F90" s="42">
-        <f>(F85/365)*F35</f>
-        <v/>
-      </c>
-      <c r="G90" s="42">
-        <f>(G85/365)*G35</f>
-        <v/>
-      </c>
-      <c r="H90" s="42">
-        <f>(H85/365)*H35</f>
-        <v/>
-      </c>
+      <c r="G90" s="42" t="n"/>
+      <c r="H90" s="42" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="41" t="inlineStr">
+      <c r="A91" s="153" t="inlineStr">
         <is>
           <t>Accounts payable: year 2</t>
         </is>
       </c>
-      <c r="F91" s="42">
-        <f>(F86/365)*F36</f>
-        <v/>
-      </c>
-      <c r="G91" s="42">
-        <f>(G86/365)*G36</f>
-        <v/>
-      </c>
-      <c r="H91" s="42">
-        <f>(H86/365)*H36</f>
-        <v/>
-      </c>
+      <c r="B91" s="154">
+        <f>(B86/365)*B36</f>
+        <v/>
+      </c>
+      <c r="C91" s="154">
+        <f>(C86/365)*C36</f>
+        <v/>
+      </c>
+      <c r="D91" s="154">
+        <f>(D86/365)*D36</f>
+        <v/>
+      </c>
+      <c r="E91" s="138" t="n"/>
+      <c r="F91" s="138" t="n"/>
+      <c r="G91" s="42" t="n"/>
+      <c r="H91" s="42" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="41" t="inlineStr">
+      <c r="A92" s="153" t="inlineStr">
         <is>
           <t>Accounts payable: year 3</t>
         </is>
       </c>
-      <c r="F92" s="42">
-        <f>(F87/365)*F37</f>
-        <v/>
-      </c>
-      <c r="G92" s="42">
-        <f>(G87/365)*G37</f>
-        <v/>
-      </c>
-      <c r="H92" s="42">
-        <f>(H87/365)*H37</f>
-        <v/>
-      </c>
+      <c r="B92" s="154">
+        <f>(B87/365)*B37</f>
+        <v/>
+      </c>
+      <c r="C92" s="154">
+        <f>(C87/365)*C37</f>
+        <v/>
+      </c>
+      <c r="D92" s="154">
+        <f>(D87/365)*D37</f>
+        <v/>
+      </c>
+      <c r="E92" s="138" t="n"/>
+      <c r="F92" s="138" t="n"/>
+      <c r="G92" s="42" t="n"/>
+      <c r="H92" s="42" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="41" t="inlineStr">
+      <c r="A93" s="153" t="inlineStr">
         <is>
           <t>Accounts payable: year 4</t>
         </is>
       </c>
-      <c r="F93" s="42">
-        <f>(F88/365)*F38</f>
-        <v/>
-      </c>
-      <c r="G93" s="42">
-        <f>(G88/365)*G38</f>
-        <v/>
-      </c>
-      <c r="H93" s="42">
-        <f>(H88/365)*H38</f>
-        <v/>
-      </c>
+      <c r="B93" s="154">
+        <f>(B88/365)*B38</f>
+        <v/>
+      </c>
+      <c r="C93" s="154">
+        <f>(C88/365)*C38</f>
+        <v/>
+      </c>
+      <c r="D93" s="154">
+        <f>(D88/365)*D38</f>
+        <v/>
+      </c>
+      <c r="E93" s="138" t="n"/>
+      <c r="F93" s="138" t="n"/>
+      <c r="G93" s="42" t="n"/>
+      <c r="H93" s="42" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="41" t="inlineStr">
+      <c r="A94" s="153" t="inlineStr">
         <is>
           <t>Accounts payable: year 5</t>
         </is>
       </c>
-      <c r="F94" s="42">
-        <f>(F89/365)*F39</f>
-        <v/>
-      </c>
-      <c r="G94" s="42">
-        <f>(G89/365)*G39</f>
-        <v/>
-      </c>
-      <c r="H94" s="42">
-        <f>(H89/365)*H39</f>
-        <v/>
-      </c>
+      <c r="B94" s="154">
+        <f>(B89/365)*B39</f>
+        <v/>
+      </c>
+      <c r="C94" s="154">
+        <f>(C89/365)*C39</f>
+        <v/>
+      </c>
+      <c r="D94" s="154">
+        <f>(D89/365)*D39</f>
+        <v/>
+      </c>
+      <c r="E94" s="138" t="n"/>
+      <c r="F94" s="138" t="n"/>
+      <c r="G94" s="42" t="n"/>
+      <c r="H94" s="42" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="41" t="inlineStr">
+      <c r="A95" s="153" t="inlineStr">
         <is>
           <t>Prepaid expenses (other current assets): year 1</t>
         </is>
       </c>
-      <c r="B95" s="135" t="inlineStr">
+      <c r="B95" s="154">
+        <f>B25*B19</f>
+        <v/>
+      </c>
+      <c r="C95" s="154">
+        <f>C25*C19</f>
+        <v/>
+      </c>
+      <c r="D95" s="154">
+        <f>D25*D19</f>
+        <v/>
+      </c>
+      <c r="E95" s="138" t="n"/>
+      <c r="F95" s="147" t="inlineStr">
         <is>
           <t>Grows at flat percent of revenue yearly.</t>
         </is>
       </c>
-      <c r="F95" s="42">
-        <f>F25*F19</f>
-        <v/>
-      </c>
-      <c r="G95" s="42">
-        <f>G25*G19</f>
-        <v/>
-      </c>
-      <c r="H95" s="42">
-        <f>H25*H19</f>
-        <v/>
-      </c>
+      <c r="G95" s="42" t="n"/>
+      <c r="H95" s="42" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="41" t="inlineStr">
+      <c r="A96" s="153" t="inlineStr">
         <is>
           <t>Prepaid expenses (other current assets): year 2</t>
         </is>
       </c>
-      <c r="F96" s="42">
-        <f>F26*F19</f>
-        <v/>
-      </c>
-      <c r="G96" s="42">
-        <f>G26*G19</f>
-        <v/>
-      </c>
-      <c r="H96" s="42">
-        <f>H26*H19</f>
-        <v/>
-      </c>
+      <c r="B96" s="154">
+        <f>B26*B19</f>
+        <v/>
+      </c>
+      <c r="C96" s="154">
+        <f>C26*C19</f>
+        <v/>
+      </c>
+      <c r="D96" s="154">
+        <f>D26*D19</f>
+        <v/>
+      </c>
+      <c r="E96" s="138" t="n"/>
+      <c r="F96" s="138" t="n"/>
+      <c r="G96" s="42" t="n"/>
+      <c r="H96" s="42" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="41" t="inlineStr">
+      <c r="A97" s="153" t="inlineStr">
         <is>
           <t>Prepaid expenses (other current assets): year 3</t>
         </is>
       </c>
-      <c r="F97" s="42">
-        <f>F27*F19</f>
-        <v/>
-      </c>
-      <c r="G97" s="42">
-        <f>G27*G19</f>
-        <v/>
-      </c>
-      <c r="H97" s="42">
-        <f>H27*H19</f>
-        <v/>
-      </c>
+      <c r="B97" s="154">
+        <f>B27*B19</f>
+        <v/>
+      </c>
+      <c r="C97" s="154">
+        <f>C27*C19</f>
+        <v/>
+      </c>
+      <c r="D97" s="154">
+        <f>D27*D19</f>
+        <v/>
+      </c>
+      <c r="E97" s="138" t="n"/>
+      <c r="F97" s="138" t="n"/>
+      <c r="G97" s="42" t="n"/>
+      <c r="H97" s="42" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="41" t="inlineStr">
+      <c r="A98" s="153" t="inlineStr">
         <is>
           <t>Prepaid expenses (other current assets): year 4</t>
         </is>
       </c>
-      <c r="F98" s="42">
-        <f>F28*F19</f>
-        <v/>
-      </c>
-      <c r="G98" s="42">
-        <f>G28*G19</f>
-        <v/>
-      </c>
-      <c r="H98" s="42">
-        <f>H28*H19</f>
-        <v/>
-      </c>
+      <c r="B98" s="154">
+        <f>B28*B19</f>
+        <v/>
+      </c>
+      <c r="C98" s="154">
+        <f>C28*C19</f>
+        <v/>
+      </c>
+      <c r="D98" s="154">
+        <f>D28*D19</f>
+        <v/>
+      </c>
+      <c r="E98" s="138" t="n"/>
+      <c r="F98" s="138" t="n"/>
+      <c r="G98" s="42" t="n"/>
+      <c r="H98" s="42" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="41" t="inlineStr">
+      <c r="A99" s="153" t="inlineStr">
         <is>
           <t>Prepaid expenses (other current assets): year 5</t>
         </is>
       </c>
-      <c r="F99" s="42">
-        <f>F29*F19</f>
-        <v/>
-      </c>
-      <c r="G99" s="42">
-        <f>G29*G19</f>
-        <v/>
-      </c>
-      <c r="H99" s="42">
-        <f>H29*H19</f>
-        <v/>
-      </c>
+      <c r="B99" s="154">
+        <f>B29*B19</f>
+        <v/>
+      </c>
+      <c r="C99" s="154">
+        <f>C29*C19</f>
+        <v/>
+      </c>
+      <c r="D99" s="154">
+        <f>D29*D19</f>
+        <v/>
+      </c>
+      <c r="E99" s="138" t="n"/>
+      <c r="F99" s="138" t="n"/>
+      <c r="G99" s="42" t="n"/>
+      <c r="H99" s="42" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="41" t="inlineStr">
+      <c r="A100" s="153" t="inlineStr">
         <is>
           <t>Accrued liabilities: year 1</t>
         </is>
       </c>
-      <c r="B100" s="135" t="inlineStr">
+      <c r="B100" s="154">
+        <f>B25*B20</f>
+        <v/>
+      </c>
+      <c r="C100" s="154">
+        <f>C25*C20</f>
+        <v/>
+      </c>
+      <c r="D100" s="154">
+        <f>D25*D20</f>
+        <v/>
+      </c>
+      <c r="E100" s="138" t="n"/>
+      <c r="F100" s="147" t="inlineStr">
         <is>
           <t>Grows at flat percent of revenue every year.</t>
         </is>
       </c>
-      <c r="F100" s="42">
-        <f>F25*F20</f>
-        <v/>
-      </c>
-      <c r="G100" s="42">
-        <f>G25*G20</f>
-        <v/>
-      </c>
-      <c r="H100" s="42">
-        <f>H25*H20</f>
-        <v/>
-      </c>
+      <c r="G100" s="42" t="n"/>
+      <c r="H100" s="42" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="41" t="inlineStr">
+      <c r="A101" s="153" t="inlineStr">
         <is>
           <t>Accrued liabilities: year 2</t>
         </is>
       </c>
-      <c r="F101" s="42">
-        <f>F26*F20</f>
-        <v/>
-      </c>
-      <c r="G101" s="42">
-        <f>G26*G20</f>
-        <v/>
-      </c>
-      <c r="H101" s="42">
-        <f>H26*H20</f>
-        <v/>
-      </c>
+      <c r="B101" s="154">
+        <f>B26*B20</f>
+        <v/>
+      </c>
+      <c r="C101" s="154">
+        <f>C26*C20</f>
+        <v/>
+      </c>
+      <c r="D101" s="154">
+        <f>D26*D20</f>
+        <v/>
+      </c>
+      <c r="E101" s="138" t="n"/>
+      <c r="F101" s="138" t="n"/>
+      <c r="G101" s="42" t="n"/>
+      <c r="H101" s="42" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="41" t="inlineStr">
+      <c r="A102" s="153" t="inlineStr">
         <is>
           <t>Accrued liabilities: year 3</t>
         </is>
       </c>
-      <c r="F102" s="42">
-        <f>F27*F20</f>
-        <v/>
-      </c>
-      <c r="G102" s="42">
-        <f>G27*G20</f>
-        <v/>
-      </c>
-      <c r="H102" s="42">
-        <f>H27*H20</f>
-        <v/>
-      </c>
+      <c r="B102" s="154">
+        <f>B27*B20</f>
+        <v/>
+      </c>
+      <c r="C102" s="154">
+        <f>C27*C20</f>
+        <v/>
+      </c>
+      <c r="D102" s="154">
+        <f>D27*D20</f>
+        <v/>
+      </c>
+      <c r="E102" s="138" t="n"/>
+      <c r="F102" s="138" t="n"/>
+      <c r="G102" s="42" t="n"/>
+      <c r="H102" s="42" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="41" t="inlineStr">
+      <c r="A103" s="153" t="inlineStr">
         <is>
           <t>Accrued liabilities: year 4</t>
         </is>
       </c>
-      <c r="F103" s="42">
-        <f>F28*F20</f>
-        <v/>
-      </c>
-      <c r="G103" s="42">
-        <f>G28*G20</f>
-        <v/>
-      </c>
-      <c r="H103" s="42">
-        <f>H28*H20</f>
-        <v/>
-      </c>
+      <c r="B103" s="154">
+        <f>B28*B20</f>
+        <v/>
+      </c>
+      <c r="C103" s="154">
+        <f>C28*C20</f>
+        <v/>
+      </c>
+      <c r="D103" s="154">
+        <f>D28*D20</f>
+        <v/>
+      </c>
+      <c r="E103" s="138" t="n"/>
+      <c r="F103" s="138" t="n"/>
+      <c r="G103" s="42" t="n"/>
+      <c r="H103" s="42" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="41" t="inlineStr">
+      <c r="A104" s="153" t="inlineStr">
         <is>
           <t>Accrued liabilities: year 5</t>
         </is>
       </c>
-      <c r="F104" s="42">
-        <f>F29*F20</f>
-        <v/>
-      </c>
-      <c r="G104" s="42">
-        <f>G29*G20</f>
-        <v/>
-      </c>
-      <c r="H104" s="42">
-        <f>H29*H20</f>
-        <v/>
-      </c>
+      <c r="B104" s="154">
+        <f>B29*B20</f>
+        <v/>
+      </c>
+      <c r="C104" s="154">
+        <f>C29*C20</f>
+        <v/>
+      </c>
+      <c r="D104" s="154">
+        <f>D29*D20</f>
+        <v/>
+      </c>
+      <c r="E104" s="138" t="n"/>
+      <c r="F104" s="138" t="n"/>
+      <c r="G104" s="42" t="n"/>
+      <c r="H104" s="42" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="41" t="inlineStr">
+      <c r="A105" s="153" t="inlineStr">
         <is>
           <t>Current operating assets (AR + inv + prepaids): year 1</t>
         </is>
       </c>
-      <c r="B105" s="135" t="inlineStr">
+      <c r="B105" s="154">
+        <f>B70+B80+B95</f>
+        <v/>
+      </c>
+      <c r="C105" s="154">
+        <f>C70+C80+C95</f>
+        <v/>
+      </c>
+      <c r="D105" s="154">
+        <f>D70+D80+D95</f>
+        <v/>
+      </c>
+      <c r="E105" s="138" t="n"/>
+      <c r="F105" s="147" t="inlineStr">
         <is>
           <t>Rises as receivables, inventory, prepaids expand.</t>
         </is>
       </c>
-      <c r="F105" s="42">
-        <f>F70+F80+F95</f>
-        <v/>
-      </c>
-      <c r="G105" s="42">
-        <f>G70+G80+G95</f>
-        <v/>
-      </c>
-      <c r="H105" s="42">
-        <f>H70+H80+H95</f>
-        <v/>
-      </c>
+      <c r="G105" s="42" t="n"/>
+      <c r="H105" s="42" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="41" t="inlineStr">
+      <c r="A106" s="153" t="inlineStr">
         <is>
           <t>Current operating assets (AR + inv + prepaids): year 2</t>
         </is>
       </c>
-      <c r="F106" s="42">
-        <f>F71+F81+F96</f>
-        <v/>
-      </c>
-      <c r="G106" s="42">
-        <f>G71+G81+G96</f>
-        <v/>
-      </c>
-      <c r="H106" s="42">
-        <f>H71+H81+H96</f>
-        <v/>
-      </c>
+      <c r="B106" s="154">
+        <f>B71+B81+B96</f>
+        <v/>
+      </c>
+      <c r="C106" s="154">
+        <f>C71+C81+C96</f>
+        <v/>
+      </c>
+      <c r="D106" s="154">
+        <f>D71+D81+D96</f>
+        <v/>
+      </c>
+      <c r="E106" s="138" t="n"/>
+      <c r="F106" s="138" t="n"/>
+      <c r="G106" s="42" t="n"/>
+      <c r="H106" s="42" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="41" t="inlineStr">
+      <c r="A107" s="153" t="inlineStr">
         <is>
           <t>Current operating assets (AR + inv + prepaids): year 3</t>
         </is>
       </c>
-      <c r="F107" s="42">
-        <f>F72+F82+F97</f>
-        <v/>
-      </c>
-      <c r="G107" s="42">
-        <f>G72+G82+G97</f>
-        <v/>
-      </c>
-      <c r="H107" s="42">
-        <f>H72+H82+H97</f>
-        <v/>
-      </c>
+      <c r="B107" s="154">
+        <f>B72+B82+B97</f>
+        <v/>
+      </c>
+      <c r="C107" s="154">
+        <f>C72+C82+C97</f>
+        <v/>
+      </c>
+      <c r="D107" s="154">
+        <f>D72+D82+D97</f>
+        <v/>
+      </c>
+      <c r="E107" s="138" t="n"/>
+      <c r="F107" s="138" t="n"/>
+      <c r="G107" s="42" t="n"/>
+      <c r="H107" s="42" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="41" t="inlineStr">
+      <c r="A108" s="153" t="inlineStr">
         <is>
           <t>Current operating assets (AR + inv + prepaids): year 4</t>
         </is>
       </c>
-      <c r="F108" s="42">
-        <f>F73+F83+F98</f>
-        <v/>
-      </c>
-      <c r="G108" s="42">
-        <f>G73+G83+G98</f>
-        <v/>
-      </c>
-      <c r="H108" s="42">
-        <f>H73+H83+H98</f>
-        <v/>
-      </c>
+      <c r="B108" s="154">
+        <f>B73+B83+B98</f>
+        <v/>
+      </c>
+      <c r="C108" s="154">
+        <f>C73+C83+C98</f>
+        <v/>
+      </c>
+      <c r="D108" s="154">
+        <f>D73+D83+D98</f>
+        <v/>
+      </c>
+      <c r="E108" s="138" t="n"/>
+      <c r="F108" s="138" t="n"/>
+      <c r="G108" s="42" t="n"/>
+      <c r="H108" s="42" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="41" t="inlineStr">
+      <c r="A109" s="153" t="inlineStr">
         <is>
           <t>Current operating assets (AR + inv + prepaids): year 5</t>
         </is>
       </c>
-      <c r="F109" s="42">
-        <f>F74+F84+F99</f>
-        <v/>
-      </c>
-      <c r="G109" s="42">
-        <f>G74+G84+G99</f>
-        <v/>
-      </c>
-      <c r="H109" s="42">
-        <f>H74+H84+H99</f>
-        <v/>
-      </c>
+      <c r="B109" s="154">
+        <f>B74+B84+B99</f>
+        <v/>
+      </c>
+      <c r="C109" s="154">
+        <f>C74+C84+C99</f>
+        <v/>
+      </c>
+      <c r="D109" s="154">
+        <f>D74+D84+D99</f>
+        <v/>
+      </c>
+      <c r="E109" s="138" t="n"/>
+      <c r="F109" s="138" t="n"/>
+      <c r="G109" s="42" t="n"/>
+      <c r="H109" s="42" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="41" t="inlineStr">
+      <c r="A110" s="153" t="inlineStr">
         <is>
           <t>Current operating liabilities (AP + accruals): year 1</t>
         </is>
       </c>
-      <c r="B110" s="135" t="inlineStr">
+      <c r="B110" s="154">
+        <f>B90+B100</f>
+        <v/>
+      </c>
+      <c r="C110" s="154">
+        <f>C90+C100</f>
+        <v/>
+      </c>
+      <c r="D110" s="154">
+        <f>D90+D100</f>
+        <v/>
+      </c>
+      <c r="E110" s="138" t="n"/>
+      <c r="F110" s="147" t="inlineStr">
         <is>
           <t>Rises as payables and accruals grow with sales.</t>
         </is>
       </c>
-      <c r="F110" s="42">
-        <f>F90+F100</f>
-        <v/>
-      </c>
-      <c r="G110" s="42">
-        <f>G90+G100</f>
-        <v/>
-      </c>
-      <c r="H110" s="42">
-        <f>H90+H100</f>
-        <v/>
-      </c>
+      <c r="G110" s="42" t="n"/>
+      <c r="H110" s="42" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="41" t="inlineStr">
+      <c r="A111" s="153" t="inlineStr">
         <is>
           <t>Current operating liabilities (AP + accruals): year 2</t>
         </is>
       </c>
-      <c r="F111" s="42">
-        <f>F91+F101</f>
-        <v/>
-      </c>
-      <c r="G111" s="42">
-        <f>G91+G101</f>
-        <v/>
-      </c>
-      <c r="H111" s="42">
-        <f>H91+H101</f>
-        <v/>
-      </c>
+      <c r="B111" s="154">
+        <f>B91+B101</f>
+        <v/>
+      </c>
+      <c r="C111" s="154">
+        <f>C91+C101</f>
+        <v/>
+      </c>
+      <c r="D111" s="154">
+        <f>D91+D101</f>
+        <v/>
+      </c>
+      <c r="E111" s="138" t="n"/>
+      <c r="F111" s="138" t="n"/>
+      <c r="G111" s="42" t="n"/>
+      <c r="H111" s="42" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="41" t="inlineStr">
+      <c r="A112" s="153" t="inlineStr">
         <is>
           <t>Current operating liabilities (AP + accruals): year 3</t>
         </is>
       </c>
-      <c r="F112" s="42">
-        <f>F92+F102</f>
-        <v/>
-      </c>
-      <c r="G112" s="42">
-        <f>G92+G102</f>
-        <v/>
-      </c>
-      <c r="H112" s="42">
-        <f>H92+H102</f>
-        <v/>
-      </c>
+      <c r="B112" s="154">
+        <f>B92+B102</f>
+        <v/>
+      </c>
+      <c r="C112" s="154">
+        <f>C92+C102</f>
+        <v/>
+      </c>
+      <c r="D112" s="154">
+        <f>D92+D102</f>
+        <v/>
+      </c>
+      <c r="E112" s="138" t="n"/>
+      <c r="F112" s="138" t="n"/>
+      <c r="G112" s="42" t="n"/>
+      <c r="H112" s="42" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="41" t="inlineStr">
+      <c r="A113" s="153" t="inlineStr">
         <is>
           <t>Current operating liabilities (AP + accruals): year 4</t>
         </is>
       </c>
-      <c r="F113" s="42">
-        <f>F93+F103</f>
-        <v/>
-      </c>
-      <c r="G113" s="42">
-        <f>G93+G103</f>
-        <v/>
-      </c>
-      <c r="H113" s="42">
-        <f>H93+H103</f>
-        <v/>
-      </c>
+      <c r="B113" s="154">
+        <f>B93+B103</f>
+        <v/>
+      </c>
+      <c r="C113" s="154">
+        <f>C93+C103</f>
+        <v/>
+      </c>
+      <c r="D113" s="154">
+        <f>D93+D103</f>
+        <v/>
+      </c>
+      <c r="E113" s="138" t="n"/>
+      <c r="F113" s="138" t="n"/>
+      <c r="G113" s="42" t="n"/>
+      <c r="H113" s="42" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="41" t="inlineStr">
+      <c r="A114" s="153" t="inlineStr">
         <is>
           <t>Current operating liabilities (AP + accruals): year 5</t>
         </is>
       </c>
-      <c r="F114" s="42">
-        <f>F94+F104</f>
-        <v/>
-      </c>
-      <c r="G114" s="42">
-        <f>G94+G104</f>
-        <v/>
-      </c>
-      <c r="H114" s="42">
-        <f>H94+H104</f>
-        <v/>
-      </c>
+      <c r="B114" s="154">
+        <f>B94+B104</f>
+        <v/>
+      </c>
+      <c r="C114" s="154">
+        <f>C94+C104</f>
+        <v/>
+      </c>
+      <c r="D114" s="154">
+        <f>D94+D104</f>
+        <v/>
+      </c>
+      <c r="E114" s="138" t="n"/>
+      <c r="F114" s="138" t="n"/>
+      <c r="G114" s="42" t="n"/>
+      <c r="H114" s="42" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="41" t="inlineStr">
+      <c r="A115" s="153" t="inlineStr">
         <is>
           <t>Net working capital: year 1</t>
         </is>
       </c>
-      <c r="B115" s="135" t="inlineStr">
+      <c r="B115" s="154">
+        <f>B105-B110</f>
+        <v/>
+      </c>
+      <c r="C115" s="154">
+        <f>C105-C110</f>
+        <v/>
+      </c>
+      <c r="D115" s="154">
+        <f>D105-D110</f>
+        <v/>
+      </c>
+      <c r="E115" s="138" t="n"/>
+      <c r="F115" s="147" t="inlineStr">
         <is>
           <t>Operating assets minus liabilities: level shifts yearly.</t>
         </is>
       </c>
-      <c r="F115" s="42">
-        <f>F105-F110</f>
-        <v/>
-      </c>
-      <c r="G115" s="42">
-        <f>G105-G110</f>
-        <v/>
-      </c>
-      <c r="H115" s="42">
-        <f>H105-H110</f>
-        <v/>
-      </c>
+      <c r="G115" s="42" t="n"/>
+      <c r="H115" s="42" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="41" t="inlineStr">
+      <c r="A116" s="153" t="inlineStr">
         <is>
           <t>Net working capital: year 2</t>
         </is>
       </c>
-      <c r="F116" s="42">
-        <f>F106-F111</f>
-        <v/>
-      </c>
-      <c r="G116" s="42">
-        <f>G106-G111</f>
-        <v/>
-      </c>
-      <c r="H116" s="42">
-        <f>H106-H111</f>
-        <v/>
-      </c>
+      <c r="B116" s="154">
+        <f>B106-B111</f>
+        <v/>
+      </c>
+      <c r="C116" s="154">
+        <f>C106-C111</f>
+        <v/>
+      </c>
+      <c r="D116" s="154">
+        <f>D106-D111</f>
+        <v/>
+      </c>
+      <c r="E116" s="138" t="n"/>
+      <c r="F116" s="138" t="n"/>
+      <c r="G116" s="42" t="n"/>
+      <c r="H116" s="42" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="41" t="inlineStr">
+      <c r="A117" s="153" t="inlineStr">
         <is>
           <t>Net working capital: year 3</t>
         </is>
       </c>
-      <c r="F117" s="42">
-        <f>F107-F112</f>
-        <v/>
-      </c>
-      <c r="G117" s="42">
-        <f>G107-G112</f>
-        <v/>
-      </c>
-      <c r="H117" s="42">
-        <f>H107-H112</f>
-        <v/>
-      </c>
+      <c r="B117" s="154">
+        <f>B107-B112</f>
+        <v/>
+      </c>
+      <c r="C117" s="154">
+        <f>C107-C112</f>
+        <v/>
+      </c>
+      <c r="D117" s="154">
+        <f>D107-D112</f>
+        <v/>
+      </c>
+      <c r="E117" s="138" t="n"/>
+      <c r="F117" s="138" t="n"/>
+      <c r="G117" s="42" t="n"/>
+      <c r="H117" s="42" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="41" t="inlineStr">
+      <c r="A118" s="153" t="inlineStr">
         <is>
           <t>Net working capital: year 4</t>
         </is>
       </c>
-      <c r="F118" s="42">
-        <f>F108-F113</f>
-        <v/>
-      </c>
-      <c r="G118" s="42">
-        <f>G108-G113</f>
-        <v/>
-      </c>
-      <c r="H118" s="42">
-        <f>H108-H113</f>
-        <v/>
-      </c>
+      <c r="B118" s="154">
+        <f>B108-B113</f>
+        <v/>
+      </c>
+      <c r="C118" s="154">
+        <f>C108-C113</f>
+        <v/>
+      </c>
+      <c r="D118" s="154">
+        <f>D108-D113</f>
+        <v/>
+      </c>
+      <c r="E118" s="138" t="n"/>
+      <c r="F118" s="138" t="n"/>
+      <c r="G118" s="42" t="n"/>
+      <c r="H118" s="42" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="41" t="inlineStr">
+      <c r="A119" s="153" t="inlineStr">
         <is>
           <t>Net working capital: year 5</t>
         </is>
       </c>
-      <c r="F119" s="42">
-        <f>F109-F114</f>
-        <v/>
-      </c>
-      <c r="G119" s="42">
-        <f>G109-G114</f>
-        <v/>
-      </c>
-      <c r="H119" s="42">
-        <f>H109-H114</f>
-        <v/>
-      </c>
+      <c r="B119" s="154">
+        <f>B109-B114</f>
+        <v/>
+      </c>
+      <c r="C119" s="154">
+        <f>C109-C114</f>
+        <v/>
+      </c>
+      <c r="D119" s="154">
+        <f>D109-D114</f>
+        <v/>
+      </c>
+      <c r="E119" s="138" t="n"/>
+      <c r="F119" s="138" t="n"/>
+      <c r="G119" s="42" t="n"/>
+      <c r="H119" s="42" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="41" t="inlineStr">
-        <is>
-          <t>ΔNWC (prior yr: prior yr minus current yr): year 1</t>
-        </is>
-      </c>
-      <c r="B120" s="135" t="inlineStr">
+      <c r="A120" s="153" t="inlineStr">
+        <is>
+          <t>ΔNWC (prior yr minus current yr): year 1</t>
+        </is>
+      </c>
+      <c r="B120" s="154">
+        <f>DCF!$E$32-B115</f>
+        <v/>
+      </c>
+      <c r="C120" s="154">
+        <f>DCF!$E$32-C115</f>
+        <v/>
+      </c>
+      <c r="D120" s="154">
+        <f>DCF!$E$32-D115</f>
+        <v/>
+      </c>
+      <c r="E120" s="138" t="n"/>
+      <c r="F120" s="147" t="inlineStr">
         <is>
           <t>Prior minus current NWC: positive releases cash.</t>
         </is>
       </c>
-      <c r="F120" s="42">
-        <f>DCF!$E$32-F115</f>
-        <v/>
-      </c>
-      <c r="G120" s="42">
-        <f>DCF!$E$32-G115</f>
-        <v/>
-      </c>
-      <c r="H120" s="42">
-        <f>DCF!$E$32-H115</f>
-        <v/>
-      </c>
+      <c r="G120" s="42" t="n"/>
+      <c r="H120" s="42" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="41" t="inlineStr">
+      <c r="A121" s="153" t="inlineStr">
         <is>
           <t>ΔNWC (prior yr: prior yr minus current yr): year 2</t>
         </is>
       </c>
-      <c r="F121" s="42">
-        <f>F115-F116</f>
-        <v/>
-      </c>
-      <c r="G121" s="42">
-        <f>G115-G116</f>
-        <v/>
-      </c>
-      <c r="H121" s="42">
-        <f>H115-H116</f>
-        <v/>
-      </c>
+      <c r="B121" s="154">
+        <f>B115-B116</f>
+        <v/>
+      </c>
+      <c r="C121" s="154">
+        <f>C115-C116</f>
+        <v/>
+      </c>
+      <c r="D121" s="154">
+        <f>D115-D116</f>
+        <v/>
+      </c>
+      <c r="E121" s="138" t="n"/>
+      <c r="F121" s="138" t="n"/>
+      <c r="G121" s="42" t="n"/>
+      <c r="H121" s="42" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="41" t="inlineStr">
+      <c r="A122" s="153" t="inlineStr">
         <is>
           <t>ΔNWC (prior yr: prior yr minus current yr): year 3</t>
         </is>
       </c>
-      <c r="F122" s="42">
-        <f>F116-F117</f>
-        <v/>
-      </c>
-      <c r="G122" s="42">
-        <f>G116-G117</f>
-        <v/>
-      </c>
-      <c r="H122" s="42">
-        <f>H116-H117</f>
-        <v/>
-      </c>
+      <c r="B122" s="154">
+        <f>B116-B117</f>
+        <v/>
+      </c>
+      <c r="C122" s="154">
+        <f>C116-C117</f>
+        <v/>
+      </c>
+      <c r="D122" s="154">
+        <f>D116-D117</f>
+        <v/>
+      </c>
+      <c r="E122" s="138" t="n"/>
+      <c r="F122" s="138" t="n"/>
+      <c r="G122" s="42" t="n"/>
+      <c r="H122" s="42" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="41" t="inlineStr">
+      <c r="A123" s="153" t="inlineStr">
         <is>
           <t>ΔNWC (prior yr: prior yr minus current yr): year 4</t>
         </is>
       </c>
-      <c r="F123" s="42">
-        <f>F117-F118</f>
-        <v/>
-      </c>
-      <c r="G123" s="42">
-        <f>G117-G118</f>
-        <v/>
-      </c>
-      <c r="H123" s="42">
-        <f>H117-H118</f>
-        <v/>
-      </c>
+      <c r="B123" s="154">
+        <f>B117-B118</f>
+        <v/>
+      </c>
+      <c r="C123" s="154">
+        <f>C117-C118</f>
+        <v/>
+      </c>
+      <c r="D123" s="154">
+        <f>D117-D118</f>
+        <v/>
+      </c>
+      <c r="E123" s="138" t="n"/>
+      <c r="F123" s="138" t="n"/>
+      <c r="G123" s="42" t="n"/>
+      <c r="H123" s="42" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="41" t="inlineStr">
+      <c r="A124" s="153" t="inlineStr">
         <is>
           <t>ΔNWC (prior yr: prior yr minus current yr): year 5</t>
         </is>
       </c>
-      <c r="F124" s="42">
-        <f>F118-F119</f>
-        <v/>
-      </c>
-      <c r="G124" s="42">
-        <f>G118-G119</f>
-        <v/>
-      </c>
-      <c r="H124" s="42">
-        <f>H118-H119</f>
-        <v/>
-      </c>
+      <c r="B124" s="154">
+        <f>B118-B119</f>
+        <v/>
+      </c>
+      <c r="C124" s="154">
+        <f>C118-C119</f>
+        <v/>
+      </c>
+      <c r="D124" s="154">
+        <f>D118-D119</f>
+        <v/>
+      </c>
+      <c r="E124" s="138" t="n"/>
+      <c r="F124" s="138" t="n"/>
+      <c r="G124" s="42" t="n"/>
+      <c r="H124" s="42" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="41" t="inlineStr">
+      <c r="A125" s="153" t="inlineStr">
         <is>
           <t>Unlevered FCF: year 1</t>
         </is>
       </c>
-      <c r="B125" s="135" t="inlineStr">
+      <c r="B125" s="154">
+        <f>B50+B55-B60+B120</f>
+        <v/>
+      </c>
+      <c r="C125" s="154">
+        <f>C50+C55-C60+C120</f>
+        <v/>
+      </c>
+      <c r="D125" s="154">
+        <f>D50+D55-D60+D120</f>
+        <v/>
+      </c>
+      <c r="E125" s="138" t="n"/>
+      <c r="F125" s="147" t="inlineStr">
         <is>
           <t>NOPAT plus depreciation minus capex plus working capital.</t>
         </is>
       </c>
-      <c r="F125" s="42">
-        <f>F50+F55-F60+F120</f>
-        <v/>
-      </c>
-      <c r="G125" s="42">
-        <f>G50+G55-G60+G120</f>
-        <v/>
-      </c>
-      <c r="H125" s="42">
-        <f>H50+H55-H60+H120</f>
-        <v/>
-      </c>
+      <c r="G125" s="42" t="n"/>
+      <c r="H125" s="42" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="41" t="inlineStr">
+      <c r="A126" s="153" t="inlineStr">
         <is>
           <t>Unlevered FCF: year 2</t>
         </is>
       </c>
-      <c r="F126" s="42">
-        <f>F51+F56-F61+F121</f>
-        <v/>
-      </c>
-      <c r="G126" s="42">
-        <f>G51+G56-G61+G121</f>
-        <v/>
-      </c>
-      <c r="H126" s="42">
-        <f>H51+H56-H61+H121</f>
-        <v/>
-      </c>
+      <c r="B126" s="154">
+        <f>B51+B56-B61+B121</f>
+        <v/>
+      </c>
+      <c r="C126" s="154">
+        <f>C51+C56-C61+C121</f>
+        <v/>
+      </c>
+      <c r="D126" s="154">
+        <f>D51+D56-D61+D121</f>
+        <v/>
+      </c>
+      <c r="E126" s="138" t="n"/>
+      <c r="F126" s="138" t="n"/>
+      <c r="G126" s="42" t="n"/>
+      <c r="H126" s="42" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="41" t="inlineStr">
+      <c r="A127" s="153" t="inlineStr">
         <is>
           <t>Unlevered FCF: year 3</t>
         </is>
       </c>
-      <c r="F127" s="42">
-        <f>F52+F57-F62+F122</f>
-        <v/>
-      </c>
-      <c r="G127" s="42">
-        <f>G52+G57-G62+G122</f>
-        <v/>
-      </c>
-      <c r="H127" s="42">
-        <f>H52+H57-H62+H122</f>
-        <v/>
-      </c>
+      <c r="B127" s="154">
+        <f>B52+B57-B62+B122</f>
+        <v/>
+      </c>
+      <c r="C127" s="154">
+        <f>C52+C57-C62+C122</f>
+        <v/>
+      </c>
+      <c r="D127" s="154">
+        <f>D52+D57-D62+D122</f>
+        <v/>
+      </c>
+      <c r="E127" s="138" t="n"/>
+      <c r="F127" s="138" t="n"/>
+      <c r="G127" s="42" t="n"/>
+      <c r="H127" s="42" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="41" t="inlineStr">
+      <c r="A128" s="153" t="inlineStr">
         <is>
           <t>Unlevered FCF: year 4</t>
         </is>
       </c>
-      <c r="F128" s="42">
-        <f>F53+F58-F63+F123</f>
-        <v/>
-      </c>
-      <c r="G128" s="42">
-        <f>G53+G58-G63+G123</f>
-        <v/>
-      </c>
-      <c r="H128" s="42">
-        <f>H53+H58-H63+H123</f>
-        <v/>
-      </c>
+      <c r="B128" s="154">
+        <f>B53+B58-B63+B123</f>
+        <v/>
+      </c>
+      <c r="C128" s="154">
+        <f>C53+C58-C63+C123</f>
+        <v/>
+      </c>
+      <c r="D128" s="154">
+        <f>D53+D58-D63+D123</f>
+        <v/>
+      </c>
+      <c r="E128" s="138" t="n"/>
+      <c r="F128" s="138" t="n"/>
+      <c r="G128" s="42" t="n"/>
+      <c r="H128" s="42" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="41" t="inlineStr">
+      <c r="A129" s="153" t="inlineStr">
         <is>
           <t>Unlevered FCF: year 5</t>
         </is>
       </c>
-      <c r="F129" s="42">
-        <f>F54+F59-F64+F124</f>
-        <v/>
-      </c>
-      <c r="G129" s="42">
-        <f>G54+G59-G64+G124</f>
-        <v/>
-      </c>
-      <c r="H129" s="42">
-        <f>H54+H59-H64+H124</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130"/>
+      <c r="B129" s="154">
+        <f>B54+B59-B64+B124</f>
+        <v/>
+      </c>
+      <c r="C129" s="154">
+        <f>C54+C59-C64+C124</f>
+        <v/>
+      </c>
+      <c r="D129" s="154">
+        <f>D54+D59-D64+D124</f>
+        <v/>
+      </c>
+      <c r="E129" s="138" t="n"/>
+      <c r="F129" s="138" t="n"/>
+      <c r="G129" s="42" t="n"/>
+      <c r="H129" s="42" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="138" t="n"/>
+      <c r="B130" s="138" t="n"/>
+      <c r="C130" s="138" t="n"/>
+      <c r="D130" s="138" t="n"/>
+      <c r="E130" s="138" t="n"/>
+      <c r="F130" s="138" t="n"/>
+    </row>
     <row r="131">
-      <c r="A131" s="23" t="inlineStr">
+      <c r="A131" s="157" t="inlineStr">
         <is>
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="F131" s="25">
-        <f>NPV(F9,F125,F126,F127,F128,F129)+(F129*(1+F10)/(F9-F10))/(1+F9)^5</f>
-        <v/>
-      </c>
-      <c r="G131" s="25">
-        <f>NPV(G9,G125,G126,G127,G128,G129)+(G129*(1+G10)/(G9-G10))/(1+G9)^5</f>
-        <v/>
-      </c>
-      <c r="H131" s="25">
-        <f>NPV(H9,H125,H126,H127,H128,H129)+(H129*(1+H10)/(H9-H10))/(1+H9)^5</f>
-        <v/>
-      </c>
+      <c r="B131" s="158">
+        <f>NPV(B9,B125,B126,B127,B128,B129)+(B129*(1+B10)/(B9-B10))/(1+B9)^5</f>
+        <v/>
+      </c>
+      <c r="C131" s="158">
+        <f>NPV(C9,C125,C126,C127,C128,C129)+(C129*(1+C10)/(C9-C10))/(1+C9)^5</f>
+        <v/>
+      </c>
+      <c r="D131" s="158">
+        <f>NPV(D9,D125,D126,D127,D128,D129)+(D129*(1+D10)/(D9-D10))/(1+D9)^5</f>
+        <v/>
+      </c>
+      <c r="E131" s="138" t="n"/>
+      <c r="F131" s="138" t="n"/>
+      <c r="G131" s="25" t="n"/>
+      <c r="H131" s="25" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="45" t="inlineStr">
+      <c r="A132" s="159" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="F132" s="46">
-        <f>(F131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
-        <v/>
-      </c>
-      <c r="G132" s="47">
-        <f>(G131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
-        <v/>
-      </c>
-      <c r="H132" s="46">
-        <f>(H131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
-        <v/>
-      </c>
+      <c r="B132" s="160">
+        <f>(B131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
+        <v/>
+      </c>
+      <c r="C132" s="161">
+        <f>(C131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
+        <v/>
+      </c>
+      <c r="D132" s="160">
+        <f>(D131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
+        <v/>
+      </c>
+      <c r="E132" s="138" t="n"/>
+      <c r="F132" s="138" t="n"/>
+      <c r="G132" s="47" t="n"/>
+      <c r="H132" s="46" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="23" t="inlineStr">
+      <c r="A133" s="157" t="inlineStr">
         <is>
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="F133" s="48">
-        <f>F132/100.0-1</f>
-        <v/>
-      </c>
-      <c r="G133" s="48">
-        <f>G132/100.0-1</f>
-        <v/>
-      </c>
-      <c r="H133" s="48">
-        <f>H132/100.0-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134"/>
+      <c r="B133" s="162">
+        <f>B132/100.0-1</f>
+        <v/>
+      </c>
+      <c r="C133" s="162">
+        <f>C132/100.0-1</f>
+        <v/>
+      </c>
+      <c r="D133" s="162">
+        <f>D132/100.0-1</f>
+        <v/>
+      </c>
+      <c r="E133" s="138" t="n"/>
+      <c r="F133" s="138" t="n"/>
+      <c r="G133" s="48" t="n"/>
+      <c r="H133" s="48" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="138" t="n"/>
+      <c r="B134" s="138" t="n"/>
+      <c r="C134" s="138" t="n"/>
+      <c r="D134" s="138" t="n"/>
+      <c r="E134" s="138" t="n"/>
+      <c r="F134" s="138" t="n"/>
+    </row>
     <row r="135">
-      <c r="A135" s="26" t="inlineStr">
+      <c r="A135" s="163" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; lease debt $1,798,441 k; funded debt $0; net cash $8,761 k.</t>
         </is>
       </c>
-    </row>
-    <row r="136"/>
+      <c r="B135" s="138" t="n"/>
+      <c r="C135" s="138" t="n"/>
+      <c r="D135" s="138" t="n"/>
+      <c r="E135" s="138" t="n"/>
+      <c r="F135" s="138" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="138" t="n"/>
+      <c r="B136" s="138" t="n"/>
+      <c r="C136" s="138" t="n"/>
+      <c r="D136" s="138" t="n"/>
+      <c r="E136" s="138" t="n"/>
+      <c r="F136" s="138" t="n"/>
+    </row>
     <row r="137">
-      <c r="A137" s="14" t="inlineStr">
+      <c r="A137" s="142" t="inlineStr">
         <is>
           <t>Pitch deck bridge (IS / CFS / BS)</t>
         </is>
       </c>
+      <c r="B137" s="138" t="n"/>
+      <c r="C137" s="138" t="n"/>
+      <c r="D137" s="138" t="n"/>
+      <c r="E137" s="138" t="n"/>
+      <c r="F137" s="138" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="41" t="inlineStr">
+      <c r="A138" s="153" t="inlineStr">
         <is>
           <t>Other income: year 1</t>
         </is>
       </c>
-      <c r="F138" s="42" t="n">
+      <c r="B138" s="154" t="n">
         <v>45000</v>
       </c>
-      <c r="G138" s="42" t="n">
+      <c r="C138" s="154" t="n">
         <v>45000</v>
       </c>
-      <c r="H138" s="42" t="n">
+      <c r="D138" s="154" t="n">
         <v>45000</v>
       </c>
+      <c r="E138" s="138" t="n"/>
+      <c r="F138" s="138" t="n"/>
+      <c r="G138" s="42" t="n"/>
+      <c r="H138" s="42" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="41" t="inlineStr">
+      <c r="A139" s="153" t="inlineStr">
         <is>
           <t>Other income: year 2</t>
         </is>
       </c>
-      <c r="F139" s="42" t="n">
+      <c r="B139" s="154" t="n">
         <v>40000</v>
       </c>
-      <c r="G139" s="42" t="n">
+      <c r="C139" s="154" t="n">
         <v>40000</v>
       </c>
-      <c r="H139" s="42" t="n">
+      <c r="D139" s="154" t="n">
         <v>40000</v>
       </c>
+      <c r="E139" s="138" t="n"/>
+      <c r="F139" s="138" t="n"/>
+      <c r="G139" s="42" t="n"/>
+      <c r="H139" s="42" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="41" t="inlineStr">
+      <c r="A140" s="153" t="inlineStr">
         <is>
           <t>Other income: year 3</t>
         </is>
       </c>
-      <c r="F140" s="42" t="n">
+      <c r="B140" s="154" t="n">
         <v>35000</v>
       </c>
-      <c r="G140" s="42" t="n">
+      <c r="C140" s="154" t="n">
         <v>35000</v>
       </c>
-      <c r="H140" s="42" t="n">
+      <c r="D140" s="154" t="n">
         <v>35000</v>
       </c>
+      <c r="E140" s="138" t="n"/>
+      <c r="F140" s="138" t="n"/>
+      <c r="G140" s="42" t="n"/>
+      <c r="H140" s="42" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="41" t="inlineStr">
+      <c r="A141" s="153" t="inlineStr">
         <is>
           <t>Other income: year 4</t>
         </is>
       </c>
-      <c r="F141" s="42" t="n">
+      <c r="B141" s="154" t="n">
         <v>30000</v>
       </c>
-      <c r="G141" s="42" t="n">
+      <c r="C141" s="154" t="n">
         <v>30000</v>
       </c>
-      <c r="H141" s="42" t="n">
+      <c r="D141" s="154" t="n">
         <v>30000</v>
       </c>
+      <c r="E141" s="138" t="n"/>
+      <c r="F141" s="138" t="n"/>
+      <c r="G141" s="42" t="n"/>
+      <c r="H141" s="42" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="41" t="inlineStr">
+      <c r="A142" s="153" t="inlineStr">
         <is>
           <t>Other income: year 5</t>
         </is>
       </c>
-      <c r="F142" s="42" t="n">
+      <c r="B142" s="154" t="n">
         <v>25000</v>
       </c>
-      <c r="G142" s="42" t="n">
+      <c r="C142" s="154" t="n">
         <v>25000</v>
       </c>
-      <c r="H142" s="42" t="n">
+      <c r="D142" s="154" t="n">
         <v>25000</v>
       </c>
+      <c r="E142" s="138" t="n"/>
+      <c r="F142" s="138" t="n"/>
+      <c r="G142" s="42" t="n"/>
+      <c r="H142" s="42" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="41" t="inlineStr">
+      <c r="A143" s="153" t="inlineStr">
         <is>
           <t>Net income: year 1</t>
         </is>
       </c>
-      <c r="F143" s="42">
-        <f>(F45+F138)*(1-F11)</f>
-        <v/>
-      </c>
-      <c r="G143" s="42">
-        <f>(G45+G138)*(1-G11)</f>
-        <v/>
-      </c>
-      <c r="H143" s="42">
-        <f>(H45+H138)*(1-H11)</f>
-        <v/>
-      </c>
+      <c r="B143" s="154">
+        <f>(B45+B138)*(1-B11)</f>
+        <v/>
+      </c>
+      <c r="C143" s="154">
+        <f>(C45+C138)*(1-C11)</f>
+        <v/>
+      </c>
+      <c r="D143" s="154">
+        <f>(D45+D138)*(1-D11)</f>
+        <v/>
+      </c>
+      <c r="E143" s="138" t="n"/>
+      <c r="F143" s="138" t="n"/>
+      <c r="G143" s="42" t="n"/>
+      <c r="H143" s="42" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="41" t="inlineStr">
+      <c r="A144" s="153" t="inlineStr">
         <is>
           <t>Net income: year 2</t>
         </is>
       </c>
-      <c r="F144" s="42">
-        <f>(F46+F139)*(1-F11)</f>
-        <v/>
-      </c>
-      <c r="G144" s="42">
-        <f>(G46+G139)*(1-G11)</f>
-        <v/>
-      </c>
-      <c r="H144" s="42">
-        <f>(H46+H139)*(1-H11)</f>
-        <v/>
-      </c>
+      <c r="B144" s="154">
+        <f>(B46+B139)*(1-B11)</f>
+        <v/>
+      </c>
+      <c r="C144" s="154">
+        <f>(C46+C139)*(1-C11)</f>
+        <v/>
+      </c>
+      <c r="D144" s="154">
+        <f>(D46+D139)*(1-D11)</f>
+        <v/>
+      </c>
+      <c r="E144" s="138" t="n"/>
+      <c r="F144" s="138" t="n"/>
+      <c r="G144" s="42" t="n"/>
+      <c r="H144" s="42" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="41" t="inlineStr">
+      <c r="A145" s="153" t="inlineStr">
         <is>
           <t>Net income: year 3</t>
         </is>
       </c>
-      <c r="F145" s="42">
-        <f>(F47+F140)*(1-F11)</f>
-        <v/>
-      </c>
-      <c r="G145" s="42">
-        <f>(G47+G140)*(1-G11)</f>
-        <v/>
-      </c>
-      <c r="H145" s="42">
-        <f>(H47+H140)*(1-H11)</f>
-        <v/>
-      </c>
+      <c r="B145" s="154">
+        <f>(B47+B140)*(1-B11)</f>
+        <v/>
+      </c>
+      <c r="C145" s="154">
+        <f>(C47+C140)*(1-C11)</f>
+        <v/>
+      </c>
+      <c r="D145" s="154">
+        <f>(D47+D140)*(1-D11)</f>
+        <v/>
+      </c>
+      <c r="E145" s="138" t="n"/>
+      <c r="F145" s="138" t="n"/>
+      <c r="G145" s="42" t="n"/>
+      <c r="H145" s="42" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="41" t="inlineStr">
+      <c r="A146" s="153" t="inlineStr">
         <is>
           <t>Net income: year 4</t>
         </is>
       </c>
-      <c r="F146" s="42">
-        <f>(F48+F141)*(1-F11)</f>
-        <v/>
-      </c>
-      <c r="G146" s="42">
-        <f>(G48+G141)*(1-G11)</f>
-        <v/>
-      </c>
-      <c r="H146" s="42">
-        <f>(H48+H141)*(1-H11)</f>
-        <v/>
-      </c>
+      <c r="B146" s="154">
+        <f>(B48+B141)*(1-B11)</f>
+        <v/>
+      </c>
+      <c r="C146" s="154">
+        <f>(C48+C141)*(1-C11)</f>
+        <v/>
+      </c>
+      <c r="D146" s="154">
+        <f>(D48+D141)*(1-D11)</f>
+        <v/>
+      </c>
+      <c r="E146" s="138" t="n"/>
+      <c r="F146" s="138" t="n"/>
+      <c r="G146" s="42" t="n"/>
+      <c r="H146" s="42" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="41" t="inlineStr">
+      <c r="A147" s="153" t="inlineStr">
         <is>
           <t>Net income: year 5</t>
         </is>
       </c>
-      <c r="F147" s="42">
-        <f>(F49+F142)*(1-F11)</f>
-        <v/>
-      </c>
-      <c r="G147" s="42">
-        <f>(G49+G142)*(1-G11)</f>
-        <v/>
-      </c>
-      <c r="H147" s="42">
-        <f>(H49+H142)*(1-H11)</f>
-        <v/>
-      </c>
+      <c r="B147" s="154">
+        <f>(B49+B142)*(1-B11)</f>
+        <v/>
+      </c>
+      <c r="C147" s="154">
+        <f>(C49+C142)*(1-C11)</f>
+        <v/>
+      </c>
+      <c r="D147" s="154">
+        <f>(D49+D142)*(1-D11)</f>
+        <v/>
+      </c>
+      <c r="E147" s="138" t="n"/>
+      <c r="F147" s="138" t="n"/>
+      <c r="G147" s="42" t="n"/>
+      <c r="H147" s="42" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="41" t="inlineStr">
+      <c r="A148" s="153" t="inlineStr">
         <is>
           <t>Cash from operations: year 1</t>
         </is>
       </c>
-      <c r="F148" s="42">
-        <f>F143+F55+F120</f>
-        <v/>
-      </c>
-      <c r="G148" s="42">
-        <f>G143+G55+G120</f>
-        <v/>
-      </c>
-      <c r="H148" s="42">
-        <f>H143+H55+H120</f>
-        <v/>
-      </c>
+      <c r="B148" s="154">
+        <f>B143+B55+B120</f>
+        <v/>
+      </c>
+      <c r="C148" s="154">
+        <f>C143+C55+C120</f>
+        <v/>
+      </c>
+      <c r="D148" s="154">
+        <f>D143+D55+D120</f>
+        <v/>
+      </c>
+      <c r="E148" s="138" t="n"/>
+      <c r="F148" s="138" t="n"/>
+      <c r="G148" s="42" t="n"/>
+      <c r="H148" s="42" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="41" t="inlineStr">
+      <c r="A149" s="153" t="inlineStr">
         <is>
           <t>Cash from operations: year 2</t>
         </is>
       </c>
-      <c r="F149" s="42">
-        <f>F144+F56+F121</f>
-        <v/>
-      </c>
-      <c r="G149" s="42">
-        <f>G144+G56+G121</f>
-        <v/>
-      </c>
-      <c r="H149" s="42">
-        <f>H144+H56+H121</f>
-        <v/>
-      </c>
+      <c r="B149" s="154">
+        <f>B144+B56+B121</f>
+        <v/>
+      </c>
+      <c r="C149" s="154">
+        <f>C144+C56+C121</f>
+        <v/>
+      </c>
+      <c r="D149" s="154">
+        <f>D144+D56+D121</f>
+        <v/>
+      </c>
+      <c r="E149" s="138" t="n"/>
+      <c r="F149" s="138" t="n"/>
+      <c r="G149" s="42" t="n"/>
+      <c r="H149" s="42" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="41" t="inlineStr">
+      <c r="A150" s="153" t="inlineStr">
         <is>
           <t>Cash from operations: year 3</t>
         </is>
       </c>
-      <c r="F150" s="42">
-        <f>F145+F57+F122</f>
-        <v/>
-      </c>
-      <c r="G150" s="42">
-        <f>G145+G57+G122</f>
-        <v/>
-      </c>
-      <c r="H150" s="42">
-        <f>H145+H57+H122</f>
-        <v/>
-      </c>
+      <c r="B150" s="154">
+        <f>B145+B57+B122</f>
+        <v/>
+      </c>
+      <c r="C150" s="154">
+        <f>C145+C57+C122</f>
+        <v/>
+      </c>
+      <c r="D150" s="154">
+        <f>D145+D57+D122</f>
+        <v/>
+      </c>
+      <c r="E150" s="138" t="n"/>
+      <c r="F150" s="138" t="n"/>
+      <c r="G150" s="42" t="n"/>
+      <c r="H150" s="42" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="41" t="inlineStr">
+      <c r="A151" s="153" t="inlineStr">
         <is>
           <t>Cash from operations: year 4</t>
         </is>
       </c>
-      <c r="F151" s="42">
-        <f>F146+F58+F123</f>
-        <v/>
-      </c>
-      <c r="G151" s="42">
-        <f>G146+G58+G123</f>
-        <v/>
-      </c>
-      <c r="H151" s="42">
-        <f>H146+H58+H123</f>
-        <v/>
-      </c>
+      <c r="B151" s="154">
+        <f>B146+B58+B123</f>
+        <v/>
+      </c>
+      <c r="C151" s="154">
+        <f>C146+C58+C123</f>
+        <v/>
+      </c>
+      <c r="D151" s="154">
+        <f>D146+D58+D123</f>
+        <v/>
+      </c>
+      <c r="E151" s="138" t="n"/>
+      <c r="F151" s="138" t="n"/>
+      <c r="G151" s="42" t="n"/>
+      <c r="H151" s="42" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="41" t="inlineStr">
+      <c r="A152" s="153" t="inlineStr">
         <is>
           <t>Cash from operations: year 5</t>
         </is>
       </c>
-      <c r="F152" s="42">
-        <f>F147+F59+F124</f>
-        <v/>
-      </c>
-      <c r="G152" s="42">
-        <f>G147+G59+G124</f>
-        <v/>
-      </c>
-      <c r="H152" s="42">
-        <f>H147+H59+H124</f>
-        <v/>
-      </c>
+      <c r="B152" s="154">
+        <f>B147+B59+B124</f>
+        <v/>
+      </c>
+      <c r="C152" s="154">
+        <f>C147+C59+C124</f>
+        <v/>
+      </c>
+      <c r="D152" s="154">
+        <f>D147+D59+D124</f>
+        <v/>
+      </c>
+      <c r="E152" s="138" t="n"/>
+      <c r="F152" s="138" t="n"/>
+      <c r="G152" s="42" t="n"/>
+      <c r="H152" s="42" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="41" t="inlineStr">
+      <c r="A153" s="153" t="inlineStr">
         <is>
           <t>Free cash flow (CFS): year 1</t>
         </is>
       </c>
-      <c r="F153" s="42">
-        <f>F148-F60</f>
-        <v/>
-      </c>
-      <c r="G153" s="42">
-        <f>G148-G60</f>
-        <v/>
-      </c>
-      <c r="H153" s="42">
-        <f>H148-H60</f>
-        <v/>
-      </c>
+      <c r="B153" s="154">
+        <f>B148-B60</f>
+        <v/>
+      </c>
+      <c r="C153" s="154">
+        <f>C148-C60</f>
+        <v/>
+      </c>
+      <c r="D153" s="154">
+        <f>D148-D60</f>
+        <v/>
+      </c>
+      <c r="E153" s="138" t="n"/>
+      <c r="F153" s="138" t="n"/>
+      <c r="G153" s="42" t="n"/>
+      <c r="H153" s="42" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="41" t="inlineStr">
+      <c r="A154" s="153" t="inlineStr">
         <is>
           <t>Free cash flow (CFS): year 2</t>
         </is>
       </c>
-      <c r="F154" s="42">
-        <f>F149-F61</f>
-        <v/>
-      </c>
-      <c r="G154" s="42">
-        <f>G149-G61</f>
-        <v/>
-      </c>
-      <c r="H154" s="42">
-        <f>H149-H61</f>
-        <v/>
-      </c>
+      <c r="B154" s="154">
+        <f>B149-B61</f>
+        <v/>
+      </c>
+      <c r="C154" s="154">
+        <f>C149-C61</f>
+        <v/>
+      </c>
+      <c r="D154" s="154">
+        <f>D149-D61</f>
+        <v/>
+      </c>
+      <c r="E154" s="138" t="n"/>
+      <c r="F154" s="138" t="n"/>
+      <c r="G154" s="42" t="n"/>
+      <c r="H154" s="42" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="41" t="inlineStr">
+      <c r="A155" s="153" t="inlineStr">
         <is>
           <t>Free cash flow (CFS): year 3</t>
         </is>
       </c>
-      <c r="F155" s="42">
-        <f>F150-F62</f>
-        <v/>
-      </c>
-      <c r="G155" s="42">
-        <f>G150-G62</f>
-        <v/>
-      </c>
-      <c r="H155" s="42">
-        <f>H150-H62</f>
-        <v/>
-      </c>
+      <c r="B155" s="154">
+        <f>B150-B62</f>
+        <v/>
+      </c>
+      <c r="C155" s="154">
+        <f>C150-C62</f>
+        <v/>
+      </c>
+      <c r="D155" s="154">
+        <f>D150-D62</f>
+        <v/>
+      </c>
+      <c r="E155" s="138" t="n"/>
+      <c r="F155" s="138" t="n"/>
+      <c r="G155" s="42" t="n"/>
+      <c r="H155" s="42" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="41" t="inlineStr">
+      <c r="A156" s="153" t="inlineStr">
         <is>
           <t>Free cash flow (CFS): year 4</t>
         </is>
       </c>
-      <c r="F156" s="42">
-        <f>F151-F63</f>
-        <v/>
-      </c>
-      <c r="G156" s="42">
-        <f>G151-G63</f>
-        <v/>
-      </c>
-      <c r="H156" s="42">
-        <f>H151-H63</f>
-        <v/>
-      </c>
+      <c r="B156" s="154">
+        <f>B151-B63</f>
+        <v/>
+      </c>
+      <c r="C156" s="154">
+        <f>C151-C63</f>
+        <v/>
+      </c>
+      <c r="D156" s="154">
+        <f>D151-D63</f>
+        <v/>
+      </c>
+      <c r="E156" s="138" t="n"/>
+      <c r="F156" s="138" t="n"/>
+      <c r="G156" s="42" t="n"/>
+      <c r="H156" s="42" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="41" t="inlineStr">
+      <c r="A157" s="153" t="inlineStr">
         <is>
           <t>Free cash flow (CFS): year 5</t>
         </is>
       </c>
-      <c r="F157" s="42">
-        <f>F152-F64</f>
-        <v/>
-      </c>
-      <c r="G157" s="42">
-        <f>G152-G64</f>
-        <v/>
-      </c>
-      <c r="H157" s="42">
-        <f>H152-H64</f>
-        <v/>
-      </c>
+      <c r="B157" s="154">
+        <f>B152-B64</f>
+        <v/>
+      </c>
+      <c r="C157" s="154">
+        <f>C152-C64</f>
+        <v/>
+      </c>
+      <c r="D157" s="154">
+        <f>D152-D64</f>
+        <v/>
+      </c>
+      <c r="E157" s="138" t="n"/>
+      <c r="F157" s="138" t="n"/>
+      <c r="G157" s="42" t="n"/>
+      <c r="H157" s="42" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="41" t="inlineStr">
+      <c r="A158" s="153" t="inlineStr">
         <is>
           <t>Share repurchases: year 1</t>
         </is>
       </c>
-      <c r="F158" s="42">
-        <f>-F21</f>
-        <v/>
-      </c>
-      <c r="G158" s="42">
-        <f>-G21</f>
-        <v/>
-      </c>
-      <c r="H158" s="42">
-        <f>-H22*H153</f>
-        <v/>
-      </c>
+      <c r="B158" s="154">
+        <f>-B21</f>
+        <v/>
+      </c>
+      <c r="C158" s="154">
+        <f>-C21</f>
+        <v/>
+      </c>
+      <c r="D158" s="154">
+        <f>-D22*D153</f>
+        <v/>
+      </c>
+      <c r="E158" s="138" t="n"/>
+      <c r="F158" s="138" t="n"/>
+      <c r="G158" s="42" t="n"/>
+      <c r="H158" s="42" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="41" t="inlineStr">
+      <c r="A159" s="153" t="inlineStr">
         <is>
           <t>Share repurchases: year 2</t>
         </is>
       </c>
-      <c r="F159" s="42">
-        <f>-F21</f>
-        <v/>
-      </c>
-      <c r="G159" s="42">
-        <f>-G21</f>
-        <v/>
-      </c>
-      <c r="H159" s="42">
-        <f>-H22*H154</f>
-        <v/>
-      </c>
+      <c r="B159" s="154">
+        <f>-B21</f>
+        <v/>
+      </c>
+      <c r="C159" s="154">
+        <f>-C21</f>
+        <v/>
+      </c>
+      <c r="D159" s="154">
+        <f>-D22*D154</f>
+        <v/>
+      </c>
+      <c r="E159" s="138" t="n"/>
+      <c r="F159" s="138" t="n"/>
+      <c r="G159" s="42" t="n"/>
+      <c r="H159" s="42" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="41" t="inlineStr">
+      <c r="A160" s="153" t="inlineStr">
         <is>
           <t>Share repurchases: year 3</t>
         </is>
       </c>
-      <c r="F160" s="42">
-        <f>-F21</f>
-        <v/>
-      </c>
-      <c r="G160" s="42">
-        <f>-G21</f>
-        <v/>
-      </c>
-      <c r="H160" s="42">
-        <f>-H22*H155</f>
-        <v/>
-      </c>
+      <c r="B160" s="154">
+        <f>-B21</f>
+        <v/>
+      </c>
+      <c r="C160" s="154">
+        <f>-C21</f>
+        <v/>
+      </c>
+      <c r="D160" s="154">
+        <f>-D22*D155</f>
+        <v/>
+      </c>
+      <c r="E160" s="138" t="n"/>
+      <c r="F160" s="138" t="n"/>
+      <c r="G160" s="42" t="n"/>
+      <c r="H160" s="42" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="41" t="inlineStr">
+      <c r="A161" s="153" t="inlineStr">
         <is>
           <t>Share repurchases: year 4</t>
         </is>
       </c>
-      <c r="F161" s="42">
-        <f>-F21</f>
-        <v/>
-      </c>
-      <c r="G161" s="42">
-        <f>-G21</f>
-        <v/>
-      </c>
-      <c r="H161" s="42">
-        <f>-H22*H156</f>
-        <v/>
-      </c>
+      <c r="B161" s="154">
+        <f>-B21</f>
+        <v/>
+      </c>
+      <c r="C161" s="154">
+        <f>-C21</f>
+        <v/>
+      </c>
+      <c r="D161" s="154">
+        <f>-D22*D156</f>
+        <v/>
+      </c>
+      <c r="E161" s="138" t="n"/>
+      <c r="F161" s="138" t="n"/>
+      <c r="G161" s="42" t="n"/>
+      <c r="H161" s="42" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="41" t="inlineStr">
+      <c r="A162" s="153" t="inlineStr">
         <is>
           <t>Share repurchases: year 5</t>
         </is>
       </c>
-      <c r="F162" s="42">
-        <f>-F21</f>
-        <v/>
-      </c>
-      <c r="G162" s="42">
-        <f>-G21</f>
-        <v/>
-      </c>
-      <c r="H162" s="42">
-        <f>-H22*H157</f>
-        <v/>
-      </c>
+      <c r="B162" s="154">
+        <f>-B21</f>
+        <v/>
+      </c>
+      <c r="C162" s="154">
+        <f>-C21</f>
+        <v/>
+      </c>
+      <c r="D162" s="154">
+        <f>-D22*D157</f>
+        <v/>
+      </c>
+      <c r="E162" s="138" t="n"/>
+      <c r="F162" s="138" t="n"/>
+      <c r="G162" s="42" t="n"/>
+      <c r="H162" s="42" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="41" t="inlineStr">
+      <c r="A163" s="153" t="inlineStr">
         <is>
           <t>Cash &amp; equivalents: year 1</t>
         </is>
       </c>
-      <c r="F163" s="42">
-        <f>DCF!$E$50+F153+F158</f>
-        <v/>
-      </c>
-      <c r="G163" s="42">
-        <f>DCF!$E$50+G153+G158</f>
-        <v/>
-      </c>
-      <c r="H163" s="42">
-        <f>DCF!$E$50+H153+H158</f>
-        <v/>
-      </c>
+      <c r="B163" s="154">
+        <f>DCF!$E$50+B153+B158</f>
+        <v/>
+      </c>
+      <c r="C163" s="154">
+        <f>DCF!$E$50+C153+C158</f>
+        <v/>
+      </c>
+      <c r="D163" s="154">
+        <f>DCF!$E$50+D153+D158</f>
+        <v/>
+      </c>
+      <c r="E163" s="138" t="n"/>
+      <c r="F163" s="138" t="n"/>
+      <c r="G163" s="42" t="n"/>
+      <c r="H163" s="42" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="41" t="inlineStr">
+      <c r="A164" s="153" t="inlineStr">
         <is>
           <t>Cash &amp; equivalents: year 2</t>
         </is>
       </c>
-      <c r="F164" s="42">
-        <f>F163+F154+F159</f>
-        <v/>
-      </c>
-      <c r="G164" s="42">
-        <f>G163+G154+G159</f>
-        <v/>
-      </c>
-      <c r="H164" s="42">
-        <f>H163+H154+H159</f>
-        <v/>
-      </c>
+      <c r="B164" s="154">
+        <f>B163+B154+B159</f>
+        <v/>
+      </c>
+      <c r="C164" s="154">
+        <f>C163+C154+C159</f>
+        <v/>
+      </c>
+      <c r="D164" s="154">
+        <f>D163+D154+D159</f>
+        <v/>
+      </c>
+      <c r="E164" s="138" t="n"/>
+      <c r="F164" s="138" t="n"/>
+      <c r="G164" s="42" t="n"/>
+      <c r="H164" s="42" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="41" t="inlineStr">
+      <c r="A165" s="153" t="inlineStr">
         <is>
           <t>Cash &amp; equivalents: year 3</t>
         </is>
       </c>
-      <c r="F165" s="42">
-        <f>F164+F155+F160</f>
-        <v/>
-      </c>
-      <c r="G165" s="42">
-        <f>G164+G155+G160</f>
-        <v/>
-      </c>
-      <c r="H165" s="42">
-        <f>H164+H155+H160</f>
-        <v/>
-      </c>
+      <c r="B165" s="154">
+        <f>B164+B155+B160</f>
+        <v/>
+      </c>
+      <c r="C165" s="154">
+        <f>C164+C155+C160</f>
+        <v/>
+      </c>
+      <c r="D165" s="154">
+        <f>D164+D155+D160</f>
+        <v/>
+      </c>
+      <c r="E165" s="138" t="n"/>
+      <c r="F165" s="138" t="n"/>
+      <c r="G165" s="42" t="n"/>
+      <c r="H165" s="42" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="41" t="inlineStr">
+      <c r="A166" s="153" t="inlineStr">
         <is>
           <t>Cash &amp; equivalents: year 4</t>
         </is>
       </c>
-      <c r="F166" s="42">
-        <f>F165+F156+F161</f>
-        <v/>
-      </c>
-      <c r="G166" s="42">
-        <f>G165+G156+G161</f>
-        <v/>
-      </c>
-      <c r="H166" s="42">
-        <f>H165+H156+H161</f>
-        <v/>
-      </c>
+      <c r="B166" s="154">
+        <f>B165+B156+B161</f>
+        <v/>
+      </c>
+      <c r="C166" s="154">
+        <f>C165+C156+C161</f>
+        <v/>
+      </c>
+      <c r="D166" s="154">
+        <f>D165+D156+D161</f>
+        <v/>
+      </c>
+      <c r="E166" s="138" t="n"/>
+      <c r="F166" s="138" t="n"/>
+      <c r="G166" s="42" t="n"/>
+      <c r="H166" s="42" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="41" t="inlineStr">
+      <c r="A167" s="153" t="inlineStr">
         <is>
           <t>Cash &amp; equivalents: year 5</t>
         </is>
       </c>
-      <c r="F167" s="42">
-        <f>F166+F157+F162</f>
-        <v/>
-      </c>
-      <c r="G167" s="42">
-        <f>G166+G157+G162</f>
-        <v/>
-      </c>
-      <c r="H167" s="42">
-        <f>H166+H157+H162</f>
-        <v/>
-      </c>
+      <c r="B167" s="154">
+        <f>B166+B157+B162</f>
+        <v/>
+      </c>
+      <c r="C167" s="154">
+        <f>C166+C157+C162</f>
+        <v/>
+      </c>
+      <c r="D167" s="154">
+        <f>D166+D157+D162</f>
+        <v/>
+      </c>
+      <c r="E167" s="138" t="n"/>
+      <c r="F167" s="138" t="n"/>
+      <c r="G167" s="42" t="n"/>
+      <c r="H167" s="42" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="41" t="inlineStr">
+      <c r="A168" s="153" t="inlineStr">
         <is>
           <t>Total assets: year 1</t>
         </is>
       </c>
-      <c r="F168" s="42">
-        <f>$B$194*F25/$B$198</f>
-        <v/>
-      </c>
-      <c r="G168" s="42">
-        <f>$B$194*G25/$B$198</f>
-        <v/>
-      </c>
-      <c r="H168" s="42">
-        <f>$B$194*H25/$B$198</f>
-        <v/>
-      </c>
+      <c r="B168" s="154">
+        <f>$B$194*B25/$B$198</f>
+        <v/>
+      </c>
+      <c r="C168" s="154">
+        <f>$B$194*C25/$B$198</f>
+        <v/>
+      </c>
+      <c r="D168" s="154">
+        <f>$B$194*D25/$B$198</f>
+        <v/>
+      </c>
+      <c r="E168" s="138" t="n"/>
+      <c r="F168" s="138" t="n"/>
+      <c r="G168" s="42" t="n"/>
+      <c r="H168" s="42" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="41" t="inlineStr">
+      <c r="A169" s="153" t="inlineStr">
         <is>
           <t>Total assets: year 2</t>
         </is>
       </c>
-      <c r="F169" s="42">
-        <f>$B$194*F26/$B$198</f>
-        <v/>
-      </c>
-      <c r="G169" s="42">
-        <f>$B$194*G26/$B$198</f>
-        <v/>
-      </c>
-      <c r="H169" s="42">
-        <f>$B$194*H26/$B$198</f>
-        <v/>
-      </c>
+      <c r="B169" s="154">
+        <f>$B$194*B26/$B$198</f>
+        <v/>
+      </c>
+      <c r="C169" s="154">
+        <f>$B$194*C26/$B$198</f>
+        <v/>
+      </c>
+      <c r="D169" s="154">
+        <f>$B$194*D26/$B$198</f>
+        <v/>
+      </c>
+      <c r="E169" s="138" t="n"/>
+      <c r="F169" s="138" t="n"/>
+      <c r="G169" s="42" t="n"/>
+      <c r="H169" s="42" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="41" t="inlineStr">
+      <c r="A170" s="153" t="inlineStr">
         <is>
           <t>Total assets: year 3</t>
         </is>
       </c>
-      <c r="F170" s="42">
-        <f>$B$194*F27/$B$198</f>
-        <v/>
-      </c>
-      <c r="G170" s="42">
-        <f>$B$194*G27/$B$198</f>
-        <v/>
-      </c>
-      <c r="H170" s="42">
-        <f>$B$194*H27/$B$198</f>
-        <v/>
-      </c>
+      <c r="B170" s="154">
+        <f>$B$194*B27/$B$198</f>
+        <v/>
+      </c>
+      <c r="C170" s="154">
+        <f>$B$194*C27/$B$198</f>
+        <v/>
+      </c>
+      <c r="D170" s="154">
+        <f>$B$194*D27/$B$198</f>
+        <v/>
+      </c>
+      <c r="E170" s="138" t="n"/>
+      <c r="F170" s="138" t="n"/>
+      <c r="G170" s="42" t="n"/>
+      <c r="H170" s="42" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="41" t="inlineStr">
+      <c r="A171" s="153" t="inlineStr">
         <is>
           <t>Total assets: year 4</t>
         </is>
       </c>
-      <c r="F171" s="42">
-        <f>$B$194*F28/$B$198</f>
-        <v/>
-      </c>
-      <c r="G171" s="42">
-        <f>$B$194*G28/$B$198</f>
-        <v/>
-      </c>
-      <c r="H171" s="42">
-        <f>$B$194*H28/$B$198</f>
-        <v/>
-      </c>
+      <c r="B171" s="154">
+        <f>$B$194*B28/$B$198</f>
+        <v/>
+      </c>
+      <c r="C171" s="154">
+        <f>$B$194*C28/$B$198</f>
+        <v/>
+      </c>
+      <c r="D171" s="154">
+        <f>$B$194*D28/$B$198</f>
+        <v/>
+      </c>
+      <c r="E171" s="138" t="n"/>
+      <c r="F171" s="138" t="n"/>
+      <c r="G171" s="42" t="n"/>
+      <c r="H171" s="42" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="41" t="inlineStr">
+      <c r="A172" s="153" t="inlineStr">
         <is>
           <t>Total assets: year 5</t>
         </is>
       </c>
-      <c r="F172" s="42">
-        <f>$B$194*F29/$B$198</f>
-        <v/>
-      </c>
-      <c r="G172" s="42">
-        <f>$B$194*G29/$B$198</f>
-        <v/>
-      </c>
-      <c r="H172" s="42">
-        <f>$B$194*H29/$B$198</f>
-        <v/>
-      </c>
+      <c r="B172" s="154">
+        <f>$B$194*B29/$B$198</f>
+        <v/>
+      </c>
+      <c r="C172" s="154">
+        <f>$B$194*C29/$B$198</f>
+        <v/>
+      </c>
+      <c r="D172" s="154">
+        <f>$B$194*D29/$B$198</f>
+        <v/>
+      </c>
+      <c r="E172" s="138" t="n"/>
+      <c r="F172" s="138" t="n"/>
+      <c r="G172" s="42" t="n"/>
+      <c r="H172" s="42" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="41" t="inlineStr">
+      <c r="A173" s="153" t="inlineStr">
         <is>
           <t>Total liabilities: year 1</t>
         </is>
       </c>
-      <c r="F173" s="42">
-        <f>$B$195*F25/$B$198</f>
-        <v/>
-      </c>
-      <c r="G173" s="42">
-        <f>$B$195*G25/$B$198</f>
-        <v/>
-      </c>
-      <c r="H173" s="42">
-        <f>$B$195*H25/$B$198</f>
-        <v/>
-      </c>
+      <c r="B173" s="154">
+        <f>$B$195*B25/$B$198</f>
+        <v/>
+      </c>
+      <c r="C173" s="154">
+        <f>$B$195*C25/$B$198</f>
+        <v/>
+      </c>
+      <c r="D173" s="154">
+        <f>$B$195*D25/$B$198</f>
+        <v/>
+      </c>
+      <c r="E173" s="138" t="n"/>
+      <c r="F173" s="138" t="n"/>
+      <c r="G173" s="42" t="n"/>
+      <c r="H173" s="42" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="41" t="inlineStr">
+      <c r="A174" s="153" t="inlineStr">
         <is>
           <t>Total liabilities: year 2</t>
         </is>
       </c>
-      <c r="F174" s="42">
-        <f>$B$195*F26/$B$198</f>
-        <v/>
-      </c>
-      <c r="G174" s="42">
-        <f>$B$195*G26/$B$198</f>
-        <v/>
-      </c>
-      <c r="H174" s="42">
-        <f>$B$195*H26/$B$198</f>
-        <v/>
-      </c>
+      <c r="B174" s="154">
+        <f>$B$195*B26/$B$198</f>
+        <v/>
+      </c>
+      <c r="C174" s="154">
+        <f>$B$195*C26/$B$198</f>
+        <v/>
+      </c>
+      <c r="D174" s="154">
+        <f>$B$195*D26/$B$198</f>
+        <v/>
+      </c>
+      <c r="E174" s="138" t="n"/>
+      <c r="F174" s="138" t="n"/>
+      <c r="G174" s="42" t="n"/>
+      <c r="H174" s="42" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="41" t="inlineStr">
+      <c r="A175" s="153" t="inlineStr">
         <is>
           <t>Total liabilities: year 3</t>
         </is>
       </c>
-      <c r="F175" s="42">
-        <f>$B$195*F27/$B$198</f>
-        <v/>
-      </c>
-      <c r="G175" s="42">
-        <f>$B$195*G27/$B$198</f>
-        <v/>
-      </c>
-      <c r="H175" s="42">
-        <f>$B$195*H27/$B$198</f>
-        <v/>
-      </c>
+      <c r="B175" s="154">
+        <f>$B$195*B27/$B$198</f>
+        <v/>
+      </c>
+      <c r="C175" s="154">
+        <f>$B$195*C27/$B$198</f>
+        <v/>
+      </c>
+      <c r="D175" s="154">
+        <f>$B$195*D27/$B$198</f>
+        <v/>
+      </c>
+      <c r="E175" s="138" t="n"/>
+      <c r="F175" s="138" t="n"/>
+      <c r="G175" s="42" t="n"/>
+      <c r="H175" s="42" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="41" t="inlineStr">
+      <c r="A176" s="153" t="inlineStr">
         <is>
           <t>Total liabilities: year 4</t>
         </is>
       </c>
-      <c r="F176" s="42">
-        <f>$B$195*F28/$B$198</f>
-        <v/>
-      </c>
-      <c r="G176" s="42">
-        <f>$B$195*G28/$B$198</f>
-        <v/>
-      </c>
-      <c r="H176" s="42">
-        <f>$B$195*H28/$B$198</f>
-        <v/>
-      </c>
+      <c r="B176" s="154">
+        <f>$B$195*B28/$B$198</f>
+        <v/>
+      </c>
+      <c r="C176" s="154">
+        <f>$B$195*C28/$B$198</f>
+        <v/>
+      </c>
+      <c r="D176" s="154">
+        <f>$B$195*D28/$B$198</f>
+        <v/>
+      </c>
+      <c r="E176" s="138" t="n"/>
+      <c r="F176" s="138" t="n"/>
+      <c r="G176" s="42" t="n"/>
+      <c r="H176" s="42" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="41" t="inlineStr">
+      <c r="A177" s="153" t="inlineStr">
         <is>
           <t>Total liabilities: year 5</t>
         </is>
       </c>
-      <c r="F177" s="42">
-        <f>$B$195*F29/$B$198</f>
-        <v/>
-      </c>
-      <c r="G177" s="42">
-        <f>$B$195*G29/$B$198</f>
-        <v/>
-      </c>
-      <c r="H177" s="42">
-        <f>$B$195*H29/$B$198</f>
-        <v/>
-      </c>
+      <c r="B177" s="154">
+        <f>$B$195*B29/$B$198</f>
+        <v/>
+      </c>
+      <c r="C177" s="154">
+        <f>$B$195*C29/$B$198</f>
+        <v/>
+      </c>
+      <c r="D177" s="154">
+        <f>$B$195*D29/$B$198</f>
+        <v/>
+      </c>
+      <c r="E177" s="138" t="n"/>
+      <c r="F177" s="138" t="n"/>
+      <c r="G177" s="42" t="n"/>
+      <c r="H177" s="42" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="41" t="inlineStr">
+      <c r="A178" s="153" t="inlineStr">
         <is>
           <t>Total equity: year 1</t>
         </is>
       </c>
-      <c r="F178" s="42">
-        <f>$B$196*F25/$B$198</f>
-        <v/>
-      </c>
-      <c r="G178" s="42">
-        <f>$B$196*G25/$B$198</f>
-        <v/>
-      </c>
-      <c r="H178" s="42">
-        <f>$B$196*H25/$B$198</f>
-        <v/>
-      </c>
+      <c r="B178" s="154">
+        <f>$B$196*B25/$B$198</f>
+        <v/>
+      </c>
+      <c r="C178" s="154">
+        <f>$B$196*C25/$B$198</f>
+        <v/>
+      </c>
+      <c r="D178" s="154">
+        <f>$B$196*D25/$B$198</f>
+        <v/>
+      </c>
+      <c r="E178" s="138" t="n"/>
+      <c r="F178" s="138" t="n"/>
+      <c r="G178" s="42" t="n"/>
+      <c r="H178" s="42" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="41" t="inlineStr">
+      <c r="A179" s="153" t="inlineStr">
         <is>
           <t>Total equity: year 2</t>
         </is>
       </c>
-      <c r="F179" s="42">
-        <f>$B$196*F26/$B$198</f>
-        <v/>
-      </c>
-      <c r="G179" s="42">
-        <f>$B$196*G26/$B$198</f>
-        <v/>
-      </c>
-      <c r="H179" s="42">
-        <f>$B$196*H26/$B$198</f>
-        <v/>
-      </c>
+      <c r="B179" s="154">
+        <f>$B$196*B26/$B$198</f>
+        <v/>
+      </c>
+      <c r="C179" s="154">
+        <f>$B$196*C26/$B$198</f>
+        <v/>
+      </c>
+      <c r="D179" s="154">
+        <f>$B$196*D26/$B$198</f>
+        <v/>
+      </c>
+      <c r="E179" s="138" t="n"/>
+      <c r="F179" s="138" t="n"/>
+      <c r="G179" s="42" t="n"/>
+      <c r="H179" s="42" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="41" t="inlineStr">
+      <c r="A180" s="153" t="inlineStr">
         <is>
           <t>Total equity: year 3</t>
         </is>
       </c>
-      <c r="F180" s="42">
-        <f>$B$196*F27/$B$198</f>
-        <v/>
-      </c>
-      <c r="G180" s="42">
-        <f>$B$196*G27/$B$198</f>
-        <v/>
-      </c>
-      <c r="H180" s="42">
-        <f>$B$196*H27/$B$198</f>
-        <v/>
-      </c>
+      <c r="B180" s="154">
+        <f>$B$196*B27/$B$198</f>
+        <v/>
+      </c>
+      <c r="C180" s="154">
+        <f>$B$196*C27/$B$198</f>
+        <v/>
+      </c>
+      <c r="D180" s="154">
+        <f>$B$196*D27/$B$198</f>
+        <v/>
+      </c>
+      <c r="E180" s="138" t="n"/>
+      <c r="F180" s="138" t="n"/>
+      <c r="G180" s="42" t="n"/>
+      <c r="H180" s="42" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="41" t="inlineStr">
+      <c r="A181" s="153" t="inlineStr">
         <is>
           <t>Total equity: year 4</t>
         </is>
       </c>
-      <c r="F181" s="42">
-        <f>$B$196*F28/$B$198</f>
-        <v/>
-      </c>
-      <c r="G181" s="42">
-        <f>$B$196*G28/$B$198</f>
-        <v/>
-      </c>
-      <c r="H181" s="42">
-        <f>$B$196*H28/$B$198</f>
-        <v/>
-      </c>
+      <c r="B181" s="154">
+        <f>$B$196*B28/$B$198</f>
+        <v/>
+      </c>
+      <c r="C181" s="154">
+        <f>$B$196*C28/$B$198</f>
+        <v/>
+      </c>
+      <c r="D181" s="154">
+        <f>$B$196*D28/$B$198</f>
+        <v/>
+      </c>
+      <c r="E181" s="138" t="n"/>
+      <c r="F181" s="138" t="n"/>
+      <c r="G181" s="42" t="n"/>
+      <c r="H181" s="42" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="41" t="inlineStr">
+      <c r="A182" s="153" t="inlineStr">
         <is>
           <t>Total equity: year 5</t>
         </is>
       </c>
-      <c r="F182" s="42">
-        <f>$B$196*F29/$B$198</f>
-        <v/>
-      </c>
-      <c r="G182" s="42">
-        <f>$B$196*G29/$B$198</f>
-        <v/>
-      </c>
-      <c r="H182" s="42">
-        <f>$B$196*H29/$B$198</f>
-        <v/>
-      </c>
+      <c r="B182" s="154">
+        <f>$B$196*B29/$B$198</f>
+        <v/>
+      </c>
+      <c r="C182" s="154">
+        <f>$B$196*C29/$B$198</f>
+        <v/>
+      </c>
+      <c r="D182" s="154">
+        <f>$B$196*D29/$B$198</f>
+        <v/>
+      </c>
+      <c r="E182" s="138" t="n"/>
+      <c r="F182" s="138" t="n"/>
+      <c r="G182" s="42" t="n"/>
+      <c r="H182" s="42" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="41" t="inlineStr">
+      <c r="A183" s="153" t="inlineStr">
         <is>
           <t>Diluted shares (000): year 1</t>
         </is>
       </c>
-      <c r="F183" s="42">
-        <f>$B$197-F21/100</f>
-        <v/>
-      </c>
-      <c r="G183" s="42">
-        <f>$B$197-G21/100</f>
-        <v/>
-      </c>
-      <c r="H183" s="42">
-        <f>$B$197-H22*H153/100</f>
-        <v/>
-      </c>
+      <c r="B183" s="154">
+        <f>$B$197-B21/100</f>
+        <v/>
+      </c>
+      <c r="C183" s="154">
+        <f>$B$197-C21/100</f>
+        <v/>
+      </c>
+      <c r="D183" s="154">
+        <f>$B$197-D22*D153/100</f>
+        <v/>
+      </c>
+      <c r="E183" s="138" t="n"/>
+      <c r="F183" s="138" t="n"/>
+      <c r="G183" s="42" t="n"/>
+      <c r="H183" s="42" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="41" t="inlineStr">
+      <c r="A184" s="153" t="inlineStr">
         <is>
           <t>Diluted shares (000): year 2</t>
         </is>
       </c>
-      <c r="F184" s="42">
-        <f>F183-F21/108</f>
-        <v/>
-      </c>
-      <c r="G184" s="42">
-        <f>G183-G21/108</f>
-        <v/>
-      </c>
-      <c r="H184" s="42">
-        <f>H183-H22*H154/108</f>
-        <v/>
-      </c>
+      <c r="B184" s="154">
+        <f>B183-B21/108</f>
+        <v/>
+      </c>
+      <c r="C184" s="154">
+        <f>C183-C21/108</f>
+        <v/>
+      </c>
+      <c r="D184" s="154">
+        <f>D183-D22*D154/108</f>
+        <v/>
+      </c>
+      <c r="E184" s="138" t="n"/>
+      <c r="F184" s="138" t="n"/>
+      <c r="G184" s="42" t="n"/>
+      <c r="H184" s="42" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="41" t="inlineStr">
+      <c r="A185" s="153" t="inlineStr">
         <is>
           <t>Diluted shares (000): year 3</t>
         </is>
       </c>
-      <c r="F185" s="42">
-        <f>F184-F21/115</f>
-        <v/>
-      </c>
-      <c r="G185" s="42">
-        <f>G184-G21/115</f>
-        <v/>
-      </c>
-      <c r="H185" s="42">
-        <f>H184-H22*H155/115</f>
-        <v/>
-      </c>
+      <c r="B185" s="154">
+        <f>B184-B21/115</f>
+        <v/>
+      </c>
+      <c r="C185" s="154">
+        <f>C184-C21/115</f>
+        <v/>
+      </c>
+      <c r="D185" s="154">
+        <f>D184-D22*D155/115</f>
+        <v/>
+      </c>
+      <c r="E185" s="138" t="n"/>
+      <c r="F185" s="138" t="n"/>
+      <c r="G185" s="42" t="n"/>
+      <c r="H185" s="42" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="41" t="inlineStr">
+      <c r="A186" s="153" t="inlineStr">
         <is>
           <t>Diluted shares (000): year 4</t>
         </is>
       </c>
-      <c r="F186" s="42">
-        <f>F185-F21/122</f>
-        <v/>
-      </c>
-      <c r="G186" s="42">
-        <f>G185-G21/122</f>
-        <v/>
-      </c>
-      <c r="H186" s="42">
-        <f>H185-H22*H156/122</f>
-        <v/>
-      </c>
+      <c r="B186" s="154">
+        <f>B185-B21/122</f>
+        <v/>
+      </c>
+      <c r="C186" s="154">
+        <f>C185-C21/122</f>
+        <v/>
+      </c>
+      <c r="D186" s="154">
+        <f>D185-D22*D156/122</f>
+        <v/>
+      </c>
+      <c r="E186" s="138" t="n"/>
+      <c r="F186" s="138" t="n"/>
+      <c r="G186" s="42" t="n"/>
+      <c r="H186" s="42" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="41" t="inlineStr">
+      <c r="A187" s="153" t="inlineStr">
         <is>
           <t>Diluted shares (000): year 5</t>
         </is>
       </c>
-      <c r="F187" s="42">
-        <f>F186-F21/130</f>
-        <v/>
-      </c>
-      <c r="G187" s="42">
-        <f>G186-G21/130</f>
-        <v/>
-      </c>
-      <c r="H187" s="42">
-        <f>H186-H22*H157/130</f>
-        <v/>
-      </c>
+      <c r="B187" s="154">
+        <f>B186-B21/130</f>
+        <v/>
+      </c>
+      <c r="C187" s="154">
+        <f>C186-C21/130</f>
+        <v/>
+      </c>
+      <c r="D187" s="154">
+        <f>D186-D22*D157/130</f>
+        <v/>
+      </c>
+      <c r="E187" s="138" t="n"/>
+      <c r="F187" s="138" t="n"/>
+      <c r="G187" s="42" t="n"/>
+      <c r="H187" s="42" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="41" t="inlineStr">
+      <c r="A188" s="153" t="inlineStr">
         <is>
           <t>Diluted EPS ($): year 1</t>
         </is>
       </c>
-      <c r="F188" s="49">
-        <f>F143/F183</f>
-        <v/>
-      </c>
-      <c r="G188" s="49">
-        <f>G143/G183</f>
-        <v/>
-      </c>
-      <c r="H188" s="49">
-        <f>H143/H183</f>
-        <v/>
-      </c>
+      <c r="B188" s="164">
+        <f>B143/B183</f>
+        <v/>
+      </c>
+      <c r="C188" s="164">
+        <f>C143/C183</f>
+        <v/>
+      </c>
+      <c r="D188" s="164">
+        <f>D143/D183</f>
+        <v/>
+      </c>
+      <c r="E188" s="138" t="n"/>
+      <c r="F188" s="138" t="n"/>
+      <c r="G188" s="49" t="n"/>
+      <c r="H188" s="49" t="n"/>
     </row>
     <row r="189">
-      <c r="A189" s="41" t="inlineStr">
+      <c r="A189" s="153" t="inlineStr">
         <is>
           <t>Diluted EPS ($): year 2</t>
         </is>
       </c>
-      <c r="F189" s="49">
-        <f>F144/F184</f>
-        <v/>
-      </c>
-      <c r="G189" s="49">
-        <f>G144/G184</f>
-        <v/>
-      </c>
-      <c r="H189" s="49">
-        <f>H144/H184</f>
-        <v/>
-      </c>
+      <c r="B189" s="164">
+        <f>B144/B184</f>
+        <v/>
+      </c>
+      <c r="C189" s="164">
+        <f>C144/C184</f>
+        <v/>
+      </c>
+      <c r="D189" s="164">
+        <f>D144/D184</f>
+        <v/>
+      </c>
+      <c r="E189" s="138" t="n"/>
+      <c r="F189" s="138" t="n"/>
+      <c r="G189" s="49" t="n"/>
+      <c r="H189" s="49" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="41" t="inlineStr">
+      <c r="A190" s="153" t="inlineStr">
         <is>
           <t>Diluted EPS ($): year 3</t>
         </is>
       </c>
-      <c r="F190" s="49">
-        <f>F145/F185</f>
-        <v/>
-      </c>
-      <c r="G190" s="49">
-        <f>G145/G185</f>
-        <v/>
-      </c>
-      <c r="H190" s="49">
-        <f>H145/H185</f>
-        <v/>
-      </c>
+      <c r="B190" s="164">
+        <f>B145/B185</f>
+        <v/>
+      </c>
+      <c r="C190" s="164">
+        <f>C145/C185</f>
+        <v/>
+      </c>
+      <c r="D190" s="164">
+        <f>D145/D185</f>
+        <v/>
+      </c>
+      <c r="E190" s="138" t="n"/>
+      <c r="F190" s="138" t="n"/>
+      <c r="G190" s="49" t="n"/>
+      <c r="H190" s="49" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="41" t="inlineStr">
+      <c r="A191" s="153" t="inlineStr">
         <is>
           <t>Diluted EPS ($): year 4</t>
         </is>
       </c>
-      <c r="F191" s="49">
-        <f>F146/F186</f>
-        <v/>
-      </c>
-      <c r="G191" s="49">
-        <f>G146/G186</f>
-        <v/>
-      </c>
-      <c r="H191" s="49">
-        <f>H146/H186</f>
-        <v/>
-      </c>
+      <c r="B191" s="164">
+        <f>B146/B186</f>
+        <v/>
+      </c>
+      <c r="C191" s="164">
+        <f>C146/C186</f>
+        <v/>
+      </c>
+      <c r="D191" s="164">
+        <f>D146/D186</f>
+        <v/>
+      </c>
+      <c r="E191" s="138" t="n"/>
+      <c r="F191" s="138" t="n"/>
+      <c r="G191" s="49" t="n"/>
+      <c r="H191" s="49" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="41" t="inlineStr">
+      <c r="A192" s="153" t="inlineStr">
         <is>
           <t>Diluted EPS ($): year 5</t>
         </is>
       </c>
-      <c r="F192" s="49">
-        <f>F147/F187</f>
-        <v/>
-      </c>
-      <c r="G192" s="49">
-        <f>G147/G187</f>
-        <v/>
-      </c>
-      <c r="H192" s="49">
-        <f>H147/H187</f>
-        <v/>
-      </c>
+      <c r="B192" s="164">
+        <f>B147/B187</f>
+        <v/>
+      </c>
+      <c r="C192" s="164">
+        <f>C147/C187</f>
+        <v/>
+      </c>
+      <c r="D192" s="164">
+        <f>D147/D187</f>
+        <v/>
+      </c>
+      <c r="E192" s="138" t="n"/>
+      <c r="F192" s="138" t="n"/>
+      <c r="G192" s="49" t="n"/>
+      <c r="H192" s="49" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="26" t="inlineStr">
+      <c r="A193" s="163" t="inlineStr">
         <is>
           <t>FY25 anchors (drivers — do not edit without source)</t>
         </is>
       </c>
+      <c r="B193" s="138" t="n"/>
+      <c r="C193" s="138" t="n"/>
+      <c r="D193" s="138" t="n"/>
+      <c r="E193" s="138" t="n"/>
+      <c r="F193" s="138" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="138" t="inlineStr">
         <is>
           <t>FY25 total assets ($000)</t>
         </is>
       </c>
-      <c r="B194" t="n">
+      <c r="B194" s="168" t="n">
         <v>8456743</v>
       </c>
+      <c r="C194" s="138" t="n"/>
+      <c r="D194" s="138" t="n"/>
+      <c r="E194" s="138" t="n"/>
+      <c r="F194" s="138" t="n">
+        <v>8456743</v>
+      </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="138" t="inlineStr">
         <is>
           <t>FY25 total liabilities ($000)</t>
         </is>
       </c>
-      <c r="B195" t="n">
+      <c r="B195" s="168" t="n">
         <v>3494903</v>
       </c>
+      <c r="C195" s="138" t="n"/>
+      <c r="D195" s="138" t="n"/>
+      <c r="E195" s="138" t="n"/>
+      <c r="F195" s="138" t="n">
+        <v>3494903</v>
+      </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="138" t="inlineStr">
         <is>
           <t>FY25 total equity ($000)</t>
         </is>
       </c>
-      <c r="B196" t="n">
+      <c r="B196" s="168" t="n">
         <v>4961840</v>
       </c>
+      <c r="C196" s="138" t="n"/>
+      <c r="D196" s="138" t="n"/>
+      <c r="E196" s="138" t="n"/>
+      <c r="F196" s="138" t="n">
+        <v>4961840</v>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="138" t="inlineStr">
         <is>
           <t>FY25 diluted shares (000)</t>
         </is>
       </c>
-      <c r="B197" t="n">
+      <c r="B197" s="168" t="n">
         <v>119068</v>
       </c>
+      <c r="C197" s="138" t="n"/>
+      <c r="D197" s="138" t="n"/>
+      <c r="E197" s="138" t="n"/>
+      <c r="F197" s="138" t="n">
+        <v>119068</v>
+      </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="138" t="inlineStr">
         <is>
           <t>FY25 net revenue ($000)</t>
         </is>
       </c>
-      <c r="B198" t="n">
+      <c r="B198" s="168" t="n">
         <v>11102600</v>
       </c>
-    </row>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
+      <c r="C198" s="138" t="n"/>
+      <c r="D198" s="138" t="n"/>
+      <c r="E198" s="138" t="n"/>
+      <c r="F198" s="138" t="n">
+        <v>11102600</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="138" t="n"/>
+      <c r="B199" s="138" t="n"/>
+      <c r="C199" s="138" t="n"/>
+      <c r="D199" s="138" t="n"/>
+      <c r="E199" s="138" t="n"/>
+      <c r="F199" s="138" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="138" t="n"/>
+      <c r="B200" s="138" t="n"/>
+      <c r="C200" s="138" t="n"/>
+      <c r="D200" s="138" t="n"/>
+      <c r="E200" s="138" t="n"/>
+      <c r="F200" s="138" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="138" t="n"/>
+      <c r="B201" s="138" t="n"/>
+      <c r="C201" s="138" t="n"/>
+      <c r="D201" s="138" t="n"/>
+      <c r="E201" s="138" t="n"/>
+      <c r="F201" s="138" t="n"/>
+    </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="138" t="inlineStr">
         <is>
           <t>FY25 stock-based compensation ($000)</t>
         </is>
       </c>
-      <c r="B202" t="n">
+      <c r="B202" s="168" t="n">
         <v>62203</v>
       </c>
+      <c r="C202" s="138" t="n"/>
+      <c r="D202" s="138" t="n"/>
+      <c r="E202" s="138" t="n"/>
+      <c r="F202" s="138" t="n">
+        <v>62203</v>
+      </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="138" t="inlineStr">
         <is>
           <t>FY25 implied lease interest ($000)</t>
         </is>
       </c>
-      <c r="B203" t="n">
+      <c r="B203" s="168" t="n">
+        <v>1028</v>
+      </c>
+      <c r="C203" s="138" t="n"/>
+      <c r="D203" s="138" t="n"/>
+      <c r="E203" s="138" t="n"/>
+      <c r="F203" s="138" t="n">
         <v>1028</v>
       </c>
     </row>
@@ -7524,23 +8410,23 @@
         <v>11102600</v>
       </c>
       <c r="C56" s="42">
-        <f>Scenarios!G25</f>
+        <f>Scenarios!$C$25</f>
         <v/>
       </c>
       <c r="D56" s="42">
-        <f>Scenarios!G26</f>
+        <f>Scenarios!$C$26</f>
         <v/>
       </c>
       <c r="E56" s="42">
-        <f>Scenarios!G27</f>
+        <f>Scenarios!$C$27</f>
         <v/>
       </c>
       <c r="F56" s="42">
-        <f>Scenarios!G28</f>
+        <f>Scenarios!$C$28</f>
         <v/>
       </c>
       <c r="G56" s="42">
-        <f>Scenarios!G29</f>
+        <f>Scenarios!$C$29</f>
         <v/>
       </c>
       <c r="I56" s="17" t="n"/>
@@ -7823,23 +8709,23 @@
         <v>11102600</v>
       </c>
       <c r="F5" s="75">
-        <f>Scenarios!G25</f>
+        <f>Scenarios!$C$25</f>
         <v/>
       </c>
       <c r="G5" s="75">
-        <f>Scenarios!G26</f>
+        <f>Scenarios!$C$26</f>
         <v/>
       </c>
       <c r="H5" s="75">
-        <f>Scenarios!G27</f>
+        <f>Scenarios!$C$27</f>
         <v/>
       </c>
       <c r="I5" s="75">
-        <f>Scenarios!G28</f>
+        <f>Scenarios!$C$28</f>
         <v/>
       </c>
       <c r="J5" s="75">
-        <f>Scenarios!G29</f>
+        <f>Scenarios!$C$29</f>
         <v/>
       </c>
     </row>
@@ -7895,23 +8781,23 @@
         <v/>
       </c>
       <c r="F7" s="20">
-        <f>Scenarios!$G$14</f>
+        <f>Scenarios!$C$14</f>
         <v/>
       </c>
       <c r="G7" s="20">
-        <f>Scenarios!$G$14</f>
+        <f>Scenarios!$C$14</f>
         <v/>
       </c>
       <c r="H7" s="20">
-        <f>Scenarios!$G$14</f>
+        <f>Scenarios!$C$14</f>
         <v/>
       </c>
       <c r="I7" s="20">
-        <f>Scenarios!$G$14</f>
+        <f>Scenarios!$C$14</f>
         <v/>
       </c>
       <c r="J7" s="20">
-        <f>Scenarios!$G$14</f>
+        <f>Scenarios!$C$14</f>
         <v/>
       </c>
     </row>
@@ -7925,23 +8811,23 @@
         <v>4818468</v>
       </c>
       <c r="F8" s="75">
-        <f>Scenarios!G35</f>
+        <f>Scenarios!$C$35</f>
         <v/>
       </c>
       <c r="G8" s="75">
-        <f>Scenarios!G36</f>
+        <f>Scenarios!$C$36</f>
         <v/>
       </c>
       <c r="H8" s="75">
-        <f>Scenarios!G37</f>
+        <f>Scenarios!$C$37</f>
         <v/>
       </c>
       <c r="I8" s="75">
-        <f>Scenarios!G38</f>
+        <f>Scenarios!$C$38</f>
         <v/>
       </c>
       <c r="J8" s="75">
-        <f>Scenarios!G39</f>
+        <f>Scenarios!$C$39</f>
         <v/>
       </c>
     </row>
@@ -7959,23 +8845,23 @@
       </c>
       <c r="D9" s="19" t="n"/>
       <c r="F9" s="32">
-        <f>Scenarios!G40</f>
+        <f>Scenarios!$C$40</f>
         <v/>
       </c>
       <c r="G9" s="32">
-        <f>Scenarios!G41</f>
+        <f>Scenarios!$C$41</f>
         <v/>
       </c>
       <c r="H9" s="32">
-        <f>Scenarios!G42</f>
+        <f>Scenarios!$C$42</f>
         <v/>
       </c>
       <c r="I9" s="32">
-        <f>Scenarios!G43</f>
+        <f>Scenarios!$C$43</f>
         <v/>
       </c>
       <c r="J9" s="32">
-        <f>Scenarios!G44</f>
+        <f>Scenarios!$C$44</f>
         <v/>
       </c>
     </row>
@@ -7996,7 +8882,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="37">
-        <f>Scenarios!$G$7</f>
+        <f>Scenarios!$C$7</f>
         <v/>
       </c>
       <c r="G10" s="37" t="n">
@@ -8022,23 +8908,23 @@
         <v>2210615</v>
       </c>
       <c r="F11" s="25">
-        <f>Scenarios!G45</f>
+        <f>Scenarios!$C$45</f>
         <v/>
       </c>
       <c r="G11" s="25">
-        <f>Scenarios!G46</f>
+        <f>Scenarios!$C$46</f>
         <v/>
       </c>
       <c r="H11" s="25">
-        <f>Scenarios!G47</f>
+        <f>Scenarios!$C$47</f>
         <v/>
       </c>
       <c r="I11" s="25">
-        <f>Scenarios!G48</f>
+        <f>Scenarios!$C$48</f>
         <v/>
       </c>
       <c r="J11" s="25">
-        <f>Scenarios!G49</f>
+        <f>Scenarios!$C$49</f>
         <v/>
       </c>
     </row>
@@ -8080,23 +8966,23 @@
         </is>
       </c>
       <c r="F13" s="75">
-        <f>-F11*Scenarios!$G$11</f>
+        <f>-F11*Scenarios!$C$11</f>
         <v/>
       </c>
       <c r="G13" s="75">
-        <f>-G11*Scenarios!$G$11</f>
+        <f>-G11*Scenarios!$C$11</f>
         <v/>
       </c>
       <c r="H13" s="75">
-        <f>-H11*Scenarios!$G$11</f>
+        <f>-H11*Scenarios!$C$11</f>
         <v/>
       </c>
       <c r="I13" s="75">
-        <f>-I11*Scenarios!$G$11</f>
+        <f>-I11*Scenarios!$C$11</f>
         <v/>
       </c>
       <c r="J13" s="75">
-        <f>-J11*Scenarios!$G$11</f>
+        <f>-J11*Scenarios!$C$11</f>
         <v/>
       </c>
     </row>
@@ -8107,23 +8993,23 @@
         </is>
       </c>
       <c r="F14" s="25">
-        <f>Scenarios!G50</f>
+        <f>Scenarios!$C$50</f>
         <v/>
       </c>
       <c r="G14" s="25">
-        <f>Scenarios!G51</f>
+        <f>Scenarios!$C$51</f>
         <v/>
       </c>
       <c r="H14" s="25">
-        <f>Scenarios!G52</f>
+        <f>Scenarios!$C$52</f>
         <v/>
       </c>
       <c r="I14" s="25">
-        <f>Scenarios!G53</f>
+        <f>Scenarios!$C$53</f>
         <v/>
       </c>
       <c r="J14" s="25">
-        <f>Scenarios!G54</f>
+        <f>Scenarios!$C$54</f>
         <v/>
       </c>
     </row>
@@ -8141,23 +9027,23 @@
       </c>
       <c r="D15" s="19" t="n"/>
       <c r="F15" s="20">
-        <f>Scenarios!$G$12</f>
+        <f>Scenarios!$C$12</f>
         <v/>
       </c>
       <c r="G15" s="20">
-        <f>Scenarios!$G$12</f>
+        <f>Scenarios!$C$12</f>
         <v/>
       </c>
       <c r="H15" s="20">
-        <f>Scenarios!$G$12</f>
+        <f>Scenarios!$C$12</f>
         <v/>
       </c>
       <c r="I15" s="20">
-        <f>Scenarios!$G$12</f>
+        <f>Scenarios!$C$12</f>
         <v/>
       </c>
       <c r="J15" s="20">
-        <f>Scenarios!$G$12</f>
+        <f>Scenarios!$C$12</f>
         <v/>
       </c>
     </row>
@@ -8168,23 +9054,23 @@
         </is>
       </c>
       <c r="F16" s="75">
-        <f>Scenarios!G55</f>
+        <f>Scenarios!$C$55</f>
         <v/>
       </c>
       <c r="G16" s="75">
-        <f>Scenarios!G56</f>
+        <f>Scenarios!$C$56</f>
         <v/>
       </c>
       <c r="H16" s="75">
-        <f>Scenarios!G57</f>
+        <f>Scenarios!$C$57</f>
         <v/>
       </c>
       <c r="I16" s="75">
-        <f>Scenarios!G58</f>
+        <f>Scenarios!$C$58</f>
         <v/>
       </c>
       <c r="J16" s="75">
-        <f>Scenarios!G59</f>
+        <f>Scenarios!$C$59</f>
         <v/>
       </c>
     </row>
@@ -8202,23 +9088,23 @@
       </c>
       <c r="D17" s="19" t="n"/>
       <c r="F17" s="20">
-        <f>Scenarios!$G$13</f>
+        <f>Scenarios!$C$13</f>
         <v/>
       </c>
       <c r="G17" s="20">
-        <f>Scenarios!$G$13</f>
+        <f>Scenarios!$C$13</f>
         <v/>
       </c>
       <c r="H17" s="20">
-        <f>Scenarios!$G$13</f>
+        <f>Scenarios!$C$13</f>
         <v/>
       </c>
       <c r="I17" s="20">
-        <f>Scenarios!$G$13</f>
+        <f>Scenarios!$C$13</f>
         <v/>
       </c>
       <c r="J17" s="20">
-        <f>Scenarios!$G$13</f>
+        <f>Scenarios!$C$13</f>
         <v/>
       </c>
     </row>
@@ -8229,23 +9115,23 @@
         </is>
       </c>
       <c r="F18" s="75">
-        <f>-Scenarios!G60</f>
+        <f>-Scenarios!$C$60</f>
         <v/>
       </c>
       <c r="G18" s="75">
-        <f>-Scenarios!G61</f>
+        <f>-Scenarios!$C$61</f>
         <v/>
       </c>
       <c r="H18" s="75">
-        <f>-Scenarios!G62</f>
+        <f>-Scenarios!$C$62</f>
         <v/>
       </c>
       <c r="I18" s="75">
-        <f>-Scenarios!G63</f>
+        <f>-Scenarios!$C$63</f>
         <v/>
       </c>
       <c r="J18" s="75">
-        <f>-Scenarios!G64</f>
+        <f>-Scenarios!$C$64</f>
         <v/>
       </c>
     </row>
@@ -8274,23 +9160,23 @@
         <v/>
       </c>
       <c r="F20" s="28">
-        <f>Scenarios!G65</f>
+        <f>Scenarios!$C$65</f>
         <v/>
       </c>
       <c r="G20" s="28">
-        <f>Scenarios!G66</f>
+        <f>Scenarios!$C$66</f>
         <v/>
       </c>
       <c r="H20" s="28">
-        <f>Scenarios!G67</f>
+        <f>Scenarios!$C$67</f>
         <v/>
       </c>
       <c r="I20" s="28">
-        <f>Scenarios!G68</f>
+        <f>Scenarios!$C$68</f>
         <v/>
       </c>
       <c r="J20" s="28">
-        <f>Scenarios!G69</f>
+        <f>Scenarios!$C$69</f>
         <v/>
       </c>
     </row>
@@ -8311,23 +9197,23 @@
         <v>190657</v>
       </c>
       <c r="F21" s="75">
-        <f>Scenarios!G70</f>
+        <f>Scenarios!$C$70</f>
         <v/>
       </c>
       <c r="G21" s="75">
-        <f>Scenarios!G71</f>
+        <f>Scenarios!$C$71</f>
         <v/>
       </c>
       <c r="H21" s="75">
-        <f>Scenarios!G72</f>
+        <f>Scenarios!$C$72</f>
         <v/>
       </c>
       <c r="I21" s="75">
-        <f>Scenarios!G73</f>
+        <f>Scenarios!$C$73</f>
         <v/>
       </c>
       <c r="J21" s="75">
-        <f>Scenarios!G74</f>
+        <f>Scenarios!$C$74</f>
         <v/>
       </c>
     </row>
@@ -8349,23 +9235,23 @@
         <v/>
       </c>
       <c r="F22" s="28">
-        <f>Scenarios!G75</f>
+        <f>Scenarios!$C$75</f>
         <v/>
       </c>
       <c r="G22" s="28">
-        <f>Scenarios!G76</f>
+        <f>Scenarios!$C$76</f>
         <v/>
       </c>
       <c r="H22" s="28">
-        <f>Scenarios!G77</f>
+        <f>Scenarios!$C$77</f>
         <v/>
       </c>
       <c r="I22" s="28">
-        <f>Scenarios!G78</f>
+        <f>Scenarios!$C$78</f>
         <v/>
       </c>
       <c r="J22" s="28">
-        <f>Scenarios!G79</f>
+        <f>Scenarios!$C$79</f>
         <v/>
       </c>
     </row>
@@ -8386,23 +9272,23 @@
         <v>1700753</v>
       </c>
       <c r="F23" s="75">
-        <f>Scenarios!G80</f>
+        <f>Scenarios!$C$80</f>
         <v/>
       </c>
       <c r="G23" s="75">
-        <f>Scenarios!G81</f>
+        <f>Scenarios!$C$81</f>
         <v/>
       </c>
       <c r="H23" s="75">
-        <f>Scenarios!G82</f>
+        <f>Scenarios!$C$82</f>
         <v/>
       </c>
       <c r="I23" s="75">
-        <f>Scenarios!G83</f>
+        <f>Scenarios!$C$83</f>
         <v/>
       </c>
       <c r="J23" s="75">
-        <f>Scenarios!G84</f>
+        <f>Scenarios!$C$84</f>
         <v/>
       </c>
     </row>
@@ -8424,23 +9310,23 @@
         <v/>
       </c>
       <c r="F24" s="28">
-        <f>Scenarios!G85</f>
+        <f>Scenarios!$C$85</f>
         <v/>
       </c>
       <c r="G24" s="28">
-        <f>Scenarios!G86</f>
+        <f>Scenarios!$C$86</f>
         <v/>
       </c>
       <c r="H24" s="28">
-        <f>Scenarios!G87</f>
+        <f>Scenarios!$C$87</f>
         <v/>
       </c>
       <c r="I24" s="28">
-        <f>Scenarios!G88</f>
+        <f>Scenarios!$C$88</f>
         <v/>
       </c>
       <c r="J24" s="28">
-        <f>Scenarios!G89</f>
+        <f>Scenarios!$C$89</f>
         <v/>
       </c>
     </row>
@@ -8461,23 +9347,23 @@
         <v>331421</v>
       </c>
       <c r="F25" s="75">
-        <f>Scenarios!G90</f>
+        <f>Scenarios!$C$90</f>
         <v/>
       </c>
       <c r="G25" s="75">
-        <f>Scenarios!G91</f>
+        <f>Scenarios!$C$91</f>
         <v/>
       </c>
       <c r="H25" s="75">
-        <f>Scenarios!G92</f>
+        <f>Scenarios!$C$92</f>
         <v/>
       </c>
       <c r="I25" s="75">
-        <f>Scenarios!G93</f>
+        <f>Scenarios!$C$93</f>
         <v/>
       </c>
       <c r="J25" s="75">
-        <f>Scenarios!G94</f>
+        <f>Scenarios!$C$94</f>
         <v/>
       </c>
     </row>
@@ -8499,23 +9385,23 @@
         <v/>
       </c>
       <c r="F26" s="20">
-        <f>Scenarios!$G$19</f>
+        <f>Scenarios!$C$19</f>
         <v/>
       </c>
       <c r="G26" s="20">
-        <f>Scenarios!$G$19</f>
+        <f>Scenarios!$C$19</f>
         <v/>
       </c>
       <c r="H26" s="20">
-        <f>Scenarios!$G$19</f>
+        <f>Scenarios!$C$19</f>
         <v/>
       </c>
       <c r="I26" s="20">
-        <f>Scenarios!$G$19</f>
+        <f>Scenarios!$C$19</f>
         <v/>
       </c>
       <c r="J26" s="20">
-        <f>Scenarios!$G$19</f>
+        <f>Scenarios!$C$19</f>
         <v/>
       </c>
     </row>
@@ -8536,23 +9422,23 @@
         <v>564089</v>
       </c>
       <c r="F27" s="75">
-        <f>Scenarios!G95</f>
+        <f>Scenarios!$C$95</f>
         <v/>
       </c>
       <c r="G27" s="75">
-        <f>Scenarios!G96</f>
+        <f>Scenarios!$C$96</f>
         <v/>
       </c>
       <c r="H27" s="75">
-        <f>Scenarios!G97</f>
+        <f>Scenarios!$C$97</f>
         <v/>
       </c>
       <c r="I27" s="75">
-        <f>Scenarios!G98</f>
+        <f>Scenarios!$C$98</f>
         <v/>
       </c>
       <c r="J27" s="75">
-        <f>Scenarios!G99</f>
+        <f>Scenarios!$C$99</f>
         <v/>
       </c>
     </row>
@@ -8574,23 +9460,23 @@
         <v/>
       </c>
       <c r="F28" s="20">
-        <f>Scenarios!$G$20</f>
+        <f>Scenarios!$C$20</f>
         <v/>
       </c>
       <c r="G28" s="20">
-        <f>Scenarios!$G$20</f>
+        <f>Scenarios!$C$20</f>
         <v/>
       </c>
       <c r="H28" s="20">
-        <f>Scenarios!$G$20</f>
+        <f>Scenarios!$C$20</f>
         <v/>
       </c>
       <c r="I28" s="20">
-        <f>Scenarios!$G$20</f>
+        <f>Scenarios!$C$20</f>
         <v/>
       </c>
       <c r="J28" s="20">
-        <f>Scenarios!$G$20</f>
+        <f>Scenarios!$C$20</f>
         <v/>
       </c>
     </row>
@@ -8611,23 +9497,23 @@
         <v>662982</v>
       </c>
       <c r="F29" s="75">
-        <f>Scenarios!G100</f>
+        <f>Scenarios!$C$100</f>
         <v/>
       </c>
       <c r="G29" s="75">
-        <f>Scenarios!G101</f>
+        <f>Scenarios!$C$101</f>
         <v/>
       </c>
       <c r="H29" s="75">
-        <f>Scenarios!G102</f>
+        <f>Scenarios!$C$102</f>
         <v/>
       </c>
       <c r="I29" s="75">
-        <f>Scenarios!G103</f>
+        <f>Scenarios!$C$103</f>
         <v/>
       </c>
       <c r="J29" s="75">
-        <f>Scenarios!G104</f>
+        <f>Scenarios!$C$104</f>
         <v/>
       </c>
     </row>
@@ -8645,23 +9531,23 @@
       </c>
       <c r="D30" s="19" t="n"/>
       <c r="F30" s="75">
-        <f>Scenarios!G105</f>
+        <f>Scenarios!$C$105</f>
         <v/>
       </c>
       <c r="G30" s="75">
-        <f>Scenarios!G106</f>
+        <f>Scenarios!$C$106</f>
         <v/>
       </c>
       <c r="H30" s="75">
-        <f>Scenarios!G107</f>
+        <f>Scenarios!$C$107</f>
         <v/>
       </c>
       <c r="I30" s="75">
-        <f>Scenarios!G108</f>
+        <f>Scenarios!$C$108</f>
         <v/>
       </c>
       <c r="J30" s="75">
-        <f>Scenarios!G109</f>
+        <f>Scenarios!$C$109</f>
         <v/>
       </c>
     </row>
@@ -8679,23 +9565,23 @@
       </c>
       <c r="D31" s="19" t="n"/>
       <c r="F31" s="75">
-        <f>Scenarios!G110</f>
+        <f>Scenarios!$C$110</f>
         <v/>
       </c>
       <c r="G31" s="75">
-        <f>Scenarios!G111</f>
+        <f>Scenarios!$C$111</f>
         <v/>
       </c>
       <c r="H31" s="75">
-        <f>Scenarios!G112</f>
+        <f>Scenarios!$C$112</f>
         <v/>
       </c>
       <c r="I31" s="75">
-        <f>Scenarios!G113</f>
+        <f>Scenarios!$C$113</f>
         <v/>
       </c>
       <c r="J31" s="75">
-        <f>Scenarios!G114</f>
+        <f>Scenarios!$C$114</f>
         <v/>
       </c>
     </row>
@@ -8716,23 +9602,23 @@
         <v>1461096</v>
       </c>
       <c r="F32" s="25">
-        <f>Scenarios!G115</f>
+        <f>Scenarios!$C$115</f>
         <v/>
       </c>
       <c r="G32" s="25">
-        <f>Scenarios!G116</f>
+        <f>Scenarios!$C$116</f>
         <v/>
       </c>
       <c r="H32" s="25">
-        <f>Scenarios!G117</f>
+        <f>Scenarios!$C$117</f>
         <v/>
       </c>
       <c r="I32" s="25">
-        <f>Scenarios!G118</f>
+        <f>Scenarios!$C$118</f>
         <v/>
       </c>
       <c r="J32" s="25">
-        <f>Scenarios!G119</f>
+        <f>Scenarios!$C$119</f>
         <v/>
       </c>
     </row>
@@ -8750,23 +9636,23 @@
       </c>
       <c r="D33" s="19" t="n"/>
       <c r="F33" s="25">
-        <f>Scenarios!G120</f>
+        <f>Scenarios!$C$120</f>
         <v/>
       </c>
       <c r="G33" s="25">
-        <f>Scenarios!G121</f>
+        <f>Scenarios!$C$121</f>
         <v/>
       </c>
       <c r="H33" s="25">
-        <f>Scenarios!G122</f>
+        <f>Scenarios!$C$122</f>
         <v/>
       </c>
       <c r="I33" s="25">
-        <f>Scenarios!G123</f>
+        <f>Scenarios!$C$123</f>
         <v/>
       </c>
       <c r="J33" s="25">
-        <f>Scenarios!G124</f>
+        <f>Scenarios!$C$124</f>
         <v/>
       </c>
     </row>
@@ -8780,23 +9666,23 @@
         </is>
       </c>
       <c r="F35" s="89">
-        <f>Scenarios!G125</f>
+        <f>Scenarios!$C$125</f>
         <v/>
       </c>
       <c r="G35" s="89">
-        <f>Scenarios!G126</f>
+        <f>Scenarios!$C$126</f>
         <v/>
       </c>
       <c r="H35" s="89">
-        <f>Scenarios!G127</f>
+        <f>Scenarios!$C$127</f>
         <v/>
       </c>
       <c r="I35" s="89">
-        <f>Scenarios!G128</f>
+        <f>Scenarios!$C$128</f>
         <v/>
       </c>
       <c r="J35" s="89">
-        <f>Scenarios!G129</f>
+        <f>Scenarios!$C$129</f>
         <v/>
       </c>
     </row>
@@ -8829,23 +9715,23 @@
         </is>
       </c>
       <c r="F37" s="91">
-        <f>1/(1+Scenarios!$G$9)^F36</f>
+        <f>1/(1+Scenarios!$C$9)^F36</f>
         <v/>
       </c>
       <c r="G37" s="91">
-        <f>1/(1+Scenarios!$G$9)^G36</f>
+        <f>1/(1+Scenarios!$C$9)^G36</f>
         <v/>
       </c>
       <c r="H37" s="91">
-        <f>1/(1+Scenarios!$G$9)^H36</f>
+        <f>1/(1+Scenarios!$C$9)^H36</f>
         <v/>
       </c>
       <c r="I37" s="91">
-        <f>1/(1+Scenarios!$G$9)^I36</f>
+        <f>1/(1+Scenarios!$C$9)^I36</f>
         <v/>
       </c>
       <c r="J37" s="91">
-        <f>1/(1+Scenarios!$G$9)^J36</f>
+        <f>1/(1+Scenarios!$C$9)^J36</f>
         <v/>
       </c>
     </row>
@@ -8913,7 +9799,7 @@
       </c>
       <c r="D43" s="19" t="n"/>
       <c r="E43" s="32">
-        <f>Scenarios!$G$10</f>
+        <f>Scenarios!$C$10</f>
         <v/>
       </c>
     </row>
@@ -8935,7 +9821,7 @@
         </is>
       </c>
       <c r="E45" s="75">
-        <f>J35*(1+Scenarios!$G$10)/(Scenarios!$G$9-Scenarios!$G$10)</f>
+        <f>J35*(1+Scenarios!$C$10)/(Scenarios!$C$9-Scenarios!$C$10)</f>
         <v/>
       </c>
     </row>
@@ -8953,7 +9839,7 @@
     <row r="47">
       <c r="A47" s="16" t="n"/>
       <c r="E47" s="94">
-        <f>J35/E44*(1+Scenarios!$G$10)/(Scenarios!$G$9-Scenarios!$G$10)</f>
+        <f>J35/E44*(1+Scenarios!$C$10)/(Scenarios!$C$9-Scenarios!$C$10)</f>
         <v/>
       </c>
     </row>
@@ -8964,7 +9850,7 @@
         </is>
       </c>
       <c r="E48" s="70">
-        <f>E45/(1+Scenarios!$G$9)^J36</f>
+        <f>E45/(1+Scenarios!$C$9)^J36</f>
         <v/>
       </c>
     </row>
@@ -9115,7 +10001,7 @@
         </is>
       </c>
       <c r="E65" s="37">
-        <f>Scenarios!$G$21</f>
+        <f>Scenarios!$C$21</f>
         <v/>
       </c>
       <c r="F65" s="37">
@@ -9482,7 +10368,7 @@
         </is>
       </c>
       <c r="E84" s="75">
-        <f>E83/(1+Scenarios!$G$9)^J36</f>
+        <f>E83/(1+Scenarios!$C$9)^J36</f>
         <v/>
       </c>
     </row>
@@ -10699,11 +11585,11 @@
         </is>
       </c>
       <c r="G60" s="121">
-        <f>Scenarios!F132</f>
+        <f>Scenarios!$B$132</f>
         <v/>
       </c>
       <c r="H60" s="121">
-        <f>Scenarios!H132</f>
+        <f>Scenarios!$D$132</f>
         <v/>
       </c>
     </row>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F13" s="147" t="inlineStr">
         <is>
-          <t>Investment scales as fixed percent of revenue.</t>
+          <t>Five-year blended average: fades 7.0% toward 6.1% revenue.</t>
         </is>
       </c>
       <c r="G13" s="20" t="n"/>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -458,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -914,6 +914,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6575,7 +6578,7 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="11"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="36" customWidth="1" min="12" max="12"/>
@@ -6684,7 +6687,11 @@
           <t>Units</t>
         </is>
       </c>
-      <c r="I5" s="56" t="n"/>
+      <c r="I5" s="169" t="inlineStr">
+        <is>
+          <t>How it moves</t>
+        </is>
+      </c>
       <c r="J5" s="127" t="inlineStr">
         <is>
           <t>Source</t>
@@ -6726,7 +6733,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I6" s="17" t="n"/>
+      <c r="I6" s="135" t="inlineStr">
+        <is>
+          <t>Prior-year ending count carried into this year.</t>
+        </is>
+      </c>
       <c r="J6" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
@@ -6759,7 +6770,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I7" s="17" t="n"/>
+      <c r="I7" s="135" t="inlineStr">
+        <is>
+          <t>New stores added in region each forecast year.</t>
+        </is>
+      </c>
       <c r="J7" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
@@ -6797,7 +6812,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I8" s="17" t="n"/>
+      <c r="I8" s="135" t="inlineStr">
+        <is>
+          <t>Stores closed yearly as leases roll off.</t>
+        </is>
+      </c>
       <c r="J8" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
@@ -6843,7 +6862,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I9" s="17" t="n"/>
+      <c r="I9" s="135" t="inlineStr">
+        <is>
+          <t>Beginning plus openings minus closures each year.</t>
+        </is>
+      </c>
       <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
@@ -6884,7 +6907,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I10" s="17" t="n"/>
+      <c r="I10" s="135" t="inlineStr">
+        <is>
+          <t>Prior-year ending count carried into this year.</t>
+        </is>
+      </c>
       <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
@@ -6917,7 +6944,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I11" s="17" t="n"/>
+      <c r="I11" s="135" t="inlineStr">
+        <is>
+          <t>New stores added in region each forecast year.</t>
+        </is>
+      </c>
       <c r="J11" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
@@ -6955,7 +6986,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I12" s="17" t="n"/>
+      <c r="I12" s="135" t="inlineStr">
+        <is>
+          <t>Stores closed yearly as leases roll off.</t>
+        </is>
+      </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
@@ -7001,7 +7036,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n"/>
+      <c r="I13" s="135" t="inlineStr">
+        <is>
+          <t>Beginning plus openings minus closures each year.</t>
+        </is>
+      </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
@@ -7042,7 +7081,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I14" s="17" t="n"/>
+      <c r="I14" s="135" t="inlineStr">
+        <is>
+          <t>Prior-year ending count carried into this year.</t>
+        </is>
+      </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
@@ -7075,7 +7118,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I15" s="17" t="n"/>
+      <c r="I15" s="135" t="inlineStr">
+        <is>
+          <t>New stores added in region each forecast year.</t>
+        </is>
+      </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
@@ -7113,7 +7160,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I16" s="17" t="n"/>
+      <c r="I16" s="135" t="inlineStr">
+        <is>
+          <t>Stores closed yearly as leases roll off.</t>
+        </is>
+      </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
@@ -7159,7 +7210,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I17" s="17" t="n"/>
+      <c r="I17" s="135" t="inlineStr">
+        <is>
+          <t>Beginning plus openings minus closures each year.</t>
+        </is>
+      </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
@@ -7195,7 +7250,11 @@
         <f>G9+G13+G17</f>
         <v/>
       </c>
-      <c r="I18" s="17" t="n"/>
+      <c r="I18" s="135" t="inlineStr">
+        <is>
+          <t>Sum of Americas, China, and Rest of World.</t>
+        </is>
+      </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-stores formula</t>
@@ -7231,7 +7290,11 @@
           <t>sq ft</t>
         </is>
       </c>
-      <c r="I19" s="17" t="n"/>
+      <c r="I19" s="135" t="inlineStr">
+        <is>
+          <t>Average box size grows modestly through FY30.</t>
+        </is>
+      </c>
       <c r="J19" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: sales per square foot</t>
@@ -7278,7 +7341,11 @@
           <t>sq ft</t>
         </is>
       </c>
-      <c r="I20" s="17" t="n"/>
+      <c r="I20" s="135" t="inlineStr">
+        <is>
+          <t>Ending stores times average square feet per store.</t>
+        </is>
+      </c>
       <c r="J20" s="128" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-sqft formula</t>
@@ -7370,7 +7437,11 @@
           <t>$/sq ft</t>
         </is>
       </c>
-      <c r="I24" s="17" t="n"/>
+      <c r="I24" s="135" t="inlineStr">
+        <is>
+          <t>Sales per foot recovers slowly after FY26 trough.</t>
+        </is>
+      </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: comparable sales &amp; SPSF</t>
@@ -7411,7 +7482,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="I25" s="17" t="n"/>
+      <c r="I25" s="135" t="inlineStr">
+        <is>
+          <t>Declines then flatlines as Americas traffic stabilizes.</t>
+        </is>
+      </c>
       <c r="J25" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: Americas comparable sales</t>
@@ -7452,7 +7527,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="I26" s="17" t="n"/>
+      <c r="I26" s="135" t="inlineStr">
+        <is>
+          <t>Strong growth moderates as China store base scales.</t>
+        </is>
+      </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: China Mainland comparable sales</t>
@@ -7493,7 +7572,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="I27" s="17" t="n"/>
+      <c r="I27" s="135" t="inlineStr">
+        <is>
+          <t>Mid-single-digit comps fading to low-single digits.</t>
+        </is>
+      </c>
       <c r="J27" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: Rest of World comparable sales</t>
@@ -7539,7 +7622,11 @@
           <t>$000</t>
         </is>
       </c>
-      <c r="I28" s="17" t="n"/>
+      <c r="I28" s="135" t="inlineStr">
+        <is>
+          <t>Last year's store revenue rolled forward annually.</t>
+        </is>
+      </c>
       <c r="J28" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: prior store-rev formula</t>
@@ -7575,7 +7662,11 @@
         <f>F28*0.71*(1+G25)+F28*0.16*(1+G26)+F28*0.13*(1+G27)</f>
         <v/>
       </c>
-      <c r="I29" s="17" t="n"/>
+      <c r="I29" s="135" t="inlineStr">
+        <is>
+          <t>Prior revenue grown by weighted geographic comp rates.</t>
+        </is>
+      </c>
       <c r="J29" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: comp-store formula</t>
@@ -7611,7 +7702,11 @@
         <f>(G7-G8+G11-G12+G15-G16)*G19*G24/1000*0.55</f>
         <v/>
       </c>
-      <c r="I30" s="17" t="n"/>
+      <c r="I30" s="135" t="inlineStr">
+        <is>
+          <t>Net new doors times sq ft, productivity, ramp.</t>
+        </is>
+      </c>
       <c r="J30" s="128" t="inlineStr">
         <is>
           <t>Revenue Drivers: net-new-store formula</t>
@@ -7647,7 +7742,11 @@
         <f>G29+G30</f>
         <v/>
       </c>
-      <c r="I31" s="17" t="n"/>
+      <c r="I31" s="135" t="inlineStr">
+        <is>
+          <t>Comparable store sales plus new store contribution.</t>
+        </is>
+      </c>
       <c r="J31" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: store-channel formula</t>
@@ -7840,7 +7939,11 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I38" s="17" t="n"/>
+      <c r="I38" s="135" t="inlineStr">
+        <is>
+          <t>Digital traffic grows modestly across forecast years.</t>
+        </is>
+      </c>
       <c r="J38" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce revenue</t>
@@ -7876,7 +7979,11 @@
       <c r="G39" s="64" t="n">
         <v>0.036</v>
       </c>
-      <c r="I39" s="17" t="n"/>
+      <c r="I39" s="135" t="inlineStr">
+        <is>
+          <t>Conversion rate recovers gradually from FY26 pressure.</t>
+        </is>
+      </c>
       <c r="J39" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: digital / traffic commentary</t>
@@ -7912,7 +8019,11 @@
       <c r="G40" s="67" t="n">
         <v>315</v>
       </c>
-      <c r="I40" s="17" t="n"/>
+      <c r="I40" s="135" t="inlineStr">
+        <is>
+          <t>Order size steps up slowly with promo normalization.</t>
+        </is>
+      </c>
       <c r="J40" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce revenue</t>
@@ -7953,7 +8064,11 @@
         <f>G38*$B$3*G39*G40/$C$3</f>
         <v/>
       </c>
-      <c r="I41" s="17" t="n"/>
+      <c r="I41" s="135" t="inlineStr">
+        <is>
+          <t>Sessions times conversion times average order value.</t>
+        </is>
+      </c>
       <c r="J41" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: e-comm formula</t>
@@ -8050,7 +8165,11 @@
           <t>$000</t>
         </is>
       </c>
-      <c r="I45" s="17" t="n"/>
+      <c r="I45" s="135" t="inlineStr">
+        <is>
+          <t>Wholesale, license, outlets: low-single-digit growth.</t>
+        </is>
+      </c>
       <c r="J45" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: channel revenue table</t>
@@ -8096,7 +8215,11 @@
           <t>$000</t>
         </is>
       </c>
-      <c r="I46" s="17" t="n"/>
+      <c r="I46" s="135" t="inlineStr">
+        <is>
+          <t>Americas revenue scales with consolidated growth rate.</t>
+        </is>
+      </c>
       <c r="J46" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
@@ -8142,7 +8265,11 @@
           <t>$000</t>
         </is>
       </c>
-      <c r="I47" s="17" t="n"/>
+      <c r="I47" s="135" t="inlineStr">
+        <is>
+          <t>China revenue grows faster than consolidated average.</t>
+        </is>
+      </c>
       <c r="J47" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
@@ -8188,7 +8315,11 @@
           <t>$000</t>
         </is>
       </c>
-      <c r="I48" s="17" t="n"/>
+      <c r="I48" s="135" t="inlineStr">
+        <is>
+          <t>Rest of World scales with total revenue growth.</t>
+        </is>
+      </c>
       <c r="J48" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
@@ -8224,7 +8355,11 @@
       <c r="G49" s="64" t="n">
         <v>0.6</v>
       </c>
-      <c r="I49" s="17" t="n"/>
+      <c r="I49" s="135" t="inlineStr">
+        <is>
+          <t>Women's share fades slightly as men's mix rises.</t>
+        </is>
+      </c>
       <c r="J49" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
@@ -8260,7 +8395,11 @@
       <c r="G50" s="64" t="n">
         <v>0.27</v>
       </c>
-      <c r="I50" s="17" t="n"/>
+      <c r="I50" s="135" t="inlineStr">
+        <is>
+          <t>Men's mix rises gradually through the forecast.</t>
+        </is>
+      </c>
       <c r="J50" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
@@ -8296,7 +8435,11 @@
       <c r="G51" s="64" t="n">
         <v>0.13</v>
       </c>
-      <c r="I51" s="17" t="n"/>
+      <c r="I51" s="135" t="inlineStr">
+        <is>
+          <t>Accessories share held steady near thirteen percent.</t>
+        </is>
+      </c>
       <c r="J51" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
@@ -8393,7 +8536,11 @@
         <f>G31+G41+G45</f>
         <v/>
       </c>
-      <c r="I55" s="17" t="n"/>
+      <c r="I55" s="135" t="inlineStr">
+        <is>
+          <t>Store channel plus e-comm plus other channels.</t>
+        </is>
+      </c>
       <c r="J55" s="18" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-rev formula</t>
@@ -8429,7 +8576,11 @@
         <f>Scenarios!$C$29</f>
         <v/>
       </c>
-      <c r="I56" s="17" t="n"/>
+      <c r="I56" s="135" t="inlineStr">
+        <is>
+          <t>Pulls Scenarios base revenue path used by DCF.</t>
+        </is>
+      </c>
       <c r="J56" s="18" t="inlineStr">
         <is>
           <t>Scenarios tab: base revenue</t>
@@ -8471,7 +8622,11 @@
         <f>G55-G56</f>
         <v/>
       </c>
-      <c r="I57" s="17" t="n"/>
+      <c r="I57" s="135" t="inlineStr">
+        <is>
+          <t>Driver-built revenue minus Scenarios base-case revenue.</t>
+        </is>
+      </c>
       <c r="J57" s="128" t="inlineStr">
         <is>
           <t>Revenue Drivers: variance formula</t>
@@ -8508,7 +8663,11 @@
         <f>IF(G56=0,"",G57/G56)</f>
         <v/>
       </c>
-      <c r="I58" s="17" t="n"/>
+      <c r="I58" s="135" t="inlineStr">
+        <is>
+          <t>Variance as percent of Scenarios consolidated revenue.</t>
+        </is>
+      </c>
       <c r="J58" s="128" t="inlineStr">
         <is>
           <t>Revenue Drivers: variance % formula</t>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -10398,23 +10398,23 @@
         <v>111380</v>
       </c>
       <c r="F75" s="25">
-        <f>F74-F73</f>
+        <f>Scenarios!$C$183</f>
         <v/>
       </c>
       <c r="G75" s="25">
-        <f>G74-G73</f>
+        <f>Scenarios!$C$184</f>
         <v/>
       </c>
       <c r="H75" s="25">
-        <f>H74-H73</f>
+        <f>Scenarios!$C$185</f>
         <v/>
       </c>
       <c r="I75" s="25">
-        <f>I74-I73</f>
+        <f>Scenarios!$C$186</f>
         <v/>
       </c>
       <c r="J75" s="25">
-        <f>J74-J73</f>
+        <f>Scenarios!$C$187</f>
         <v/>
       </c>
     </row>
@@ -10428,23 +10428,23 @@
         <v>1579183</v>
       </c>
       <c r="F77" s="75">
-        <f>F14</f>
+        <f>Scenarios!$C$143</f>
         <v/>
       </c>
       <c r="G77" s="75">
-        <f>G14</f>
+        <f>Scenarios!$C$144</f>
         <v/>
       </c>
       <c r="H77" s="75">
-        <f>H14</f>
+        <f>Scenarios!$C$145</f>
         <v/>
       </c>
       <c r="I77" s="75">
-        <f>I14</f>
+        <f>Scenarios!$C$146</f>
         <v/>
       </c>
       <c r="J77" s="75">
-        <f>J14</f>
+        <f>Scenarios!$C$147</f>
         <v/>
       </c>
     </row>
@@ -10459,23 +10459,23 @@
         <v/>
       </c>
       <c r="F78" s="101">
-        <f>F77/F75</f>
+        <f>Scenarios!$C$188</f>
         <v/>
       </c>
       <c r="G78" s="101">
-        <f>G77/G75</f>
+        <f>Scenarios!$C$189</f>
         <v/>
       </c>
       <c r="H78" s="101">
-        <f>H77/H75</f>
+        <f>Scenarios!$C$190</f>
         <v/>
       </c>
       <c r="I78" s="101">
-        <f>I77/I75</f>
+        <f>Scenarios!$C$191</f>
         <v/>
       </c>
       <c r="J78" s="101">
-        <f>J77/J75</f>
+        <f>Scenarios!$C$192</f>
         <v/>
       </c>
     </row>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -8677,7 +8677,7 @@
     <row r="59">
       <c r="A59" s="26" t="inlineStr">
         <is>
-          <t>Note: DCF / Scenarios consolidated revenue is the valuation anchor — drivers do not feed the DCF. A small variance vs Scenarios means the bottom-up path still hangs together, so the Scenarios case stays viable. Bigger gaps = revisit drivers or Scenarios assumptions.</t>
+          <t>Note: DCF / Scenarios consolidated revenue is the valuation anchor: drivers do not feed the DCF. A small variance vs Scenarios means the bottom-up path still hangs together, so the Scenarios case stays viable. Bigger gaps = revisit drivers or Scenarios assumptions.</t>
         </is>
       </c>
     </row>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -10713,23 +10713,23 @@
       </c>
       <c r="D99" s="19" t="n"/>
       <c r="F99" s="110">
-        <f>(NPV($A99,$F$35:$J$35)+($J$35*(1+F$98)/($A99-F$98))/(1+$A99)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A99,$F$35:$J$35)+($J$35*(1+F$98)/($A99-F$98))/(1+$A99)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="G99" s="110">
-        <f>(NPV($A99,$F$35:$J$35)+($J$35*(1+G$98)/($A99-G$98))/(1+$A99)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A99,$F$35:$J$35)+($J$35*(1+G$98)/($A99-G$98))/(1+$A99)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="H99" s="110">
-        <f>(NPV($A99,$F$35:$J$35)+($J$35*(1+H$98)/($A99-H$98))/(1+$A99)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A99,$F$35:$J$35)+($J$35*(1+H$98)/($A99-H$98))/(1+$A99)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="I99" s="110">
-        <f>(NPV(0.095,F35:J35)+(J35*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E50+E51)/E55</f>
+        <f>(NPV($A99,$F$35:$J$35)+($J$35*(1+I$98)/($A99-I$98))/(1+$A99)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="J99" s="110">
-        <f>(NPV(0.095,F35:J35)+(J35*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E50+E51)/E55</f>
+        <f>(NPV($A99,$F$35:$J$35)+($J$35*(1+J$98)/($A99-J$98))/(1+$A99)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
     </row>
@@ -10739,23 +10739,23 @@
       </c>
       <c r="D100" s="19" t="n"/>
       <c r="F100" s="110">
-        <f>(NPV($A100,$F$35:$J$35)+($J$35*(1+F$98)/($A100-F$98))/(1+$A100)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A100,$F$35:$J$35)+($J$35*(1+F$98)/($A100-F$98))/(1+$A100)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="G100" s="110">
-        <f>(NPV($A100,$F$35:$J$35)+($J$35*(1+G$98)/($A100-G$98))/(1+$A100)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A100,$F$35:$J$35)+($J$35*(1+G$98)/($A100-G$98))/(1+$A100)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="H100" s="110">
-        <f>(NPV($A100,$F$35:$J$35)+($J$35*(1+H$98)/($A100-H$98))/(1+$A100)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A100,$F$35:$J$35)+($J$35*(1+H$98)/($A100-H$98))/(1+$A100)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="I100" s="110">
-        <f>(NPV(0.1,F35:J35)+(J35*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E50+E51)/E55</f>
+        <f>(NPV($A100,$F$35:$J$35)+($J$35*(1+I$98)/($A100-I$98))/(1+$A100)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="J100" s="110">
-        <f>(NPV(0.1,F35:J35)+(J35*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E50+E51)/E55</f>
+        <f>(NPV($A100,$F$35:$J$35)+($J$35*(1+J$98)/($A100-J$98))/(1+$A100)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
     </row>
@@ -10765,23 +10765,23 @@
       </c>
       <c r="D101" s="19" t="n"/>
       <c r="F101" s="110">
-        <f>(NPV($A101,$F$35:$J$35)+($J$35*(1+F$98)/($A101-F$98))/(1+$A101)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A101,$F$35:$J$35)+($J$35*(1+F$98)/($A101-F$98))/(1+$A101)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="G101" s="110">
-        <f>(NPV($A101,$F$35:$J$35)+($J$35*(1+G$98)/($A101-G$98))/(1+$A101)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A101,$F$35:$J$35)+($J$35*(1+G$98)/($A101-G$98))/(1+$A101)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="H101" s="111">
-        <f>(NPV($A101,$F$35:$J$35)+($J$35*(1+H$98)/($A101-H$98))/(1+$A101)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A101,$F$35:$J$35)+($J$35*(1+H$98)/($A101-H$98))/(1+$A101)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="I101" s="110">
-        <f>(NPV(0.105,F35:J35)+(J35*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E50+E51)/E55</f>
+        <f>(NPV($A101,$F$35:$J$35)+($J$35*(1+I$98)/($A101-I$98))/(1+$A101)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="J101" s="110">
-        <f>(NPV(0.105,F35:J35)+(J35*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E50+E51)/E55</f>
+        <f>(NPV($A101,$F$35:$J$35)+($J$35*(1+J$98)/($A101-J$98))/(1+$A101)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
     </row>
@@ -10791,23 +10791,23 @@
       </c>
       <c r="D102" s="19" t="n"/>
       <c r="F102" s="110">
-        <f>(NPV($A102,$F$35:$J$35)+($J$35*(1+F$98)/($A102-F$98))/(1+$A102)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A102,$F$35:$J$35)+($J$35*(1+F$98)/($A102-F$98))/(1+$A102)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="G102" s="110">
-        <f>(NPV($A102,$F$35:$J$35)+($J$35*(1+G$98)/($A102-G$98))/(1+$A102)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A102,$F$35:$J$35)+($J$35*(1+G$98)/($A102-G$98))/(1+$A102)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="H102" s="110">
-        <f>(NPV($A102,$F$35:$J$35)+($J$35*(1+H$98)/($A102-H$98))/(1+$A102)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A102,$F$35:$J$35)+($J$35*(1+H$98)/($A102-H$98))/(1+$A102)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="I102" s="110">
-        <f>(NPV(0.11,F35:J35)+(J35*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E50+E51)/E55</f>
+        <f>(NPV($A102,$F$35:$J$35)+($J$35*(1+I$98)/($A102-I$98))/(1+$A102)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="J102" s="110">
-        <f>(NPV(0.11,F35:J35)+(J35*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E50+E51)/E55</f>
+        <f>(NPV($A102,$F$35:$J$35)+($J$35*(1+J$98)/($A102-J$98))/(1+$A102)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
     </row>
@@ -10817,23 +10817,23 @@
       </c>
       <c r="D103" s="19" t="n"/>
       <c r="F103" s="110">
-        <f>(NPV($A103,$F$35:$J$35)+($J$35*(1+F$98)/($A103-F$98))/(1+$A103)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A103,$F$35:$J$35)+($J$35*(1+F$98)/($A103-F$98))/(1+$A103)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="G103" s="110">
-        <f>(NPV($A103,$F$35:$J$35)+($J$35*(1+G$98)/($A103-G$98))/(1+$A103)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A103,$F$35:$J$35)+($J$35*(1+G$98)/($A103-G$98))/(1+$A103)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="H103" s="110">
-        <f>(NPV($A103,$F$35:$J$35)+($J$35*(1+H$98)/($A103-H$98))/(1+$A103)^$E$36+$E$50+$E$51)/$E$55</f>
+        <f>(NPV($A103,$F$35:$J$35)+($J$35*(1+H$98)/($A103-H$98))/(1+$A103)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="I103" s="110">
-        <f>(NPV(0.115,F35:J35)+(J35*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E50+E51)/E55</f>
+        <f>(NPV($A103,$F$35:$J$35)+($J$35*(1+I$98)/($A103-I$98))/(1+$A103)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
       <c r="J103" s="110">
-        <f>(NPV(0.115,F35:J35)+(J35*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E50+E51)/E55</f>
+        <f>(NPV($A103,$F$35:$J$35)+($J$35*(1+J$98)/($A103-J$98))/(1+$A103)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
       </c>
     </row>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="169" formatCode="0.0x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="61">
+  <fonts count="69">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -383,6 +383,52 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <i val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -458,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -917,6 +963,42 @@
     <xf numFmtId="0" fontId="58" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="61" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="62" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1282,21 +1364,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="171" t="n"/>
+      <c r="B1" s="171" t="n"/>
+    </row>
     <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="171" t="n"/>
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>GLOBAL INVESTMENT SOCIETY | INVESTMENT RESEARCH DIVISION</t>
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="171" t="n"/>
+      <c r="B3" s="171" t="n"/>
+    </row>
     <row r="4">
+      <c r="A4" s="171" t="n"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>lululemon athletica inc. (NASDAQ: LULU)</t>
@@ -1304,20 +1396,31 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" s="171" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Discounted Cash Flow Valuation — Unlevered Free Cash Flow</t>
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="171" t="n"/>
+      <c r="B6" s="171" t="n"/>
+    </row>
     <row r="7">
+      <c r="A7" s="171" t="n"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Recommendation: LONG / OVERWEIGHT</t>
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="171" t="n"/>
+      <c r="B8" s="171" t="n"/>
+    </row>
     <row r="9">
+      <c r="A9" s="171" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>FONT / COLOR CONVENTION</t>
@@ -1325,6 +1428,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" s="171" t="n"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Blue font = figures reported by the company (click value or source link)</t>
@@ -1332,9 +1436,15 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" s="171" t="n"/>
       <c r="B11" s="7" t="n"/>
     </row>
+    <row r="12">
+      <c r="A12" s="171" t="n"/>
+      <c r="B12" s="171" t="n"/>
+    </row>
     <row r="13">
+      <c r="A13" s="171" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
           <t>TABS</t>
@@ -1342,6 +1452,7 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" s="171" t="n"/>
       <c r="B14" s="9" t="inlineStr">
         <is>
           <t>WACC • Revenue Drivers • Scenarios • DCF • Comps / Football Field</t>
@@ -1349,12 +1460,23 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" s="171" t="n"/>
       <c r="B15" s="5" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" s="171" t="n"/>
+      <c r="B16" s="171" t="n"/>
+    </row>
     <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="171" t="n"/>
       <c r="B17" s="5" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="171" t="n"/>
+      <c r="B18" s="171" t="n"/>
+    </row>
     <row r="19">
+      <c r="A19" s="171" t="n"/>
       <c r="B19" s="11" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1"/>
@@ -1388,10 +1510,10 @@
           <t>WEIGHTED AVERAGE COST OF CAPITAL</t>
         </is>
       </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-      <c r="E1" s="13" t="n"/>
+      <c r="B1" s="172" t="n"/>
+      <c r="C1" s="172" t="n"/>
+      <c r="D1" s="172" t="n"/>
+      <c r="E1" s="172" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
@@ -1406,6 +1528,7 @@
         </is>
       </c>
       <c r="D2" s="15" t="n"/>
+      <c r="E2" s="171" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
@@ -1458,12 +1581,23 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="171" t="n"/>
+      <c r="B6" s="171" t="n"/>
+      <c r="C6" s="171" t="n"/>
+      <c r="D6" s="171" t="n"/>
+      <c r="E6" s="171" t="n"/>
+    </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Capital structure (market values)</t>
         </is>
       </c>
+      <c r="B7" s="171" t="n"/>
+      <c r="C7" s="171" t="n"/>
+      <c r="D7" s="171" t="n"/>
+      <c r="E7" s="171" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -1536,6 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" s="26" t="n"/>
+      <c r="B12" s="171" t="n"/>
+      <c r="C12" s="171" t="n"/>
+      <c r="D12" s="171" t="n"/>
+      <c r="E12" s="171" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
@@ -1560,17 +1698,31 @@
           <t>Total debt equivalents</t>
         </is>
       </c>
+      <c r="B14" s="171" t="n"/>
+      <c r="C14" s="171" t="n"/>
+      <c r="D14" s="171" t="n"/>
       <c r="E14" s="25">
         <f>E11+E13</f>
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="171" t="n"/>
+      <c r="B15" s="171" t="n"/>
+      <c r="C15" s="171" t="n"/>
+      <c r="D15" s="171" t="n"/>
+      <c r="E15" s="171" t="n"/>
+    </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Beta (unlever → relever)</t>
         </is>
       </c>
+      <c r="B16" s="171" t="n"/>
+      <c r="C16" s="171" t="n"/>
+      <c r="D16" s="171" t="n"/>
+      <c r="E16" s="171" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
@@ -1731,6 +1883,10 @@
     </row>
     <row r="26">
       <c r="A26" s="26" t="n"/>
+      <c r="B26" s="171" t="n"/>
+      <c r="C26" s="171" t="n"/>
+      <c r="D26" s="171" t="n"/>
+      <c r="E26" s="171" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="26" t="inlineStr">
@@ -1738,6 +1894,10 @@
           <t>Yahoo βL = 0.86 (Beta 5Y Monthly). No vendor publishes D/E inside the regression.</t>
         </is>
       </c>
+      <c r="B27" s="171" t="n"/>
+      <c r="C27" s="171" t="n"/>
+      <c r="D27" s="171" t="n"/>
+      <c r="E27" s="171" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="26" t="inlineStr">
@@ -1745,6 +1905,10 @@
           <t>Unlever at Yahoo market D/E = $2.14B debt (mrq) ÷ $11.14B mkt cap ≈ 0.19 → βu ≈ 0.76.</t>
         </is>
       </c>
+      <c r="B28" s="171" t="n"/>
+      <c r="C28" s="171" t="n"/>
+      <c r="D28" s="171" t="n"/>
+      <c r="E28" s="171" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="26" t="inlineStr">
@@ -1752,9 +1916,17 @@
           <t>Relever at WACC D/E = FY25 10-K leases ÷ our market cap ≈ 0.16 → β used ≈ 0.84.</t>
         </is>
       </c>
+      <c r="B29" s="171" t="n"/>
+      <c r="C29" s="171" t="n"/>
+      <c r="D29" s="171" t="n"/>
+      <c r="E29" s="171" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="26" t="n"/>
+      <c r="B30" s="171" t="n"/>
+      <c r="C30" s="171" t="n"/>
+      <c r="D30" s="171" t="n"/>
+      <c r="E30" s="171" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -1762,6 +1934,10 @@
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
+      <c r="B31" s="171" t="n"/>
+      <c r="C31" s="171" t="n"/>
+      <c r="D31" s="171" t="n"/>
+      <c r="E31" s="171" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
@@ -1769,17 +1945,31 @@
           <t>Cost of equity = rf + β × ERP</t>
         </is>
       </c>
+      <c r="B32" s="171" t="n"/>
+      <c r="C32" s="171" t="n"/>
+      <c r="D32" s="171" t="n"/>
       <c r="E32" s="30">
         <f>E3+E25*E4</f>
         <v/>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="171" t="n"/>
+      <c r="B33" s="171" t="n"/>
+      <c r="C33" s="171" t="n"/>
+      <c r="D33" s="171" t="n"/>
+      <c r="E33" s="171" t="n"/>
+    </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Cost of debt (lease-equivalent)</t>
         </is>
       </c>
+      <c r="B34" s="171" t="n"/>
+      <c r="C34" s="171" t="n"/>
+      <c r="D34" s="171" t="n"/>
+      <c r="E34" s="171" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
@@ -1804,17 +1994,31 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
+      <c r="B36" s="171" t="n"/>
+      <c r="C36" s="171" t="n"/>
+      <c r="D36" s="171" t="n"/>
       <c r="E36" s="31">
         <f>E35*(1-E5)</f>
         <v/>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="171" t="n"/>
+      <c r="B37" s="171" t="n"/>
+      <c r="C37" s="171" t="n"/>
+      <c r="D37" s="171" t="n"/>
+      <c r="E37" s="171" t="n"/>
+    </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
           <t>WACC weights</t>
         </is>
       </c>
+      <c r="B38" s="171" t="n"/>
+      <c r="C38" s="171" t="n"/>
+      <c r="D38" s="171" t="n"/>
+      <c r="E38" s="171" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
@@ -1858,6 +2062,9 @@
           <t>WACC</t>
         </is>
       </c>
+      <c r="B41" s="171" t="n"/>
+      <c r="C41" s="171" t="n"/>
+      <c r="D41" s="171" t="n"/>
       <c r="E41" s="33">
         <f>E39*E32+E40*E36</f>
         <v/>
@@ -1913,33 +2120,33 @@
           <t>SCENARIO ANALYSIS</t>
         </is>
       </c>
-      <c r="B1" s="137" t="n"/>
-      <c r="C1" s="137" t="n"/>
-      <c r="D1" s="137" t="n"/>
-      <c r="E1" s="137" t="n"/>
-      <c r="F1" s="137" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="13" t="n"/>
+      <c r="B1" s="173" t="n"/>
+      <c r="C1" s="173" t="n"/>
+      <c r="D1" s="173" t="n"/>
+      <c r="E1" s="173" t="n"/>
+      <c r="F1" s="173" t="n"/>
+      <c r="G1" s="172" t="n"/>
+      <c r="H1" s="172" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="138" t="n"/>
-      <c r="B2" s="165" t="inlineStr">
+      <c r="A2" s="174" t="n"/>
+      <c r="B2" s="175" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="C2" s="166" t="inlineStr">
+      <c r="C2" s="176" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D2" s="167" t="inlineStr">
+      <c r="D2" s="177" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="E2" s="138" t="n"/>
-      <c r="F2" s="138" t="n"/>
+      <c r="E2" s="174" t="n"/>
+      <c r="F2" s="174" t="n"/>
       <c r="G2" s="35" t="n"/>
       <c r="H2" s="36" t="n"/>
     </row>
@@ -1949,19 +2156,21 @@
           <t>Key assumptions (5-yr forecast)</t>
         </is>
       </c>
-      <c r="B3" s="138" t="n"/>
-      <c r="C3" s="138" t="n"/>
-      <c r="D3" s="138" t="n"/>
-      <c r="E3" s="143" t="inlineStr">
+      <c r="B3" s="174" t="n"/>
+      <c r="C3" s="174" t="n"/>
+      <c r="D3" s="174" t="n"/>
+      <c r="E3" s="178" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="F3" s="143" t="inlineStr">
+      <c r="F3" s="178" t="inlineStr">
         <is>
           <t>How it moves</t>
         </is>
       </c>
+      <c r="G3" s="171" t="n"/>
+      <c r="H3" s="171" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="144" t="inlineStr">
@@ -1983,7 +2192,7 @@
           <t>LULU Q2 FY2026 earnings release</t>
         </is>
       </c>
-      <c r="F4" s="147" t="inlineStr">
+      <c r="F4" s="179" t="inlineStr">
         <is>
           <t>Year-one sales change: bear falls most.</t>
         </is>
@@ -2011,7 +2220,7 @@
           <t>StockAnalysis: LULU 3Y revenue forecast</t>
         </is>
       </c>
-      <c r="F5" s="147" t="inlineStr">
+      <c r="F5" s="179" t="inlineStr">
         <is>
           <t>Years two-five average growth: bull fastest.</t>
         </is>
@@ -2039,7 +2248,7 @@
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs</t>
         </is>
       </c>
-      <c r="F6" s="147" t="inlineStr">
+      <c r="F6" s="179" t="inlineStr">
         <is>
           <t>Starting operating margin before linear ramp.</t>
         </is>
@@ -2067,7 +2276,7 @@
           <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
         </is>
       </c>
-      <c r="F7" s="147" t="inlineStr">
+      <c r="F7" s="179" t="inlineStr">
         <is>
           <t>One-time year-one EBIT boost: zero after.</t>
         </is>
@@ -2095,7 +2304,7 @@
           <t>FY2025 10-K: Operating margin 19.9% (one hit)</t>
         </is>
       </c>
-      <c r="F8" s="147" t="inlineStr">
+      <c r="F8" s="179" t="inlineStr">
         <is>
           <t>Year-five target margin after linear ramp.</t>
         </is>
@@ -2124,7 +2333,7 @@
           <t>WACC tab: CAPM build</t>
         </is>
       </c>
-      <c r="F9" s="147" t="inlineStr">
+      <c r="F9" s="179" t="inlineStr">
         <is>
           <t>Flat discount rate: higher bear, lower bull.</t>
         </is>
@@ -2152,7 +2361,7 @@
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
-      <c r="F10" s="147" t="inlineStr">
+      <c r="F10" s="179" t="inlineStr">
         <is>
           <t>Perpetuity growth rate: flat across all years.</t>
         </is>
@@ -2180,7 +2389,7 @@
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
       </c>
-      <c r="F11" s="147" t="inlineStr">
+      <c r="F11" s="179" t="inlineStr">
         <is>
           <t>Flat tax percentage applied every forecast year.</t>
         </is>
@@ -2208,7 +2417,7 @@
           <t>LULU CF statement (10-K)</t>
         </is>
       </c>
-      <c r="F12" s="147" t="inlineStr">
+      <c r="F12" s="179" t="inlineStr">
         <is>
           <t>Depreciation scales as fixed percent of revenue.</t>
         </is>
@@ -2236,7 +2445,7 @@
           <t>LULU 10-K: 2026 capex guide $725–745M</t>
         </is>
       </c>
-      <c r="F13" s="147" t="inlineStr">
+      <c r="F13" s="179" t="inlineStr">
         <is>
           <t>Five-year blended average: fades 7.0% toward 6.1% revenue.</t>
         </is>
@@ -2264,7 +2473,7 @@
           <t>LULU FY2025 10-K: Gross profit &amp; COGS</t>
         </is>
       </c>
-      <c r="F14" s="147" t="inlineStr">
+      <c r="F14" s="179" t="inlineStr">
         <is>
           <t>Merchandise margin held flat every forecast year.</t>
         </is>
@@ -2295,7 +2504,7 @@
           <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
       </c>
-      <c r="F15" s="147" t="inlineStr">
+      <c r="F15" s="179" t="inlineStr">
         <is>
           <t>Collection days held flat near six yearly.</t>
         </is>
@@ -2326,7 +2535,7 @@
           <t>LULU FY2025 10-K: Inventories &amp; COGS</t>
         </is>
       </c>
-      <c r="F16" s="147" t="inlineStr">
+      <c r="F16" s="179" t="inlineStr">
         <is>
           <t>Starting inventory days before annual decline begins.</t>
         </is>
@@ -2354,7 +2563,7 @@
           <t>LULU FY2025 10-K: inventory &amp; markdown outlook</t>
         </is>
       </c>
-      <c r="F17" s="147" t="inlineStr">
+      <c r="F17" s="179" t="inlineStr">
         <is>
           <t>Inventory days fall one day each year.</t>
         </is>
@@ -2385,7 +2594,7 @@
           <t>LULU FY2025 10-K: Accounts payable &amp; COGS</t>
         </is>
       </c>
-      <c r="F18" s="147" t="inlineStr">
+      <c r="F18" s="179" t="inlineStr">
         <is>
           <t>Payment days held flat near twenty-five yearly.</t>
         </is>
@@ -2416,7 +2625,7 @@
           <t>LULU FY2025 10-K: other current assets (residual)</t>
         </is>
       </c>
-      <c r="F19" s="147" t="inlineStr">
+      <c r="F19" s="179" t="inlineStr">
         <is>
           <t>Other current assets flat percent of revenue.</t>
         </is>
@@ -2447,7 +2656,7 @@
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
       </c>
-      <c r="F20" s="147" t="inlineStr">
+      <c r="F20" s="179" t="inlineStr">
         <is>
           <t>Accrued payables flat percent of revenue.</t>
         </is>
@@ -2470,8 +2679,8 @@
       <c r="D21" s="148" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="138" t="n"/>
-      <c r="F21" s="147" t="inlineStr">
+      <c r="E21" s="174" t="n"/>
+      <c r="F21" s="179" t="inlineStr">
         <is>
           <t>Bear base retire fixed dollars yearly.</t>
         </is>
@@ -2494,8 +2703,8 @@
       <c r="D22" s="145" t="n">
         <v>0.75</v>
       </c>
-      <c r="E22" s="138" t="n"/>
-      <c r="F22" s="147" t="inlineStr">
+      <c r="E22" s="174" t="n"/>
+      <c r="F22" s="179" t="inlineStr">
         <is>
           <t>Bull spends set percent of free cash.</t>
         </is>
@@ -2504,12 +2713,14 @@
       <c r="H22" s="20" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="138" t="n"/>
-      <c r="B23" s="138" t="n"/>
-      <c r="C23" s="138" t="n"/>
-      <c r="D23" s="138" t="n"/>
-      <c r="E23" s="138" t="n"/>
-      <c r="F23" s="138" t="n"/>
+      <c r="A23" s="174" t="n"/>
+      <c r="B23" s="174" t="n"/>
+      <c r="C23" s="174" t="n"/>
+      <c r="D23" s="174" t="n"/>
+      <c r="E23" s="174" t="n"/>
+      <c r="F23" s="174" t="n"/>
+      <c r="G23" s="171" t="n"/>
+      <c r="H23" s="171" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="142" t="inlineStr">
@@ -2517,11 +2728,13 @@
           <t>5-year forecast paths (by scenario)</t>
         </is>
       </c>
-      <c r="B24" s="138" t="n"/>
-      <c r="C24" s="138" t="n"/>
-      <c r="D24" s="138" t="n"/>
-      <c r="E24" s="138" t="n"/>
-      <c r="F24" s="138" t="n"/>
+      <c r="B24" s="174" t="n"/>
+      <c r="C24" s="174" t="n"/>
+      <c r="D24" s="174" t="n"/>
+      <c r="E24" s="174" t="n"/>
+      <c r="F24" s="174" t="n"/>
+      <c r="G24" s="171" t="n"/>
+      <c r="H24" s="171" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="153" t="inlineStr">
@@ -2541,8 +2754,8 @@
         <f>$B$198*(1+D4)</f>
         <v/>
       </c>
-      <c r="E25" s="138" t="n"/>
-      <c r="F25" s="147" t="inlineStr">
+      <c r="E25" s="174" t="n"/>
+      <c r="F25" s="179" t="inlineStr">
         <is>
           <t>Grows or shrinks using scenario-specific growth rates.</t>
         </is>
@@ -2568,8 +2781,8 @@
         <f>D25*(1+D5)</f>
         <v/>
       </c>
-      <c r="E26" s="138" t="n"/>
-      <c r="F26" s="138" t="n"/>
+      <c r="E26" s="174" t="n"/>
+      <c r="F26" s="174" t="n"/>
       <c r="G26" s="42" t="n"/>
       <c r="H26" s="42" t="n"/>
     </row>
@@ -2591,8 +2804,8 @@
         <f>D26*(1+D5)</f>
         <v/>
       </c>
-      <c r="E27" s="138" t="n"/>
-      <c r="F27" s="138" t="n"/>
+      <c r="E27" s="174" t="n"/>
+      <c r="F27" s="174" t="n"/>
       <c r="G27" s="42" t="n"/>
       <c r="H27" s="42" t="n"/>
     </row>
@@ -2614,8 +2827,8 @@
         <f>D27*(1+D5)</f>
         <v/>
       </c>
-      <c r="E28" s="138" t="n"/>
-      <c r="F28" s="138" t="n"/>
+      <c r="E28" s="174" t="n"/>
+      <c r="F28" s="174" t="n"/>
       <c r="G28" s="42" t="n"/>
       <c r="H28" s="42" t="n"/>
     </row>
@@ -2637,8 +2850,8 @@
         <f>D28*(1+D5)</f>
         <v/>
       </c>
-      <c r="E29" s="138" t="n"/>
-      <c r="F29" s="138" t="n"/>
+      <c r="E29" s="174" t="n"/>
+      <c r="F29" s="174" t="n"/>
       <c r="G29" s="42" t="n"/>
       <c r="H29" s="42" t="n"/>
     </row>
@@ -2660,8 +2873,8 @@
         <f>D14</f>
         <v/>
       </c>
-      <c r="E30" s="138" t="n"/>
-      <c r="F30" s="147" t="inlineStr">
+      <c r="E30" s="174" t="n"/>
+      <c r="F30" s="179" t="inlineStr">
         <is>
           <t>Stays flat at scenario margin every year.</t>
         </is>
@@ -2687,8 +2900,8 @@
         <f>D14</f>
         <v/>
       </c>
-      <c r="E31" s="138" t="n"/>
-      <c r="F31" s="138" t="n"/>
+      <c r="E31" s="174" t="n"/>
+      <c r="F31" s="174" t="n"/>
       <c r="G31" s="43" t="n"/>
       <c r="H31" s="43" t="n"/>
     </row>
@@ -2710,8 +2923,8 @@
         <f>D14</f>
         <v/>
       </c>
-      <c r="E32" s="138" t="n"/>
-      <c r="F32" s="138" t="n"/>
+      <c r="E32" s="174" t="n"/>
+      <c r="F32" s="174" t="n"/>
       <c r="G32" s="43" t="n"/>
       <c r="H32" s="43" t="n"/>
     </row>
@@ -2733,8 +2946,8 @@
         <f>D14</f>
         <v/>
       </c>
-      <c r="E33" s="138" t="n"/>
-      <c r="F33" s="138" t="n"/>
+      <c r="E33" s="174" t="n"/>
+      <c r="F33" s="174" t="n"/>
       <c r="G33" s="43" t="n"/>
       <c r="H33" s="43" t="n"/>
     </row>
@@ -2756,8 +2969,8 @@
         <f>D14</f>
         <v/>
       </c>
-      <c r="E34" s="138" t="n"/>
-      <c r="F34" s="138" t="n"/>
+      <c r="E34" s="174" t="n"/>
+      <c r="F34" s="174" t="n"/>
       <c r="G34" s="43" t="n"/>
       <c r="H34" s="43" t="n"/>
     </row>
@@ -2779,8 +2992,8 @@
         <f>D25*(1-D30)</f>
         <v/>
       </c>
-      <c r="E35" s="138" t="n"/>
-      <c r="F35" s="147" t="inlineStr">
+      <c r="E35" s="174" t="n"/>
+      <c r="F35" s="179" t="inlineStr">
         <is>
           <t>Moves with revenue when gross margin stays flat.</t>
         </is>
@@ -2806,8 +3019,8 @@
         <f>D26*(1-D31)</f>
         <v/>
       </c>
-      <c r="E36" s="138" t="n"/>
-      <c r="F36" s="138" t="n"/>
+      <c r="E36" s="174" t="n"/>
+      <c r="F36" s="174" t="n"/>
       <c r="G36" s="42" t="n"/>
       <c r="H36" s="42" t="n"/>
     </row>
@@ -2829,8 +3042,8 @@
         <f>D27*(1-D32)</f>
         <v/>
       </c>
-      <c r="E37" s="138" t="n"/>
-      <c r="F37" s="138" t="n"/>
+      <c r="E37" s="174" t="n"/>
+      <c r="F37" s="174" t="n"/>
       <c r="G37" s="42" t="n"/>
       <c r="H37" s="42" t="n"/>
     </row>
@@ -2852,8 +3065,8 @@
         <f>D28*(1-D33)</f>
         <v/>
       </c>
-      <c r="E38" s="138" t="n"/>
-      <c r="F38" s="138" t="n"/>
+      <c r="E38" s="174" t="n"/>
+      <c r="F38" s="174" t="n"/>
       <c r="G38" s="42" t="n"/>
       <c r="H38" s="42" t="n"/>
     </row>
@@ -2875,8 +3088,8 @@
         <f>D29*(1-D34)</f>
         <v/>
       </c>
-      <c r="E39" s="138" t="n"/>
-      <c r="F39" s="138" t="n"/>
+      <c r="E39" s="174" t="n"/>
+      <c r="F39" s="174" t="n"/>
       <c r="G39" s="42" t="n"/>
       <c r="H39" s="42" t="n"/>
     </row>
@@ -2898,8 +3111,8 @@
         <f>D6+(D8-D6)*0/4</f>
         <v/>
       </c>
-      <c r="E40" s="138" t="n"/>
-      <c r="F40" s="147" t="inlineStr">
+      <c r="E40" s="174" t="n"/>
+      <c r="F40" s="179" t="inlineStr">
         <is>
           <t>Linearly ramps from run-rate toward terminal margin.</t>
         </is>
@@ -2925,8 +3138,8 @@
         <f>D6+(D8-D6)*1/4</f>
         <v/>
       </c>
-      <c r="E41" s="138" t="n"/>
-      <c r="F41" s="138" t="n"/>
+      <c r="E41" s="174" t="n"/>
+      <c r="F41" s="174" t="n"/>
       <c r="G41" s="43" t="n"/>
       <c r="H41" s="43" t="n"/>
     </row>
@@ -2948,8 +3161,8 @@
         <f>D6+(D8-D6)*2/4</f>
         <v/>
       </c>
-      <c r="E42" s="138" t="n"/>
-      <c r="F42" s="138" t="n"/>
+      <c r="E42" s="174" t="n"/>
+      <c r="F42" s="174" t="n"/>
       <c r="G42" s="43" t="n"/>
       <c r="H42" s="43" t="n"/>
     </row>
@@ -2971,8 +3184,8 @@
         <f>D6+(D8-D6)*3/4</f>
         <v/>
       </c>
-      <c r="E43" s="138" t="n"/>
-      <c r="F43" s="138" t="n"/>
+      <c r="E43" s="174" t="n"/>
+      <c r="F43" s="174" t="n"/>
       <c r="G43" s="43" t="n"/>
       <c r="H43" s="43" t="n"/>
     </row>
@@ -2994,8 +3207,8 @@
         <f>D6+(D8-D6)*4/4</f>
         <v/>
       </c>
-      <c r="E44" s="138" t="n"/>
-      <c r="F44" s="138" t="n"/>
+      <c r="E44" s="174" t="n"/>
+      <c r="F44" s="174" t="n"/>
       <c r="G44" s="43" t="n"/>
       <c r="H44" s="43" t="n"/>
     </row>
@@ -3017,8 +3230,8 @@
         <f>D25*D40+D7</f>
         <v/>
       </c>
-      <c r="E45" s="138" t="n"/>
-      <c r="F45" s="147" t="inlineStr">
+      <c r="E45" s="174" t="n"/>
+      <c r="F45" s="179" t="inlineStr">
         <is>
           <t>Revenue times margin: year one adds tariff refund.</t>
         </is>
@@ -3044,8 +3257,8 @@
         <f>D26*D41</f>
         <v/>
       </c>
-      <c r="E46" s="138" t="n"/>
-      <c r="F46" s="138" t="n"/>
+      <c r="E46" s="174" t="n"/>
+      <c r="F46" s="174" t="n"/>
       <c r="G46" s="42" t="n"/>
       <c r="H46" s="42" t="n"/>
     </row>
@@ -3067,8 +3280,8 @@
         <f>D27*D42</f>
         <v/>
       </c>
-      <c r="E47" s="138" t="n"/>
-      <c r="F47" s="138" t="n"/>
+      <c r="E47" s="174" t="n"/>
+      <c r="F47" s="174" t="n"/>
       <c r="G47" s="42" t="n"/>
       <c r="H47" s="42" t="n"/>
     </row>
@@ -3090,8 +3303,8 @@
         <f>D28*D43</f>
         <v/>
       </c>
-      <c r="E48" s="138" t="n"/>
-      <c r="F48" s="138" t="n"/>
+      <c r="E48" s="174" t="n"/>
+      <c r="F48" s="174" t="n"/>
       <c r="G48" s="42" t="n"/>
       <c r="H48" s="42" t="n"/>
     </row>
@@ -3113,8 +3326,8 @@
         <f>D29*D44</f>
         <v/>
       </c>
-      <c r="E49" s="138" t="n"/>
-      <c r="F49" s="138" t="n"/>
+      <c r="E49" s="174" t="n"/>
+      <c r="F49" s="174" t="n"/>
       <c r="G49" s="42" t="n"/>
       <c r="H49" s="42" t="n"/>
     </row>
@@ -3136,8 +3349,8 @@
         <f>D45*(1-$C$11)</f>
         <v/>
       </c>
-      <c r="E50" s="138" t="n"/>
-      <c r="F50" s="147" t="inlineStr">
+      <c r="E50" s="174" t="n"/>
+      <c r="F50" s="179" t="inlineStr">
         <is>
           <t>EBIT taxed at flat cash rate each year.</t>
         </is>
@@ -3163,8 +3376,8 @@
         <f>D46*(1-$C$11)</f>
         <v/>
       </c>
-      <c r="E51" s="138" t="n"/>
-      <c r="F51" s="138" t="n"/>
+      <c r="E51" s="174" t="n"/>
+      <c r="F51" s="174" t="n"/>
       <c r="G51" s="42" t="n"/>
       <c r="H51" s="42" t="n"/>
     </row>
@@ -3186,8 +3399,8 @@
         <f>D47*(1-$C$11)</f>
         <v/>
       </c>
-      <c r="E52" s="138" t="n"/>
-      <c r="F52" s="138" t="n"/>
+      <c r="E52" s="174" t="n"/>
+      <c r="F52" s="174" t="n"/>
       <c r="G52" s="42" t="n"/>
       <c r="H52" s="42" t="n"/>
     </row>
@@ -3209,8 +3422,8 @@
         <f>D48*(1-$C$11)</f>
         <v/>
       </c>
-      <c r="E53" s="138" t="n"/>
-      <c r="F53" s="138" t="n"/>
+      <c r="E53" s="174" t="n"/>
+      <c r="F53" s="174" t="n"/>
       <c r="G53" s="42" t="n"/>
       <c r="H53" s="42" t="n"/>
     </row>
@@ -3232,8 +3445,8 @@
         <f>D49*(1-$C$11)</f>
         <v/>
       </c>
-      <c r="E54" s="138" t="n"/>
-      <c r="F54" s="138" t="n"/>
+      <c r="E54" s="174" t="n"/>
+      <c r="F54" s="174" t="n"/>
       <c r="G54" s="42" t="n"/>
       <c r="H54" s="42" t="n"/>
     </row>
@@ -3255,8 +3468,8 @@
         <f>D25*D12</f>
         <v/>
       </c>
-      <c r="E55" s="138" t="n"/>
-      <c r="F55" s="147" t="inlineStr">
+      <c r="E55" s="174" t="n"/>
+      <c r="F55" s="179" t="inlineStr">
         <is>
           <t>Scales upward with revenue at fixed percentage annually.</t>
         </is>
@@ -3282,8 +3495,8 @@
         <f>D26*D12</f>
         <v/>
       </c>
-      <c r="E56" s="138" t="n"/>
-      <c r="F56" s="138" t="n"/>
+      <c r="E56" s="174" t="n"/>
+      <c r="F56" s="174" t="n"/>
       <c r="G56" s="42" t="n"/>
       <c r="H56" s="42" t="n"/>
     </row>
@@ -3305,8 +3518,8 @@
         <f>D27*D12</f>
         <v/>
       </c>
-      <c r="E57" s="138" t="n"/>
-      <c r="F57" s="138" t="n"/>
+      <c r="E57" s="174" t="n"/>
+      <c r="F57" s="174" t="n"/>
       <c r="G57" s="42" t="n"/>
       <c r="H57" s="42" t="n"/>
     </row>
@@ -3328,8 +3541,8 @@
         <f>D28*D12</f>
         <v/>
       </c>
-      <c r="E58" s="138" t="n"/>
-      <c r="F58" s="138" t="n"/>
+      <c r="E58" s="174" t="n"/>
+      <c r="F58" s="174" t="n"/>
       <c r="G58" s="42" t="n"/>
       <c r="H58" s="42" t="n"/>
     </row>
@@ -3351,8 +3564,8 @@
         <f>D29*D12</f>
         <v/>
       </c>
-      <c r="E59" s="138" t="n"/>
-      <c r="F59" s="138" t="n"/>
+      <c r="E59" s="174" t="n"/>
+      <c r="F59" s="174" t="n"/>
       <c r="G59" s="42" t="n"/>
       <c r="H59" s="42" t="n"/>
     </row>
@@ -3374,8 +3587,8 @@
         <f>D25*D13</f>
         <v/>
       </c>
-      <c r="E60" s="138" t="n"/>
-      <c r="F60" s="147" t="inlineStr">
+      <c r="E60" s="174" t="n"/>
+      <c r="F60" s="179" t="inlineStr">
         <is>
           <t>Scales upward with revenue at fixed percentage annually.</t>
         </is>
@@ -3401,8 +3614,8 @@
         <f>D26*D13</f>
         <v/>
       </c>
-      <c r="E61" s="138" t="n"/>
-      <c r="F61" s="138" t="n"/>
+      <c r="E61" s="174" t="n"/>
+      <c r="F61" s="174" t="n"/>
       <c r="G61" s="42" t="n"/>
       <c r="H61" s="42" t="n"/>
     </row>
@@ -3424,8 +3637,8 @@
         <f>D27*D13</f>
         <v/>
       </c>
-      <c r="E62" s="138" t="n"/>
-      <c r="F62" s="138" t="n"/>
+      <c r="E62" s="174" t="n"/>
+      <c r="F62" s="174" t="n"/>
       <c r="G62" s="42" t="n"/>
       <c r="H62" s="42" t="n"/>
     </row>
@@ -3447,8 +3660,8 @@
         <f>D28*D13</f>
         <v/>
       </c>
-      <c r="E63" s="138" t="n"/>
-      <c r="F63" s="138" t="n"/>
+      <c r="E63" s="174" t="n"/>
+      <c r="F63" s="174" t="n"/>
       <c r="G63" s="42" t="n"/>
       <c r="H63" s="42" t="n"/>
     </row>
@@ -3470,8 +3683,8 @@
         <f>D29*D13</f>
         <v/>
       </c>
-      <c r="E64" s="138" t="n"/>
-      <c r="F64" s="138" t="n"/>
+      <c r="E64" s="174" t="n"/>
+      <c r="F64" s="174" t="n"/>
       <c r="G64" s="42" t="n"/>
       <c r="H64" s="42" t="n"/>
     </row>
@@ -3493,8 +3706,8 @@
         <f>D15</f>
         <v/>
       </c>
-      <c r="E65" s="138" t="n"/>
-      <c r="F65" s="147" t="inlineStr">
+      <c r="E65" s="174" t="n"/>
+      <c r="F65" s="179" t="inlineStr">
         <is>
           <t>Held flat at six days every forecast year.</t>
         </is>
@@ -3520,8 +3733,8 @@
         <f>D15</f>
         <v/>
       </c>
-      <c r="E66" s="138" t="n"/>
-      <c r="F66" s="138" t="n"/>
+      <c r="E66" s="174" t="n"/>
+      <c r="F66" s="174" t="n"/>
       <c r="G66" s="44" t="n"/>
       <c r="H66" s="44" t="n"/>
     </row>
@@ -3543,8 +3756,8 @@
         <f>D15</f>
         <v/>
       </c>
-      <c r="E67" s="138" t="n"/>
-      <c r="F67" s="138" t="n"/>
+      <c r="E67" s="174" t="n"/>
+      <c r="F67" s="174" t="n"/>
       <c r="G67" s="44" t="n"/>
       <c r="H67" s="44" t="n"/>
     </row>
@@ -3566,8 +3779,8 @@
         <f>D15</f>
         <v/>
       </c>
-      <c r="E68" s="138" t="n"/>
-      <c r="F68" s="138" t="n"/>
+      <c r="E68" s="174" t="n"/>
+      <c r="F68" s="174" t="n"/>
       <c r="G68" s="44" t="n"/>
       <c r="H68" s="44" t="n"/>
     </row>
@@ -3589,8 +3802,8 @@
         <f>D15</f>
         <v/>
       </c>
-      <c r="E69" s="138" t="n"/>
-      <c r="F69" s="138" t="n"/>
+      <c r="E69" s="174" t="n"/>
+      <c r="F69" s="174" t="n"/>
       <c r="G69" s="44" t="n"/>
       <c r="H69" s="44" t="n"/>
     </row>
@@ -3612,8 +3825,8 @@
         <f>(D65/365)*D25</f>
         <v/>
       </c>
-      <c r="E70" s="138" t="n"/>
-      <c r="F70" s="147" t="inlineStr">
+      <c r="E70" s="174" t="n"/>
+      <c r="F70" s="179" t="inlineStr">
         <is>
           <t>Tracks revenue changes while collection days stay flat.</t>
         </is>
@@ -3639,8 +3852,8 @@
         <f>(D66/365)*D26</f>
         <v/>
       </c>
-      <c r="E71" s="138" t="n"/>
-      <c r="F71" s="138" t="n"/>
+      <c r="E71" s="174" t="n"/>
+      <c r="F71" s="174" t="n"/>
       <c r="G71" s="42" t="n"/>
       <c r="H71" s="42" t="n"/>
     </row>
@@ -3662,8 +3875,8 @@
         <f>(D67/365)*D27</f>
         <v/>
       </c>
-      <c r="E72" s="138" t="n"/>
-      <c r="F72" s="138" t="n"/>
+      <c r="E72" s="174" t="n"/>
+      <c r="F72" s="174" t="n"/>
       <c r="G72" s="42" t="n"/>
       <c r="H72" s="42" t="n"/>
     </row>
@@ -3685,8 +3898,8 @@
         <f>(D68/365)*D28</f>
         <v/>
       </c>
-      <c r="E73" s="138" t="n"/>
-      <c r="F73" s="138" t="n"/>
+      <c r="E73" s="174" t="n"/>
+      <c r="F73" s="174" t="n"/>
       <c r="G73" s="42" t="n"/>
       <c r="H73" s="42" t="n"/>
     </row>
@@ -3708,8 +3921,8 @@
         <f>(D69/365)*D29</f>
         <v/>
       </c>
-      <c r="E74" s="138" t="n"/>
-      <c r="F74" s="138" t="n"/>
+      <c r="E74" s="174" t="n"/>
+      <c r="F74" s="174" t="n"/>
       <c r="G74" s="42" t="n"/>
       <c r="H74" s="42" t="n"/>
     </row>
@@ -3731,8 +3944,8 @@
         <f>D16-D17*1</f>
         <v/>
       </c>
-      <c r="E75" s="138" t="n"/>
-      <c r="F75" s="147" t="inlineStr">
+      <c r="E75" s="174" t="n"/>
+      <c r="F75" s="179" t="inlineStr">
         <is>
           <t>Falls one day per year across five years.</t>
         </is>
@@ -3758,8 +3971,8 @@
         <f>D16-D17*2</f>
         <v/>
       </c>
-      <c r="E76" s="138" t="n"/>
-      <c r="F76" s="138" t="n"/>
+      <c r="E76" s="174" t="n"/>
+      <c r="F76" s="174" t="n"/>
       <c r="G76" s="44" t="n"/>
       <c r="H76" s="44" t="n"/>
     </row>
@@ -3781,8 +3994,8 @@
         <f>D16-D17*3</f>
         <v/>
       </c>
-      <c r="E77" s="138" t="n"/>
-      <c r="F77" s="138" t="n"/>
+      <c r="E77" s="174" t="n"/>
+      <c r="F77" s="174" t="n"/>
       <c r="G77" s="44" t="n"/>
       <c r="H77" s="44" t="n"/>
     </row>
@@ -3804,8 +4017,8 @@
         <f>D16-D17*4</f>
         <v/>
       </c>
-      <c r="E78" s="138" t="n"/>
-      <c r="F78" s="138" t="n"/>
+      <c r="E78" s="174" t="n"/>
+      <c r="F78" s="174" t="n"/>
       <c r="G78" s="44" t="n"/>
       <c r="H78" s="44" t="n"/>
     </row>
@@ -3827,8 +4040,8 @@
         <f>D16-D17*5</f>
         <v/>
       </c>
-      <c r="E79" s="138" t="n"/>
-      <c r="F79" s="138" t="n"/>
+      <c r="E79" s="174" t="n"/>
+      <c r="F79" s="174" t="n"/>
       <c r="G79" s="44" t="n"/>
       <c r="H79" s="44" t="n"/>
     </row>
@@ -3850,8 +4063,8 @@
         <f>(D75/365)*D35</f>
         <v/>
       </c>
-      <c r="E80" s="138" t="n"/>
-      <c r="F80" s="147" t="inlineStr">
+      <c r="E80" s="174" t="n"/>
+      <c r="F80" s="179" t="inlineStr">
         <is>
           <t>Declines with DIO days: grows with rising COGS.</t>
         </is>
@@ -3877,8 +4090,8 @@
         <f>(D76/365)*D36</f>
         <v/>
       </c>
-      <c r="E81" s="138" t="n"/>
-      <c r="F81" s="138" t="n"/>
+      <c r="E81" s="174" t="n"/>
+      <c r="F81" s="174" t="n"/>
       <c r="G81" s="42" t="n"/>
       <c r="H81" s="42" t="n"/>
     </row>
@@ -3900,8 +4113,8 @@
         <f>(D77/365)*D37</f>
         <v/>
       </c>
-      <c r="E82" s="138" t="n"/>
-      <c r="F82" s="138" t="n"/>
+      <c r="E82" s="174" t="n"/>
+      <c r="F82" s="174" t="n"/>
       <c r="G82" s="42" t="n"/>
       <c r="H82" s="42" t="n"/>
     </row>
@@ -3923,8 +4136,8 @@
         <f>(D78/365)*D38</f>
         <v/>
       </c>
-      <c r="E83" s="138" t="n"/>
-      <c r="F83" s="138" t="n"/>
+      <c r="E83" s="174" t="n"/>
+      <c r="F83" s="174" t="n"/>
       <c r="G83" s="42" t="n"/>
       <c r="H83" s="42" t="n"/>
     </row>
@@ -3946,8 +4159,8 @@
         <f>(D79/365)*D39</f>
         <v/>
       </c>
-      <c r="E84" s="138" t="n"/>
-      <c r="F84" s="138" t="n"/>
+      <c r="E84" s="174" t="n"/>
+      <c r="F84" s="174" t="n"/>
       <c r="G84" s="42" t="n"/>
       <c r="H84" s="42" t="n"/>
     </row>
@@ -3969,8 +4182,8 @@
         <f>D18</f>
         <v/>
       </c>
-      <c r="E85" s="138" t="n"/>
-      <c r="F85" s="147" t="inlineStr">
+      <c r="E85" s="174" t="n"/>
+      <c r="F85" s="179" t="inlineStr">
         <is>
           <t>Held flat at twenty-five days every year.</t>
         </is>
@@ -3996,8 +4209,8 @@
         <f>D18</f>
         <v/>
       </c>
-      <c r="E86" s="138" t="n"/>
-      <c r="F86" s="138" t="n"/>
+      <c r="E86" s="174" t="n"/>
+      <c r="F86" s="174" t="n"/>
       <c r="G86" s="44" t="n"/>
       <c r="H86" s="44" t="n"/>
     </row>
@@ -4019,8 +4232,8 @@
         <f>D18</f>
         <v/>
       </c>
-      <c r="E87" s="138" t="n"/>
-      <c r="F87" s="138" t="n"/>
+      <c r="E87" s="174" t="n"/>
+      <c r="F87" s="174" t="n"/>
       <c r="G87" s="44" t="n"/>
       <c r="H87" s="44" t="n"/>
     </row>
@@ -4042,8 +4255,8 @@
         <f>D18</f>
         <v/>
       </c>
-      <c r="E88" s="138" t="n"/>
-      <c r="F88" s="138" t="n"/>
+      <c r="E88" s="174" t="n"/>
+      <c r="F88" s="174" t="n"/>
       <c r="G88" s="44" t="n"/>
       <c r="H88" s="44" t="n"/>
     </row>
@@ -4065,8 +4278,8 @@
         <f>D18</f>
         <v/>
       </c>
-      <c r="E89" s="138" t="n"/>
-      <c r="F89" s="138" t="n"/>
+      <c r="E89" s="174" t="n"/>
+      <c r="F89" s="174" t="n"/>
       <c r="G89" s="44" t="n"/>
       <c r="H89" s="44" t="n"/>
     </row>
@@ -4088,8 +4301,8 @@
         <f>(D85/365)*D35</f>
         <v/>
       </c>
-      <c r="E90" s="138" t="n"/>
-      <c r="F90" s="147" t="inlineStr">
+      <c r="E90" s="174" t="n"/>
+      <c r="F90" s="179" t="inlineStr">
         <is>
           <t>Grows with COGS while payment days remain flat.</t>
         </is>
@@ -4115,8 +4328,8 @@
         <f>(D86/365)*D36</f>
         <v/>
       </c>
-      <c r="E91" s="138" t="n"/>
-      <c r="F91" s="138" t="n"/>
+      <c r="E91" s="174" t="n"/>
+      <c r="F91" s="174" t="n"/>
       <c r="G91" s="42" t="n"/>
       <c r="H91" s="42" t="n"/>
     </row>
@@ -4138,8 +4351,8 @@
         <f>(D87/365)*D37</f>
         <v/>
       </c>
-      <c r="E92" s="138" t="n"/>
-      <c r="F92" s="138" t="n"/>
+      <c r="E92" s="174" t="n"/>
+      <c r="F92" s="174" t="n"/>
       <c r="G92" s="42" t="n"/>
       <c r="H92" s="42" t="n"/>
     </row>
@@ -4161,8 +4374,8 @@
         <f>(D88/365)*D38</f>
         <v/>
       </c>
-      <c r="E93" s="138" t="n"/>
-      <c r="F93" s="138" t="n"/>
+      <c r="E93" s="174" t="n"/>
+      <c r="F93" s="174" t="n"/>
       <c r="G93" s="42" t="n"/>
       <c r="H93" s="42" t="n"/>
     </row>
@@ -4184,8 +4397,8 @@
         <f>(D89/365)*D39</f>
         <v/>
       </c>
-      <c r="E94" s="138" t="n"/>
-      <c r="F94" s="138" t="n"/>
+      <c r="E94" s="174" t="n"/>
+      <c r="F94" s="174" t="n"/>
       <c r="G94" s="42" t="n"/>
       <c r="H94" s="42" t="n"/>
     </row>
@@ -4207,8 +4420,8 @@
         <f>D25*D19</f>
         <v/>
       </c>
-      <c r="E95" s="138" t="n"/>
-      <c r="F95" s="147" t="inlineStr">
+      <c r="E95" s="174" t="n"/>
+      <c r="F95" s="179" t="inlineStr">
         <is>
           <t>Grows at flat percent of revenue yearly.</t>
         </is>
@@ -4234,8 +4447,8 @@
         <f>D26*D19</f>
         <v/>
       </c>
-      <c r="E96" s="138" t="n"/>
-      <c r="F96" s="138" t="n"/>
+      <c r="E96" s="174" t="n"/>
+      <c r="F96" s="174" t="n"/>
       <c r="G96" s="42" t="n"/>
       <c r="H96" s="42" t="n"/>
     </row>
@@ -4257,8 +4470,8 @@
         <f>D27*D19</f>
         <v/>
       </c>
-      <c r="E97" s="138" t="n"/>
-      <c r="F97" s="138" t="n"/>
+      <c r="E97" s="174" t="n"/>
+      <c r="F97" s="174" t="n"/>
       <c r="G97" s="42" t="n"/>
       <c r="H97" s="42" t="n"/>
     </row>
@@ -4280,8 +4493,8 @@
         <f>D28*D19</f>
         <v/>
       </c>
-      <c r="E98" s="138" t="n"/>
-      <c r="F98" s="138" t="n"/>
+      <c r="E98" s="174" t="n"/>
+      <c r="F98" s="174" t="n"/>
       <c r="G98" s="42" t="n"/>
       <c r="H98" s="42" t="n"/>
     </row>
@@ -4303,8 +4516,8 @@
         <f>D29*D19</f>
         <v/>
       </c>
-      <c r="E99" s="138" t="n"/>
-      <c r="F99" s="138" t="n"/>
+      <c r="E99" s="174" t="n"/>
+      <c r="F99" s="174" t="n"/>
       <c r="G99" s="42" t="n"/>
       <c r="H99" s="42" t="n"/>
     </row>
@@ -4326,8 +4539,8 @@
         <f>D25*D20</f>
         <v/>
       </c>
-      <c r="E100" s="138" t="n"/>
-      <c r="F100" s="147" t="inlineStr">
+      <c r="E100" s="174" t="n"/>
+      <c r="F100" s="179" t="inlineStr">
         <is>
           <t>Grows at flat percent of revenue every year.</t>
         </is>
@@ -4353,8 +4566,8 @@
         <f>D26*D20</f>
         <v/>
       </c>
-      <c r="E101" s="138" t="n"/>
-      <c r="F101" s="138" t="n"/>
+      <c r="E101" s="174" t="n"/>
+      <c r="F101" s="174" t="n"/>
       <c r="G101" s="42" t="n"/>
       <c r="H101" s="42" t="n"/>
     </row>
@@ -4376,8 +4589,8 @@
         <f>D27*D20</f>
         <v/>
       </c>
-      <c r="E102" s="138" t="n"/>
-      <c r="F102" s="138" t="n"/>
+      <c r="E102" s="174" t="n"/>
+      <c r="F102" s="174" t="n"/>
       <c r="G102" s="42" t="n"/>
       <c r="H102" s="42" t="n"/>
     </row>
@@ -4399,8 +4612,8 @@
         <f>D28*D20</f>
         <v/>
       </c>
-      <c r="E103" s="138" t="n"/>
-      <c r="F103" s="138" t="n"/>
+      <c r="E103" s="174" t="n"/>
+      <c r="F103" s="174" t="n"/>
       <c r="G103" s="42" t="n"/>
       <c r="H103" s="42" t="n"/>
     </row>
@@ -4422,8 +4635,8 @@
         <f>D29*D20</f>
         <v/>
       </c>
-      <c r="E104" s="138" t="n"/>
-      <c r="F104" s="138" t="n"/>
+      <c r="E104" s="174" t="n"/>
+      <c r="F104" s="174" t="n"/>
       <c r="G104" s="42" t="n"/>
       <c r="H104" s="42" t="n"/>
     </row>
@@ -4445,8 +4658,8 @@
         <f>D70+D80+D95</f>
         <v/>
       </c>
-      <c r="E105" s="138" t="n"/>
-      <c r="F105" s="147" t="inlineStr">
+      <c r="E105" s="174" t="n"/>
+      <c r="F105" s="179" t="inlineStr">
         <is>
           <t>Rises as receivables, inventory, prepaids expand.</t>
         </is>
@@ -4472,8 +4685,8 @@
         <f>D71+D81+D96</f>
         <v/>
       </c>
-      <c r="E106" s="138" t="n"/>
-      <c r="F106" s="138" t="n"/>
+      <c r="E106" s="174" t="n"/>
+      <c r="F106" s="174" t="n"/>
       <c r="G106" s="42" t="n"/>
       <c r="H106" s="42" t="n"/>
     </row>
@@ -4495,8 +4708,8 @@
         <f>D72+D82+D97</f>
         <v/>
       </c>
-      <c r="E107" s="138" t="n"/>
-      <c r="F107" s="138" t="n"/>
+      <c r="E107" s="174" t="n"/>
+      <c r="F107" s="174" t="n"/>
       <c r="G107" s="42" t="n"/>
       <c r="H107" s="42" t="n"/>
     </row>
@@ -4518,8 +4731,8 @@
         <f>D73+D83+D98</f>
         <v/>
       </c>
-      <c r="E108" s="138" t="n"/>
-      <c r="F108" s="138" t="n"/>
+      <c r="E108" s="174" t="n"/>
+      <c r="F108" s="174" t="n"/>
       <c r="G108" s="42" t="n"/>
       <c r="H108" s="42" t="n"/>
     </row>
@@ -4541,8 +4754,8 @@
         <f>D74+D84+D99</f>
         <v/>
       </c>
-      <c r="E109" s="138" t="n"/>
-      <c r="F109" s="138" t="n"/>
+      <c r="E109" s="174" t="n"/>
+      <c r="F109" s="174" t="n"/>
       <c r="G109" s="42" t="n"/>
       <c r="H109" s="42" t="n"/>
     </row>
@@ -4564,8 +4777,8 @@
         <f>D90+D100</f>
         <v/>
       </c>
-      <c r="E110" s="138" t="n"/>
-      <c r="F110" s="147" t="inlineStr">
+      <c r="E110" s="174" t="n"/>
+      <c r="F110" s="179" t="inlineStr">
         <is>
           <t>Rises as payables and accruals grow with sales.</t>
         </is>
@@ -4591,8 +4804,8 @@
         <f>D91+D101</f>
         <v/>
       </c>
-      <c r="E111" s="138" t="n"/>
-      <c r="F111" s="138" t="n"/>
+      <c r="E111" s="174" t="n"/>
+      <c r="F111" s="174" t="n"/>
       <c r="G111" s="42" t="n"/>
       <c r="H111" s="42" t="n"/>
     </row>
@@ -4614,8 +4827,8 @@
         <f>D92+D102</f>
         <v/>
       </c>
-      <c r="E112" s="138" t="n"/>
-      <c r="F112" s="138" t="n"/>
+      <c r="E112" s="174" t="n"/>
+      <c r="F112" s="174" t="n"/>
       <c r="G112" s="42" t="n"/>
       <c r="H112" s="42" t="n"/>
     </row>
@@ -4637,8 +4850,8 @@
         <f>D93+D103</f>
         <v/>
       </c>
-      <c r="E113" s="138" t="n"/>
-      <c r="F113" s="138" t="n"/>
+      <c r="E113" s="174" t="n"/>
+      <c r="F113" s="174" t="n"/>
       <c r="G113" s="42" t="n"/>
       <c r="H113" s="42" t="n"/>
     </row>
@@ -4660,8 +4873,8 @@
         <f>D94+D104</f>
         <v/>
       </c>
-      <c r="E114" s="138" t="n"/>
-      <c r="F114" s="138" t="n"/>
+      <c r="E114" s="174" t="n"/>
+      <c r="F114" s="174" t="n"/>
       <c r="G114" s="42" t="n"/>
       <c r="H114" s="42" t="n"/>
     </row>
@@ -4683,8 +4896,8 @@
         <f>D105-D110</f>
         <v/>
       </c>
-      <c r="E115" s="138" t="n"/>
-      <c r="F115" s="147" t="inlineStr">
+      <c r="E115" s="174" t="n"/>
+      <c r="F115" s="179" t="inlineStr">
         <is>
           <t>Operating assets minus liabilities: level shifts yearly.</t>
         </is>
@@ -4710,8 +4923,8 @@
         <f>D106-D111</f>
         <v/>
       </c>
-      <c r="E116" s="138" t="n"/>
-      <c r="F116" s="138" t="n"/>
+      <c r="E116" s="174" t="n"/>
+      <c r="F116" s="174" t="n"/>
       <c r="G116" s="42" t="n"/>
       <c r="H116" s="42" t="n"/>
     </row>
@@ -4733,8 +4946,8 @@
         <f>D107-D112</f>
         <v/>
       </c>
-      <c r="E117" s="138" t="n"/>
-      <c r="F117" s="138" t="n"/>
+      <c r="E117" s="174" t="n"/>
+      <c r="F117" s="174" t="n"/>
       <c r="G117" s="42" t="n"/>
       <c r="H117" s="42" t="n"/>
     </row>
@@ -4756,8 +4969,8 @@
         <f>D108-D113</f>
         <v/>
       </c>
-      <c r="E118" s="138" t="n"/>
-      <c r="F118" s="138" t="n"/>
+      <c r="E118" s="174" t="n"/>
+      <c r="F118" s="174" t="n"/>
       <c r="G118" s="42" t="n"/>
       <c r="H118" s="42" t="n"/>
     </row>
@@ -4779,8 +4992,8 @@
         <f>D109-D114</f>
         <v/>
       </c>
-      <c r="E119" s="138" t="n"/>
-      <c r="F119" s="138" t="n"/>
+      <c r="E119" s="174" t="n"/>
+      <c r="F119" s="174" t="n"/>
       <c r="G119" s="42" t="n"/>
       <c r="H119" s="42" t="n"/>
     </row>
@@ -4802,8 +5015,8 @@
         <f>DCF!$E$32-D115</f>
         <v/>
       </c>
-      <c r="E120" s="138" t="n"/>
-      <c r="F120" s="147" t="inlineStr">
+      <c r="E120" s="174" t="n"/>
+      <c r="F120" s="179" t="inlineStr">
         <is>
           <t>Prior minus current NWC: positive releases cash.</t>
         </is>
@@ -4829,8 +5042,8 @@
         <f>D115-D116</f>
         <v/>
       </c>
-      <c r="E121" s="138" t="n"/>
-      <c r="F121" s="138" t="n"/>
+      <c r="E121" s="174" t="n"/>
+      <c r="F121" s="174" t="n"/>
       <c r="G121" s="42" t="n"/>
       <c r="H121" s="42" t="n"/>
     </row>
@@ -4852,8 +5065,8 @@
         <f>D116-D117</f>
         <v/>
       </c>
-      <c r="E122" s="138" t="n"/>
-      <c r="F122" s="138" t="n"/>
+      <c r="E122" s="174" t="n"/>
+      <c r="F122" s="174" t="n"/>
       <c r="G122" s="42" t="n"/>
       <c r="H122" s="42" t="n"/>
     </row>
@@ -4875,8 +5088,8 @@
         <f>D117-D118</f>
         <v/>
       </c>
-      <c r="E123" s="138" t="n"/>
-      <c r="F123" s="138" t="n"/>
+      <c r="E123" s="174" t="n"/>
+      <c r="F123" s="174" t="n"/>
       <c r="G123" s="42" t="n"/>
       <c r="H123" s="42" t="n"/>
     </row>
@@ -4898,8 +5111,8 @@
         <f>D118-D119</f>
         <v/>
       </c>
-      <c r="E124" s="138" t="n"/>
-      <c r="F124" s="138" t="n"/>
+      <c r="E124" s="174" t="n"/>
+      <c r="F124" s="174" t="n"/>
       <c r="G124" s="42" t="n"/>
       <c r="H124" s="42" t="n"/>
     </row>
@@ -4921,8 +5134,8 @@
         <f>D50+D55-D60+D120</f>
         <v/>
       </c>
-      <c r="E125" s="138" t="n"/>
-      <c r="F125" s="147" t="inlineStr">
+      <c r="E125" s="174" t="n"/>
+      <c r="F125" s="179" t="inlineStr">
         <is>
           <t>NOPAT plus depreciation minus capex plus working capital.</t>
         </is>
@@ -4948,8 +5161,8 @@
         <f>D51+D56-D61+D121</f>
         <v/>
       </c>
-      <c r="E126" s="138" t="n"/>
-      <c r="F126" s="138" t="n"/>
+      <c r="E126" s="174" t="n"/>
+      <c r="F126" s="174" t="n"/>
       <c r="G126" s="42" t="n"/>
       <c r="H126" s="42" t="n"/>
     </row>
@@ -4971,8 +5184,8 @@
         <f>D52+D57-D62+D122</f>
         <v/>
       </c>
-      <c r="E127" s="138" t="n"/>
-      <c r="F127" s="138" t="n"/>
+      <c r="E127" s="174" t="n"/>
+      <c r="F127" s="174" t="n"/>
       <c r="G127" s="42" t="n"/>
       <c r="H127" s="42" t="n"/>
     </row>
@@ -4994,8 +5207,8 @@
         <f>D53+D58-D63+D123</f>
         <v/>
       </c>
-      <c r="E128" s="138" t="n"/>
-      <c r="F128" s="138" t="n"/>
+      <c r="E128" s="174" t="n"/>
+      <c r="F128" s="174" t="n"/>
       <c r="G128" s="42" t="n"/>
       <c r="H128" s="42" t="n"/>
     </row>
@@ -5017,18 +5230,20 @@
         <f>D54+D59-D64+D124</f>
         <v/>
       </c>
-      <c r="E129" s="138" t="n"/>
-      <c r="F129" s="138" t="n"/>
+      <c r="E129" s="174" t="n"/>
+      <c r="F129" s="174" t="n"/>
       <c r="G129" s="42" t="n"/>
       <c r="H129" s="42" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="138" t="n"/>
-      <c r="B130" s="138" t="n"/>
-      <c r="C130" s="138" t="n"/>
-      <c r="D130" s="138" t="n"/>
-      <c r="E130" s="138" t="n"/>
-      <c r="F130" s="138" t="n"/>
+      <c r="A130" s="174" t="n"/>
+      <c r="B130" s="174" t="n"/>
+      <c r="C130" s="174" t="n"/>
+      <c r="D130" s="174" t="n"/>
+      <c r="E130" s="174" t="n"/>
+      <c r="F130" s="174" t="n"/>
+      <c r="G130" s="171" t="n"/>
+      <c r="H130" s="171" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="157" t="inlineStr">
@@ -5048,8 +5263,8 @@
         <f>NPV(D9,D125,D126,D127,D128,D129)+(D129*(1+D10)/(D9-D10))/(1+D9)^5</f>
         <v/>
       </c>
-      <c r="E131" s="138" t="n"/>
-      <c r="F131" s="138" t="n"/>
+      <c r="E131" s="174" t="n"/>
+      <c r="F131" s="174" t="n"/>
       <c r="G131" s="25" t="n"/>
       <c r="H131" s="25" t="n"/>
     </row>
@@ -5071,8 +5286,8 @@
         <f>(D131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
         <v/>
       </c>
-      <c r="E132" s="138" t="n"/>
-      <c r="F132" s="138" t="n"/>
+      <c r="E132" s="174" t="n"/>
+      <c r="F132" s="174" t="n"/>
       <c r="G132" s="47" t="n"/>
       <c r="H132" s="46" t="n"/>
     </row>
@@ -5094,18 +5309,20 @@
         <f>D132/100.0-1</f>
         <v/>
       </c>
-      <c r="E133" s="138" t="n"/>
-      <c r="F133" s="138" t="n"/>
+      <c r="E133" s="174" t="n"/>
+      <c r="F133" s="174" t="n"/>
       <c r="G133" s="48" t="n"/>
       <c r="H133" s="48" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="138" t="n"/>
-      <c r="B134" s="138" t="n"/>
-      <c r="C134" s="138" t="n"/>
-      <c r="D134" s="138" t="n"/>
-      <c r="E134" s="138" t="n"/>
-      <c r="F134" s="138" t="n"/>
+      <c r="A134" s="174" t="n"/>
+      <c r="B134" s="174" t="n"/>
+      <c r="C134" s="174" t="n"/>
+      <c r="D134" s="174" t="n"/>
+      <c r="E134" s="174" t="n"/>
+      <c r="F134" s="174" t="n"/>
+      <c r="G134" s="171" t="n"/>
+      <c r="H134" s="171" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="163" t="inlineStr">
@@ -5113,19 +5330,23 @@
           <t>Current price $100.00; cash $1,807,202 k; lease debt $1,798,441 k; funded debt $0; net cash $8,761 k.</t>
         </is>
       </c>
-      <c r="B135" s="138" t="n"/>
-      <c r="C135" s="138" t="n"/>
-      <c r="D135" s="138" t="n"/>
-      <c r="E135" s="138" t="n"/>
-      <c r="F135" s="138" t="n"/>
+      <c r="B135" s="174" t="n"/>
+      <c r="C135" s="174" t="n"/>
+      <c r="D135" s="174" t="n"/>
+      <c r="E135" s="174" t="n"/>
+      <c r="F135" s="174" t="n"/>
+      <c r="G135" s="171" t="n"/>
+      <c r="H135" s="171" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="138" t="n"/>
-      <c r="B136" s="138" t="n"/>
-      <c r="C136" s="138" t="n"/>
-      <c r="D136" s="138" t="n"/>
-      <c r="E136" s="138" t="n"/>
-      <c r="F136" s="138" t="n"/>
+      <c r="A136" s="174" t="n"/>
+      <c r="B136" s="174" t="n"/>
+      <c r="C136" s="174" t="n"/>
+      <c r="D136" s="174" t="n"/>
+      <c r="E136" s="174" t="n"/>
+      <c r="F136" s="174" t="n"/>
+      <c r="G136" s="171" t="n"/>
+      <c r="H136" s="171" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="142" t="inlineStr">
@@ -5133,11 +5354,13 @@
           <t>Pitch deck bridge (IS / CFS / BS)</t>
         </is>
       </c>
-      <c r="B137" s="138" t="n"/>
-      <c r="C137" s="138" t="n"/>
-      <c r="D137" s="138" t="n"/>
-      <c r="E137" s="138" t="n"/>
-      <c r="F137" s="138" t="n"/>
+      <c r="B137" s="174" t="n"/>
+      <c r="C137" s="174" t="n"/>
+      <c r="D137" s="174" t="n"/>
+      <c r="E137" s="174" t="n"/>
+      <c r="F137" s="174" t="n"/>
+      <c r="G137" s="171" t="n"/>
+      <c r="H137" s="171" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="153" t="inlineStr">
@@ -5154,8 +5377,8 @@
       <c r="D138" s="154" t="n">
         <v>45000</v>
       </c>
-      <c r="E138" s="138" t="n"/>
-      <c r="F138" s="138" t="n"/>
+      <c r="E138" s="174" t="n"/>
+      <c r="F138" s="174" t="n"/>
       <c r="G138" s="42" t="n"/>
       <c r="H138" s="42" t="n"/>
     </row>
@@ -5174,8 +5397,8 @@
       <c r="D139" s="154" t="n">
         <v>40000</v>
       </c>
-      <c r="E139" s="138" t="n"/>
-      <c r="F139" s="138" t="n"/>
+      <c r="E139" s="174" t="n"/>
+      <c r="F139" s="174" t="n"/>
       <c r="G139" s="42" t="n"/>
       <c r="H139" s="42" t="n"/>
     </row>
@@ -5194,8 +5417,8 @@
       <c r="D140" s="154" t="n">
         <v>35000</v>
       </c>
-      <c r="E140" s="138" t="n"/>
-      <c r="F140" s="138" t="n"/>
+      <c r="E140" s="174" t="n"/>
+      <c r="F140" s="174" t="n"/>
       <c r="G140" s="42" t="n"/>
       <c r="H140" s="42" t="n"/>
     </row>
@@ -5214,8 +5437,8 @@
       <c r="D141" s="154" t="n">
         <v>30000</v>
       </c>
-      <c r="E141" s="138" t="n"/>
-      <c r="F141" s="138" t="n"/>
+      <c r="E141" s="174" t="n"/>
+      <c r="F141" s="174" t="n"/>
       <c r="G141" s="42" t="n"/>
       <c r="H141" s="42" t="n"/>
     </row>
@@ -5234,8 +5457,8 @@
       <c r="D142" s="154" t="n">
         <v>25000</v>
       </c>
-      <c r="E142" s="138" t="n"/>
-      <c r="F142" s="138" t="n"/>
+      <c r="E142" s="174" t="n"/>
+      <c r="F142" s="174" t="n"/>
       <c r="G142" s="42" t="n"/>
       <c r="H142" s="42" t="n"/>
     </row>
@@ -5257,8 +5480,8 @@
         <f>(D45+D138)*(1-D11)</f>
         <v/>
       </c>
-      <c r="E143" s="138" t="n"/>
-      <c r="F143" s="138" t="n"/>
+      <c r="E143" s="174" t="n"/>
+      <c r="F143" s="174" t="n"/>
       <c r="G143" s="42" t="n"/>
       <c r="H143" s="42" t="n"/>
     </row>
@@ -5280,8 +5503,8 @@
         <f>(D46+D139)*(1-D11)</f>
         <v/>
       </c>
-      <c r="E144" s="138" t="n"/>
-      <c r="F144" s="138" t="n"/>
+      <c r="E144" s="174" t="n"/>
+      <c r="F144" s="174" t="n"/>
       <c r="G144" s="42" t="n"/>
       <c r="H144" s="42" t="n"/>
     </row>
@@ -5303,8 +5526,8 @@
         <f>(D47+D140)*(1-D11)</f>
         <v/>
       </c>
-      <c r="E145" s="138" t="n"/>
-      <c r="F145" s="138" t="n"/>
+      <c r="E145" s="174" t="n"/>
+      <c r="F145" s="174" t="n"/>
       <c r="G145" s="42" t="n"/>
       <c r="H145" s="42" t="n"/>
     </row>
@@ -5326,8 +5549,8 @@
         <f>(D48+D141)*(1-D11)</f>
         <v/>
       </c>
-      <c r="E146" s="138" t="n"/>
-      <c r="F146" s="138" t="n"/>
+      <c r="E146" s="174" t="n"/>
+      <c r="F146" s="174" t="n"/>
       <c r="G146" s="42" t="n"/>
       <c r="H146" s="42" t="n"/>
     </row>
@@ -5349,8 +5572,8 @@
         <f>(D49+D142)*(1-D11)</f>
         <v/>
       </c>
-      <c r="E147" s="138" t="n"/>
-      <c r="F147" s="138" t="n"/>
+      <c r="E147" s="174" t="n"/>
+      <c r="F147" s="174" t="n"/>
       <c r="G147" s="42" t="n"/>
       <c r="H147" s="42" t="n"/>
     </row>
@@ -5372,8 +5595,8 @@
         <f>D143+D55+D120</f>
         <v/>
       </c>
-      <c r="E148" s="138" t="n"/>
-      <c r="F148" s="138" t="n"/>
+      <c r="E148" s="174" t="n"/>
+      <c r="F148" s="174" t="n"/>
       <c r="G148" s="42" t="n"/>
       <c r="H148" s="42" t="n"/>
     </row>
@@ -5395,8 +5618,8 @@
         <f>D144+D56+D121</f>
         <v/>
       </c>
-      <c r="E149" s="138" t="n"/>
-      <c r="F149" s="138" t="n"/>
+      <c r="E149" s="174" t="n"/>
+      <c r="F149" s="174" t="n"/>
       <c r="G149" s="42" t="n"/>
       <c r="H149" s="42" t="n"/>
     </row>
@@ -5418,8 +5641,8 @@
         <f>D145+D57+D122</f>
         <v/>
       </c>
-      <c r="E150" s="138" t="n"/>
-      <c r="F150" s="138" t="n"/>
+      <c r="E150" s="174" t="n"/>
+      <c r="F150" s="174" t="n"/>
       <c r="G150" s="42" t="n"/>
       <c r="H150" s="42" t="n"/>
     </row>
@@ -5441,8 +5664,8 @@
         <f>D146+D58+D123</f>
         <v/>
       </c>
-      <c r="E151" s="138" t="n"/>
-      <c r="F151" s="138" t="n"/>
+      <c r="E151" s="174" t="n"/>
+      <c r="F151" s="174" t="n"/>
       <c r="G151" s="42" t="n"/>
       <c r="H151" s="42" t="n"/>
     </row>
@@ -5464,8 +5687,8 @@
         <f>D147+D59+D124</f>
         <v/>
       </c>
-      <c r="E152" s="138" t="n"/>
-      <c r="F152" s="138" t="n"/>
+      <c r="E152" s="174" t="n"/>
+      <c r="F152" s="174" t="n"/>
       <c r="G152" s="42" t="n"/>
       <c r="H152" s="42" t="n"/>
     </row>
@@ -5487,8 +5710,8 @@
         <f>D148-D60</f>
         <v/>
       </c>
-      <c r="E153" s="138" t="n"/>
-      <c r="F153" s="138" t="n"/>
+      <c r="E153" s="174" t="n"/>
+      <c r="F153" s="174" t="n"/>
       <c r="G153" s="42" t="n"/>
       <c r="H153" s="42" t="n"/>
     </row>
@@ -5510,8 +5733,8 @@
         <f>D149-D61</f>
         <v/>
       </c>
-      <c r="E154" s="138" t="n"/>
-      <c r="F154" s="138" t="n"/>
+      <c r="E154" s="174" t="n"/>
+      <c r="F154" s="174" t="n"/>
       <c r="G154" s="42" t="n"/>
       <c r="H154" s="42" t="n"/>
     </row>
@@ -5533,8 +5756,8 @@
         <f>D150-D62</f>
         <v/>
       </c>
-      <c r="E155" s="138" t="n"/>
-      <c r="F155" s="138" t="n"/>
+      <c r="E155" s="174" t="n"/>
+      <c r="F155" s="174" t="n"/>
       <c r="G155" s="42" t="n"/>
       <c r="H155" s="42" t="n"/>
     </row>
@@ -5556,8 +5779,8 @@
         <f>D151-D63</f>
         <v/>
       </c>
-      <c r="E156" s="138" t="n"/>
-      <c r="F156" s="138" t="n"/>
+      <c r="E156" s="174" t="n"/>
+      <c r="F156" s="174" t="n"/>
       <c r="G156" s="42" t="n"/>
       <c r="H156" s="42" t="n"/>
     </row>
@@ -5579,8 +5802,8 @@
         <f>D152-D64</f>
         <v/>
       </c>
-      <c r="E157" s="138" t="n"/>
-      <c r="F157" s="138" t="n"/>
+      <c r="E157" s="174" t="n"/>
+      <c r="F157" s="174" t="n"/>
       <c r="G157" s="42" t="n"/>
       <c r="H157" s="42" t="n"/>
     </row>
@@ -5602,8 +5825,8 @@
         <f>-D22*D153</f>
         <v/>
       </c>
-      <c r="E158" s="138" t="n"/>
-      <c r="F158" s="138" t="n"/>
+      <c r="E158" s="174" t="n"/>
+      <c r="F158" s="174" t="n"/>
       <c r="G158" s="42" t="n"/>
       <c r="H158" s="42" t="n"/>
     </row>
@@ -5625,8 +5848,8 @@
         <f>-D22*D154</f>
         <v/>
       </c>
-      <c r="E159" s="138" t="n"/>
-      <c r="F159" s="138" t="n"/>
+      <c r="E159" s="174" t="n"/>
+      <c r="F159" s="174" t="n"/>
       <c r="G159" s="42" t="n"/>
       <c r="H159" s="42" t="n"/>
     </row>
@@ -5648,8 +5871,8 @@
         <f>-D22*D155</f>
         <v/>
       </c>
-      <c r="E160" s="138" t="n"/>
-      <c r="F160" s="138" t="n"/>
+      <c r="E160" s="174" t="n"/>
+      <c r="F160" s="174" t="n"/>
       <c r="G160" s="42" t="n"/>
       <c r="H160" s="42" t="n"/>
     </row>
@@ -5671,8 +5894,8 @@
         <f>-D22*D156</f>
         <v/>
       </c>
-      <c r="E161" s="138" t="n"/>
-      <c r="F161" s="138" t="n"/>
+      <c r="E161" s="174" t="n"/>
+      <c r="F161" s="174" t="n"/>
       <c r="G161" s="42" t="n"/>
       <c r="H161" s="42" t="n"/>
     </row>
@@ -5694,8 +5917,8 @@
         <f>-D22*D157</f>
         <v/>
       </c>
-      <c r="E162" s="138" t="n"/>
-      <c r="F162" s="138" t="n"/>
+      <c r="E162" s="174" t="n"/>
+      <c r="F162" s="174" t="n"/>
       <c r="G162" s="42" t="n"/>
       <c r="H162" s="42" t="n"/>
     </row>
@@ -5717,8 +5940,8 @@
         <f>DCF!$E$50+D153+D158</f>
         <v/>
       </c>
-      <c r="E163" s="138" t="n"/>
-      <c r="F163" s="138" t="n"/>
+      <c r="E163" s="174" t="n"/>
+      <c r="F163" s="174" t="n"/>
       <c r="G163" s="42" t="n"/>
       <c r="H163" s="42" t="n"/>
     </row>
@@ -5740,8 +5963,8 @@
         <f>D163+D154+D159</f>
         <v/>
       </c>
-      <c r="E164" s="138" t="n"/>
-      <c r="F164" s="138" t="n"/>
+      <c r="E164" s="174" t="n"/>
+      <c r="F164" s="174" t="n"/>
       <c r="G164" s="42" t="n"/>
       <c r="H164" s="42" t="n"/>
     </row>
@@ -5763,8 +5986,8 @@
         <f>D164+D155+D160</f>
         <v/>
       </c>
-      <c r="E165" s="138" t="n"/>
-      <c r="F165" s="138" t="n"/>
+      <c r="E165" s="174" t="n"/>
+      <c r="F165" s="174" t="n"/>
       <c r="G165" s="42" t="n"/>
       <c r="H165" s="42" t="n"/>
     </row>
@@ -5786,8 +6009,8 @@
         <f>D165+D156+D161</f>
         <v/>
       </c>
-      <c r="E166" s="138" t="n"/>
-      <c r="F166" s="138" t="n"/>
+      <c r="E166" s="174" t="n"/>
+      <c r="F166" s="174" t="n"/>
       <c r="G166" s="42" t="n"/>
       <c r="H166" s="42" t="n"/>
     </row>
@@ -5809,8 +6032,8 @@
         <f>D166+D157+D162</f>
         <v/>
       </c>
-      <c r="E167" s="138" t="n"/>
-      <c r="F167" s="138" t="n"/>
+      <c r="E167" s="174" t="n"/>
+      <c r="F167" s="174" t="n"/>
       <c r="G167" s="42" t="n"/>
       <c r="H167" s="42" t="n"/>
     </row>
@@ -5832,8 +6055,8 @@
         <f>$B$194*D25/$B$198</f>
         <v/>
       </c>
-      <c r="E168" s="138" t="n"/>
-      <c r="F168" s="138" t="n"/>
+      <c r="E168" s="174" t="n"/>
+      <c r="F168" s="174" t="n"/>
       <c r="G168" s="42" t="n"/>
       <c r="H168" s="42" t="n"/>
     </row>
@@ -5855,8 +6078,8 @@
         <f>$B$194*D26/$B$198</f>
         <v/>
       </c>
-      <c r="E169" s="138" t="n"/>
-      <c r="F169" s="138" t="n"/>
+      <c r="E169" s="174" t="n"/>
+      <c r="F169" s="174" t="n"/>
       <c r="G169" s="42" t="n"/>
       <c r="H169" s="42" t="n"/>
     </row>
@@ -5878,8 +6101,8 @@
         <f>$B$194*D27/$B$198</f>
         <v/>
       </c>
-      <c r="E170" s="138" t="n"/>
-      <c r="F170" s="138" t="n"/>
+      <c r="E170" s="174" t="n"/>
+      <c r="F170" s="174" t="n"/>
       <c r="G170" s="42" t="n"/>
       <c r="H170" s="42" t="n"/>
     </row>
@@ -5901,8 +6124,8 @@
         <f>$B$194*D28/$B$198</f>
         <v/>
       </c>
-      <c r="E171" s="138" t="n"/>
-      <c r="F171" s="138" t="n"/>
+      <c r="E171" s="174" t="n"/>
+      <c r="F171" s="174" t="n"/>
       <c r="G171" s="42" t="n"/>
       <c r="H171" s="42" t="n"/>
     </row>
@@ -5924,8 +6147,8 @@
         <f>$B$194*D29/$B$198</f>
         <v/>
       </c>
-      <c r="E172" s="138" t="n"/>
-      <c r="F172" s="138" t="n"/>
+      <c r="E172" s="174" t="n"/>
+      <c r="F172" s="174" t="n"/>
       <c r="G172" s="42" t="n"/>
       <c r="H172" s="42" t="n"/>
     </row>
@@ -5947,8 +6170,8 @@
         <f>$B$195*D25/$B$198</f>
         <v/>
       </c>
-      <c r="E173" s="138" t="n"/>
-      <c r="F173" s="138" t="n"/>
+      <c r="E173" s="174" t="n"/>
+      <c r="F173" s="174" t="n"/>
       <c r="G173" s="42" t="n"/>
       <c r="H173" s="42" t="n"/>
     </row>
@@ -5970,8 +6193,8 @@
         <f>$B$195*D26/$B$198</f>
         <v/>
       </c>
-      <c r="E174" s="138" t="n"/>
-      <c r="F174" s="138" t="n"/>
+      <c r="E174" s="174" t="n"/>
+      <c r="F174" s="174" t="n"/>
       <c r="G174" s="42" t="n"/>
       <c r="H174" s="42" t="n"/>
     </row>
@@ -5993,8 +6216,8 @@
         <f>$B$195*D27/$B$198</f>
         <v/>
       </c>
-      <c r="E175" s="138" t="n"/>
-      <c r="F175" s="138" t="n"/>
+      <c r="E175" s="174" t="n"/>
+      <c r="F175" s="174" t="n"/>
       <c r="G175" s="42" t="n"/>
       <c r="H175" s="42" t="n"/>
     </row>
@@ -6016,8 +6239,8 @@
         <f>$B$195*D28/$B$198</f>
         <v/>
       </c>
-      <c r="E176" s="138" t="n"/>
-      <c r="F176" s="138" t="n"/>
+      <c r="E176" s="174" t="n"/>
+      <c r="F176" s="174" t="n"/>
       <c r="G176" s="42" t="n"/>
       <c r="H176" s="42" t="n"/>
     </row>
@@ -6039,8 +6262,8 @@
         <f>$B$195*D29/$B$198</f>
         <v/>
       </c>
-      <c r="E177" s="138" t="n"/>
-      <c r="F177" s="138" t="n"/>
+      <c r="E177" s="174" t="n"/>
+      <c r="F177" s="174" t="n"/>
       <c r="G177" s="42" t="n"/>
       <c r="H177" s="42" t="n"/>
     </row>
@@ -6062,8 +6285,8 @@
         <f>$B$196*D25/$B$198</f>
         <v/>
       </c>
-      <c r="E178" s="138" t="n"/>
-      <c r="F178" s="138" t="n"/>
+      <c r="E178" s="174" t="n"/>
+      <c r="F178" s="174" t="n"/>
       <c r="G178" s="42" t="n"/>
       <c r="H178" s="42" t="n"/>
     </row>
@@ -6085,8 +6308,8 @@
         <f>$B$196*D26/$B$198</f>
         <v/>
       </c>
-      <c r="E179" s="138" t="n"/>
-      <c r="F179" s="138" t="n"/>
+      <c r="E179" s="174" t="n"/>
+      <c r="F179" s="174" t="n"/>
       <c r="G179" s="42" t="n"/>
       <c r="H179" s="42" t="n"/>
     </row>
@@ -6108,8 +6331,8 @@
         <f>$B$196*D27/$B$198</f>
         <v/>
       </c>
-      <c r="E180" s="138" t="n"/>
-      <c r="F180" s="138" t="n"/>
+      <c r="E180" s="174" t="n"/>
+      <c r="F180" s="174" t="n"/>
       <c r="G180" s="42" t="n"/>
       <c r="H180" s="42" t="n"/>
     </row>
@@ -6131,8 +6354,8 @@
         <f>$B$196*D28/$B$198</f>
         <v/>
       </c>
-      <c r="E181" s="138" t="n"/>
-      <c r="F181" s="138" t="n"/>
+      <c r="E181" s="174" t="n"/>
+      <c r="F181" s="174" t="n"/>
       <c r="G181" s="42" t="n"/>
       <c r="H181" s="42" t="n"/>
     </row>
@@ -6154,8 +6377,8 @@
         <f>$B$196*D29/$B$198</f>
         <v/>
       </c>
-      <c r="E182" s="138" t="n"/>
-      <c r="F182" s="138" t="n"/>
+      <c r="E182" s="174" t="n"/>
+      <c r="F182" s="174" t="n"/>
       <c r="G182" s="42" t="n"/>
       <c r="H182" s="42" t="n"/>
     </row>
@@ -6177,8 +6400,8 @@
         <f>$B$197-D22*D153/100</f>
         <v/>
       </c>
-      <c r="E183" s="138" t="n"/>
-      <c r="F183" s="138" t="n"/>
+      <c r="E183" s="174" t="n"/>
+      <c r="F183" s="174" t="n"/>
       <c r="G183" s="42" t="n"/>
       <c r="H183" s="42" t="n"/>
     </row>
@@ -6200,8 +6423,8 @@
         <f>D183-D22*D154/108</f>
         <v/>
       </c>
-      <c r="E184" s="138" t="n"/>
-      <c r="F184" s="138" t="n"/>
+      <c r="E184" s="174" t="n"/>
+      <c r="F184" s="174" t="n"/>
       <c r="G184" s="42" t="n"/>
       <c r="H184" s="42" t="n"/>
     </row>
@@ -6223,8 +6446,8 @@
         <f>D184-D22*D155/115</f>
         <v/>
       </c>
-      <c r="E185" s="138" t="n"/>
-      <c r="F185" s="138" t="n"/>
+      <c r="E185" s="174" t="n"/>
+      <c r="F185" s="174" t="n"/>
       <c r="G185" s="42" t="n"/>
       <c r="H185" s="42" t="n"/>
     </row>
@@ -6246,8 +6469,8 @@
         <f>D185-D22*D156/122</f>
         <v/>
       </c>
-      <c r="E186" s="138" t="n"/>
-      <c r="F186" s="138" t="n"/>
+      <c r="E186" s="174" t="n"/>
+      <c r="F186" s="174" t="n"/>
       <c r="G186" s="42" t="n"/>
       <c r="H186" s="42" t="n"/>
     </row>
@@ -6269,8 +6492,8 @@
         <f>D186-D22*D157/130</f>
         <v/>
       </c>
-      <c r="E187" s="138" t="n"/>
-      <c r="F187" s="138" t="n"/>
+      <c r="E187" s="174" t="n"/>
+      <c r="F187" s="174" t="n"/>
       <c r="G187" s="42" t="n"/>
       <c r="H187" s="42" t="n"/>
     </row>
@@ -6292,8 +6515,8 @@
         <f>D143/D183</f>
         <v/>
       </c>
-      <c r="E188" s="138" t="n"/>
-      <c r="F188" s="138" t="n"/>
+      <c r="E188" s="174" t="n"/>
+      <c r="F188" s="174" t="n"/>
       <c r="G188" s="49" t="n"/>
       <c r="H188" s="49" t="n"/>
     </row>
@@ -6315,8 +6538,8 @@
         <f>D144/D184</f>
         <v/>
       </c>
-      <c r="E189" s="138" t="n"/>
-      <c r="F189" s="138" t="n"/>
+      <c r="E189" s="174" t="n"/>
+      <c r="F189" s="174" t="n"/>
       <c r="G189" s="49" t="n"/>
       <c r="H189" s="49" t="n"/>
     </row>
@@ -6338,8 +6561,8 @@
         <f>D145/D185</f>
         <v/>
       </c>
-      <c r="E190" s="138" t="n"/>
-      <c r="F190" s="138" t="n"/>
+      <c r="E190" s="174" t="n"/>
+      <c r="F190" s="174" t="n"/>
       <c r="G190" s="49" t="n"/>
       <c r="H190" s="49" t="n"/>
     </row>
@@ -6361,8 +6584,8 @@
         <f>D146/D186</f>
         <v/>
       </c>
-      <c r="E191" s="138" t="n"/>
-      <c r="F191" s="138" t="n"/>
+      <c r="E191" s="174" t="n"/>
+      <c r="F191" s="174" t="n"/>
       <c r="G191" s="49" t="n"/>
       <c r="H191" s="49" t="n"/>
     </row>
@@ -6384,8 +6607,8 @@
         <f>D147/D187</f>
         <v/>
       </c>
-      <c r="E192" s="138" t="n"/>
-      <c r="F192" s="138" t="n"/>
+      <c r="E192" s="174" t="n"/>
+      <c r="F192" s="174" t="n"/>
       <c r="G192" s="49" t="n"/>
       <c r="H192" s="49" t="n"/>
     </row>
@@ -6395,147 +6618,169 @@
           <t>FY25 anchors (drivers — do not edit without source)</t>
         </is>
       </c>
-      <c r="B193" s="138" t="n"/>
-      <c r="C193" s="138" t="n"/>
-      <c r="D193" s="138" t="n"/>
-      <c r="E193" s="138" t="n"/>
-      <c r="F193" s="138" t="n"/>
+      <c r="B193" s="174" t="n"/>
+      <c r="C193" s="174" t="n"/>
+      <c r="D193" s="174" t="n"/>
+      <c r="E193" s="174" t="n"/>
+      <c r="F193" s="174" t="n"/>
+      <c r="G193" s="171" t="n"/>
+      <c r="H193" s="171" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="138" t="inlineStr">
+      <c r="A194" s="174" t="inlineStr">
         <is>
           <t>FY25 total assets ($000)</t>
         </is>
       </c>
-      <c r="B194" s="168" t="n">
+      <c r="B194" s="180" t="n">
         <v>8456743</v>
       </c>
-      <c r="C194" s="138" t="n"/>
-      <c r="D194" s="138" t="n"/>
-      <c r="E194" s="138" t="n"/>
-      <c r="F194" s="138" t="n">
+      <c r="C194" s="174" t="n"/>
+      <c r="D194" s="174" t="n"/>
+      <c r="E194" s="174" t="n"/>
+      <c r="F194" s="174" t="n">
         <v>8456743</v>
       </c>
+      <c r="G194" s="171" t="n"/>
+      <c r="H194" s="171" t="n"/>
     </row>
     <row r="195">
-      <c r="A195" s="138" t="inlineStr">
+      <c r="A195" s="174" t="inlineStr">
         <is>
           <t>FY25 total liabilities ($000)</t>
         </is>
       </c>
-      <c r="B195" s="168" t="n">
+      <c r="B195" s="180" t="n">
         <v>3494903</v>
       </c>
-      <c r="C195" s="138" t="n"/>
-      <c r="D195" s="138" t="n"/>
-      <c r="E195" s="138" t="n"/>
-      <c r="F195" s="138" t="n">
+      <c r="C195" s="174" t="n"/>
+      <c r="D195" s="174" t="n"/>
+      <c r="E195" s="174" t="n"/>
+      <c r="F195" s="174" t="n">
         <v>3494903</v>
       </c>
+      <c r="G195" s="171" t="n"/>
+      <c r="H195" s="171" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="138" t="inlineStr">
+      <c r="A196" s="174" t="inlineStr">
         <is>
           <t>FY25 total equity ($000)</t>
         </is>
       </c>
-      <c r="B196" s="168" t="n">
+      <c r="B196" s="180" t="n">
         <v>4961840</v>
       </c>
-      <c r="C196" s="138" t="n"/>
-      <c r="D196" s="138" t="n"/>
-      <c r="E196" s="138" t="n"/>
-      <c r="F196" s="138" t="n">
+      <c r="C196" s="174" t="n"/>
+      <c r="D196" s="174" t="n"/>
+      <c r="E196" s="174" t="n"/>
+      <c r="F196" s="174" t="n">
         <v>4961840</v>
       </c>
+      <c r="G196" s="171" t="n"/>
+      <c r="H196" s="171" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="138" t="inlineStr">
+      <c r="A197" s="174" t="inlineStr">
         <is>
           <t>FY25 diluted shares (000)</t>
         </is>
       </c>
-      <c r="B197" s="168" t="n">
+      <c r="B197" s="180" t="n">
         <v>119068</v>
       </c>
-      <c r="C197" s="138" t="n"/>
-      <c r="D197" s="138" t="n"/>
-      <c r="E197" s="138" t="n"/>
-      <c r="F197" s="138" t="n">
+      <c r="C197" s="174" t="n"/>
+      <c r="D197" s="174" t="n"/>
+      <c r="E197" s="174" t="n"/>
+      <c r="F197" s="174" t="n">
         <v>119068</v>
       </c>
+      <c r="G197" s="171" t="n"/>
+      <c r="H197" s="171" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="138" t="inlineStr">
+      <c r="A198" s="174" t="inlineStr">
         <is>
           <t>FY25 net revenue ($000)</t>
         </is>
       </c>
-      <c r="B198" s="168" t="n">
+      <c r="B198" s="180" t="n">
         <v>11102600</v>
       </c>
-      <c r="C198" s="138" t="n"/>
-      <c r="D198" s="138" t="n"/>
-      <c r="E198" s="138" t="n"/>
-      <c r="F198" s="138" t="n">
+      <c r="C198" s="174" t="n"/>
+      <c r="D198" s="174" t="n"/>
+      <c r="E198" s="174" t="n"/>
+      <c r="F198" s="174" t="n">
         <v>11102600</v>
       </c>
+      <c r="G198" s="171" t="n"/>
+      <c r="H198" s="171" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="138" t="n"/>
-      <c r="B199" s="138" t="n"/>
-      <c r="C199" s="138" t="n"/>
-      <c r="D199" s="138" t="n"/>
-      <c r="E199" s="138" t="n"/>
-      <c r="F199" s="138" t="n"/>
+      <c r="A199" s="174" t="n"/>
+      <c r="B199" s="174" t="n"/>
+      <c r="C199" s="174" t="n"/>
+      <c r="D199" s="174" t="n"/>
+      <c r="E199" s="174" t="n"/>
+      <c r="F199" s="174" t="n"/>
+      <c r="G199" s="171" t="n"/>
+      <c r="H199" s="171" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="138" t="n"/>
-      <c r="B200" s="138" t="n"/>
-      <c r="C200" s="138" t="n"/>
-      <c r="D200" s="138" t="n"/>
-      <c r="E200" s="138" t="n"/>
-      <c r="F200" s="138" t="n"/>
+      <c r="A200" s="174" t="n"/>
+      <c r="B200" s="174" t="n"/>
+      <c r="C200" s="174" t="n"/>
+      <c r="D200" s="174" t="n"/>
+      <c r="E200" s="174" t="n"/>
+      <c r="F200" s="174" t="n"/>
+      <c r="G200" s="171" t="n"/>
+      <c r="H200" s="171" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="138" t="n"/>
-      <c r="B201" s="138" t="n"/>
-      <c r="C201" s="138" t="n"/>
-      <c r="D201" s="138" t="n"/>
-      <c r="E201" s="138" t="n"/>
-      <c r="F201" s="138" t="n"/>
+      <c r="A201" s="174" t="n"/>
+      <c r="B201" s="174" t="n"/>
+      <c r="C201" s="174" t="n"/>
+      <c r="D201" s="174" t="n"/>
+      <c r="E201" s="174" t="n"/>
+      <c r="F201" s="174" t="n"/>
+      <c r="G201" s="171" t="n"/>
+      <c r="H201" s="171" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="138" t="inlineStr">
+      <c r="A202" s="174" t="inlineStr">
         <is>
           <t>FY25 stock-based compensation ($000)</t>
         </is>
       </c>
-      <c r="B202" s="168" t="n">
+      <c r="B202" s="180" t="n">
         <v>62203</v>
       </c>
-      <c r="C202" s="138" t="n"/>
-      <c r="D202" s="138" t="n"/>
-      <c r="E202" s="138" t="n"/>
-      <c r="F202" s="138" t="n">
+      <c r="C202" s="174" t="n"/>
+      <c r="D202" s="174" t="n"/>
+      <c r="E202" s="174" t="n"/>
+      <c r="F202" s="174" t="n">
         <v>62203</v>
       </c>
+      <c r="G202" s="171" t="n"/>
+      <c r="H202" s="171" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="138" t="inlineStr">
+      <c r="A203" s="174" t="inlineStr">
         <is>
           <t>FY25 implied lease interest ($000)</t>
         </is>
       </c>
-      <c r="B203" s="168" t="n">
+      <c r="B203" s="180" t="n">
         <v>1028</v>
       </c>
-      <c r="C203" s="138" t="n"/>
-      <c r="D203" s="138" t="n"/>
-      <c r="E203" s="138" t="n"/>
-      <c r="F203" s="138" t="n">
+      <c r="C203" s="174" t="n"/>
+      <c r="D203" s="174" t="n"/>
+      <c r="E203" s="174" t="n"/>
+      <c r="F203" s="174" t="n">
         <v>1028</v>
       </c>
+      <c r="G203" s="171" t="n"/>
+      <c r="H203" s="171" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6590,43 +6835,55 @@
           <t>Revenue drivers (FY26–30)</t>
         </is>
       </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-      <c r="E1" s="13" t="n"/>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="13" t="n"/>
-      <c r="I1" s="13" t="n"/>
-      <c r="J1" s="13" t="n"/>
-      <c r="K1" s="13" t="n"/>
+      <c r="B1" s="172" t="n"/>
+      <c r="C1" s="172" t="n"/>
+      <c r="D1" s="172" t="n"/>
+      <c r="E1" s="172" t="n"/>
+      <c r="F1" s="172" t="n"/>
+      <c r="G1" s="172" t="n"/>
+      <c r="H1" s="172" t="n"/>
+      <c r="I1" s="172" t="n"/>
+      <c r="J1" s="172" t="n"/>
+      <c r="K1" s="172" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="26" t="n"/>
-      <c r="B2" s="132" t="inlineStr">
+      <c r="B2" s="181" t="inlineStr">
         <is>
           <t>×1,000,000 (sessions in millions → count)</t>
         </is>
       </c>
-      <c r="C2" s="132" t="inlineStr">
+      <c r="C2" s="181" t="inlineStr">
         <is>
           <t>÷1,000 ($ → $000 on this tab)</t>
         </is>
       </c>
+      <c r="D2" s="171" t="n"/>
+      <c r="E2" s="171" t="n"/>
+      <c r="F2" s="171" t="n"/>
+      <c r="G2" s="171" t="n"/>
+      <c r="H2" s="171" t="n"/>
+      <c r="I2" s="171" t="n"/>
+      <c r="J2" s="171" t="n"/>
+      <c r="K2" s="171" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="171" t="inlineStr">
         <is>
           <t>Unit conversions (drivers)</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="171" t="n">
         <v>1000000</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="171" t="n">
         <v>1000</v>
       </c>
-      <c r="H3" s="133" t="inlineStr">
+      <c r="D3" s="171" t="n"/>
+      <c r="E3" s="171" t="n"/>
+      <c r="F3" s="171" t="n"/>
+      <c r="G3" s="171" t="n"/>
+      <c r="H3" s="182" t="inlineStr">
         <is>
           <t>see B2/C2</t>
         </is>
@@ -6645,6 +6902,16 @@
           <t>I. STORE FLEET &amp; SQUARE FOOTAGE (company-operated)</t>
         </is>
       </c>
+      <c r="B4" s="171" t="n"/>
+      <c r="C4" s="171" t="n"/>
+      <c r="D4" s="171" t="n"/>
+      <c r="E4" s="171" t="n"/>
+      <c r="F4" s="171" t="n"/>
+      <c r="G4" s="171" t="n"/>
+      <c r="H4" s="171" t="n"/>
+      <c r="I4" s="171" t="n"/>
+      <c r="J4" s="171" t="n"/>
+      <c r="K4" s="171" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="53" t="inlineStr">
@@ -6687,12 +6954,12 @@
           <t>Units</t>
         </is>
       </c>
-      <c r="I5" s="169" t="inlineStr">
+      <c r="I5" s="183" t="inlineStr">
         <is>
           <t>How it moves</t>
         </is>
       </c>
-      <c r="J5" s="127" t="inlineStr">
+      <c r="J5" s="184" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -6733,7 +7000,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I6" s="135" t="inlineStr">
+      <c r="I6" s="185" t="inlineStr">
         <is>
           <t>Prior-year ending count carried into this year.</t>
         </is>
@@ -6743,6 +7010,7 @@
           <t>Revenue Drivers: beginning-stores formula</t>
         </is>
       </c>
+      <c r="K6" s="171" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="41" t="inlineStr">
@@ -6750,6 +7018,7 @@
           <t>Americas — openings</t>
         </is>
       </c>
+      <c r="B7" s="171" t="n"/>
       <c r="C7" s="60" t="n">
         <v>8</v>
       </c>
@@ -6770,7 +7039,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I7" s="135" t="inlineStr">
+      <c r="I7" s="185" t="inlineStr">
         <is>
           <t>New stores added in region each forecast year.</t>
         </is>
@@ -6792,6 +7061,7 @@
           <t>Americas — closures</t>
         </is>
       </c>
+      <c r="B8" s="171" t="n"/>
       <c r="C8" s="60" t="n">
         <v>3</v>
       </c>
@@ -6812,7 +7082,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I8" s="135" t="inlineStr">
+      <c r="I8" s="185" t="inlineStr">
         <is>
           <t>Stores closed yearly as leases roll off.</t>
         </is>
@@ -6862,7 +7132,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I9" s="135" t="inlineStr">
+      <c r="I9" s="185" t="inlineStr">
         <is>
           <t>Beginning plus openings minus closures each year.</t>
         </is>
@@ -6872,6 +7142,7 @@
           <t>Revenue Drivers: ending-stores formula</t>
         </is>
       </c>
+      <c r="K9" s="171" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="41" t="inlineStr">
@@ -6907,7 +7178,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I10" s="135" t="inlineStr">
+      <c r="I10" s="185" t="inlineStr">
         <is>
           <t>Prior-year ending count carried into this year.</t>
         </is>
@@ -6917,6 +7188,7 @@
           <t>Revenue Drivers: beginning-stores formula</t>
         </is>
       </c>
+      <c r="K10" s="171" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="41" t="inlineStr">
@@ -6924,6 +7196,7 @@
           <t>China Mainland — openings</t>
         </is>
       </c>
+      <c r="B11" s="171" t="n"/>
       <c r="C11" s="60" t="n">
         <v>20</v>
       </c>
@@ -6944,7 +7217,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I11" s="135" t="inlineStr">
+      <c r="I11" s="185" t="inlineStr">
         <is>
           <t>New stores added in region each forecast year.</t>
         </is>
@@ -6966,6 +7239,7 @@
           <t>China Mainland — closures</t>
         </is>
       </c>
+      <c r="B12" s="171" t="n"/>
       <c r="C12" s="60" t="n">
         <v>1</v>
       </c>
@@ -6986,7 +7260,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I12" s="135" t="inlineStr">
+      <c r="I12" s="185" t="inlineStr">
         <is>
           <t>Stores closed yearly as leases roll off.</t>
         </is>
@@ -7036,7 +7310,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I13" s="135" t="inlineStr">
+      <c r="I13" s="185" t="inlineStr">
         <is>
           <t>Beginning plus openings minus closures each year.</t>
         </is>
@@ -7046,6 +7320,7 @@
           <t>Revenue Drivers: ending-stores formula</t>
         </is>
       </c>
+      <c r="K13" s="171" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="41" t="inlineStr">
@@ -7081,7 +7356,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I14" s="135" t="inlineStr">
+      <c r="I14" s="185" t="inlineStr">
         <is>
           <t>Prior-year ending count carried into this year.</t>
         </is>
@@ -7091,6 +7366,7 @@
           <t>Revenue Drivers: beginning-stores formula</t>
         </is>
       </c>
+      <c r="K14" s="171" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="41" t="inlineStr">
@@ -7098,6 +7374,7 @@
           <t>Rest of World — openings</t>
         </is>
       </c>
+      <c r="B15" s="171" t="n"/>
       <c r="C15" s="60" t="n">
         <v>7</v>
       </c>
@@ -7118,7 +7395,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I15" s="135" t="inlineStr">
+      <c r="I15" s="185" t="inlineStr">
         <is>
           <t>New stores added in region each forecast year.</t>
         </is>
@@ -7140,6 +7417,7 @@
           <t>Rest of World — closures</t>
         </is>
       </c>
+      <c r="B16" s="171" t="n"/>
       <c r="C16" s="60" t="n">
         <v>2</v>
       </c>
@@ -7160,7 +7438,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I16" s="135" t="inlineStr">
+      <c r="I16" s="185" t="inlineStr">
         <is>
           <t>Stores closed yearly as leases roll off.</t>
         </is>
@@ -7210,7 +7488,7 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="I17" s="135" t="inlineStr">
+      <c r="I17" s="185" t="inlineStr">
         <is>
           <t>Beginning plus openings minus closures each year.</t>
         </is>
@@ -7220,6 +7498,7 @@
           <t>Revenue Drivers: ending-stores formula</t>
         </is>
       </c>
+      <c r="K17" s="171" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="61" t="inlineStr">
@@ -7250,7 +7529,8 @@
         <f>G9+G13+G17</f>
         <v/>
       </c>
-      <c r="I18" s="135" t="inlineStr">
+      <c r="H18" s="171" t="n"/>
+      <c r="I18" s="185" t="inlineStr">
         <is>
           <t>Sum of Americas, China, and Rest of World.</t>
         </is>
@@ -7260,6 +7540,7 @@
           <t>Revenue Drivers: total-stores formula</t>
         </is>
       </c>
+      <c r="K18" s="171" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="41" t="inlineStr">
@@ -7290,7 +7571,7 @@
           <t>sq ft</t>
         </is>
       </c>
-      <c r="I19" s="135" t="inlineStr">
+      <c r="I19" s="185" t="inlineStr">
         <is>
           <t>Average box size grows modestly through FY30.</t>
         </is>
@@ -7341,16 +7622,30 @@
           <t>sq ft</t>
         </is>
       </c>
-      <c r="I20" s="135" t="inlineStr">
+      <c r="I20" s="185" t="inlineStr">
         <is>
           <t>Ending stores times average square feet per store.</t>
         </is>
       </c>
-      <c r="J20" s="128" t="inlineStr">
+      <c r="J20" s="186" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-sqft formula</t>
         </is>
       </c>
+      <c r="K20" s="171" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="171" t="n"/>
+      <c r="B21" s="171" t="n"/>
+      <c r="C21" s="171" t="n"/>
+      <c r="D21" s="171" t="n"/>
+      <c r="E21" s="171" t="n"/>
+      <c r="F21" s="171" t="n"/>
+      <c r="G21" s="171" t="n"/>
+      <c r="H21" s="171" t="n"/>
+      <c r="I21" s="171" t="n"/>
+      <c r="J21" s="171" t="n"/>
+      <c r="K21" s="171" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
@@ -7358,6 +7653,16 @@
           <t>II. STORE PRODUCTIVITY (brick &amp; mortar channel)</t>
         </is>
       </c>
+      <c r="B22" s="171" t="n"/>
+      <c r="C22" s="171" t="n"/>
+      <c r="D22" s="171" t="n"/>
+      <c r="E22" s="171" t="n"/>
+      <c r="F22" s="171" t="n"/>
+      <c r="G22" s="171" t="n"/>
+      <c r="H22" s="171" t="n"/>
+      <c r="I22" s="171" t="n"/>
+      <c r="J22" s="171" t="n"/>
+      <c r="K22" s="171" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="53" t="inlineStr">
@@ -7401,7 +7706,7 @@
         </is>
       </c>
       <c r="I23" s="56" t="n"/>
-      <c r="J23" s="129" t="inlineStr">
+      <c r="J23" s="187" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -7437,7 +7742,7 @@
           <t>$/sq ft</t>
         </is>
       </c>
-      <c r="I24" s="135" t="inlineStr">
+      <c r="I24" s="185" t="inlineStr">
         <is>
           <t>Sales per foot recovers slowly after FY26 trough.</t>
         </is>
@@ -7482,7 +7787,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="I25" s="135" t="inlineStr">
+      <c r="I25" s="185" t="inlineStr">
         <is>
           <t>Declines then flatlines as Americas traffic stabilizes.</t>
         </is>
@@ -7527,7 +7832,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="I26" s="135" t="inlineStr">
+      <c r="I26" s="185" t="inlineStr">
         <is>
           <t>Strong growth moderates as China store base scales.</t>
         </is>
@@ -7572,7 +7877,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="I27" s="135" t="inlineStr">
+      <c r="I27" s="185" t="inlineStr">
         <is>
           <t>Mid-single-digit comps fading to low-single digits.</t>
         </is>
@@ -7622,7 +7927,7 @@
           <t>$000</t>
         </is>
       </c>
-      <c r="I28" s="135" t="inlineStr">
+      <c r="I28" s="185" t="inlineStr">
         <is>
           <t>Last year's store revenue rolled forward annually.</t>
         </is>
@@ -7632,6 +7937,7 @@
           <t>Revenue Drivers: prior store-rev formula</t>
         </is>
       </c>
+      <c r="K28" s="171" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="41" t="inlineStr">
@@ -7662,7 +7968,8 @@
         <f>F28*0.71*(1+G25)+F28*0.16*(1+G26)+F28*0.13*(1+G27)</f>
         <v/>
       </c>
-      <c r="I29" s="135" t="inlineStr">
+      <c r="H29" s="171" t="n"/>
+      <c r="I29" s="185" t="inlineStr">
         <is>
           <t>Prior revenue grown by weighted geographic comp rates.</t>
         </is>
@@ -7672,6 +7979,7 @@
           <t>Revenue Drivers: comp-store formula</t>
         </is>
       </c>
+      <c r="K29" s="171" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="41" t="inlineStr">
@@ -7702,16 +8010,18 @@
         <f>(G7-G8+G11-G12+G15-G16)*G19*G24/1000*0.55</f>
         <v/>
       </c>
-      <c r="I30" s="135" t="inlineStr">
+      <c r="H30" s="171" t="n"/>
+      <c r="I30" s="185" t="inlineStr">
         <is>
           <t>Net new doors times sq ft, productivity, ramp.</t>
         </is>
       </c>
-      <c r="J30" s="128" t="inlineStr">
+      <c r="J30" s="186" t="inlineStr">
         <is>
           <t>Revenue Drivers: net-new-store formula</t>
         </is>
       </c>
+      <c r="K30" s="171" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="61" t="inlineStr">
@@ -7742,7 +8052,8 @@
         <f>G29+G30</f>
         <v/>
       </c>
-      <c r="I31" s="135" t="inlineStr">
+      <c r="H31" s="171" t="n"/>
+      <c r="I31" s="185" t="inlineStr">
         <is>
           <t>Comparable store sales plus new store contribution.</t>
         </is>
@@ -7752,6 +8063,7 @@
           <t>Revenue Drivers: store-channel formula</t>
         </is>
       </c>
+      <c r="K31" s="171" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="41" t="n"/>
@@ -7810,6 +8122,7 @@
       <c r="G33" s="64" t="n">
         <v>0.29</v>
       </c>
+      <c r="H33" s="171" t="n"/>
       <c r="I33" s="17" t="n"/>
       <c r="J33" s="18" t="inlineStr">
         <is>
@@ -7842,6 +8155,7 @@
       <c r="G34" s="67" t="n">
         <v>122</v>
       </c>
+      <c r="H34" s="171" t="n"/>
       <c r="I34" s="17" t="n"/>
       <c r="J34" s="18" t="inlineStr">
         <is>
@@ -7854,12 +8168,35 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="171" t="n"/>
+      <c r="B35" s="171" t="n"/>
+      <c r="C35" s="171" t="n"/>
+      <c r="D35" s="171" t="n"/>
+      <c r="E35" s="171" t="n"/>
+      <c r="F35" s="171" t="n"/>
+      <c r="G35" s="171" t="n"/>
+      <c r="H35" s="171" t="n"/>
+      <c r="I35" s="171" t="n"/>
+      <c r="J35" s="171" t="n"/>
+      <c r="K35" s="171" t="n"/>
+    </row>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
           <t>III. DIRECT-TO-CONSUMER (e-commerce / digital)</t>
         </is>
       </c>
+      <c r="B36" s="171" t="n"/>
+      <c r="C36" s="171" t="n"/>
+      <c r="D36" s="171" t="n"/>
+      <c r="E36" s="171" t="n"/>
+      <c r="F36" s="171" t="n"/>
+      <c r="G36" s="171" t="n"/>
+      <c r="H36" s="171" t="n"/>
+      <c r="I36" s="171" t="n"/>
+      <c r="J36" s="171" t="n"/>
+      <c r="K36" s="171" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="53" t="inlineStr">
@@ -7903,7 +8240,7 @@
         </is>
       </c>
       <c r="I37" s="56" t="n"/>
-      <c r="J37" s="129" t="inlineStr">
+      <c r="J37" s="187" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -7939,7 +8276,7 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I38" s="135" t="inlineStr">
+      <c r="I38" s="185" t="inlineStr">
         <is>
           <t>Digital traffic grows modestly across forecast years.</t>
         </is>
@@ -7979,7 +8316,8 @@
       <c r="G39" s="64" t="n">
         <v>0.036</v>
       </c>
-      <c r="I39" s="135" t="inlineStr">
+      <c r="H39" s="171" t="n"/>
+      <c r="I39" s="185" t="inlineStr">
         <is>
           <t>Conversion rate recovers gradually from FY26 pressure.</t>
         </is>
@@ -8019,7 +8357,8 @@
       <c r="G40" s="67" t="n">
         <v>315</v>
       </c>
-      <c r="I40" s="135" t="inlineStr">
+      <c r="H40" s="171" t="n"/>
+      <c r="I40" s="185" t="inlineStr">
         <is>
           <t>Order size steps up slowly with promo normalization.</t>
         </is>
@@ -8064,7 +8403,8 @@
         <f>G38*$B$3*G39*G40/$C$3</f>
         <v/>
       </c>
-      <c r="I41" s="135" t="inlineStr">
+      <c r="H41" s="171" t="n"/>
+      <c r="I41" s="185" t="inlineStr">
         <is>
           <t>Sessions times conversion times average order value.</t>
         </is>
@@ -8074,6 +8414,20 @@
           <t>Revenue Drivers: e-comm formula</t>
         </is>
       </c>
+      <c r="K41" s="171" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="171" t="n"/>
+      <c r="B42" s="171" t="n"/>
+      <c r="C42" s="171" t="n"/>
+      <c r="D42" s="171" t="n"/>
+      <c r="E42" s="171" t="n"/>
+      <c r="F42" s="171" t="n"/>
+      <c r="G42" s="171" t="n"/>
+      <c r="H42" s="171" t="n"/>
+      <c r="I42" s="171" t="n"/>
+      <c r="J42" s="171" t="n"/>
+      <c r="K42" s="171" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
@@ -8081,6 +8435,16 @@
           <t>IV. OTHER CHANNELS, GEOGRAPHY &amp; PRODUCT MIX</t>
         </is>
       </c>
+      <c r="B43" s="171" t="n"/>
+      <c r="C43" s="171" t="n"/>
+      <c r="D43" s="171" t="n"/>
+      <c r="E43" s="171" t="n"/>
+      <c r="F43" s="171" t="n"/>
+      <c r="G43" s="171" t="n"/>
+      <c r="H43" s="171" t="n"/>
+      <c r="I43" s="171" t="n"/>
+      <c r="J43" s="171" t="n"/>
+      <c r="K43" s="171" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="53" t="inlineStr">
@@ -8124,7 +8488,7 @@
         </is>
       </c>
       <c r="I44" s="56" t="n"/>
-      <c r="J44" s="129" t="inlineStr">
+      <c r="J44" s="187" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -8165,7 +8529,7 @@
           <t>$000</t>
         </is>
       </c>
-      <c r="I45" s="135" t="inlineStr">
+      <c r="I45" s="185" t="inlineStr">
         <is>
           <t>Wholesale, license, outlets: low-single-digit growth.</t>
         </is>
@@ -8215,7 +8579,7 @@
           <t>$000</t>
         </is>
       </c>
-      <c r="I46" s="135" t="inlineStr">
+      <c r="I46" s="185" t="inlineStr">
         <is>
           <t>Americas revenue scales with consolidated growth rate.</t>
         </is>
@@ -8265,7 +8629,7 @@
           <t>$000</t>
         </is>
       </c>
-      <c r="I47" s="135" t="inlineStr">
+      <c r="I47" s="185" t="inlineStr">
         <is>
           <t>China revenue grows faster than consolidated average.</t>
         </is>
@@ -8315,7 +8679,7 @@
           <t>$000</t>
         </is>
       </c>
-      <c r="I48" s="135" t="inlineStr">
+      <c r="I48" s="185" t="inlineStr">
         <is>
           <t>Rest of World scales with total revenue growth.</t>
         </is>
@@ -8355,7 +8719,8 @@
       <c r="G49" s="64" t="n">
         <v>0.6</v>
       </c>
-      <c r="I49" s="135" t="inlineStr">
+      <c r="H49" s="171" t="n"/>
+      <c r="I49" s="185" t="inlineStr">
         <is>
           <t>Women's share fades slightly as men's mix rises.</t>
         </is>
@@ -8395,7 +8760,8 @@
       <c r="G50" s="64" t="n">
         <v>0.27</v>
       </c>
-      <c r="I50" s="135" t="inlineStr">
+      <c r="H50" s="171" t="n"/>
+      <c r="I50" s="185" t="inlineStr">
         <is>
           <t>Men's mix rises gradually through the forecast.</t>
         </is>
@@ -8435,7 +8801,8 @@
       <c r="G51" s="64" t="n">
         <v>0.13</v>
       </c>
-      <c r="I51" s="135" t="inlineStr">
+      <c r="H51" s="171" t="n"/>
+      <c r="I51" s="185" t="inlineStr">
         <is>
           <t>Accessories share held steady near thirteen percent.</t>
         </is>
@@ -8450,6 +8817,19 @@
           <t>https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
         </is>
       </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="171" t="n"/>
+      <c r="B52" s="171" t="n"/>
+      <c r="C52" s="171" t="n"/>
+      <c r="D52" s="171" t="n"/>
+      <c r="E52" s="171" t="n"/>
+      <c r="F52" s="171" t="n"/>
+      <c r="G52" s="171" t="n"/>
+      <c r="H52" s="171" t="n"/>
+      <c r="I52" s="171" t="n"/>
+      <c r="J52" s="171" t="n"/>
+      <c r="K52" s="171" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
@@ -8457,6 +8837,16 @@
           <t>V. CONSOLIDATED REVENUE &amp; RECONCILIATION</t>
         </is>
       </c>
+      <c r="B53" s="171" t="n"/>
+      <c r="C53" s="171" t="n"/>
+      <c r="D53" s="171" t="n"/>
+      <c r="E53" s="171" t="n"/>
+      <c r="F53" s="171" t="n"/>
+      <c r="G53" s="171" t="n"/>
+      <c r="H53" s="171" t="n"/>
+      <c r="I53" s="171" t="n"/>
+      <c r="J53" s="171" t="n"/>
+      <c r="K53" s="171" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="53" t="inlineStr">
@@ -8500,7 +8890,7 @@
         </is>
       </c>
       <c r="I54" s="56" t="n"/>
-      <c r="J54" s="129" t="inlineStr">
+      <c r="J54" s="187" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -8536,7 +8926,8 @@
         <f>G31+G41+G45</f>
         <v/>
       </c>
-      <c r="I55" s="135" t="inlineStr">
+      <c r="H55" s="171" t="n"/>
+      <c r="I55" s="185" t="inlineStr">
         <is>
           <t>Store channel plus e-comm plus other channels.</t>
         </is>
@@ -8546,6 +8937,7 @@
           <t>Revenue Drivers: total-rev formula</t>
         </is>
       </c>
+      <c r="K55" s="171" t="n"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="41" t="inlineStr">
@@ -8576,7 +8968,8 @@
         <f>Scenarios!$C$29</f>
         <v/>
       </c>
-      <c r="I56" s="135" t="inlineStr">
+      <c r="H56" s="171" t="n"/>
+      <c r="I56" s="185" t="inlineStr">
         <is>
           <t>Pulls Scenarios base revenue path used by DCF.</t>
         </is>
@@ -8586,7 +8979,7 @@
           <t>Scenarios tab: base revenue</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="171" t="inlineStr">
         <is>
           <t>Scenarios tab: base revenue</t>
         </is>
@@ -8622,16 +9015,18 @@
         <f>G55-G56</f>
         <v/>
       </c>
-      <c r="I57" s="135" t="inlineStr">
+      <c r="H57" s="171" t="n"/>
+      <c r="I57" s="185" t="inlineStr">
         <is>
           <t>Driver-built revenue minus Scenarios base-case revenue.</t>
         </is>
       </c>
-      <c r="J57" s="128" t="inlineStr">
+      <c r="J57" s="186" t="inlineStr">
         <is>
           <t>Revenue Drivers: variance formula</t>
         </is>
       </c>
+      <c r="K57" s="171" t="n"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="41" t="inlineStr">
@@ -8663,16 +9058,18 @@
         <f>IF(G56=0,"",G57/G56)</f>
         <v/>
       </c>
-      <c r="I58" s="135" t="inlineStr">
+      <c r="H58" s="171" t="n"/>
+      <c r="I58" s="185" t="inlineStr">
         <is>
           <t>Variance as percent of Scenarios consolidated revenue.</t>
         </is>
       </c>
-      <c r="J58" s="128" t="inlineStr">
+      <c r="J58" s="186" t="inlineStr">
         <is>
           <t>Revenue Drivers: variance % formula</t>
         </is>
       </c>
+      <c r="K58" s="171" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="26" t="inlineStr">
@@ -8680,6 +9077,16 @@
           <t>Note: DCF / Scenarios consolidated revenue is the valuation anchor: drivers do not feed the DCF. A small variance vs Scenarios means the bottom-up path still hangs together, so the Scenarios case stays viable. Bigger gaps = revisit drivers or Scenarios assumptions.</t>
         </is>
       </c>
+      <c r="B59" s="171" t="n"/>
+      <c r="C59" s="171" t="n"/>
+      <c r="D59" s="171" t="n"/>
+      <c r="E59" s="171" t="n"/>
+      <c r="F59" s="171" t="n"/>
+      <c r="G59" s="171" t="n"/>
+      <c r="H59" s="171" t="n"/>
+      <c r="I59" s="171" t="n"/>
+      <c r="J59" s="171" t="n"/>
+      <c r="K59" s="171" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8787,17 +9194,18 @@
           <t>DISCOUNTED CASH FLOW — BASE CASE (US$ thousands)</t>
         </is>
       </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-      <c r="E1" s="13" t="n"/>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="13" t="n"/>
-      <c r="I1" s="13" t="n"/>
-      <c r="J1" s="13" t="n"/>
+      <c r="B1" s="172" t="n"/>
+      <c r="C1" s="172" t="n"/>
+      <c r="D1" s="172" t="n"/>
+      <c r="E1" s="172" t="n"/>
+      <c r="F1" s="172" t="n"/>
+      <c r="G1" s="172" t="n"/>
+      <c r="H1" s="172" t="n"/>
+      <c r="I1" s="172" t="n"/>
+      <c r="J1" s="172" t="n"/>
     </row>
     <row r="2">
+      <c r="A2" s="171" t="n"/>
       <c r="B2" s="78" t="n"/>
       <c r="C2" s="78" t="inlineStr">
         <is>
@@ -8842,21 +9250,35 @@
           <t>Forecast linked to Scenarios (base case)</t>
         </is>
       </c>
+      <c r="B3" s="171" t="n"/>
       <c r="C3" s="19" t="n"/>
+      <c r="D3" s="171" t="n"/>
       <c r="E3" s="83" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
+      <c r="F3" s="171" t="n"/>
+      <c r="G3" s="171" t="n"/>
+      <c r="H3" s="171" t="n"/>
+      <c r="I3" s="171" t="n"/>
+      <c r="J3" s="171" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="38" t="n"/>
+      <c r="B4" s="171" t="n"/>
       <c r="C4" s="85" t="n"/>
       <c r="D4" s="85" t="inlineStr">
         <is>
           <t>Revenue Drivers tab</t>
         </is>
       </c>
+      <c r="E4" s="171" t="n"/>
+      <c r="F4" s="171" t="n"/>
+      <c r="G4" s="171" t="n"/>
+      <c r="H4" s="171" t="n"/>
+      <c r="I4" s="171" t="n"/>
+      <c r="J4" s="171" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -8864,6 +9286,9 @@
           <t>Net revenue</t>
         </is>
       </c>
+      <c r="B5" s="171" t="n"/>
+      <c r="C5" s="171" t="n"/>
+      <c r="D5" s="171" t="n"/>
       <c r="E5" s="74" t="n">
         <v>11102600</v>
       </c>
@@ -8901,6 +9326,7 @@
         </is>
       </c>
       <c r="D6" s="19" t="n"/>
+      <c r="E6" s="171" t="n"/>
       <c r="F6" s="32">
         <f>F5/E5-1</f>
         <v/>
@@ -8966,6 +9392,9 @@
           <t>Cost of goods sold (COGS)</t>
         </is>
       </c>
+      <c r="B8" s="171" t="n"/>
+      <c r="C8" s="171" t="n"/>
+      <c r="D8" s="171" t="n"/>
       <c r="E8" s="74" t="n">
         <v>4818468</v>
       </c>
@@ -9003,6 +9432,7 @@
         </is>
       </c>
       <c r="D9" s="19" t="n"/>
+      <c r="E9" s="171" t="n"/>
       <c r="F9" s="32">
         <f>Scenarios!$C$40</f>
         <v/>
@@ -9063,6 +9493,9 @@
           <t>EBIT (incl. FY26 refund)</t>
         </is>
       </c>
+      <c r="B11" s="171" t="n"/>
+      <c r="C11" s="171" t="n"/>
+      <c r="D11" s="171" t="n"/>
       <c r="E11" s="76" t="n">
         <v>2210615</v>
       </c>
@@ -9093,6 +9526,9 @@
           <t>Reported EBIT margin % (incl. FY26 refund)</t>
         </is>
       </c>
+      <c r="B12" s="171" t="n"/>
+      <c r="C12" s="171" t="n"/>
+      <c r="D12" s="171" t="n"/>
       <c r="E12" s="77">
         <f>E11/E5</f>
         <v/>
@@ -9124,6 +9560,10 @@
           <t>Less: unlevered tax (cash tax rate)</t>
         </is>
       </c>
+      <c r="B13" s="171" t="n"/>
+      <c r="C13" s="171" t="n"/>
+      <c r="D13" s="171" t="n"/>
+      <c r="E13" s="171" t="n"/>
       <c r="F13" s="75">
         <f>-F11*Scenarios!$C$11</f>
         <v/>
@@ -9151,6 +9591,10 @@
           <t>NOPAT</t>
         </is>
       </c>
+      <c r="B14" s="171" t="n"/>
+      <c r="C14" s="171" t="n"/>
+      <c r="D14" s="171" t="n"/>
+      <c r="E14" s="171" t="n"/>
       <c r="F14" s="25">
         <f>Scenarios!$C$50</f>
         <v/>
@@ -9185,6 +9629,7 @@
         </is>
       </c>
       <c r="D15" s="19" t="n"/>
+      <c r="E15" s="171" t="n"/>
       <c r="F15" s="20">
         <f>Scenarios!$C$12</f>
         <v/>
@@ -9212,6 +9657,10 @@
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
+      <c r="B16" s="171" t="n"/>
+      <c r="C16" s="171" t="n"/>
+      <c r="D16" s="171" t="n"/>
+      <c r="E16" s="171" t="n"/>
       <c r="F16" s="75">
         <f>Scenarios!$C$55</f>
         <v/>
@@ -9246,6 +9695,7 @@
         </is>
       </c>
       <c r="D17" s="19" t="n"/>
+      <c r="E17" s="171" t="n"/>
       <c r="F17" s="20">
         <f>Scenarios!$C$13</f>
         <v/>
@@ -9273,6 +9723,10 @@
           <t>Less: capital expenditures</t>
         </is>
       </c>
+      <c r="B18" s="171" t="n"/>
+      <c r="C18" s="171" t="n"/>
+      <c r="D18" s="171" t="n"/>
+      <c r="E18" s="171" t="n"/>
       <c r="F18" s="75">
         <f>-Scenarios!$C$60</f>
         <v/>
@@ -9300,6 +9754,15 @@
           <t>Working capital schedule (driver-based) [click − to collapse detail]</t>
         </is>
       </c>
+      <c r="B19" s="171" t="n"/>
+      <c r="C19" s="171" t="n"/>
+      <c r="D19" s="171" t="n"/>
+      <c r="E19" s="171" t="n"/>
+      <c r="F19" s="171" t="n"/>
+      <c r="G19" s="171" t="n"/>
+      <c r="H19" s="171" t="n"/>
+      <c r="I19" s="171" t="n"/>
+      <c r="J19" s="171" t="n"/>
     </row>
     <row r="20" outlineLevel="1" ht="150" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -9689,6 +10152,7 @@
         </is>
       </c>
       <c r="D30" s="19" t="n"/>
+      <c r="E30" s="171" t="n"/>
       <c r="F30" s="75">
         <f>Scenarios!$C$105</f>
         <v/>
@@ -9723,6 +10187,7 @@
         </is>
       </c>
       <c r="D31" s="19" t="n"/>
+      <c r="E31" s="171" t="n"/>
       <c r="F31" s="75">
         <f>Scenarios!$C$110</f>
         <v/>
@@ -9794,6 +10259,7 @@
         </is>
       </c>
       <c r="D33" s="19" t="n"/>
+      <c r="E33" s="171" t="n"/>
       <c r="F33" s="25">
         <f>Scenarios!$C$120</f>
         <v/>
@@ -9817,6 +10283,15 @@
     </row>
     <row r="34">
       <c r="A34" s="26" t="n"/>
+      <c r="B34" s="171" t="n"/>
+      <c r="C34" s="171" t="n"/>
+      <c r="D34" s="171" t="n"/>
+      <c r="E34" s="171" t="n"/>
+      <c r="F34" s="171" t="n"/>
+      <c r="G34" s="171" t="n"/>
+      <c r="H34" s="171" t="n"/>
+      <c r="I34" s="171" t="n"/>
+      <c r="J34" s="171" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
@@ -9824,6 +10299,10 @@
           <t>Unlevered free cash flow</t>
         </is>
       </c>
+      <c r="B35" s="171" t="n"/>
+      <c r="C35" s="171" t="n"/>
+      <c r="D35" s="171" t="n"/>
+      <c r="E35" s="171" t="n"/>
       <c r="F35" s="89">
         <f>Scenarios!$C$125</f>
         <v/>
@@ -9851,6 +10330,10 @@
           <t>Discount period (years)</t>
         </is>
       </c>
+      <c r="B36" s="171" t="n"/>
+      <c r="C36" s="171" t="n"/>
+      <c r="D36" s="171" t="n"/>
+      <c r="E36" s="171" t="n"/>
       <c r="F36" s="90" t="n">
         <v>1</v>
       </c>
@@ -9873,6 +10356,10 @@
           <t>Discount factor @ WACC</t>
         </is>
       </c>
+      <c r="B37" s="171" t="n"/>
+      <c r="C37" s="171" t="n"/>
+      <c r="D37" s="171" t="n"/>
+      <c r="E37" s="171" t="n"/>
       <c r="F37" s="91">
         <f>1/(1+Scenarios!$C$9)^F36</f>
         <v/>
@@ -9900,6 +10387,10 @@
           <t>PV of unlevered FCF</t>
         </is>
       </c>
+      <c r="B38" s="171" t="n"/>
+      <c r="C38" s="171" t="n"/>
+      <c r="D38" s="171" t="n"/>
+      <c r="E38" s="171" t="n"/>
       <c r="F38" s="25">
         <f>F35*F37</f>
         <v/>
@@ -9921,8 +10412,29 @@
         <v/>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="171" t="n"/>
+      <c r="B39" s="171" t="n"/>
+      <c r="C39" s="171" t="n"/>
+      <c r="D39" s="171" t="n"/>
+      <c r="E39" s="171" t="n"/>
+      <c r="F39" s="171" t="n"/>
+      <c r="G39" s="171" t="n"/>
+      <c r="H39" s="171" t="n"/>
+      <c r="I39" s="171" t="n"/>
+      <c r="J39" s="171" t="n"/>
+    </row>
     <row r="40">
       <c r="A40" s="15" t="n"/>
+      <c r="B40" s="171" t="n"/>
+      <c r="C40" s="171" t="n"/>
+      <c r="D40" s="171" t="n"/>
+      <c r="E40" s="171" t="n"/>
+      <c r="F40" s="171" t="n"/>
+      <c r="G40" s="171" t="n"/>
+      <c r="H40" s="171" t="n"/>
+      <c r="I40" s="171" t="n"/>
+      <c r="J40" s="171" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="93" t="inlineStr">
@@ -9930,8 +10442,15 @@
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
+      <c r="B41" s="172" t="n"/>
+      <c r="C41" s="172" t="n"/>
+      <c r="D41" s="171" t="n"/>
+      <c r="E41" s="171" t="n"/>
+      <c r="F41" s="171" t="n"/>
+      <c r="G41" s="171" t="n"/>
+      <c r="H41" s="171" t="n"/>
+      <c r="I41" s="171" t="n"/>
+      <c r="J41" s="171" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="23" t="inlineStr">
@@ -9939,10 +10458,18 @@
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
+      <c r="B42" s="171" t="n"/>
+      <c r="C42" s="171" t="n"/>
+      <c r="D42" s="171" t="n"/>
       <c r="E42" s="70">
         <f>SUM(F38:J38)</f>
         <v/>
       </c>
+      <c r="F42" s="171" t="n"/>
+      <c r="G42" s="171" t="n"/>
+      <c r="H42" s="171" t="n"/>
+      <c r="I42" s="171" t="n"/>
+      <c r="J42" s="171" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
@@ -9961,6 +10488,11 @@
         <f>Scenarios!$C$10</f>
         <v/>
       </c>
+      <c r="F43" s="171" t="n"/>
+      <c r="G43" s="171" t="n"/>
+      <c r="H43" s="171" t="n"/>
+      <c r="I43" s="171" t="n"/>
+      <c r="J43" s="171" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="23" t="inlineStr">
@@ -9968,10 +10500,18 @@
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
+      <c r="B44" s="171" t="n"/>
+      <c r="C44" s="171" t="n"/>
+      <c r="D44" s="171" t="n"/>
       <c r="E44" s="25">
         <f>J11+J16</f>
         <v/>
       </c>
+      <c r="F44" s="171" t="n"/>
+      <c r="G44" s="171" t="n"/>
+      <c r="H44" s="171" t="n"/>
+      <c r="I44" s="171" t="n"/>
+      <c r="J44" s="171" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -9979,10 +10519,18 @@
           <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
         </is>
       </c>
+      <c r="B45" s="171" t="n"/>
+      <c r="C45" s="171" t="n"/>
+      <c r="D45" s="171" t="n"/>
       <c r="E45" s="75">
         <f>J35*(1+Scenarios!$C$10)/(Scenarios!$C$9-Scenarios!$C$10)</f>
         <v/>
       </c>
+      <c r="F45" s="171" t="n"/>
+      <c r="G45" s="171" t="n"/>
+      <c r="H45" s="171" t="n"/>
+      <c r="I45" s="171" t="n"/>
+      <c r="J45" s="171" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -9990,17 +10538,33 @@
           <t>Implied exit EV/EBITDA = Gordon TV / FY30 EBITDA</t>
         </is>
       </c>
+      <c r="B46" s="171" t="n"/>
+      <c r="C46" s="171" t="n"/>
+      <c r="D46" s="171" t="n"/>
       <c r="E46" s="94">
         <f>E45/E44</f>
         <v/>
       </c>
+      <c r="F46" s="171" t="n"/>
+      <c r="G46" s="171" t="n"/>
+      <c r="H46" s="171" t="n"/>
+      <c r="I46" s="171" t="n"/>
+      <c r="J46" s="171" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="n"/>
+      <c r="B47" s="171" t="n"/>
+      <c r="C47" s="171" t="n"/>
+      <c r="D47" s="171" t="n"/>
       <c r="E47" s="94">
         <f>J35/E44*(1+Scenarios!$C$10)/(Scenarios!$C$9-Scenarios!$C$10)</f>
         <v/>
       </c>
+      <c r="F47" s="171" t="n"/>
+      <c r="G47" s="171" t="n"/>
+      <c r="H47" s="171" t="n"/>
+      <c r="I47" s="171" t="n"/>
+      <c r="J47" s="171" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="23" t="inlineStr">
@@ -10008,10 +10572,18 @@
           <t>PV of terminal value</t>
         </is>
       </c>
+      <c r="B48" s="171" t="n"/>
+      <c r="C48" s="171" t="n"/>
+      <c r="D48" s="171" t="n"/>
       <c r="E48" s="70">
         <f>E45/(1+Scenarios!$C$9)^J36</f>
         <v/>
       </c>
+      <c r="F48" s="171" t="n"/>
+      <c r="G48" s="171" t="n"/>
+      <c r="H48" s="171" t="n"/>
+      <c r="I48" s="171" t="n"/>
+      <c r="J48" s="171" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
@@ -10019,10 +10591,18 @@
           <t>Enterprise value</t>
         </is>
       </c>
+      <c r="B49" s="171" t="n"/>
+      <c r="C49" s="171" t="n"/>
+      <c r="D49" s="171" t="n"/>
       <c r="E49" s="25">
         <f>E42+E48</f>
         <v/>
       </c>
+      <c r="F49" s="171" t="n"/>
+      <c r="G49" s="171" t="n"/>
+      <c r="H49" s="171" t="n"/>
+      <c r="I49" s="171" t="n"/>
+      <c r="J49" s="171" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
@@ -10030,6 +10610,7 @@
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
+      <c r="B50" s="171" t="n"/>
       <c r="C50" s="95" t="inlineStr">
         <is>
           <t>10-K</t>
@@ -10039,6 +10620,11 @@
       <c r="E50" s="74" t="n">
         <v>1807202</v>
       </c>
+      <c r="F50" s="171" t="n"/>
+      <c r="G50" s="171" t="n"/>
+      <c r="H50" s="171" t="n"/>
+      <c r="I50" s="171" t="n"/>
+      <c r="J50" s="171" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
@@ -10056,12 +10642,35 @@
       <c r="E51" s="74" t="n">
         <v>-1798441</v>
       </c>
+      <c r="F51" s="171" t="n"/>
+      <c r="G51" s="171" t="n"/>
+      <c r="H51" s="171" t="n"/>
+      <c r="I51" s="171" t="n"/>
+      <c r="J51" s="171" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="26" t="n"/>
+      <c r="B52" s="171" t="n"/>
+      <c r="C52" s="171" t="n"/>
+      <c r="D52" s="171" t="n"/>
+      <c r="E52" s="171" t="n"/>
+      <c r="F52" s="171" t="n"/>
+      <c r="G52" s="171" t="n"/>
+      <c r="H52" s="171" t="n"/>
+      <c r="I52" s="171" t="n"/>
+      <c r="J52" s="171" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="26" t="n"/>
+      <c r="B53" s="171" t="n"/>
+      <c r="C53" s="171" t="n"/>
+      <c r="D53" s="171" t="n"/>
+      <c r="E53" s="171" t="n"/>
+      <c r="F53" s="171" t="n"/>
+      <c r="G53" s="171" t="n"/>
+      <c r="H53" s="171" t="n"/>
+      <c r="I53" s="171" t="n"/>
+      <c r="J53" s="171" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="23" t="inlineStr">
@@ -10069,10 +10678,18 @@
           <t>Equity value</t>
         </is>
       </c>
+      <c r="B54" s="171" t="n"/>
+      <c r="C54" s="171" t="n"/>
+      <c r="D54" s="171" t="n"/>
       <c r="E54" s="25">
         <f>E49+E50+E51</f>
         <v/>
       </c>
+      <c r="F54" s="171" t="n"/>
+      <c r="G54" s="171" t="n"/>
+      <c r="H54" s="171" t="n"/>
+      <c r="I54" s="171" t="n"/>
+      <c r="J54" s="171" t="n"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
@@ -10080,6 +10697,7 @@
           <t>Shares outstanding (000)</t>
         </is>
       </c>
+      <c r="B55" s="171" t="n"/>
       <c r="C55" s="95" t="inlineStr">
         <is>
           <t>10-K</t>
@@ -10089,6 +10707,11 @@
       <c r="E55" s="74" t="n">
         <v>111380</v>
       </c>
+      <c r="F55" s="171" t="n"/>
+      <c r="G55" s="171" t="n"/>
+      <c r="H55" s="171" t="n"/>
+      <c r="I55" s="171" t="n"/>
+      <c r="J55" s="171" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="23" t="inlineStr">
@@ -10096,10 +10719,18 @@
           <t>Implied value per share</t>
         </is>
       </c>
+      <c r="B56" s="171" t="n"/>
+      <c r="C56" s="171" t="n"/>
+      <c r="D56" s="171" t="n"/>
       <c r="E56" s="96">
         <f>E54/E55</f>
         <v/>
       </c>
+      <c r="F56" s="171" t="n"/>
+      <c r="G56" s="171" t="n"/>
+      <c r="H56" s="171" t="n"/>
+      <c r="I56" s="171" t="n"/>
+      <c r="J56" s="171" t="n"/>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
@@ -10107,6 +10738,7 @@
           <t>Current share price</t>
         </is>
       </c>
+      <c r="B57" s="171" t="n"/>
       <c r="C57" s="95" t="inlineStr">
         <is>
           <t>NASDAQ</t>
@@ -10116,6 +10748,11 @@
       <c r="E57" s="97" t="n">
         <v>100</v>
       </c>
+      <c r="F57" s="171" t="n"/>
+      <c r="G57" s="171" t="n"/>
+      <c r="H57" s="171" t="n"/>
+      <c r="I57" s="171" t="n"/>
+      <c r="J57" s="171" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="23" t="inlineStr">
@@ -10123,17 +10760,57 @@
           <t>Implied upside / (downside)</t>
         </is>
       </c>
+      <c r="B58" s="171" t="n"/>
+      <c r="C58" s="171" t="n"/>
+      <c r="D58" s="171" t="n"/>
       <c r="E58" s="98">
         <f>E56/E57-1</f>
         <v/>
       </c>
+      <c r="F58" s="171" t="n"/>
+      <c r="G58" s="171" t="n"/>
+      <c r="H58" s="171" t="n"/>
+      <c r="I58" s="171" t="n"/>
+      <c r="J58" s="171" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="n"/>
+      <c r="B59" s="171" t="n"/>
+      <c r="C59" s="171" t="n"/>
+      <c r="D59" s="171" t="n"/>
       <c r="E59" s="32">
         <f>E48/E49</f>
         <v/>
       </c>
+      <c r="F59" s="171" t="n"/>
+      <c r="G59" s="171" t="n"/>
+      <c r="H59" s="171" t="n"/>
+      <c r="I59" s="171" t="n"/>
+      <c r="J59" s="171" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="171" t="n"/>
+      <c r="B60" s="171" t="n"/>
+      <c r="C60" s="171" t="n"/>
+      <c r="D60" s="171" t="n"/>
+      <c r="E60" s="171" t="n"/>
+      <c r="F60" s="171" t="n"/>
+      <c r="G60" s="171" t="n"/>
+      <c r="H60" s="171" t="n"/>
+      <c r="I60" s="171" t="n"/>
+      <c r="J60" s="171" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="171" t="n"/>
+      <c r="B61" s="171" t="n"/>
+      <c r="C61" s="171" t="n"/>
+      <c r="D61" s="171" t="n"/>
+      <c r="E61" s="171" t="n"/>
+      <c r="F61" s="171" t="n"/>
+      <c r="G61" s="171" t="n"/>
+      <c r="H61" s="171" t="n"/>
+      <c r="I61" s="171" t="n"/>
+      <c r="J61" s="171" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
@@ -10141,10 +10818,15 @@
           <t>SHARE REPURCHASE &amp; EPS ACCRETION SCHEDULE</t>
         </is>
       </c>
-      <c r="B62" s="13" t="n"/>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
+      <c r="B62" s="172" t="n"/>
+      <c r="C62" s="172" t="n"/>
+      <c r="D62" s="172" t="n"/>
+      <c r="E62" s="172" t="n"/>
+      <c r="F62" s="171" t="n"/>
+      <c r="G62" s="171" t="n"/>
+      <c r="H62" s="171" t="n"/>
+      <c r="I62" s="171" t="n"/>
+      <c r="J62" s="171" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="26" t="inlineStr">
@@ -10152,6 +10834,27 @@
           <t>Guardrail: implied value per share above still divides equity value by Day-1 shares (E55 = 111,380k). This schedule does not change intrinsic DCF per share.</t>
         </is>
       </c>
+      <c r="B63" s="171" t="n"/>
+      <c r="C63" s="171" t="n"/>
+      <c r="D63" s="171" t="n"/>
+      <c r="E63" s="171" t="n"/>
+      <c r="F63" s="171" t="n"/>
+      <c r="G63" s="171" t="n"/>
+      <c r="H63" s="171" t="n"/>
+      <c r="I63" s="171" t="n"/>
+      <c r="J63" s="171" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="171" t="n"/>
+      <c r="B64" s="171" t="n"/>
+      <c r="C64" s="171" t="n"/>
+      <c r="D64" s="171" t="n"/>
+      <c r="E64" s="171" t="n"/>
+      <c r="F64" s="171" t="n"/>
+      <c r="G64" s="171" t="n"/>
+      <c r="H64" s="171" t="n"/>
+      <c r="I64" s="171" t="n"/>
+      <c r="J64" s="171" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -10159,6 +10862,9 @@
           <t>Annual repurchase budget ($000) — base case</t>
         </is>
       </c>
+      <c r="B65" s="171" t="n"/>
+      <c r="C65" s="171" t="n"/>
+      <c r="D65" s="171" t="n"/>
       <c r="E65" s="37">
         <f>Scenarios!$C$21</f>
         <v/>
@@ -10190,6 +10896,9 @@
           <t>Cost of equity — share-price growth rate</t>
         </is>
       </c>
+      <c r="B66" s="171" t="n"/>
+      <c r="C66" s="171" t="n"/>
+      <c r="D66" s="171" t="n"/>
       <c r="E66" s="20" t="n">
         <v>0.105</v>
       </c>
@@ -10214,12 +10923,28 @@
         <v/>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="171" t="n"/>
+      <c r="B67" s="171" t="n"/>
+      <c r="C67" s="171" t="n"/>
+      <c r="D67" s="171" t="n"/>
+      <c r="E67" s="171" t="n"/>
+      <c r="F67" s="171" t="n"/>
+      <c r="G67" s="171" t="n"/>
+      <c r="H67" s="171" t="n"/>
+      <c r="I67" s="171" t="n"/>
+      <c r="J67" s="171" t="n"/>
+    </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
           <t>Unlevered free cash flow (from DCF above)</t>
         </is>
       </c>
+      <c r="B68" s="171" t="n"/>
+      <c r="C68" s="171" t="n"/>
+      <c r="D68" s="171" t="n"/>
+      <c r="E68" s="171" t="n"/>
       <c r="F68" s="75">
         <f>F35</f>
         <v/>
@@ -10247,6 +10972,9 @@
           <t>Repurchase cash deployed (= fixed budget)</t>
         </is>
       </c>
+      <c r="B69" s="171" t="n"/>
+      <c r="C69" s="171" t="n"/>
+      <c r="D69" s="171" t="n"/>
       <c r="E69" s="75" t="n">
         <v>0</v>
       </c>
@@ -10277,6 +11005,10 @@
           <t>Repurchase as % of UFCF (derived)</t>
         </is>
       </c>
+      <c r="B70" s="171" t="n"/>
+      <c r="C70" s="171" t="n"/>
+      <c r="D70" s="171" t="n"/>
+      <c r="E70" s="171" t="n"/>
       <c r="F70" s="32">
         <f>F69/F68</f>
         <v/>
@@ -10298,12 +11030,27 @@
         <v/>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="171" t="n"/>
+      <c r="B71" s="171" t="n"/>
+      <c r="C71" s="171" t="n"/>
+      <c r="D71" s="171" t="n"/>
+      <c r="E71" s="171" t="n"/>
+      <c r="F71" s="171" t="n"/>
+      <c r="G71" s="171" t="n"/>
+      <c r="H71" s="171" t="n"/>
+      <c r="I71" s="171" t="n"/>
+      <c r="J71" s="171" t="n"/>
+    </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
           <t>Projected share price ($)</t>
         </is>
       </c>
+      <c r="B72" s="171" t="n"/>
+      <c r="C72" s="171" t="n"/>
+      <c r="D72" s="171" t="n"/>
       <c r="E72" s="99" t="n">
         <v>100</v>
       </c>
@@ -10334,6 +11081,9 @@
           <t>Shares retired (000)</t>
         </is>
       </c>
+      <c r="B73" s="171" t="n"/>
+      <c r="C73" s="171" t="n"/>
+      <c r="D73" s="171" t="n"/>
       <c r="E73" s="75" t="n">
         <v>0</v>
       </c>
@@ -10364,6 +11114,9 @@
           <t>Beginning shares (000)</t>
         </is>
       </c>
+      <c r="B74" s="171" t="n"/>
+      <c r="C74" s="171" t="n"/>
+      <c r="D74" s="171" t="n"/>
       <c r="E74" s="22" t="n">
         <v>111380</v>
       </c>
@@ -10394,6 +11147,9 @@
           <t>Ending shares (000)</t>
         </is>
       </c>
+      <c r="B75" s="171" t="n"/>
+      <c r="C75" s="171" t="n"/>
+      <c r="D75" s="171" t="n"/>
       <c r="E75" s="100" t="n">
         <v>111380</v>
       </c>
@@ -10418,12 +11174,27 @@
         <v/>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="171" t="n"/>
+      <c r="B76" s="171" t="n"/>
+      <c r="C76" s="171" t="n"/>
+      <c r="D76" s="171" t="n"/>
+      <c r="E76" s="171" t="n"/>
+      <c r="F76" s="171" t="n"/>
+      <c r="G76" s="171" t="n"/>
+      <c r="H76" s="171" t="n"/>
+      <c r="I76" s="171" t="n"/>
+      <c r="J76" s="171" t="n"/>
+    </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
           <t>Projected net income ($000)</t>
         </is>
       </c>
+      <c r="B77" s="171" t="n"/>
+      <c r="C77" s="171" t="n"/>
+      <c r="D77" s="171" t="n"/>
       <c r="E77" s="22" t="n">
         <v>1579183</v>
       </c>
@@ -10454,6 +11225,9 @@
           <t>Accretive EPS ($/share) = Net income ÷ ending shares</t>
         </is>
       </c>
+      <c r="B78" s="171" t="n"/>
+      <c r="C78" s="171" t="n"/>
+      <c r="D78" s="171" t="n"/>
       <c r="E78" s="101">
         <f>E77/E75</f>
         <v/>
@@ -10479,10 +11253,29 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="171" t="n"/>
+      <c r="B79" s="171" t="n"/>
+      <c r="C79" s="171" t="n"/>
+      <c r="D79" s="171" t="n"/>
+      <c r="E79" s="171" t="n"/>
+      <c r="F79" s="171" t="n"/>
+      <c r="G79" s="171" t="n"/>
+      <c r="H79" s="171" t="n"/>
+      <c r="I79" s="171" t="n"/>
+      <c r="J79" s="171" t="n"/>
+    </row>
     <row r="80">
       <c r="A80" s="93" t="n"/>
-      <c r="B80" s="13" t="n"/>
-      <c r="C80" s="13" t="n"/>
+      <c r="B80" s="172" t="n"/>
+      <c r="C80" s="172" t="n"/>
+      <c r="D80" s="171" t="n"/>
+      <c r="E80" s="171" t="n"/>
+      <c r="F80" s="171" t="n"/>
+      <c r="G80" s="171" t="n"/>
+      <c r="H80" s="171" t="n"/>
+      <c r="I80" s="171" t="n"/>
+      <c r="J80" s="171" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="15" t="inlineStr">
@@ -10490,6 +11283,15 @@
           <t>Exit multiple is the Gordon identity — not a peer pick or an average</t>
         </is>
       </c>
+      <c r="B81" s="171" t="n"/>
+      <c r="C81" s="171" t="n"/>
+      <c r="D81" s="171" t="n"/>
+      <c r="E81" s="171" t="n"/>
+      <c r="F81" s="171" t="n"/>
+      <c r="G81" s="171" t="n"/>
+      <c r="H81" s="171" t="n"/>
+      <c r="I81" s="171" t="n"/>
+      <c r="J81" s="171" t="n"/>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
@@ -10508,6 +11310,11 @@
         <f>E46</f>
         <v/>
       </c>
+      <c r="F82" s="171" t="n"/>
+      <c r="G82" s="171" t="n"/>
+      <c r="H82" s="171" t="n"/>
+      <c r="I82" s="171" t="n"/>
+      <c r="J82" s="171" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
@@ -10515,10 +11322,18 @@
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
       </c>
+      <c r="B83" s="171" t="n"/>
+      <c r="C83" s="171" t="n"/>
+      <c r="D83" s="171" t="n"/>
       <c r="E83" s="75">
         <f>E44*E82</f>
         <v/>
       </c>
+      <c r="F83" s="171" t="n"/>
+      <c r="G83" s="171" t="n"/>
+      <c r="H83" s="171" t="n"/>
+      <c r="I83" s="171" t="n"/>
+      <c r="J83" s="171" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
@@ -10526,10 +11341,18 @@
           <t>PV of terminal value</t>
         </is>
       </c>
+      <c r="B84" s="171" t="n"/>
+      <c r="C84" s="171" t="n"/>
+      <c r="D84" s="171" t="n"/>
       <c r="E84" s="75">
         <f>E83/(1+Scenarios!$C$9)^J36</f>
         <v/>
       </c>
+      <c r="F84" s="171" t="n"/>
+      <c r="G84" s="171" t="n"/>
+      <c r="H84" s="171" t="n"/>
+      <c r="I84" s="171" t="n"/>
+      <c r="J84" s="171" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="23" t="inlineStr">
@@ -10537,10 +11360,18 @@
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
+      <c r="B85" s="171" t="n"/>
+      <c r="C85" s="171" t="n"/>
+      <c r="D85" s="171" t="n"/>
       <c r="E85" s="25">
         <f>E42+E84</f>
         <v/>
       </c>
+      <c r="F85" s="171" t="n"/>
+      <c r="G85" s="171" t="n"/>
+      <c r="H85" s="171" t="n"/>
+      <c r="I85" s="171" t="n"/>
+      <c r="J85" s="171" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="23" t="inlineStr">
@@ -10548,10 +11379,30 @@
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
+      <c r="B86" s="171" t="n"/>
+      <c r="C86" s="171" t="n"/>
+      <c r="D86" s="171" t="n"/>
       <c r="E86" s="102">
         <f>(E85+E50+E51)/E55</f>
         <v/>
       </c>
+      <c r="F86" s="171" t="n"/>
+      <c r="G86" s="171" t="n"/>
+      <c r="H86" s="171" t="n"/>
+      <c r="I86" s="171" t="n"/>
+      <c r="J86" s="171" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="171" t="n"/>
+      <c r="B87" s="171" t="n"/>
+      <c r="C87" s="171" t="n"/>
+      <c r="D87" s="171" t="n"/>
+      <c r="E87" s="171" t="n"/>
+      <c r="F87" s="171" t="n"/>
+      <c r="G87" s="171" t="n"/>
+      <c r="H87" s="171" t="n"/>
+      <c r="I87" s="171" t="n"/>
+      <c r="J87" s="171" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
@@ -10559,9 +11410,15 @@
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
       </c>
-      <c r="B88" s="13" t="n"/>
-      <c r="C88" s="13" t="n"/>
-      <c r="D88" s="13" t="n"/>
+      <c r="B88" s="172" t="n"/>
+      <c r="C88" s="172" t="n"/>
+      <c r="D88" s="172" t="n"/>
+      <c r="E88" s="171" t="n"/>
+      <c r="F88" s="171" t="n"/>
+      <c r="G88" s="171" t="n"/>
+      <c r="H88" s="171" t="n"/>
+      <c r="I88" s="171" t="n"/>
+      <c r="J88" s="171" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="103" t="inlineStr"/>
@@ -10572,6 +11429,12 @@
         </is>
       </c>
       <c r="D89" s="54" t="n"/>
+      <c r="E89" s="171" t="n"/>
+      <c r="F89" s="171" t="n"/>
+      <c r="G89" s="171" t="n"/>
+      <c r="H89" s="171" t="n"/>
+      <c r="I89" s="171" t="n"/>
+      <c r="J89" s="171" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="23" t="inlineStr">
@@ -10591,6 +11454,12 @@
         <f>B90-C90</f>
         <v/>
       </c>
+      <c r="E90" s="171" t="n"/>
+      <c r="F90" s="171" t="n"/>
+      <c r="G90" s="171" t="n"/>
+      <c r="H90" s="171" t="n"/>
+      <c r="I90" s="171" t="n"/>
+      <c r="J90" s="171" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="23" t="inlineStr">
@@ -10610,6 +11479,12 @@
         <f>B91-C91</f>
         <v/>
       </c>
+      <c r="E91" s="171" t="n"/>
+      <c r="F91" s="171" t="n"/>
+      <c r="G91" s="171" t="n"/>
+      <c r="H91" s="171" t="n"/>
+      <c r="I91" s="171" t="n"/>
+      <c r="J91" s="171" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
@@ -10623,6 +11498,12 @@
         <f>(B90-C90)/B90</f>
         <v/>
       </c>
+      <c r="E92" s="171" t="n"/>
+      <c r="F92" s="171" t="n"/>
+      <c r="G92" s="171" t="n"/>
+      <c r="H92" s="171" t="n"/>
+      <c r="I92" s="171" t="n"/>
+      <c r="J92" s="171" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="23" t="inlineStr">
@@ -10642,6 +11523,12 @@
         <f>B93-C93</f>
         <v/>
       </c>
+      <c r="E93" s="171" t="n"/>
+      <c r="F93" s="171" t="n"/>
+      <c r="G93" s="171" t="n"/>
+      <c r="H93" s="171" t="n"/>
+      <c r="I93" s="171" t="n"/>
+      <c r="J93" s="171" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="68" t="inlineStr">
@@ -10658,6 +11545,36 @@
         <v/>
       </c>
       <c r="D94" s="26" t="n"/>
+      <c r="E94" s="171" t="n"/>
+      <c r="F94" s="171" t="n"/>
+      <c r="G94" s="171" t="n"/>
+      <c r="H94" s="171" t="n"/>
+      <c r="I94" s="171" t="n"/>
+      <c r="J94" s="171" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="171" t="n"/>
+      <c r="B95" s="171" t="n"/>
+      <c r="C95" s="171" t="n"/>
+      <c r="D95" s="171" t="n"/>
+      <c r="E95" s="171" t="n"/>
+      <c r="F95" s="171" t="n"/>
+      <c r="G95" s="171" t="n"/>
+      <c r="H95" s="171" t="n"/>
+      <c r="I95" s="171" t="n"/>
+      <c r="J95" s="171" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="171" t="n"/>
+      <c r="B96" s="171" t="n"/>
+      <c r="C96" s="171" t="n"/>
+      <c r="D96" s="171" t="n"/>
+      <c r="E96" s="171" t="n"/>
+      <c r="F96" s="171" t="n"/>
+      <c r="G96" s="171" t="n"/>
+      <c r="H96" s="171" t="n"/>
+      <c r="I96" s="171" t="n"/>
+      <c r="J96" s="171" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
@@ -10665,13 +11582,15 @@
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
       </c>
-      <c r="B97" s="13" t="n"/>
-      <c r="C97" s="13" t="n"/>
-      <c r="D97" s="13" t="n"/>
-      <c r="E97" s="13" t="n"/>
-      <c r="F97" s="13" t="n"/>
-      <c r="G97" s="13" t="n"/>
-      <c r="H97" s="13" t="n"/>
+      <c r="B97" s="172" t="n"/>
+      <c r="C97" s="172" t="n"/>
+      <c r="D97" s="172" t="n"/>
+      <c r="E97" s="172" t="n"/>
+      <c r="F97" s="172" t="n"/>
+      <c r="G97" s="172" t="n"/>
+      <c r="H97" s="172" t="n"/>
+      <c r="I97" s="171" t="n"/>
+      <c r="J97" s="171" t="n"/>
     </row>
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="108" t="inlineStr">
@@ -10686,6 +11605,7 @@
         </is>
       </c>
       <c r="D98" s="19" t="n"/>
+      <c r="E98" s="171" t="n"/>
       <c r="F98" s="109" t="n">
         <v>0.015</v>
       </c>
@@ -10706,12 +11626,14 @@
       <c r="A99" s="109" t="n">
         <v>0.095</v>
       </c>
+      <c r="B99" s="171" t="n"/>
       <c r="C99" s="95" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
       </c>
       <c r="D99" s="19" t="n"/>
+      <c r="E99" s="171" t="n"/>
       <c r="F99" s="110">
         <f>(NPV($A99,$F$35:$J$35)+($J$35*(1+F$98)/($A99-F$98))/(1+$A99)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
@@ -10737,7 +11659,10 @@
       <c r="A100" s="109" t="n">
         <v>0.1</v>
       </c>
+      <c r="B100" s="171" t="n"/>
+      <c r="C100" s="171" t="n"/>
       <c r="D100" s="19" t="n"/>
+      <c r="E100" s="171" t="n"/>
       <c r="F100" s="110">
         <f>(NPV($A100,$F$35:$J$35)+($J$35*(1+F$98)/($A100-F$98))/(1+$A100)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
@@ -10763,7 +11688,10 @@
       <c r="A101" s="109" t="n">
         <v>0.105</v>
       </c>
+      <c r="B101" s="171" t="n"/>
+      <c r="C101" s="171" t="n"/>
       <c r="D101" s="19" t="n"/>
+      <c r="E101" s="171" t="n"/>
       <c r="F101" s="110">
         <f>(NPV($A101,$F$35:$J$35)+($J$35*(1+F$98)/($A101-F$98))/(1+$A101)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
@@ -10789,7 +11717,10 @@
       <c r="A102" s="109" t="n">
         <v>0.11</v>
       </c>
+      <c r="B102" s="171" t="n"/>
+      <c r="C102" s="171" t="n"/>
       <c r="D102" s="19" t="n"/>
+      <c r="E102" s="171" t="n"/>
       <c r="F102" s="110">
         <f>(NPV($A102,$F$35:$J$35)+($J$35*(1+F$98)/($A102-F$98))/(1+$A102)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
@@ -10815,7 +11746,10 @@
       <c r="A103" s="109" t="n">
         <v>0.115</v>
       </c>
+      <c r="B103" s="171" t="n"/>
+      <c r="C103" s="171" t="n"/>
       <c r="D103" s="19" t="n"/>
+      <c r="E103" s="171" t="n"/>
       <c r="F103" s="110">
         <f>(NPV($A103,$F$35:$J$35)+($J$35*(1+F$98)/($A103-F$98))/(1+$A103)^$J$36+$E$50+$E$51)/$E$55</f>
         <v/>
@@ -10838,6 +11772,7 @@
       </c>
     </row>
     <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="171" t="n"/>
       <c r="B104" s="17" t="n"/>
       <c r="C104" s="18" t="inlineStr">
         <is>
@@ -10845,6 +11780,12 @@
         </is>
       </c>
       <c r="D104" s="19" t="n"/>
+      <c r="E104" s="171" t="n"/>
+      <c r="F104" s="171" t="n"/>
+      <c r="G104" s="171" t="n"/>
+      <c r="H104" s="171" t="n"/>
+      <c r="I104" s="171" t="n"/>
+      <c r="J104" s="171" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -10932,15 +11873,18 @@
           <t>RELATIVE VALUATION — IMPLIED PRICE RANGES (FOOTBALL FIELD)</t>
         </is>
       </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-      <c r="E1" s="13" t="n"/>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="13" t="n"/>
+      <c r="B1" s="172" t="n"/>
+      <c r="C1" s="172" t="n"/>
+      <c r="D1" s="172" t="n"/>
+      <c r="E1" s="172" t="n"/>
+      <c r="F1" s="172" t="n"/>
+      <c r="G1" s="172" t="n"/>
+      <c r="H1" s="172" t="n"/>
+      <c r="I1" s="171" t="n"/>
+      <c r="J1" s="171" t="n"/>
     </row>
     <row r="2">
+      <c r="A2" s="171" t="n"/>
       <c r="B2" s="15" t="n"/>
       <c r="C2" s="15" t="inlineStr">
         <is>
@@ -10948,6 +11892,12 @@
         </is>
       </c>
       <c r="D2" s="15" t="n"/>
+      <c r="E2" s="171" t="n"/>
+      <c r="F2" s="171" t="n"/>
+      <c r="G2" s="171" t="n"/>
+      <c r="H2" s="171" t="n"/>
+      <c r="I2" s="171" t="n"/>
+      <c r="J2" s="171" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
@@ -10955,6 +11905,15 @@
           <t>LULU operating metrics (FY2025A / FY2026E)</t>
         </is>
       </c>
+      <c r="B3" s="171" t="n"/>
+      <c r="C3" s="171" t="n"/>
+      <c r="D3" s="171" t="n"/>
+      <c r="E3" s="171" t="n"/>
+      <c r="F3" s="171" t="n"/>
+      <c r="G3" s="171" t="n"/>
+      <c r="H3" s="171" t="n"/>
+      <c r="I3" s="171" t="n"/>
+      <c r="J3" s="171" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -10962,6 +11921,7 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
+      <c r="B4" s="171" t="n"/>
       <c r="C4" s="95" t="inlineStr">
         <is>
           <t>10-K</t>
@@ -10971,6 +11931,11 @@
       <c r="E4" s="74" t="n">
         <v>11102600</v>
       </c>
+      <c r="F4" s="171" t="n"/>
+      <c r="G4" s="171" t="n"/>
+      <c r="H4" s="171" t="n"/>
+      <c r="I4" s="171" t="n"/>
+      <c r="J4" s="171" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -10978,10 +11943,18 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
+      <c r="B5" s="171" t="n"/>
+      <c r="C5" s="171" t="n"/>
+      <c r="D5" s="171" t="n"/>
       <c r="E5" s="75">
         <f>DCF!$E$11+DCF!$E$16</f>
         <v/>
       </c>
+      <c r="F5" s="171" t="n"/>
+      <c r="G5" s="171" t="n"/>
+      <c r="H5" s="171" t="n"/>
+      <c r="I5" s="171" t="n"/>
+      <c r="J5" s="171" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -10989,31 +11962,44 @@
           <t>FY2030E terminal EBITDA (DCF EBIT + D&amp;A)</t>
         </is>
       </c>
+      <c r="B6" s="171" t="n"/>
       <c r="C6" s="95" t="inlineStr">
         <is>
           <t>↳ DCF base case</t>
         </is>
       </c>
+      <c r="D6" s="171" t="n"/>
       <c r="E6" s="75">
         <f>DCF!E44</f>
         <v/>
       </c>
+      <c r="F6" s="171" t="n"/>
+      <c r="G6" s="171" t="n"/>
+      <c r="H6" s="171" t="n"/>
+      <c r="I6" s="171" t="n"/>
+      <c r="J6" s="171" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>FY2026E diluted EPS (guidance midpoint)</t>
-        </is>
-      </c>
+          <t>FY2026E diluted EPS (model base case)</t>
+        </is>
+      </c>
+      <c r="B7" s="171" t="n"/>
       <c r="C7" s="95" t="inlineStr">
         <is>
-          <t>Release</t>
+          <t>DCF base case</t>
         </is>
       </c>
       <c r="D7" s="19" t="n"/>
-      <c r="E7" s="97" t="n">
-        <v>9.609999999999999</v>
-      </c>
+      <c r="E7" s="170" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="F7" s="171" t="n"/>
+      <c r="G7" s="171" t="n"/>
+      <c r="H7" s="171" t="n"/>
+      <c r="I7" s="171" t="n"/>
+      <c r="J7" s="171" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -11021,6 +12007,7 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
+      <c r="B8" s="171" t="n"/>
       <c r="C8" s="95" t="inlineStr">
         <is>
           <t>10-K</t>
@@ -11030,6 +12017,11 @@
       <c r="E8" s="74" t="n">
         <v>1807202</v>
       </c>
+      <c r="F8" s="171" t="n"/>
+      <c r="G8" s="171" t="n"/>
+      <c r="H8" s="171" t="n"/>
+      <c r="I8" s="171" t="n"/>
+      <c r="J8" s="171" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -11037,6 +12029,7 @@
           <t>Shares outstanding (000)</t>
         </is>
       </c>
+      <c r="B9" s="171" t="n"/>
       <c r="C9" s="95" t="inlineStr">
         <is>
           <t>10-K</t>
@@ -11046,6 +12039,11 @@
       <c r="E9" s="74" t="n">
         <v>111380</v>
       </c>
+      <c r="F9" s="171" t="n"/>
+      <c r="G9" s="171" t="n"/>
+      <c r="H9" s="171" t="n"/>
+      <c r="I9" s="171" t="n"/>
+      <c r="J9" s="171" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
@@ -11053,6 +12051,7 @@
           <t>Current share price</t>
         </is>
       </c>
+      <c r="B10" s="171" t="n"/>
       <c r="C10" s="95" t="inlineStr">
         <is>
           <t>NASDAQ</t>
@@ -11062,20 +12061,53 @@
       <c r="E10" s="97" t="n">
         <v>100</v>
       </c>
+      <c r="F10" s="171" t="n"/>
+      <c r="G10" s="171" t="n"/>
+      <c r="H10" s="171" t="n"/>
+      <c r="I10" s="171" t="n"/>
+      <c r="J10" s="171" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="107" t="n"/>
+      <c r="B11" s="171" t="n"/>
+      <c r="C11" s="171" t="n"/>
+      <c r="D11" s="171" t="n"/>
       <c r="E11" s="112">
         <f>(E10*E9-E8)/E5</f>
         <v/>
       </c>
+      <c r="F11" s="171" t="n"/>
+      <c r="G11" s="171" t="n"/>
+      <c r="H11" s="171" t="n"/>
+      <c r="I11" s="171" t="n"/>
+      <c r="J11" s="171" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="107" t="n"/>
+      <c r="B12" s="171" t="n"/>
+      <c r="C12" s="171" t="n"/>
+      <c r="D12" s="171" t="n"/>
       <c r="E12" s="112">
         <f>E10/E7</f>
         <v/>
       </c>
+      <c r="F12" s="171" t="n"/>
+      <c r="G12" s="171" t="n"/>
+      <c r="H12" s="171" t="n"/>
+      <c r="I12" s="171" t="n"/>
+      <c r="J12" s="171" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="171" t="n"/>
+      <c r="B13" s="171" t="n"/>
+      <c r="C13" s="171" t="n"/>
+      <c r="D13" s="171" t="n"/>
+      <c r="E13" s="171" t="n"/>
+      <c r="F13" s="171" t="n"/>
+      <c r="G13" s="171" t="n"/>
+      <c r="H13" s="171" t="n"/>
+      <c r="I13" s="171" t="n"/>
+      <c r="J13" s="171" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -11083,6 +12115,15 @@
           <t>EXIT MULTIPLE BUILD — FY2030E TERMINAL YEAR</t>
         </is>
       </c>
+      <c r="B14" s="171" t="n"/>
+      <c r="C14" s="171" t="n"/>
+      <c r="D14" s="171" t="n"/>
+      <c r="E14" s="171" t="n"/>
+      <c r="F14" s="171" t="n"/>
+      <c r="G14" s="171" t="n"/>
+      <c r="H14" s="171" t="n"/>
+      <c r="I14" s="171" t="n"/>
+      <c r="J14" s="171" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="107" t="inlineStr">
@@ -11090,6 +12131,15 @@
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
+      <c r="B15" s="171" t="n"/>
+      <c r="C15" s="171" t="n"/>
+      <c r="D15" s="171" t="n"/>
+      <c r="E15" s="171" t="n"/>
+      <c r="F15" s="171" t="n"/>
+      <c r="G15" s="171" t="n"/>
+      <c r="H15" s="171" t="n"/>
+      <c r="I15" s="171" t="n"/>
+      <c r="J15" s="171" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -11097,9 +12147,27 @@
           <t>PITCHBOOK PUBCOMPS — daily EV / TTM EBITDA as of 04-Sep-2026 ($000)</t>
         </is>
       </c>
+      <c r="B16" s="171" t="n"/>
+      <c r="C16" s="171" t="n"/>
+      <c r="D16" s="171" t="n"/>
+      <c r="E16" s="171" t="n"/>
+      <c r="F16" s="171" t="n"/>
+      <c r="G16" s="171" t="n"/>
+      <c r="H16" s="171" t="n"/>
+      <c r="I16" s="171" t="n"/>
+      <c r="J16" s="171" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="26" t="n"/>
+      <c r="B17" s="171" t="n"/>
+      <c r="C17" s="171" t="n"/>
+      <c r="D17" s="171" t="n"/>
+      <c r="E17" s="171" t="n"/>
+      <c r="F17" s="171" t="n"/>
+      <c r="G17" s="171" t="n"/>
+      <c r="H17" s="171" t="n"/>
+      <c r="I17" s="171" t="n"/>
+      <c r="J17" s="171" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="113" t="inlineStr">
@@ -11119,6 +12187,9 @@
           <t>EV/EBITDA</t>
         </is>
       </c>
+      <c r="F18" s="171" t="n"/>
+      <c r="G18" s="171" t="n"/>
+      <c r="H18" s="171" t="n"/>
       <c r="I18" s="114" t="inlineStr">
         <is>
           <t>EV ($000)</t>
@@ -11147,6 +12218,9 @@
         <f>IF(J19&lt;=0,"n.m.",I19/J19)</f>
         <v/>
       </c>
+      <c r="F19" s="171" t="n"/>
+      <c r="G19" s="171" t="n"/>
+      <c r="H19" s="171" t="n"/>
       <c r="I19" s="116" t="n">
         <v>11890440</v>
       </c>
@@ -11171,6 +12245,9 @@
         <f>IF(J20&lt;=0,"n.m.",I20/J20)</f>
         <v/>
       </c>
+      <c r="F20" s="171" t="n"/>
+      <c r="G20" s="171" t="n"/>
+      <c r="H20" s="171" t="n"/>
       <c r="I20" s="116" t="n">
         <v>3208397</v>
       </c>
@@ -11195,6 +12272,9 @@
         <f>IF(J21&lt;=0,"n.m.",I21/J21)</f>
         <v/>
       </c>
+      <c r="F21" s="171" t="n"/>
+      <c r="G21" s="171" t="n"/>
+      <c r="H21" s="171" t="n"/>
       <c r="I21" s="116" t="n">
         <v>35661944</v>
       </c>
@@ -11219,6 +12299,9 @@
         <f>IF(J22&lt;=0,"n.m.",I22/J22)</f>
         <v/>
       </c>
+      <c r="F22" s="171" t="n"/>
+      <c r="G22" s="171" t="n"/>
+      <c r="H22" s="171" t="n"/>
       <c r="I22" s="116" t="n">
         <v>58972350</v>
       </c>
@@ -11243,6 +12326,9 @@
         <f>IF(J23&lt;=0,"n.m.",I23/J23)</f>
         <v/>
       </c>
+      <c r="F23" s="171" t="n"/>
+      <c r="G23" s="171" t="n"/>
+      <c r="H23" s="171" t="n"/>
       <c r="I23" s="116" t="n">
         <v>10555510</v>
       </c>
@@ -11267,6 +12353,9 @@
         <f>IF(J24&lt;=0,"n.m.",I24/J24)</f>
         <v/>
       </c>
+      <c r="F24" s="171" t="n"/>
+      <c r="G24" s="171" t="n"/>
+      <c r="H24" s="171" t="n"/>
       <c r="I24" s="116" t="n">
         <v>27284350</v>
       </c>
@@ -11291,6 +12380,9 @@
         <f>IF(J25&lt;=0,"n.m.",I25/J25)</f>
         <v/>
       </c>
+      <c r="F25" s="171" t="n"/>
+      <c r="G25" s="171" t="n"/>
+      <c r="H25" s="171" t="n"/>
       <c r="I25" s="116" t="n">
         <v>7153911</v>
       </c>
@@ -11315,6 +12407,9 @@
         <f>IF(J26&lt;=0,"n.m.",I26/J26)</f>
         <v/>
       </c>
+      <c r="F26" s="171" t="n"/>
+      <c r="G26" s="171" t="n"/>
+      <c r="H26" s="171" t="n"/>
       <c r="I26" s="116" t="n">
         <v>616045</v>
       </c>
@@ -11339,6 +12434,9 @@
         <f>IF(J27&lt;=0,"n.m.",I27/J27)</f>
         <v/>
       </c>
+      <c r="F27" s="171" t="n"/>
+      <c r="G27" s="171" t="n"/>
+      <c r="H27" s="171" t="n"/>
       <c r="I27" s="116" t="n">
         <v>9422753</v>
       </c>
@@ -11363,6 +12461,9 @@
         <f>IF(J28&lt;=0,"n.m.",I28/J28)</f>
         <v/>
       </c>
+      <c r="F28" s="171" t="n"/>
+      <c r="G28" s="171" t="n"/>
+      <c r="H28" s="171" t="n"/>
       <c r="I28" s="116" t="n">
         <v>1598873</v>
       </c>
@@ -11387,6 +12488,9 @@
         <f>IF(J29&lt;=0,"n.m.",I29/J29)</f>
         <v/>
       </c>
+      <c r="F29" s="171" t="n"/>
+      <c r="G29" s="171" t="n"/>
+      <c r="H29" s="171" t="n"/>
       <c r="I29" s="116" t="n">
         <v>5236269</v>
       </c>
@@ -11394,11 +12498,41 @@
         <v>407521</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="171" t="n"/>
+      <c r="B30" s="171" t="n"/>
+      <c r="C30" s="171" t="n"/>
+      <c r="D30" s="171" t="n"/>
+      <c r="E30" s="171" t="n"/>
+      <c r="F30" s="171" t="n"/>
+      <c r="G30" s="171" t="n"/>
+      <c r="H30" s="171" t="n"/>
+      <c r="I30" s="171" t="n"/>
+      <c r="J30" s="171" t="n"/>
+    </row>
     <row r="31">
       <c r="A31" s="14" t="n"/>
+      <c r="B31" s="171" t="n"/>
+      <c r="C31" s="171" t="n"/>
+      <c r="D31" s="171" t="n"/>
+      <c r="E31" s="171" t="n"/>
+      <c r="F31" s="171" t="n"/>
+      <c r="G31" s="171" t="n"/>
+      <c r="H31" s="171" t="n"/>
+      <c r="I31" s="171" t="n"/>
+      <c r="J31" s="171" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="26" t="n"/>
+      <c r="B32" s="171" t="n"/>
+      <c r="C32" s="171" t="n"/>
+      <c r="D32" s="171" t="n"/>
+      <c r="E32" s="171" t="n"/>
+      <c r="F32" s="171" t="n"/>
+      <c r="G32" s="171" t="n"/>
+      <c r="H32" s="171" t="n"/>
+      <c r="I32" s="171" t="n"/>
+      <c r="J32" s="171" t="n"/>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
@@ -11416,6 +12550,11 @@
       <c r="E33" s="117" t="n">
         <v>10</v>
       </c>
+      <c r="F33" s="171" t="n"/>
+      <c r="G33" s="171" t="n"/>
+      <c r="H33" s="171" t="n"/>
+      <c r="I33" s="171" t="n"/>
+      <c r="J33" s="171" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
@@ -11433,6 +12572,11 @@
       <c r="E34" s="117" t="n">
         <v>2</v>
       </c>
+      <c r="F34" s="171" t="n"/>
+      <c r="G34" s="171" t="n"/>
+      <c r="H34" s="171" t="n"/>
+      <c r="I34" s="171" t="n"/>
+      <c r="J34" s="171" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="68" t="inlineStr">
@@ -11451,6 +12595,11 @@
         <f>E33/E34</f>
         <v/>
       </c>
+      <c r="F35" s="171" t="n"/>
+      <c r="G35" s="171" t="n"/>
+      <c r="H35" s="171" t="n"/>
+      <c r="I35" s="171" t="n"/>
+      <c r="J35" s="171" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
@@ -11470,6 +12619,23 @@
           <t>n.a.</t>
         </is>
       </c>
+      <c r="F36" s="171" t="n"/>
+      <c r="G36" s="171" t="n"/>
+      <c r="H36" s="171" t="n"/>
+      <c r="I36" s="171" t="n"/>
+      <c r="J36" s="171" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="171" t="n"/>
+      <c r="B37" s="171" t="n"/>
+      <c r="C37" s="171" t="n"/>
+      <c r="D37" s="171" t="n"/>
+      <c r="E37" s="171" t="n"/>
+      <c r="F37" s="171" t="n"/>
+      <c r="G37" s="171" t="n"/>
+      <c r="H37" s="171" t="n"/>
+      <c r="I37" s="171" t="n"/>
+      <c r="J37" s="171" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -11477,6 +12643,15 @@
           <t>Averages (live Excel AVERAGE — shown so TV is not a blended print)</t>
         </is>
       </c>
+      <c r="B38" s="171" t="n"/>
+      <c r="C38" s="171" t="n"/>
+      <c r="D38" s="171" t="n"/>
+      <c r="E38" s="171" t="n"/>
+      <c r="F38" s="171" t="n"/>
+      <c r="G38" s="171" t="n"/>
+      <c r="H38" s="171" t="n"/>
+      <c r="I38" s="171" t="n"/>
+      <c r="J38" s="171" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -11495,6 +12670,11 @@
         <f>AVERAGE(E19,E22,E21,E23,E25,E27,E29)</f>
         <v/>
       </c>
+      <c r="F39" s="171" t="n"/>
+      <c r="G39" s="171" t="n"/>
+      <c r="H39" s="171" t="n"/>
+      <c r="I39" s="171" t="n"/>
+      <c r="J39" s="171" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -11513,6 +12693,11 @@
         <f>AVERAGE(E19,E21,E22,E23,E24,E25,E26,E27,E28,E29)</f>
         <v/>
       </c>
+      <c r="F40" s="171" t="n"/>
+      <c r="G40" s="171" t="n"/>
+      <c r="H40" s="171" t="n"/>
+      <c r="I40" s="171" t="n"/>
+      <c r="J40" s="171" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="107" t="inlineStr">
@@ -11520,6 +12705,27 @@
           <t>We do not average peers for terminal value, and we do not use Alo 5.0x EV/Sales as EV/EBITDA.</t>
         </is>
       </c>
+      <c r="B41" s="171" t="n"/>
+      <c r="C41" s="171" t="n"/>
+      <c r="D41" s="171" t="n"/>
+      <c r="E41" s="171" t="n"/>
+      <c r="F41" s="171" t="n"/>
+      <c r="G41" s="171" t="n"/>
+      <c r="H41" s="171" t="n"/>
+      <c r="I41" s="171" t="n"/>
+      <c r="J41" s="171" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="171" t="n"/>
+      <c r="B42" s="171" t="n"/>
+      <c r="C42" s="171" t="n"/>
+      <c r="D42" s="171" t="n"/>
+      <c r="E42" s="171" t="n"/>
+      <c r="F42" s="171" t="n"/>
+      <c r="G42" s="171" t="n"/>
+      <c r="H42" s="171" t="n"/>
+      <c r="I42" s="171" t="n"/>
+      <c r="J42" s="171" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
@@ -11527,6 +12733,15 @@
           <t>Terminal multiple selection (DCF exit method)</t>
         </is>
       </c>
+      <c r="B43" s="171" t="n"/>
+      <c r="C43" s="171" t="n"/>
+      <c r="D43" s="171" t="n"/>
+      <c r="E43" s="171" t="n"/>
+      <c r="F43" s="171" t="n"/>
+      <c r="G43" s="171" t="n"/>
+      <c r="H43" s="171" t="n"/>
+      <c r="I43" s="171" t="n"/>
+      <c r="J43" s="171" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -11534,10 +12749,18 @@
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
+      <c r="B44" s="171" t="n"/>
+      <c r="C44" s="171" t="n"/>
+      <c r="D44" s="171" t="n"/>
       <c r="E44" s="94">
         <f>DCF!E46</f>
         <v/>
       </c>
+      <c r="F44" s="171" t="n"/>
+      <c r="G44" s="171" t="n"/>
+      <c r="H44" s="171" t="n"/>
+      <c r="I44" s="171" t="n"/>
+      <c r="J44" s="171" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="68" t="inlineStr">
@@ -11545,10 +12768,18 @@
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
+      <c r="B45" s="171" t="n"/>
+      <c r="C45" s="171" t="n"/>
+      <c r="D45" s="171" t="n"/>
       <c r="E45" s="104">
         <f>DCF!E82</f>
         <v/>
       </c>
+      <c r="F45" s="171" t="n"/>
+      <c r="G45" s="171" t="n"/>
+      <c r="H45" s="171" t="n"/>
+      <c r="I45" s="171" t="n"/>
+      <c r="J45" s="171" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -11556,10 +12787,18 @@
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
+      <c r="B46" s="171" t="n"/>
+      <c r="C46" s="171" t="n"/>
+      <c r="D46" s="171" t="n"/>
       <c r="E46" s="94">
         <f>E45-E44</f>
         <v/>
       </c>
+      <c r="F46" s="171" t="n"/>
+      <c r="G46" s="171" t="n"/>
+      <c r="H46" s="171" t="n"/>
+      <c r="I46" s="171" t="n"/>
+      <c r="J46" s="171" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="68" t="inlineStr">
@@ -11567,9 +12806,27 @@
           <t>Rationale for selected exit (Gordon identity, not a peer pick)</t>
         </is>
       </c>
+      <c r="B47" s="171" t="n"/>
+      <c r="C47" s="171" t="n"/>
+      <c r="D47" s="171" t="n"/>
+      <c r="E47" s="171" t="n"/>
+      <c r="F47" s="171" t="n"/>
+      <c r="G47" s="171" t="n"/>
+      <c r="H47" s="171" t="n"/>
+      <c r="I47" s="171" t="n"/>
+      <c r="J47" s="171" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="41" t="n"/>
+      <c r="B48" s="171" t="n"/>
+      <c r="C48" s="171" t="n"/>
+      <c r="D48" s="171" t="n"/>
+      <c r="E48" s="171" t="n"/>
+      <c r="F48" s="171" t="n"/>
+      <c r="G48" s="171" t="n"/>
+      <c r="H48" s="171" t="n"/>
+      <c r="I48" s="171" t="n"/>
+      <c r="J48" s="171" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="41" t="inlineStr">
@@ -11577,6 +12834,15 @@
           <t>• At base WACC ~9.0% and g 2.25% that identity is ~7.4x FY30 EBITDA — not a peer average</t>
         </is>
       </c>
+      <c r="B49" s="171" t="n"/>
+      <c r="C49" s="171" t="n"/>
+      <c r="D49" s="171" t="n"/>
+      <c r="E49" s="171" t="n"/>
+      <c r="F49" s="171" t="n"/>
+      <c r="G49" s="171" t="n"/>
+      <c r="H49" s="171" t="n"/>
+      <c r="I49" s="171" t="n"/>
+      <c r="J49" s="171" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="41" t="inlineStr">
@@ -11584,6 +12850,15 @@
           <t>• PitchBook pubcomps (04-Sep-2026) are the current tape: each multiple is daily EV / TTM EBITDA</t>
         </is>
       </c>
+      <c r="B50" s="171" t="n"/>
+      <c r="C50" s="171" t="n"/>
+      <c r="D50" s="171" t="n"/>
+      <c r="E50" s="171" t="n"/>
+      <c r="F50" s="171" t="n"/>
+      <c r="G50" s="171" t="n"/>
+      <c r="H50" s="171" t="n"/>
+      <c r="I50" s="171" t="n"/>
+      <c r="J50" s="171" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="41" t="inlineStr">
@@ -11591,6 +12866,15 @@
           <t>• That tape is a check, not the exit. A 2.25% g / 15.5% OM year is not today’s NKE/WSM multiple</t>
         </is>
       </c>
+      <c r="B51" s="171" t="n"/>
+      <c r="C51" s="171" t="n"/>
+      <c r="D51" s="171" t="n"/>
+      <c r="E51" s="171" t="n"/>
+      <c r="F51" s="171" t="n"/>
+      <c r="G51" s="171" t="n"/>
+      <c r="H51" s="171" t="n"/>
+      <c r="I51" s="171" t="n"/>
+      <c r="J51" s="171" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="41" t="inlineStr">
@@ -11598,6 +12882,15 @@
           <t>• Alo has no EV/EBITDA print. Implied 5.0x is EV/Sales (unclosed $10bn ask / ~$2bn parent sales) — not the FY30 exit</t>
         </is>
       </c>
+      <c r="B52" s="171" t="n"/>
+      <c r="C52" s="171" t="n"/>
+      <c r="D52" s="171" t="n"/>
+      <c r="E52" s="171" t="n"/>
+      <c r="F52" s="171" t="n"/>
+      <c r="G52" s="171" t="n"/>
+      <c r="H52" s="171" t="n"/>
+      <c r="I52" s="171" t="n"/>
+      <c r="J52" s="171" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="41" t="inlineStr">
@@ -11605,6 +12898,27 @@
           <t>• PitchBook LULU is ~4.7x TTM. Gordon ~7.4x is a partial recovery, not a re-rate to WSM ~15x</t>
         </is>
       </c>
+      <c r="B53" s="171" t="n"/>
+      <c r="C53" s="171" t="n"/>
+      <c r="D53" s="171" t="n"/>
+      <c r="E53" s="171" t="n"/>
+      <c r="F53" s="171" t="n"/>
+      <c r="G53" s="171" t="n"/>
+      <c r="H53" s="171" t="n"/>
+      <c r="I53" s="171" t="n"/>
+      <c r="J53" s="171" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="171" t="n"/>
+      <c r="B54" s="171" t="n"/>
+      <c r="C54" s="171" t="n"/>
+      <c r="D54" s="171" t="n"/>
+      <c r="E54" s="171" t="n"/>
+      <c r="F54" s="171" t="n"/>
+      <c r="G54" s="171" t="n"/>
+      <c r="H54" s="171" t="n"/>
+      <c r="I54" s="171" t="n"/>
+      <c r="J54" s="171" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
@@ -11612,6 +12926,15 @@
           <t>Methodology / multiple ranges (FY2030E terminal EBITDA — football field)</t>
         </is>
       </c>
+      <c r="B55" s="171" t="n"/>
+      <c r="C55" s="171" t="n"/>
+      <c r="D55" s="171" t="n"/>
+      <c r="E55" s="171" t="n"/>
+      <c r="F55" s="171" t="n"/>
+      <c r="G55" s="171" t="n"/>
+      <c r="H55" s="171" t="n"/>
+      <c r="I55" s="171" t="n"/>
+      <c r="J55" s="171" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="113" t="inlineStr">
@@ -11646,6 +12969,8 @@
           <t>Implied px (high)</t>
         </is>
       </c>
+      <c r="I56" s="171" t="n"/>
+      <c r="J56" s="171" t="n"/>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
@@ -11675,6 +13000,8 @@
         <f>(E6*F57+E8)/E9</f>
         <v/>
       </c>
+      <c r="I57" s="171" t="n"/>
+      <c r="J57" s="171" t="n"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="68" t="inlineStr">
@@ -11693,10 +13020,14 @@
         <f>DCF!E82</f>
         <v/>
       </c>
+      <c r="F58" s="171" t="n"/>
       <c r="G58" s="122">
         <f>(E6*E58+E8)/E9</f>
         <v/>
       </c>
+      <c r="H58" s="171" t="n"/>
+      <c r="I58" s="171" t="n"/>
+      <c r="J58" s="171" t="n"/>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
@@ -11726,6 +13057,8 @@
         <f>E7*F59</f>
         <v/>
       </c>
+      <c r="I59" s="171" t="n"/>
+      <c r="J59" s="171" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -11733,6 +13066,9 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
+      <c r="B60" s="171" t="n"/>
+      <c r="C60" s="171" t="n"/>
+      <c r="D60" s="171" t="n"/>
       <c r="E60" s="123" t="inlineStr">
         <is>
           <t>—</t>
@@ -11751,6 +13087,20 @@
         <f>Scenarios!$D$132</f>
         <v/>
       </c>
+      <c r="I60" s="171" t="n"/>
+      <c r="J60" s="171" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="171" t="n"/>
+      <c r="B61" s="171" t="n"/>
+      <c r="C61" s="171" t="n"/>
+      <c r="D61" s="171" t="n"/>
+      <c r="E61" s="171" t="n"/>
+      <c r="F61" s="171" t="n"/>
+      <c r="G61" s="171" t="n"/>
+      <c r="H61" s="171" t="n"/>
+      <c r="I61" s="171" t="n"/>
+      <c r="J61" s="171" t="n"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
@@ -11758,6 +13108,7 @@
           <t>Current price</t>
         </is>
       </c>
+      <c r="B62" s="171" t="n"/>
       <c r="C62" s="95" t="inlineStr">
         <is>
           <t>NASDAQ</t>
@@ -11767,6 +13118,11 @@
       <c r="E62" s="125" t="n">
         <v>100</v>
       </c>
+      <c r="F62" s="171" t="n"/>
+      <c r="G62" s="171" t="n"/>
+      <c r="H62" s="171" t="n"/>
+      <c r="I62" s="171" t="n"/>
+      <c r="J62" s="171" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="26" t="inlineStr">
@@ -11774,6 +13130,15 @@
           <t>Note: pubcomps are PitchBook 04-Sep-2026 (EV/EBITDA = daily EV / TTM EBITDA). UAA excluded from the mean. Selected TV is Gordon implied, not the PitchBook average. Alo EV/EBITDA is n.a.</t>
         </is>
       </c>
+      <c r="B63" s="171" t="n"/>
+      <c r="C63" s="171" t="n"/>
+      <c r="D63" s="171" t="n"/>
+      <c r="E63" s="171" t="n"/>
+      <c r="F63" s="171" t="n"/>
+      <c r="G63" s="171" t="n"/>
+      <c r="H63" s="171" t="n"/>
+      <c r="I63" s="171" t="n"/>
+      <c r="J63" s="171" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -6638,9 +6638,7 @@
       <c r="C194" s="174" t="n"/>
       <c r="D194" s="174" t="n"/>
       <c r="E194" s="174" t="n"/>
-      <c r="F194" s="174" t="n">
-        <v>8456743</v>
-      </c>
+      <c r="F194" s="174" t="n"/>
       <c r="G194" s="171" t="n"/>
       <c r="H194" s="171" t="n"/>
     </row>
@@ -6656,9 +6654,7 @@
       <c r="C195" s="174" t="n"/>
       <c r="D195" s="174" t="n"/>
       <c r="E195" s="174" t="n"/>
-      <c r="F195" s="174" t="n">
-        <v>3494903</v>
-      </c>
+      <c r="F195" s="174" t="n"/>
       <c r="G195" s="171" t="n"/>
       <c r="H195" s="171" t="n"/>
     </row>
@@ -6674,9 +6670,7 @@
       <c r="C196" s="174" t="n"/>
       <c r="D196" s="174" t="n"/>
       <c r="E196" s="174" t="n"/>
-      <c r="F196" s="174" t="n">
-        <v>4961840</v>
-      </c>
+      <c r="F196" s="174" t="n"/>
       <c r="G196" s="171" t="n"/>
       <c r="H196" s="171" t="n"/>
     </row>
@@ -6692,9 +6686,7 @@
       <c r="C197" s="174" t="n"/>
       <c r="D197" s="174" t="n"/>
       <c r="E197" s="174" t="n"/>
-      <c r="F197" s="174" t="n">
-        <v>119068</v>
-      </c>
+      <c r="F197" s="174" t="n"/>
       <c r="G197" s="171" t="n"/>
       <c r="H197" s="171" t="n"/>
     </row>
@@ -6710,9 +6702,7 @@
       <c r="C198" s="174" t="n"/>
       <c r="D198" s="174" t="n"/>
       <c r="E198" s="174" t="n"/>
-      <c r="F198" s="174" t="n">
-        <v>11102600</v>
-      </c>
+      <c r="F198" s="174" t="n"/>
       <c r="G198" s="171" t="n"/>
       <c r="H198" s="171" t="n"/>
     </row>
@@ -6758,9 +6748,7 @@
       <c r="C202" s="174" t="n"/>
       <c r="D202" s="174" t="n"/>
       <c r="E202" s="174" t="n"/>
-      <c r="F202" s="174" t="n">
-        <v>62203</v>
-      </c>
+      <c r="F202" s="174" t="n"/>
       <c r="G202" s="171" t="n"/>
       <c r="H202" s="171" t="n"/>
     </row>
@@ -6776,9 +6764,7 @@
       <c r="C203" s="174" t="n"/>
       <c r="D203" s="174" t="n"/>
       <c r="E203" s="174" t="n"/>
-      <c r="F203" s="174" t="n">
-        <v>1028</v>
-      </c>
+      <c r="F203" s="174" t="n"/>
       <c r="G203" s="171" t="n"/>
       <c r="H203" s="171" t="n"/>
     </row>

--- a/LULU/model18_wsp_formulas.xlsx
+++ b/LULU/model18_wsp_formulas.xlsx
@@ -3334,7 +3334,7 @@
     <row r="50">
       <c r="A50" s="153" t="inlineStr">
         <is>
-          <t>NOPAT: year 1</t>
+          <t>EBIT after tax: year 1</t>
         </is>
       </c>
       <c r="B50" s="154">
@@ -3361,7 +3361,7 @@
     <row r="51">
       <c r="A51" s="153" t="inlineStr">
         <is>
-          <t>NOPAT: year 2</t>
+          <t>EBIT after tax: year 2</t>
         </is>
       </c>
       <c r="B51" s="154">
@@ -3384,7 +3384,7 @@
     <row r="52">
       <c r="A52" s="153" t="inlineStr">
         <is>
-          <t>NOPAT: year 3</t>
+          <t>EBIT after tax: year 3</t>
         </is>
       </c>
       <c r="B52" s="154">
@@ -3407,7 +3407,7 @@
     <row r="53">
       <c r="A53" s="153" t="inlineStr">
         <is>
-          <t>NOPAT: year 4</t>
+          <t>EBIT after tax: year 4</t>
         </is>
       </c>
       <c r="B53" s="154">
@@ -3430,7 +3430,7 @@
     <row r="54">
       <c r="A54" s="153" t="inlineStr">
         <is>
-          <t>NOPAT: year 5</t>
+          <t>EBIT after tax: year 5</t>
         </is>
       </c>
       <c r="B54" s="154">
@@ -5137,7 +5137,7 @@
       <c r="E125" s="174" t="n"/>
       <c r="F125" s="179" t="inlineStr">
         <is>
-          <t>NOPAT plus depreciation minus capex plus working capital.</t>
+          <t>After-tax EBIT plus depreciation minus capex plus working capital.</t>
         </is>
       </c>
       <c r="G125" s="42" t="n"/>
@@ -9574,7 +9574,7 @@
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>NOPAT</t>
+          <t>EBIT after tax</t>
         </is>
       </c>
       <c r="B14" s="171" t="n"/>
